--- a/Excel/Main/Test.xlsx
+++ b/Excel/Main/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6B1851-944C-4BA1-912B-DB1A9795CECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE402E5A-EEBB-4FAB-8126-890C99D45F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="501">
   <si>
     <t>Id</t>
   </si>
@@ -1850,22 +1850,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>受击治疗</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>事件目标替换</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>被击</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>放置降序</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Normal</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -1878,6 +1862,22 @@
   </si>
   <si>
     <t>CCB普攻,受击治疗</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>火墙附魔</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>余火墙</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹道命中</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Fire":600}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3115,7 +3115,7 @@
         <v>410</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -6456,7 +6456,7 @@
         <v>176</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="BA1" t="s">
         <v>177</v>
@@ -7386,35 +7386,29 @@
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AF8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG8" s="8"/>
       <c r="AO8" s="8" t="s">
-        <v>496</v>
+        <v>425</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="AW8">
-        <v>1</v>
+        <v>493</v>
       </c>
       <c r="AX8">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AZ8">
         <v>2</v>
@@ -7423,10 +7417,13 @@
         <v>1</v>
       </c>
       <c r="CE8" s="8"/>
+      <c r="CJ8" s="8" t="s">
+        <v>500</v>
+      </c>
       <c r="CL8" s="8"/>
       <c r="CM8" s="8"/>
       <c r="CW8" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">

--- a/Excel/Main/Test.xlsx
+++ b/Excel/Main/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE402E5A-EEBB-4FAB-8126-890C99D45F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312A2039-899E-4C8B-B582-45612A81DD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="499">
   <si>
     <t>Id</t>
   </si>
@@ -663,9 +663,6 @@
   </si>
   <si>
     <t>System.Collections.Generic.Dictionary&lt;string,object&gt;</t>
-  </si>
-  <si>
-    <t>不要删！</t>
   </si>
   <si>
     <t>Hip</t>
@@ -1859,10 +1856,6 @@
   </si>
   <si>
     <t>治疗2</t>
-  </si>
-  <si>
-    <t>CCB普攻,受击治疗</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>火墙附魔</t>
@@ -2439,10 +2432,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -2611,7 +2604,7 @@
         <v>39</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="BA1" t="s">
         <v>40</v>
@@ -2781,7 +2774,7 @@
         <v>93</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="BA2" t="s">
         <v>94</v>
@@ -2823,7 +2816,7 @@
         <v>106</v>
       </c>
       <c r="BN2" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="BO2" t="s">
         <v>107</v>
@@ -3047,27 +3040,16 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3109,13 +3091,13 @@
         <v>1</v>
       </c>
       <c r="AG5" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="AH5" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="AI5" s="8" t="s">
         <v>484</v>
-      </c>
-      <c r="AH5" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="AI5" s="8" t="s">
-        <v>496</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3133,44 +3115,44 @@
         <v>0.25</v>
       </c>
       <c r="BB5" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="BD5" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="BD5" s="8" t="s">
+      <c r="BE5" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="BE5" s="8" t="s">
+      <c r="BF5" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="BF5" s="8" t="s">
+      <c r="BG5" s="8" t="s">
         <v>414</v>
-      </c>
-      <c r="BG5" s="8" t="s">
-        <v>415</v>
       </c>
       <c r="BH5">
         <v>6</v>
       </c>
       <c r="BI5" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="BJ5" s="8" t="s">
         <v>416</v>
-      </c>
-      <c r="BJ5" s="8" t="s">
-        <v>417</v>
       </c>
       <c r="BK5" s="5"/>
       <c r="BM5" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="BN5" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="BN5" s="8" t="s">
+      <c r="BP5" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="BP5" s="8" t="s">
+      <c r="BQ5" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="BR5" s="8" t="s">
         <v>420</v>
-      </c>
-      <c r="BQ5" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="BR5" s="8" t="s">
-        <v>421</v>
       </c>
       <c r="BS5">
         <v>1</v>
@@ -3190,19 +3172,19 @@
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
+        <v>429</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="8" t="s">
         <v>431</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>432</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3248,13 +3230,13 @@
         <v>-1</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AI8" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AK8">
         <v>3</v>
@@ -3281,10 +3263,10 @@
         <v>1</v>
       </c>
       <c r="BB8" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="BD8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="BE8" t="str">
         <f t="shared" ref="BE8" si="0">"half_"&amp;D8</f>
@@ -3295,25 +3277,25 @@
         <v>otter</v>
       </c>
       <c r="BG8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BH8">
         <v>5</v>
       </c>
       <c r="BI8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BM8" t="s">
+        <v>123</v>
+      </c>
+      <c r="BN8" t="s">
         <v>124</v>
       </c>
-      <c r="BN8" t="s">
+      <c r="BP8" t="s">
         <v>125</v>
       </c>
-      <c r="BP8" t="s">
-        <v>126</v>
-      </c>
       <c r="BQ8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BS8">
         <v>1</v>
@@ -3321,19 +3303,19 @@
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D9" t="s">
+        <v>429</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="8" t="s">
         <v>431</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>432</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3379,10 +3361,10 @@
         <v>1</v>
       </c>
       <c r="AG9" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AH9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AI9" s="8"/>
       <c r="AK9">
@@ -3410,10 +3392,10 @@
         <v>1</v>
       </c>
       <c r="BB9" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="BD9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="BE9" t="str">
         <f t="shared" ref="BE9" si="2">"half_"&amp;D9</f>
@@ -3424,25 +3406,25 @@
         <v>otter</v>
       </c>
       <c r="BG9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BH9">
         <v>5</v>
       </c>
       <c r="BI9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BM9" t="s">
+        <v>123</v>
+      </c>
+      <c r="BN9" t="s">
         <v>124</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BP9" t="s">
         <v>125</v>
       </c>
-      <c r="BP9" t="s">
-        <v>126</v>
-      </c>
       <c r="BQ9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BS9">
         <v>1</v>
@@ -6309,328 +6291,328 @@
   <sheetData>
     <row r="1" spans="1:111" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>131</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>132</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>133</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="I1" t="s">
         <v>134</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>135</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="U1" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" t="s">
         <v>149</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>150</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" t="s">
         <v>152</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>153</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>154</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>155</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>156</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>157</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>158</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>159</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>160</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>161</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>162</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>163</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>164</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>165</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>166</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>167</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>168</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>169</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>170</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>171</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>172</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>173</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>174</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>175</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="BA1" t="s">
         <v>176</v>
       </c>
-      <c r="AZ1" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>177</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>178</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>179</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>180</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>181</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
+        <v>181</v>
+      </c>
+      <c r="BI1" t="s">
         <v>182</v>
       </c>
-      <c r="BH1" t="s">
-        <v>182</v>
-      </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>183</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>184</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>185</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>186</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>187</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>188</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>189</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>190</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>191</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="BT1" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="BU1" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="BS1" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="BT1" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="BU1" s="4" t="s">
+      <c r="BV1" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="BV1" s="4" t="s">
+      <c r="BW1" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="BW1" s="4" t="s">
+      <c r="BX1" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="BX1" s="4" t="s">
+      <c r="BY1" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="BY1" s="4" t="s">
+      <c r="BZ1" t="s">
         <v>197</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CB1" t="s">
         <v>199</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>200</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>201</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>202</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>203</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>204</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>205</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>206</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="CK1" t="s">
         <v>207</v>
       </c>
-      <c r="CJ1" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>208</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>209</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>210</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>211</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
+        <v>191</v>
+      </c>
+      <c r="CQ1" t="s">
         <v>212</v>
       </c>
-      <c r="CP1" t="s">
-        <v>192</v>
-      </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>213</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>214</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>215</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>216</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>217</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>218</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
+        <v>217</v>
+      </c>
+      <c r="CY1" t="s">
         <v>219</v>
       </c>
-      <c r="CX1" t="s">
-        <v>218</v>
-      </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>220</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>221</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>222</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>223</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>224</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>225</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>226</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>227</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:111" x14ac:dyDescent="0.25">
@@ -6644,325 +6626,325 @@
         <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2" t="s">
         <v>229</v>
-      </c>
-      <c r="F2" t="s">
-        <v>230</v>
       </c>
       <c r="G2" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J2" t="s">
         <v>231</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="Y2" t="s">
         <v>246</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>247</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AB2" t="s">
         <v>249</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>250</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>251</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>252</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>253</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>254</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>255</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>256</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>257</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>258</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>259</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>260</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>261</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>262</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>263</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>264</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>265</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>266</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>267</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>268</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>269</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>270</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>271</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>272</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>273</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>274</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>275</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>276</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>277</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>278</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>279</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>280</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>281</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>282</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>283</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>284</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>285</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>286</v>
       </c>
       <c r="BM2" t="s">
         <v>77</v>
       </c>
       <c r="BN2" t="s">
+        <v>286</v>
+      </c>
+      <c r="BO2" t="s">
         <v>287</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BP2" t="s">
         <v>288</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BQ2" t="s">
         <v>289</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>290</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="BT2" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="BU2" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="BS2" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="BT2" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="BU2" s="4" t="s">
+      <c r="BV2" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="BV2" s="4" t="s">
+      <c r="BW2" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="BW2" s="4" t="s">
+      <c r="BX2" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="BX2" s="4" t="s">
+      <c r="BY2" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="BY2" s="4" t="s">
+      <c r="BZ2" t="s">
         <v>296</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CA2" t="s">
         <v>297</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CB2" t="s">
         <v>298</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>299</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>300</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>301</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>302</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>303</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>304</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" t="s">
         <v>305</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CJ2" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="CK2" t="s">
         <v>306</v>
       </c>
-      <c r="CJ2" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="CK2" t="s">
+      <c r="CL2" t="s">
         <v>307</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CM2" t="s">
         <v>308</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CN2" t="s">
         <v>309</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CO2" t="s">
         <v>310</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CP2" t="s">
         <v>311</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CQ2" t="s">
         <v>312</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CR2" t="s">
         <v>313</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CS2" t="s">
         <v>314</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CT2" t="s">
         <v>315</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CU2" t="s">
         <v>316</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CV2" t="s">
         <v>317</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CW2" t="s">
         <v>318</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CX2" t="s">
         <v>319</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CY2" t="s">
         <v>320</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CZ2" t="s">
         <v>321</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DA2" t="s">
         <v>322</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DB2" t="s">
         <v>323</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DC2" t="s">
         <v>324</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DD2" t="s">
         <v>325</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DE2" t="s">
         <v>326</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DF2" t="s">
         <v>327</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DG2" t="s">
         <v>328</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:111" x14ac:dyDescent="0.25">
@@ -6985,19 +6967,19 @@
         <v>114</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I3" t="s">
         <v>112</v>
       </c>
       <c r="J3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>331</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>114</v>
@@ -7060,7 +7042,7 @@
         <v>112</v>
       </c>
       <c r="AG3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AH3" t="s">
         <v>112</v>
@@ -7084,16 +7066,16 @@
         <v>112</v>
       </c>
       <c r="AO3" t="s">
+        <v>332</v>
+      </c>
+      <c r="AP3" t="s">
         <v>333</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>334</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AS3" t="s">
         <v>112</v>
@@ -7105,7 +7087,7 @@
         <v>112</v>
       </c>
       <c r="AV3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AW3" t="s">
         <v>112</v>
@@ -7135,7 +7117,7 @@
         <v>112</v>
       </c>
       <c r="BF3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BG3" t="s">
         <v>112</v>
@@ -7162,10 +7144,10 @@
         <v>115</v>
       </c>
       <c r="BO3" t="s">
+        <v>336</v>
+      </c>
+      <c r="BP3" t="s">
         <v>337</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>338</v>
       </c>
       <c r="BQ3" t="s">
         <v>113</v>
@@ -7174,7 +7156,7 @@
         <v>113</v>
       </c>
       <c r="BS3" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="BT3" s="4" t="s">
         <v>113</v>
@@ -7186,19 +7168,19 @@
         <v>114</v>
       </c>
       <c r="BW3" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="BX3" s="4" t="s">
         <v>112</v>
       </c>
       <c r="BY3" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="BZ3" t="s">
         <v>120</v>
       </c>
       <c r="CA3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="CB3" t="s">
         <v>120</v>
@@ -7210,22 +7192,22 @@
         <v>120</v>
       </c>
       <c r="CE3" t="s">
+        <v>340</v>
+      </c>
+      <c r="CF3" t="s">
         <v>341</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>342</v>
       </c>
       <c r="CG3" t="s">
         <v>2</v>
       </c>
       <c r="CH3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="CI3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="CJ3" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="CK3" t="s">
         <v>116</v>
@@ -7243,7 +7225,7 @@
         <v>119</v>
       </c>
       <c r="CP3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="CQ3" t="s">
         <v>119</v>
@@ -7255,28 +7237,28 @@
         <v>121</v>
       </c>
       <c r="CT3" t="s">
+        <v>343</v>
+      </c>
+      <c r="CU3" t="s">
         <v>344</v>
       </c>
-      <c r="CU3" t="s">
-        <v>345</v>
-      </c>
       <c r="CV3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="CW3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="CX3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="CY3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="CZ3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="DA3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="DB3" t="s">
         <v>112</v>
@@ -7299,7 +7281,7 @@
     </row>
     <row r="4" spans="1:111" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:111" x14ac:dyDescent="0.25">
@@ -7312,13 +7294,13 @@
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6"/>
@@ -7326,13 +7308,13 @@
         <v>2</v>
       </c>
       <c r="AO6" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AR6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AV6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AX6">
         <v>1</v>
@@ -7341,31 +7323,31 @@
         <v>1</v>
       </c>
       <c r="BZ6" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="CE6" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="CE6" s="8" t="s">
-        <v>427</v>
-      </c>
       <c r="CF6" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="CG6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="CJ6" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="CK6" s="8"/>
       <c r="CW6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J7" s="8"/>
       <c r="O7"/>
@@ -7376,7 +7358,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AT7">
         <v>2.5</v>
@@ -7386,26 +7368,26 @@
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>499</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AG8" s="8"/>
       <c r="AO8" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AX8">
         <v>0</v>
@@ -7418,12 +7400,12 @@
       </c>
       <c r="CE8" s="8"/>
       <c r="CJ8" s="8" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="CL8" s="8"/>
       <c r="CM8" s="8"/>
       <c r="CW8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
@@ -7441,16 +7423,16 @@
     </row>
     <row r="10" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AC10">
         <v>1</v>
@@ -7459,14 +7441,14 @@
         <v>1</v>
       </c>
       <c r="AG10" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="BB10">
         <v>1</v>
       </c>
       <c r="CJ10" s="3"/>
       <c r="CS10" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="DB10">
         <v>1</v>
@@ -7480,32 +7462,32 @@
     </row>
     <row r="11" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AC11">
         <v>1</v>
       </c>
       <c r="AG11" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AJ11" s="8"/>
       <c r="AT11">
         <v>99</v>
       </c>
       <c r="AV11" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AX11">
         <v>99999</v>
@@ -7529,10 +7511,10 @@
         <v>1</v>
       </c>
       <c r="BW11" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="CE11" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CJ11" s="3"/>
       <c r="CL11" s="8"/>
@@ -7548,28 +7530,28 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>458</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>459</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AC12">
         <v>2</v>
       </c>
       <c r="AO12" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AR12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="BB12">
         <v>4</v>
@@ -7579,10 +7561,10 @@
       </c>
       <c r="CJ12" s="3"/>
       <c r="CS12" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="CW12" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
@@ -7595,19 +7577,19 @@
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14"/>
@@ -7636,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="BN14" s="12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="BR14">
         <v>6</v>
@@ -7651,13 +7633,13 @@
         <v>1</v>
       </c>
       <c r="BW14" s="17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="BX14" s="14"/>
       <c r="BY14" s="14"/>
       <c r="BZ14" s="12"/>
       <c r="CE14" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CH14" s="12"/>
       <c r="CK14" s="12"/>
@@ -7670,16 +7652,16 @@
     </row>
     <row r="15" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15"/>
@@ -7702,10 +7684,10 @@
         <v>1</v>
       </c>
       <c r="AR15" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AV15" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AX15">
         <v>1</v>
@@ -7721,7 +7703,7 @@
       </c>
       <c r="BM15" s="12"/>
       <c r="BN15" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="BR15">
         <v>5.5</v>
@@ -7734,15 +7716,15 @@
       <c r="BY15" s="14"/>
       <c r="BZ15" s="12"/>
       <c r="CE15" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CH15" s="12"/>
       <c r="CJ15" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="CK15" s="12"/>
       <c r="CL15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="CM15">
         <v>-0.8</v>
@@ -7754,7 +7736,7 @@
       <c r="CU15" s="12"/>
       <c r="CV15" s="12"/>
       <c r="CW15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="DF15">
         <v>1</v>
@@ -7762,17 +7744,17 @@
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="15" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
@@ -7791,14 +7773,14 @@
         <v>1</v>
       </c>
       <c r="AG16" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AJ16" s="12"/>
       <c r="AR16" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AV16" s="12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AX16">
         <v>9</v>
@@ -7825,7 +7807,7 @@
       <c r="BX16" s="16"/>
       <c r="BY16" s="16"/>
       <c r="CE16" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CJ16" s="15"/>
       <c r="CL16" s="12"/>
@@ -7841,19 +7823,19 @@
     </row>
     <row r="17" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I17">
         <v>1</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M17"/>
       <c r="N17"/>
@@ -7875,10 +7857,10 @@
         <v>1</v>
       </c>
       <c r="AR17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AV17" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AX17">
         <v>1</v>
@@ -7891,7 +7873,7 @@
       </c>
       <c r="BM17" s="12"/>
       <c r="BN17" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="BT17" s="14"/>
       <c r="BU17" s="14"/>
@@ -7902,11 +7884,11 @@
       <c r="BZ17" s="12"/>
       <c r="CH17" s="12"/>
       <c r="CJ17" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="CK17" s="12"/>
       <c r="CL17" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="CM17">
         <v>-0.8</v>
@@ -7918,7 +7900,7 @@
       <c r="CU17" s="12"/>
       <c r="CV17" s="12"/>
       <c r="CW17" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="DF17">
         <v>1</v>
@@ -7926,19 +7908,19 @@
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C18" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="M18"/>
       <c r="N18"/>
@@ -7960,10 +7942,10 @@
         <v>1</v>
       </c>
       <c r="AR18" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AV18" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AX18">
         <v>1</v>
@@ -7976,7 +7958,7 @@
       </c>
       <c r="BM18" s="12"/>
       <c r="BN18" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="BT18" s="14"/>
       <c r="BU18" s="14"/>
@@ -7987,11 +7969,11 @@
       <c r="BZ18" s="12"/>
       <c r="CH18" s="12"/>
       <c r="CJ18" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="CK18" s="12"/>
       <c r="CL18" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="CM18">
         <v>-0.8</v>
@@ -8003,7 +7985,7 @@
       <c r="CU18" s="12"/>
       <c r="CV18" s="12"/>
       <c r="CW18" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="DF18">
         <v>1</v>
@@ -8014,27 +7996,27 @@
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AC20">
         <v>1</v>
       </c>
       <c r="AR20" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="BT20"/>
       <c r="CJ20" s="3"/>
       <c r="CS20" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.25">
@@ -9488,34 +9470,34 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F1" t="s">
         <v>356</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>357</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>358</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>359</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>360</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>361</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>362</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>363</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>364</v>
-      </c>
-      <c r="O1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -9529,40 +9511,40 @@
         <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F2" t="s">
         <v>366</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>367</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>368</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>369</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>370</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>371</v>
-      </c>
-      <c r="K2" t="s">
-        <v>372</v>
       </c>
       <c r="L2" t="s">
         <v>51</v>
       </c>
       <c r="M2" t="s">
+        <v>372</v>
+      </c>
+      <c r="N2" t="s">
         <v>373</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>374</v>
       </c>
-      <c r="O2" t="s">
-        <v>375</v>
-      </c>
       <c r="P2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -9591,13 +9573,13 @@
         <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K3" t="s">
         <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M3" t="s">
         <v>112</v>
@@ -9606,7 +9588,7 @@
         <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P3" t="s">
         <v>121</v>
@@ -9638,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9649,10 +9631,10 @@
         <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9663,7 +9645,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" t="s">
         <v>121</v>
@@ -9698,22 +9680,22 @@
         <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
       </c>
       <c r="F2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G2" t="s">
         <v>379</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>380</v>
       </c>
-      <c r="H2" t="s">
-        <v>381</v>
-      </c>
       <c r="I2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9742,24 +9724,24 @@
         <v>114</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -9786,34 +9768,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1" t="s">
         <v>382</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>383</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>384</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>385</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>386</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>387</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>388</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>389</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>390</v>
-      </c>
-      <c r="L1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9821,34 +9803,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" t="s">
         <v>392</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>393</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>394</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>395</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>396</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>397</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>398</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>399</v>
       </c>
-      <c r="J2" t="s">
-        <v>400</v>
-      </c>
       <c r="K2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L2" t="s">
         <v>94</v>
@@ -9865,7 +9847,7 @@
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -9919,28 +9901,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
       </c>
       <c r="D2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E2" t="s">
         <v>402</v>
-      </c>
-      <c r="E2" t="s">
-        <v>403</v>
       </c>
       <c r="F2" t="s">
         <v>77</v>
       </c>
       <c r="G2" t="s">
+        <v>403</v>
+      </c>
+      <c r="H2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I2" t="s">
         <v>404</v>
-      </c>
-      <c r="H2" t="s">
-        <v>257</v>
-      </c>
-      <c r="I2" t="s">
-        <v>405</v>
       </c>
       <c r="J2" t="s">
         <v>52</v>
@@ -9969,7 +9951,7 @@
         <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I3" t="s">
         <v>114</v>

--- a/Excel/Main/Test.xlsx
+++ b/Excel/Main/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312A2039-899E-4C8B-B582-45612A81DD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2503EC4E-78C1-4059-9D4C-735F3AEA4897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2347" yWindow="2581" windowWidth="17953" windowHeight="10398" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="500">
   <si>
     <t>Id</t>
   </si>
@@ -1871,6 +1871,10 @@
   </si>
   <si>
     <t>{"Fire":600}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCB普攻,获取猫猫</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3097,7 +3101,7 @@
         <v>409</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="AK5">
         <v>0</v>

--- a/Excel/Main/Test.xlsx
+++ b/Excel/Main/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2503EC4E-78C1-4059-9D4C-735F3AEA4897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7241B5CF-2F70-42BC-912B-D9D7582146C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2347" yWindow="2581" windowWidth="17953" windowHeight="10398" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="508">
   <si>
     <t>Id</t>
   </si>
@@ -1353,9 +1353,6 @@
   </si>
   <si>
     <t>0,0</t>
-  </si>
-  <si>
-    <t>死亡</t>
   </si>
   <si>
     <t>凛冬击中</t>
@@ -1772,40 +1769,10 @@
     <t>猫死亡</t>
   </si>
   <si>
-    <t>{"Sanity":100}</t>
-  </si>
-  <si>
     <t>减速</t>
   </si>
   <si>
     <t>Real</t>
-  </si>
-  <si>
-    <t>撤退</t>
-  </si>
-  <si>
-    <t>猫索敌</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>猫爆炸</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>猫死亡</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>猫撤退爆炸</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>猫死亡爆炸</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>猫索敌,猫爆炸,猫死亡,猫撤退爆炸,猫死亡爆炸,猫诱导</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>无</t>
@@ -1876,13 +1843,64 @@
   <si>
     <t>CCB普攻,获取猫猫</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫索敌</t>
+  </si>
+  <si>
+    <t>充能释放</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>部署猫后续</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>部署干员</t>
+  </si>
+  <si>
+    <t>离场</t>
+  </si>
+  <si>
+    <t>{"UnitId":"猫诱导后续","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"猫诱导"}</t>
+  </si>
+  <si>
+    <t>终点距离</t>
+  </si>
+  <si>
+    <t>猫后续死亡</t>
+  </si>
+  <si>
+    <t>{"Sanity":0.25}</t>
+  </si>
+  <si>
+    <t>猫诱导</t>
+  </si>
+  <si>
+    <t>token_10004_otter_motter</t>
+  </si>
+  <si>
+    <t>猫索敌,猫诱导</t>
+  </si>
+  <si>
+    <t>特种</t>
+  </si>
+  <si>
+    <t>头像_召唤物_机械水獭</t>
+  </si>
+  <si>
+    <t>猫诱导后续</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1970,14 +1988,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1985,34 +1995,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2052,7 +2034,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2091,21 +2073,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2436,10 +2403,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -2450,7 +2417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS596"/>
+  <dimension ref="A1:BS598"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2608,7 +2575,7 @@
         <v>39</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="BA1" t="s">
         <v>40</v>
@@ -2778,7 +2745,7 @@
         <v>93</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="BA2" t="s">
         <v>94</v>
@@ -2820,7 +2787,7 @@
         <v>106</v>
       </c>
       <c r="BN2" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="BO2" t="s">
         <v>107</v>
@@ -3046,14 +3013,14 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3095,13 +3062,13 @@
         <v>1</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3119,44 +3086,44 @@
         <v>0.25</v>
       </c>
       <c r="BB5" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="BD5" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="BD5" s="8" t="s">
+      <c r="BE5" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="BE5" s="8" t="s">
+      <c r="BF5" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="BF5" s="8" t="s">
+      <c r="BG5" s="8" t="s">
         <v>413</v>
-      </c>
-      <c r="BG5" s="8" t="s">
-        <v>414</v>
       </c>
       <c r="BH5">
         <v>6</v>
       </c>
       <c r="BI5" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="BJ5" s="8" t="s">
         <v>415</v>
-      </c>
-      <c r="BJ5" s="8" t="s">
-        <v>416</v>
       </c>
       <c r="BK5" s="5"/>
       <c r="BM5" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="BN5" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="BN5" s="8" t="s">
+      <c r="BP5" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="BP5" s="8" t="s">
+      <c r="BQ5" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="BR5" s="8" t="s">
         <v>419</v>
-      </c>
-      <c r="BQ5" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="BR5" s="8" t="s">
-        <v>420</v>
       </c>
       <c r="BS5">
         <v>1</v>
@@ -3176,19 +3143,19 @@
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>457</v>
+        <v>502</v>
       </c>
       <c r="B8" t="s">
         <v>126</v>
       </c>
       <c r="D8" t="s">
+        <v>428</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3203,7 +3170,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>1000</v>
+        <v>553</v>
       </c>
       <c r="N8" s="8"/>
       <c r="O8">
@@ -3234,13 +3201,13 @@
         <v>-1</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>454</v>
+        <v>502</v>
       </c>
       <c r="AH8" t="s">
         <v>122</v>
       </c>
       <c r="AI8" s="8" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="AK8">
         <v>3</v>
@@ -3267,17 +3234,17 @@
         <v>1</v>
       </c>
       <c r="BB8" s="8" t="s">
-        <v>433</v>
+        <v>505</v>
       </c>
       <c r="BD8" t="s">
-        <v>432</v>
+        <v>506</v>
       </c>
       <c r="BE8" t="str">
-        <f t="shared" ref="BE8" si="0">"half_"&amp;D8</f>
+        <f t="shared" ref="BE8:BE9" si="0">"half_"&amp;D8</f>
         <v>half_otter</v>
       </c>
       <c r="BF8" t="str">
-        <f t="shared" ref="BF8" si="1">D8</f>
+        <f t="shared" ref="BF8:BF9" si="1">D8</f>
         <v>otter</v>
       </c>
       <c r="BG8" t="s">
@@ -3307,19 +3274,19 @@
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>464</v>
+        <v>507</v>
       </c>
       <c r="B9" t="s">
         <v>126</v>
       </c>
       <c r="D9" t="s">
+        <v>428</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="F9" s="8" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3331,10 +3298,10 @@
         <v>90</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>1000</v>
+        <v>553</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9">
@@ -3356,7 +3323,7 @@
         <v>0.05</v>
       </c>
       <c r="Z9">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -3364,13 +3331,18 @@
       <c r="AD9">
         <v>1</v>
       </c>
+      <c r="AE9">
+        <v>-1</v>
+      </c>
       <c r="AG9" s="8" t="s">
-        <v>454</v>
+        <v>507</v>
       </c>
       <c r="AH9" t="s">
         <v>122</v>
       </c>
-      <c r="AI9" s="8"/>
+      <c r="AI9" s="8" t="s">
+        <v>469</v>
+      </c>
       <c r="AK9">
         <v>3</v>
       </c>
@@ -3381,7 +3353,7 @@
         <v>1</v>
       </c>
       <c r="AO9">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="AP9">
         <v>0</v>
@@ -3396,17 +3368,17 @@
         <v>1</v>
       </c>
       <c r="BB9" s="8" t="s">
-        <v>433</v>
+        <v>505</v>
       </c>
       <c r="BD9" t="s">
-        <v>432</v>
+        <v>506</v>
       </c>
       <c r="BE9" t="str">
-        <f t="shared" ref="BE9" si="2">"half_"&amp;D9</f>
+        <f t="shared" si="0"/>
         <v>half_otter</v>
       </c>
       <c r="BF9" t="str">
-        <f t="shared" ref="BF9" si="3">D9</f>
+        <f t="shared" si="1"/>
         <v>otter</v>
       </c>
       <c r="BG9" t="s">
@@ -3434,34 +3406,160 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="35:63" x14ac:dyDescent="0.25">
-      <c r="AI23" s="8"/>
-    </row>
-    <row r="29" spans="35:63" x14ac:dyDescent="0.25">
-      <c r="AI29" s="8"/>
-      <c r="BK29" s="8"/>
+    <row r="10" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AI10" s="8"/>
+      <c r="BB10" s="8"/>
+    </row>
+    <row r="11" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="B11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" t="s">
+        <v>428</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>90</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>1000</v>
+      </c>
+      <c r="N11" s="8"/>
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>10</v>
+      </c>
+      <c r="Y11">
+        <v>0.05</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI11" s="8"/>
+      <c r="AK11">
+        <v>3</v>
+      </c>
+      <c r="AL11">
+        <v>-0.5</v>
+      </c>
+      <c r="AN11">
+        <v>1</v>
+      </c>
+      <c r="AO11">
+        <v>99</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>1</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>1</v>
+      </c>
+      <c r="BB11" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>431</v>
+      </c>
+      <c r="BE11" t="str">
+        <f t="shared" ref="BE11" si="2">"half_"&amp;D11</f>
+        <v>half_otter</v>
+      </c>
+      <c r="BF11" t="str">
+        <f t="shared" ref="BF11" si="3">D11</f>
+        <v>otter</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>128</v>
+      </c>
+      <c r="BH11">
+        <v>5</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>127</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>123</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>124</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>125</v>
+      </c>
+      <c r="BQ11" t="s">
+        <v>125</v>
+      </c>
+      <c r="BS11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="35:63" x14ac:dyDescent="0.25">
+      <c r="AI25" s="8"/>
     </row>
     <row r="31" spans="35:63" x14ac:dyDescent="0.25">
       <c r="AI31" s="8"/>
-    </row>
-    <row r="32" spans="35:63" x14ac:dyDescent="0.25">
-      <c r="AI32" s="8"/>
+      <c r="BK31" s="8"/>
     </row>
     <row r="33" spans="4:70" x14ac:dyDescent="0.25">
       <c r="AI33" s="8"/>
-      <c r="BK33" s="8"/>
-    </row>
-    <row r="34" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D34" s="6"/>
-      <c r="E34" s="1"/>
-      <c r="BO34" s="7"/>
-      <c r="BR34" s="7"/>
-    </row>
-    <row r="35" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D35" s="6"/>
-      <c r="E35" s="1"/>
-      <c r="BO35" s="7"/>
-      <c r="BR35" s="7"/>
+    </row>
+    <row r="34" spans="4:70" x14ac:dyDescent="0.25">
+      <c r="AI34" s="8"/>
+    </row>
+    <row r="35" spans="4:70" x14ac:dyDescent="0.25">
+      <c r="AI35" s="8"/>
+      <c r="BK35" s="8"/>
     </row>
     <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="6"/>
@@ -3496,11 +3594,13 @@
     <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="6"/>
       <c r="E41" s="1"/>
+      <c r="BO41" s="7"/>
       <c r="BR41" s="7"/>
     </row>
     <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="6"/>
       <c r="E42" s="1"/>
+      <c r="BO42" s="7"/>
       <c r="BR42" s="7"/>
     </row>
     <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
@@ -3511,13 +3611,11 @@
     <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="6"/>
       <c r="E44" s="1"/>
-      <c r="BO44" s="7"/>
       <c r="BR44" s="7"/>
     </row>
     <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="6"/>
       <c r="E45" s="1"/>
-      <c r="BO45" s="7"/>
       <c r="BR45" s="7"/>
     </row>
     <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
@@ -4693,6 +4791,7 @@
     <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="6"/>
       <c r="E241" s="1"/>
+      <c r="BO241" s="7"/>
       <c r="BR241" s="7"/>
     </row>
     <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
@@ -4704,7 +4803,6 @@
     <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="6"/>
       <c r="E243" s="1"/>
-      <c r="BO243" s="7"/>
       <c r="BR243" s="7"/>
     </row>
     <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
@@ -4950,6 +5048,7 @@
     <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="6"/>
       <c r="E284" s="1"/>
+      <c r="BO284" s="7"/>
       <c r="BR284" s="7"/>
     </row>
     <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
@@ -4961,7 +5060,6 @@
     <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="6"/>
       <c r="E286" s="1"/>
-      <c r="BO286" s="7"/>
       <c r="BR286" s="7"/>
     </row>
     <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
@@ -5285,11 +5383,13 @@
     <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="6"/>
       <c r="E340" s="1"/>
+      <c r="BO340" s="7"/>
       <c r="BR340" s="7"/>
     </row>
     <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="6"/>
       <c r="E341" s="1"/>
+      <c r="BO341" s="7"/>
       <c r="BR341" s="7"/>
     </row>
     <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
@@ -5300,13 +5400,11 @@
     <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="6"/>
       <c r="E343" s="1"/>
-      <c r="BO343" s="7"/>
       <c r="BR343" s="7"/>
     </row>
     <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="6"/>
       <c r="E344" s="1"/>
-      <c r="BO344" s="7"/>
       <c r="BR344" s="7"/>
     </row>
     <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
@@ -5504,23 +5602,23 @@
     <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="6"/>
       <c r="E377" s="1"/>
+      <c r="BO377" s="7"/>
       <c r="BR377" s="7"/>
     </row>
     <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="6"/>
       <c r="E378" s="1"/>
+      <c r="BO378" s="7"/>
       <c r="BR378" s="7"/>
     </row>
     <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="6"/>
       <c r="E379" s="1"/>
-      <c r="BO379" s="7"/>
       <c r="BR379" s="7"/>
     </row>
     <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="6"/>
       <c r="E380" s="1"/>
-      <c r="BO380" s="7"/>
       <c r="BR380" s="7"/>
     </row>
     <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
@@ -5652,45 +5750,45 @@
     <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D402" s="6"/>
       <c r="E402" s="1"/>
+      <c r="BO402" s="7"/>
       <c r="BR402" s="7"/>
     </row>
     <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D403" s="6"/>
       <c r="E403" s="1"/>
+      <c r="BO403" s="7"/>
       <c r="BR403" s="7"/>
     </row>
     <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D404" s="6"/>
       <c r="E404" s="1"/>
-      <c r="BO404" s="7"/>
       <c r="BR404" s="7"/>
     </row>
     <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D405" s="6"/>
       <c r="E405" s="1"/>
-      <c r="BO405" s="7"/>
       <c r="BR405" s="7"/>
     </row>
     <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D406" s="6"/>
       <c r="E406" s="1"/>
+      <c r="BO406" s="7"/>
       <c r="BR406" s="7"/>
     </row>
     <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D407" s="6"/>
       <c r="E407" s="1"/>
+      <c r="BO407" s="7"/>
       <c r="BR407" s="7"/>
     </row>
     <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D408" s="6"/>
       <c r="E408" s="1"/>
-      <c r="BO408" s="7"/>
       <c r="BR408" s="7"/>
     </row>
     <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D409" s="6"/>
       <c r="E409" s="1"/>
-      <c r="BO409" s="7"/>
       <c r="BR409" s="7"/>
     </row>
     <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
@@ -5786,10 +5884,14 @@
     <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D425" s="6"/>
       <c r="E425" s="1"/>
+      <c r="BO425" s="7"/>
+      <c r="BR425" s="7"/>
     </row>
     <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D426" s="6"/>
       <c r="E426" s="1"/>
+      <c r="BO426" s="7"/>
+      <c r="BR426" s="7"/>
     </row>
     <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D427" s="6"/>
@@ -6103,13 +6205,13 @@
       <c r="D504" s="6"/>
       <c r="E504" s="1"/>
     </row>
-    <row r="572" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D572" s="6"/>
-      <c r="E572" s="1"/>
-    </row>
-    <row r="573" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="D573" s="6"/>
-      <c r="E573" s="1"/>
+    <row r="505" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="D505" s="6"/>
+      <c r="E505" s="1"/>
+    </row>
+    <row r="506" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="D506" s="6"/>
+      <c r="E506" s="1"/>
     </row>
     <row r="574" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D574" s="6"/>
@@ -6202,6 +6304,14 @@
     <row r="596" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D596" s="6"/>
       <c r="E596" s="1"/>
+    </row>
+    <row r="597" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="D597" s="6"/>
+      <c r="E597" s="1"/>
+    </row>
+    <row r="598" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="D598" s="6"/>
+      <c r="E598" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -6213,7 +6323,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH832"/>
+  <dimension ref="A1:DH833"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6310,7 +6420,7 @@
         <v>133</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I1" t="s">
         <v>134</v>
@@ -6442,7 +6552,7 @@
         <v>175</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="BA1" t="s">
         <v>176</v>
@@ -6496,10 +6606,10 @@
         <v>191</v>
       </c>
       <c r="BS1" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="BT1" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="BU1" s="4" t="s">
         <v>192</v>
@@ -6547,7 +6657,7 @@
         <v>206</v>
       </c>
       <c r="CJ1" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="CK1" t="s">
         <v>207</v>
@@ -6639,7 +6749,7 @@
         <v>51</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I2" t="s">
         <v>230</v>
@@ -6828,10 +6938,10 @@
         <v>290</v>
       </c>
       <c r="BS2" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BT2" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BU2" s="4" t="s">
         <v>291</v>
@@ -6879,7 +6989,7 @@
         <v>305</v>
       </c>
       <c r="CJ2" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="CK2" t="s">
         <v>306</v>
@@ -6971,7 +7081,7 @@
         <v>114</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I3" t="s">
         <v>112</v>
@@ -6983,7 +7093,7 @@
         <v>330</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>114</v>
@@ -7160,7 +7270,7 @@
         <v>113</v>
       </c>
       <c r="BS3" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="BT3" s="4" t="s">
         <v>113</v>
@@ -7211,7 +7321,7 @@
         <v>342</v>
       </c>
       <c r="CJ3" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="CK3" t="s">
         <v>116</v>
@@ -7298,13 +7408,13 @@
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6"/>
@@ -7312,10 +7422,10 @@
         <v>2</v>
       </c>
       <c r="AO6" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AR6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AV6" t="s">
         <v>349</v>
@@ -7327,31 +7437,31 @@
         <v>1</v>
       </c>
       <c r="BZ6" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="CE6" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="CE6" s="8" t="s">
-        <v>426</v>
-      </c>
       <c r="CF6" s="8" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="CG6" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="CJ6" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="CK6" s="8"/>
       <c r="CW6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J7" s="8"/>
       <c r="O7"/>
@@ -7362,7 +7472,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="8" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="AT7">
         <v>2.5</v>
@@ -7372,26 +7482,26 @@
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="AC8">
         <v>2</v>
       </c>
       <c r="AG8" s="8"/>
       <c r="AO8" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="AX8">
         <v>0</v>
@@ -7404,12 +7514,12 @@
       </c>
       <c r="CE8" s="8"/>
       <c r="CJ8" s="8" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="CL8" s="8"/>
       <c r="CM8" s="8"/>
       <c r="CW8" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
@@ -7427,16 +7537,16 @@
     </row>
     <row r="10" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AC10">
         <v>1</v>
@@ -7445,14 +7555,14 @@
         <v>1</v>
       </c>
       <c r="AG10" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="BB10">
         <v>1</v>
       </c>
       <c r="CJ10" s="3"/>
       <c r="CS10" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="DB10">
         <v>1</v>
@@ -7466,32 +7576,32 @@
     </row>
     <row r="11" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AC11">
         <v>1</v>
       </c>
       <c r="AG11" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AJ11" s="8"/>
       <c r="AT11">
         <v>99</v>
       </c>
       <c r="AV11" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AX11">
         <v>99999</v>
@@ -7515,10 +7625,10 @@
         <v>1</v>
       </c>
       <c r="BW11" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="CE11" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="CJ11" s="3"/>
       <c r="CL11" s="8"/>
@@ -7534,28 +7644,28 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>457</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>458</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AC12">
         <v>2</v>
       </c>
       <c r="AO12" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AR12" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="BB12">
         <v>4</v>
@@ -7565,10 +7675,10 @@
       </c>
       <c r="CJ12" s="3"/>
       <c r="CS12" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="CW12" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
@@ -7581,7 +7691,7 @@
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="C14" t="s">
         <v>346</v>
@@ -7589,158 +7699,117 @@
       <c r="I14">
         <v>1</v>
       </c>
-      <c r="J14" s="18" t="s">
-        <v>461</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="L14" s="13"/>
+      <c r="J14" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="L14" s="12"/>
       <c r="M14"/>
       <c r="N14"/>
-      <c r="O14" s="13"/>
+      <c r="O14" s="12"/>
       <c r="P14"/>
       <c r="Q14"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="13"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
       <c r="AC14">
         <v>2</v>
       </c>
       <c r="AD14">
         <v>1</v>
       </c>
-      <c r="AT14" s="12">
-        <v>0.5</v>
+      <c r="AT14" s="8">
+        <v>0.4</v>
       </c>
       <c r="BB14">
         <v>1</v>
       </c>
-      <c r="BN14" s="12" t="s">
+      <c r="BM14" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="BN14" s="8" t="s">
         <v>470</v>
       </c>
       <c r="BR14">
         <v>6</v>
       </c>
-      <c r="BT14" s="14">
+      <c r="BT14" s="13">
         <v>1</v>
       </c>
-      <c r="BU14" s="14">
+      <c r="BU14" s="13">
         <v>1</v>
       </c>
-      <c r="BV14" s="14">
+      <c r="BV14" s="13">
         <v>1</v>
       </c>
-      <c r="BW14" s="17" t="s">
-        <v>482</v>
-      </c>
-      <c r="BX14" s="14"/>
-      <c r="BY14" s="14"/>
-      <c r="BZ14" s="12"/>
-      <c r="CE14" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="CH14" s="12"/>
-      <c r="CK14" s="12"/>
-      <c r="CR14" s="12"/>
-      <c r="CU14" s="12"/>
-      <c r="CV14" s="12"/>
+      <c r="BW14" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="BX14" s="13"/>
+      <c r="BY14" s="13"/>
+      <c r="BZ14" s="8"/>
+      <c r="CE14" s="8"/>
+      <c r="CH14" s="8"/>
+      <c r="CK14" s="8"/>
+      <c r="CR14" s="8"/>
+      <c r="CU14" s="8"/>
+      <c r="CV14" s="8"/>
       <c r="DF14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="C15" t="s">
+        <v>470</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>346</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="J15" s="8"/>
+      <c r="K15" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L15" s="13"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15" s="13"/>
-      <c r="P15"/>
-      <c r="Q15"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
       <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="AJ15" s="8"/>
+      <c r="AR15" t="s">
+        <v>351</v>
+      </c>
+      <c r="AV15" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="AX15">
+        <v>999</v>
+      </c>
+      <c r="AZ15">
         <v>2</v>
       </c>
-      <c r="AD15">
+      <c r="BB15">
         <v>1</v>
       </c>
-      <c r="AR15" t="s">
-        <v>456</v>
-      </c>
-      <c r="AV15" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="AX15">
+      <c r="BT15"/>
+      <c r="CE15" s="8"/>
+      <c r="CJ15" s="3"/>
+      <c r="CL15" s="8"/>
+      <c r="DB15">
         <v>1</v>
       </c>
-      <c r="BB15">
-        <v>99</v>
-      </c>
-      <c r="BC15">
-        <v>11</v>
-      </c>
-      <c r="BD15">
-        <v>0.5</v>
-      </c>
-      <c r="BM15" s="12"/>
-      <c r="BN15" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="BR15">
-        <v>5.5</v>
-      </c>
-      <c r="BT15" s="14"/>
-      <c r="BU15" s="14"/>
-      <c r="BV15" s="14"/>
-      <c r="BW15" s="17"/>
-      <c r="BX15" s="14"/>
-      <c r="BY15" s="14"/>
-      <c r="BZ15" s="12"/>
-      <c r="CE15" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="CH15" s="12"/>
-      <c r="CJ15" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="CK15" s="12"/>
-      <c r="CL15" t="s">
-        <v>473</v>
-      </c>
-      <c r="CM15">
-        <v>-0.8</v>
-      </c>
-      <c r="CP15">
-        <v>6</v>
-      </c>
-      <c r="CR15" s="12"/>
-      <c r="CU15" s="12"/>
-      <c r="CV15" s="12"/>
-      <c r="CW15" t="s">
-        <v>353</v>
+      <c r="DE15">
+        <v>1</v>
       </c>
       <c r="DF15">
         <v>1</v>
@@ -7748,211 +7817,80 @@
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16" s="12"/>
-      <c r="K16" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
+      <c r="L16" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="AC16">
         <v>1</v>
       </c>
-      <c r="AG16" s="12" t="s">
+      <c r="AG16" t="s">
         <v>348</v>
-      </c>
-      <c r="AJ16" s="12"/>
-      <c r="AR16" t="s">
-        <v>351</v>
-      </c>
-      <c r="AV16" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="AX16">
-        <v>9</v>
-      </c>
-      <c r="AZ16">
-        <v>2</v>
       </c>
       <c r="BB16">
         <v>1</v>
       </c>
-      <c r="BC16">
-        <v>11</v>
-      </c>
-      <c r="BD16">
-        <v>0.5</v>
-      </c>
-      <c r="BR16">
-        <v>5.5</v>
-      </c>
+      <c r="BM16" s="8"/>
       <c r="BT16"/>
-      <c r="BU16" s="16"/>
-      <c r="BV16" s="16"/>
-      <c r="BW16" s="16"/>
-      <c r="BX16" s="16"/>
-      <c r="BY16" s="16"/>
-      <c r="CE16" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="CJ16" s="15"/>
-      <c r="CL16" s="12"/>
-      <c r="DB16">
-        <v>1</v>
-      </c>
-      <c r="DE16">
-        <v>1</v>
-      </c>
-      <c r="DF16">
-        <v>1</v>
+      <c r="CJ16" s="3"/>
+      <c r="CS16" s="8" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="17" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="C17" t="s">
-        <v>346</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17" s="13"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="AC17">
-        <v>2</v>
-      </c>
-      <c r="AD17">
-        <v>1</v>
-      </c>
-      <c r="AR17" t="s">
-        <v>456</v>
-      </c>
-      <c r="AV17" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="AX17">
-        <v>1</v>
-      </c>
-      <c r="BB17">
-        <v>99</v>
-      </c>
-      <c r="BC17">
-        <v>11</v>
-      </c>
-      <c r="BM17" s="12"/>
-      <c r="BN17" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="BT17" s="14"/>
-      <c r="BU17" s="14"/>
-      <c r="BV17" s="14"/>
-      <c r="BW17" s="14"/>
-      <c r="BX17" s="14"/>
-      <c r="BY17" s="14"/>
-      <c r="BZ17" s="12"/>
-      <c r="CH17" s="12"/>
-      <c r="CJ17" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="CK17" s="12"/>
-      <c r="CL17" t="s">
-        <v>473</v>
-      </c>
-      <c r="CM17">
-        <v>-0.8</v>
-      </c>
-      <c r="CP17">
-        <v>6</v>
-      </c>
-      <c r="CR17" s="12"/>
-      <c r="CU17" s="12"/>
-      <c r="CV17" s="12"/>
-      <c r="CW17" t="s">
-        <v>353</v>
-      </c>
-      <c r="DF17">
-        <v>1</v>
-      </c>
+      <c r="CJ17" s="3"/>
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="C18" t="s">
         <v>346</v>
       </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>352</v>
-      </c>
+      <c r="J18" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="L18" s="12"/>
       <c r="M18"/>
       <c r="N18"/>
-      <c r="O18" s="13"/>
+      <c r="O18" s="12"/>
       <c r="P18"/>
       <c r="Q18"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="13"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
       <c r="AC18">
         <v>2</v>
       </c>
       <c r="AD18">
         <v>1</v>
       </c>
+      <c r="AO18" t="s">
+        <v>499</v>
+      </c>
       <c r="AR18" t="s">
-        <v>456</v>
-      </c>
-      <c r="AV18" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="AV18" s="8" t="s">
         <v>350</v>
       </c>
       <c r="AX18">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BB18">
         <v>99</v>
@@ -7960,24 +7898,38 @@
       <c r="BC18">
         <v>11</v>
       </c>
-      <c r="BM18" s="12"/>
-      <c r="BN18" s="12" t="s">
+      <c r="BD18">
+        <v>0.5</v>
+      </c>
+      <c r="BN18" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="BR18">
+        <v>6</v>
+      </c>
+      <c r="BT18" s="13">
+        <v>1</v>
+      </c>
+      <c r="BU18" s="13">
+        <v>1</v>
+      </c>
+      <c r="BV18" s="13">
+        <v>1</v>
+      </c>
+      <c r="BW18" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="BX18" s="13"/>
+      <c r="BY18" s="13"/>
+      <c r="BZ18" s="8"/>
+      <c r="CE18" s="8"/>
+      <c r="CH18" s="8"/>
+      <c r="CJ18" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="CK18" s="8"/>
+      <c r="CL18" t="s">
         <v>471</v>
-      </c>
-      <c r="BT18" s="14"/>
-      <c r="BU18" s="14"/>
-      <c r="BV18" s="14"/>
-      <c r="BW18" s="14"/>
-      <c r="BX18" s="14"/>
-      <c r="BY18" s="14"/>
-      <c r="BZ18" s="12"/>
-      <c r="CH18" s="12"/>
-      <c r="CJ18" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="CK18" s="12"/>
-      <c r="CL18" t="s">
-        <v>473</v>
       </c>
       <c r="CM18">
         <v>-0.8</v>
@@ -7985,47 +7937,105 @@
       <c r="CP18">
         <v>6</v>
       </c>
-      <c r="CR18" s="12"/>
-      <c r="CU18" s="12"/>
-      <c r="CV18" s="12"/>
+      <c r="CR18" s="8"/>
+      <c r="CU18" s="8"/>
+      <c r="CV18" s="8"/>
       <c r="CW18" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="DF18">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="AJ19" s="8"/>
+      <c r="AV19" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="AX19">
+        <v>9</v>
+      </c>
+      <c r="AZ19">
+        <v>2</v>
+      </c>
+      <c r="BB19">
+        <v>1</v>
+      </c>
+      <c r="BC19">
+        <v>11</v>
+      </c>
+      <c r="BD19">
+        <v>0.5</v>
+      </c>
+      <c r="BT19"/>
+      <c r="CE19" s="8"/>
       <c r="CJ19" s="3"/>
+      <c r="CL19" s="8"/>
+      <c r="DB19">
+        <v>1</v>
+      </c>
+      <c r="DE19">
+        <v>1</v>
+      </c>
+      <c r="DF19">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="AG20" s="8"/>
+      <c r="AJ20" s="8"/>
+      <c r="AV20" s="8"/>
+      <c r="BT20"/>
+      <c r="CE20" s="8"/>
+      <c r="CJ20" s="3"/>
+      <c r="CL20" s="8"/>
+    </row>
+    <row r="21" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AR21" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="AC20">
-        <v>1</v>
-      </c>
-      <c r="AR20" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="BT20"/>
-      <c r="CJ20" s="3"/>
-      <c r="CS20" s="8" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="21" spans="1:110" x14ac:dyDescent="0.25">
       <c r="BT21"/>
       <c r="CJ21" s="3"/>
+      <c r="CS21" s="8" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="22" spans="1:110" x14ac:dyDescent="0.25">
       <c r="BT22"/>
@@ -8036,16 +8046,17 @@
       <c r="CJ23" s="3"/>
     </row>
     <row r="24" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BT24"/>
       <c r="CJ24" s="3"/>
     </row>
-    <row r="26" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ26" s="3"/>
+    <row r="25" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ25" s="3"/>
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="BT27"/>
+      <c r="CJ27" s="3"/>
     </row>
     <row r="28" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ28" s="3"/>
+      <c r="BT28"/>
     </row>
     <row r="29" spans="1:110" x14ac:dyDescent="0.25">
       <c r="CJ29" s="3"/>
@@ -8053,33 +8064,33 @@
     <row r="30" spans="1:110" x14ac:dyDescent="0.25">
       <c r="CJ30" s="3"/>
     </row>
-    <row r="33" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ33" s="3"/>
+    <row r="31" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ31" s="3"/>
     </row>
     <row r="34" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ34" s="3"/>
     </row>
-    <row r="38" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT38"/>
+    <row r="35" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ35" s="3"/>
     </row>
     <row r="39" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ39" s="3"/>
-    </row>
-    <row r="44" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT44"/>
-    </row>
-    <row r="47" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT47"/>
-      <c r="CJ47" s="3"/>
+      <c r="BT39"/>
+    </row>
+    <row r="40" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ40" s="3"/>
+    </row>
+    <row r="45" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT45"/>
     </row>
     <row r="48" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT48"/>
-    </row>
-    <row r="50" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT50"/>
+      <c r="CJ48" s="3"/>
+    </row>
+    <row r="49" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT49"/>
     </row>
     <row r="51" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ51" s="3"/>
+      <c r="BT51"/>
     </row>
     <row r="52" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ52" s="3"/>
@@ -8090,20 +8101,20 @@
     <row r="54" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ54" s="3"/>
     </row>
-    <row r="59" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ59" s="3"/>
+    <row r="55" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ55" s="3"/>
     </row>
     <row r="60" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ60" s="3"/>
     </row>
-    <row r="66" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ66" s="3"/>
+    <row r="61" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ61" s="3"/>
     </row>
     <row r="67" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ67" s="3"/>
     </row>
-    <row r="69" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ69" s="3"/>
+    <row r="68" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ68" s="3"/>
     </row>
     <row r="70" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ70" s="3"/>
@@ -8115,50 +8126,50 @@
       <c r="CJ72" s="3"/>
     </row>
     <row r="73" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT73"/>
+      <c r="CJ73" s="3"/>
     </row>
     <row r="74" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT74"/>
     </row>
     <row r="75" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT75"/>
-      <c r="CJ75" s="3"/>
     </row>
     <row r="76" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT76"/>
       <c r="CJ76" s="3"/>
     </row>
     <row r="77" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ77" s="3"/>
     </row>
     <row r="78" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT78"/>
+      <c r="CJ78" s="3"/>
     </row>
     <row r="79" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ79" s="3"/>
-    </row>
-    <row r="83" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT83"/>
+      <c r="BT79"/>
+    </row>
+    <row r="80" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ80" s="3"/>
     </row>
     <row r="84" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ84" s="3"/>
-    </row>
-    <row r="92" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ92" s="3"/>
+      <c r="BT84"/>
+    </row>
+    <row r="85" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ85" s="3"/>
     </row>
     <row r="93" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ93" s="3"/>
     </row>
     <row r="94" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT94"/>
-    </row>
-    <row r="99" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT99"/>
+      <c r="CJ94" s="3"/>
+    </row>
+    <row r="95" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT95"/>
     </row>
     <row r="100" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT100"/>
-      <c r="CJ100" s="3"/>
     </row>
     <row r="101" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT101"/>
       <c r="CJ101" s="3"/>
     </row>
     <row r="102" spans="72:88" x14ac:dyDescent="0.25">
@@ -8171,10 +8182,10 @@
       <c r="CJ104" s="3"/>
     </row>
     <row r="105" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT105"/>
+      <c r="CJ105" s="3"/>
     </row>
     <row r="106" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ106" s="3"/>
+      <c r="BT106"/>
     </row>
     <row r="107" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ107" s="3"/>
@@ -8186,10 +8197,10 @@
       <c r="CJ109" s="3"/>
     </row>
     <row r="110" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT110"/>
+      <c r="CJ110" s="3"/>
     </row>
     <row r="111" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ111" s="3"/>
+      <c r="BT111"/>
     </row>
     <row r="112" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ112" s="3"/>
@@ -8200,8 +8211,8 @@
     <row r="114" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ114" s="3"/>
     </row>
-    <row r="117" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ117" s="3"/>
+    <row r="115" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ115" s="3"/>
     </row>
     <row r="118" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ118" s="3"/>
@@ -8215,11 +8226,11 @@
     <row r="121" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ121" s="3"/>
     </row>
-    <row r="123" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT123"/>
+    <row r="122" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ122" s="3"/>
     </row>
     <row r="124" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ124" s="3"/>
+      <c r="BT124"/>
     </row>
     <row r="125" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ125" s="3"/>
@@ -8230,17 +8241,17 @@
     <row r="127" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ127" s="3"/>
     </row>
-    <row r="131" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ131" s="3"/>
-    </row>
-    <row r="133" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT133"/>
+    <row r="128" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ128" s="3"/>
+    </row>
+    <row r="132" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ132" s="3"/>
     </row>
     <row r="134" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT134"/>
-      <c r="CJ134" s="3"/>
     </row>
     <row r="135" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT135"/>
       <c r="CJ135" s="3"/>
     </row>
     <row r="136" spans="72:88" x14ac:dyDescent="0.25">
@@ -8252,50 +8263,50 @@
     <row r="138" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ138" s="3"/>
     </row>
-    <row r="140" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT140"/>
+    <row r="139" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ139" s="3"/>
     </row>
     <row r="141" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ141" s="3"/>
+      <c r="BT141"/>
     </row>
     <row r="142" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ142" s="3"/>
     </row>
-    <row r="144" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ144" s="3"/>
+    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ143" s="3"/>
     </row>
     <row r="145" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ145" s="3"/>
     </row>
-    <row r="147" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT147"/>
+    <row r="146" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ146" s="3"/>
     </row>
     <row r="148" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ148" s="3"/>
-    </row>
-    <row r="151" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ151" s="3"/>
+      <c r="BT148"/>
+    </row>
+    <row r="149" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ149" s="3"/>
     </row>
     <row r="152" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ152" s="3"/>
     </row>
-    <row r="155" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ155" s="3"/>
-    </row>
-    <row r="157" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ157" s="3"/>
-    </row>
-    <row r="159" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT159"/>
+    <row r="153" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ153" s="3"/>
+    </row>
+    <row r="156" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ156" s="3"/>
+    </row>
+    <row r="158" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ158" s="3"/>
     </row>
     <row r="160" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ160" s="3"/>
+      <c r="BT160"/>
     </row>
     <row r="161" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ161" s="3"/>
     </row>
-    <row r="163" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ163" s="3"/>
+    <row r="162" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ162" s="3"/>
     </row>
     <row r="164" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ164" s="3"/>
@@ -8303,187 +8314,186 @@
     <row r="165" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ165" s="3"/>
     </row>
-    <row r="170" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ170" s="3"/>
+    <row r="166" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ166" s="3"/>
     </row>
     <row r="171" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ171" s="3"/>
     </row>
-    <row r="174" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ174" s="3"/>
+    <row r="172" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ172" s="3"/>
     </row>
     <row r="175" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ175" s="3"/>
     </row>
-    <row r="179" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ179" s="3"/>
-    </row>
-    <row r="183" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ183" s="3"/>
-    </row>
-    <row r="185" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ185" s="3"/>
+    <row r="176" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ176" s="3"/>
+    </row>
+    <row r="180" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ180" s="3"/>
+    </row>
+    <row r="184" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ184" s="3"/>
     </row>
     <row r="186" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ186" s="3"/>
     </row>
-    <row r="188" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ188" s="3"/>
+    <row r="187" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ187" s="3"/>
     </row>
     <row r="189" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ189" s="3"/>
     </row>
-    <row r="191" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT191"/>
+    <row r="190" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ190" s="3"/>
     </row>
     <row r="192" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT192"/>
-      <c r="CJ192" s="3"/>
     </row>
     <row r="193" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT193"/>
       <c r="CJ193" s="3"/>
     </row>
-    <row r="195" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ195" s="3"/>
-    </row>
-    <row r="204" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT204"/>
+    <row r="194" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ194" s="3"/>
+    </row>
+    <row r="196" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ196" s="3"/>
     </row>
     <row r="205" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT205"/>
-      <c r="CJ205" s="3"/>
     </row>
     <row r="206" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT206"/>
       <c r="CJ206" s="3"/>
     </row>
     <row r="207" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ207" s="3"/>
     </row>
     <row r="208" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT208"/>
+      <c r="CJ208" s="3"/>
     </row>
     <row r="209" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT209"/>
-      <c r="CJ209" s="3"/>
     </row>
     <row r="210" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT210"/>
       <c r="CJ210" s="3"/>
     </row>
-    <row r="212" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT212"/>
+    <row r="211" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ211" s="3"/>
     </row>
     <row r="213" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT213"/>
-      <c r="CJ213" s="3"/>
     </row>
     <row r="214" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT214"/>
       <c r="CJ214" s="3"/>
     </row>
-    <row r="216" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT216"/>
+    <row r="215" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ215" s="3"/>
     </row>
     <row r="217" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ217" s="3"/>
-    </row>
-    <row r="220" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ220" s="3"/>
-    </row>
-    <row r="224" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ224" s="3"/>
-    </row>
-    <row r="226" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT226"/>
+      <c r="BT217"/>
+    </row>
+    <row r="218" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ218" s="3"/>
+    </row>
+    <row r="221" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ221" s="3"/>
+    </row>
+    <row r="225" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ225" s="3"/>
     </row>
     <row r="227" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ227" s="3"/>
-    </row>
-    <row r="234" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT234"/>
+      <c r="BT227"/>
+    </row>
+    <row r="228" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ228" s="3"/>
     </row>
     <row r="235" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ235" s="3"/>
+      <c r="BT235"/>
     </row>
     <row r="236" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ236" s="3"/>
     </row>
-    <row r="238" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT238"/>
+    <row r="237" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ237" s="3"/>
     </row>
     <row r="239" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT239"/>
-      <c r="CJ239" s="3"/>
     </row>
     <row r="240" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT240"/>
       <c r="CJ240" s="3"/>
     </row>
-    <row r="246" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT246"/>
+    <row r="241" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ241" s="3"/>
     </row>
     <row r="247" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT247"/>
-      <c r="CJ247" s="3"/>
     </row>
     <row r="248" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT248"/>
       <c r="CJ248" s="3"/>
     </row>
     <row r="249" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT249"/>
       <c r="CJ249" s="3"/>
     </row>
-    <row r="254" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT254"/>
+    <row r="250" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ250" s="3"/>
     </row>
     <row r="255" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT255"/>
     </row>
-    <row r="259" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT259"/>
+    <row r="256" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT256"/>
     </row>
     <row r="260" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ260" s="3"/>
+      <c r="BT260"/>
     </row>
     <row r="261" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT261"/>
+      <c r="CJ261" s="3"/>
     </row>
     <row r="262" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ262" s="3"/>
-    </row>
-    <row r="272" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT272"/>
+      <c r="BT262"/>
+    </row>
+    <row r="263" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ263" s="3"/>
     </row>
     <row r="273" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ273" s="3"/>
-    </row>
-    <row r="275" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT275"/>
+      <c r="BT273"/>
+    </row>
+    <row r="274" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ274" s="3"/>
     </row>
     <row r="276" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ276" s="3"/>
-    </row>
-    <row r="284" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT284"/>
+      <c r="BT276"/>
+    </row>
+    <row r="277" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ277" s="3"/>
     </row>
     <row r="285" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ285" s="3"/>
-    </row>
-    <row r="289" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT289"/>
+      <c r="BT285"/>
+    </row>
+    <row r="286" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ286" s="3"/>
     </row>
     <row r="290" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ290" s="3"/>
-    </row>
-    <row r="292" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT292"/>
+      <c r="BT290"/>
+    </row>
+    <row r="291" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ291" s="3"/>
     </row>
     <row r="293" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ293" s="3"/>
-    </row>
-    <row r="309" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT309"/>
+      <c r="BT293"/>
+    </row>
+    <row r="294" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ294" s="3"/>
     </row>
     <row r="310" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT310"/>
-      <c r="CJ310" s="3"/>
     </row>
     <row r="311" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT311"/>
@@ -8495,49 +8505,50 @@
     </row>
     <row r="313" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT313"/>
-    </row>
-    <row r="315" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT315"/>
+      <c r="CJ313" s="3"/>
+    </row>
+    <row r="314" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT314"/>
     </row>
     <row r="316" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT316"/>
-      <c r="CJ316" s="3"/>
     </row>
     <row r="317" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT317"/>
       <c r="CJ317" s="3"/>
     </row>
     <row r="318" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT318"/>
       <c r="CJ318" s="3"/>
     </row>
-    <row r="322" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT322"/>
+    <row r="319" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ319" s="3"/>
     </row>
     <row r="323" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ323" s="3"/>
-    </row>
-    <row r="325" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT325"/>
+      <c r="BT323"/>
+    </row>
+    <row r="324" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ324" s="3"/>
     </row>
     <row r="326" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT326"/>
-      <c r="CJ326" s="3"/>
     </row>
     <row r="327" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT327"/>
       <c r="CJ327" s="3"/>
     </row>
     <row r="328" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT328"/>
       <c r="CJ328" s="3"/>
     </row>
-    <row r="344" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT344"/>
+    <row r="329" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ329" s="3"/>
     </row>
     <row r="345" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ345" s="3"/>
-    </row>
-    <row r="353" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ353" s="3"/>
+      <c r="BT345"/>
+    </row>
+    <row r="346" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ346" s="3"/>
     </row>
     <row r="354" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ354" s="3"/>
@@ -8551,47 +8562,47 @@
     <row r="357" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ357" s="3"/>
     </row>
-    <row r="359" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT359"/>
+    <row r="358" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ358" s="3"/>
     </row>
     <row r="360" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ360" s="3"/>
+      <c r="BT360"/>
     </row>
     <row r="361" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT361"/>
+      <c r="CJ361" s="3"/>
     </row>
     <row r="362" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT362"/>
-      <c r="CJ362" s="3"/>
     </row>
     <row r="363" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT363"/>
       <c r="CJ363" s="3"/>
     </row>
-    <row r="365" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT365"/>
+    <row r="364" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ364" s="3"/>
     </row>
     <row r="366" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT366"/>
-      <c r="CJ366" s="3"/>
     </row>
     <row r="367" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT367"/>
       <c r="CJ367" s="3"/>
     </row>
     <row r="368" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT368"/>
       <c r="CJ368" s="3"/>
     </row>
-    <row r="370" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ370" s="3"/>
-    </row>
-    <row r="372" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ372" s="3"/>
-    </row>
-    <row r="374" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ374" s="3"/>
-    </row>
-    <row r="377" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ377" s="3"/>
+    <row r="369" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ369" s="3"/>
+    </row>
+    <row r="371" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ371" s="3"/>
+    </row>
+    <row r="373" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ373" s="3"/>
+    </row>
+    <row r="375" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ375" s="3"/>
     </row>
     <row r="378" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ378" s="3"/>
@@ -8609,17 +8620,17 @@
       <c r="CJ382" s="3"/>
     </row>
     <row r="383" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT383"/>
+      <c r="CJ383" s="3"/>
     </row>
     <row r="384" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT384"/>
-      <c r="CJ384" s="3"/>
     </row>
     <row r="385" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT385"/>
       <c r="CJ385" s="3"/>
     </row>
     <row r="386" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT386"/>
       <c r="CJ386" s="3"/>
     </row>
     <row r="387" spans="72:88" x14ac:dyDescent="0.25">
@@ -8631,37 +8642,36 @@
     <row r="389" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ389" s="3"/>
     </row>
-    <row r="391" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ391" s="3"/>
+    <row r="390" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ390" s="3"/>
     </row>
     <row r="392" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ392" s="3"/>
     </row>
     <row r="393" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT393"/>
+      <c r="CJ393" s="3"/>
     </row>
     <row r="394" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT394"/>
-      <c r="CJ394" s="3"/>
     </row>
     <row r="395" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT395"/>
       <c r="CJ395" s="3"/>
     </row>
     <row r="396" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT396"/>
       <c r="CJ396" s="3"/>
     </row>
     <row r="397" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ397" s="3"/>
     </row>
-    <row r="399" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ399" s="3"/>
+    <row r="398" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ398" s="3"/>
     </row>
     <row r="400" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ400" s="3"/>
     </row>
     <row r="401" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT401"/>
       <c r="CJ401" s="3"/>
     </row>
     <row r="402" spans="72:88" x14ac:dyDescent="0.25">
@@ -8669,6 +8679,7 @@
       <c r="CJ402" s="3"/>
     </row>
     <row r="403" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT403"/>
       <c r="CJ403" s="3"/>
     </row>
     <row r="404" spans="72:88" x14ac:dyDescent="0.25">
@@ -8677,70 +8688,70 @@
     <row r="405" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ405" s="3"/>
     </row>
-    <row r="407" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT407"/>
-      <c r="CJ407" s="3"/>
+    <row r="406" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ406" s="3"/>
     </row>
     <row r="408" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT408"/>
       <c r="CJ408" s="3"/>
     </row>
     <row r="409" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ409" s="3"/>
     </row>
-    <row r="411" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT411"/>
-      <c r="CJ411" s="3"/>
+    <row r="410" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ410" s="3"/>
     </row>
     <row r="412" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT412"/>
       <c r="CJ412" s="3"/>
     </row>
     <row r="413" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT413"/>
       <c r="CJ413" s="3"/>
     </row>
-    <row r="415" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ415" s="3"/>
-    </row>
-    <row r="417" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ417" s="3"/>
-    </row>
-    <row r="420" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ420" s="3"/>
+    <row r="414" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ414" s="3"/>
+    </row>
+    <row r="416" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ416" s="3"/>
+    </row>
+    <row r="418" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ418" s="3"/>
     </row>
     <row r="421" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ421" s="3"/>
     </row>
-    <row r="425" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT425"/>
+    <row r="422" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ422" s="3"/>
     </row>
     <row r="426" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT426"/>
-      <c r="CJ426" s="3"/>
     </row>
     <row r="427" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT427"/>
       <c r="CJ427" s="3"/>
     </row>
     <row r="428" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT428"/>
       <c r="CJ428" s="3"/>
     </row>
     <row r="429" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ429" s="3"/>
     </row>
     <row r="430" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT430"/>
+      <c r="CJ430" s="3"/>
     </row>
     <row r="431" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ431" s="3"/>
-    </row>
-    <row r="433" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ433" s="3"/>
+      <c r="BT431"/>
+    </row>
+    <row r="432" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ432" s="3"/>
     </row>
     <row r="434" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ434" s="3"/>
     </row>
-    <row r="436" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ436" s="3"/>
+    <row r="435" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ435" s="3"/>
     </row>
     <row r="437" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ437" s="3"/>
@@ -8760,75 +8771,74 @@
     <row r="442" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ442" s="3"/>
     </row>
-    <row r="444" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT444"/>
+    <row r="443" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ443" s="3"/>
     </row>
     <row r="445" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ445" s="3"/>
+      <c r="BT445"/>
     </row>
     <row r="446" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ446" s="3"/>
     </row>
-    <row r="479" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS479" s="10"/>
-      <c r="BT479" s="11"/>
-    </row>
-    <row r="480" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H480" s="10"/>
-      <c r="CJ480" s="10"/>
-    </row>
-    <row r="486" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT486"/>
-    </row>
-    <row r="487" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="447" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ447" s="3"/>
+    </row>
+    <row r="480" spans="71:72" x14ac:dyDescent="0.25">
+      <c r="BS480" s="10"/>
+      <c r="BT480" s="11"/>
+    </row>
+    <row r="481" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H481" s="10"/>
+      <c r="CJ481" s="10"/>
+    </row>
+    <row r="487" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT487"/>
-      <c r="CJ487" s="3"/>
-    </row>
-    <row r="488" spans="72:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="488" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT488"/>
       <c r="CJ488" s="3"/>
     </row>
-    <row r="489" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="489" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT489"/>
       <c r="CJ489" s="3"/>
     </row>
-    <row r="506" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT506"/>
+    <row r="490" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CJ490" s="3"/>
     </row>
     <row r="507" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ507" s="3"/>
-    </row>
-    <row r="539" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT539"/>
+      <c r="BT507"/>
+    </row>
+    <row r="508" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ508" s="3"/>
     </row>
     <row r="540" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT540"/>
-      <c r="CJ540" s="3"/>
     </row>
     <row r="541" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT541"/>
       <c r="CJ541" s="3"/>
     </row>
-    <row r="557" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT557"/>
+    <row r="542" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ542" s="3"/>
     </row>
     <row r="558" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ558" s="3"/>
-    </row>
-    <row r="564" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT564"/>
+      <c r="BT558"/>
+    </row>
+    <row r="559" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ559" s="3"/>
     </row>
     <row r="565" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT565"/>
-      <c r="CJ565" s="3"/>
     </row>
     <row r="566" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT566"/>
       <c r="CJ566" s="3"/>
     </row>
-    <row r="571" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT571"/>
+    <row r="567" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ567" s="3"/>
     </row>
     <row r="572" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT572"/>
-      <c r="CJ572" s="3"/>
     </row>
     <row r="573" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT573"/>
@@ -8887,40 +8897,40 @@
       <c r="CJ586" s="3"/>
     </row>
     <row r="587" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT587"/>
       <c r="CJ587" s="3"/>
     </row>
-    <row r="591" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT591"/>
+    <row r="588" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ588" s="3"/>
     </row>
     <row r="592" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT592"/>
-      <c r="CJ592" s="3"/>
     </row>
     <row r="593" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT593"/>
       <c r="CJ593" s="3"/>
     </row>
     <row r="594" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT594"/>
+      <c r="CJ594" s="3"/>
     </row>
     <row r="595" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ595" s="3"/>
-    </row>
-    <row r="598" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT598"/>
+      <c r="BT595"/>
+    </row>
+    <row r="596" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ596" s="3"/>
     </row>
     <row r="599" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT599"/>
-      <c r="CJ599" s="3"/>
     </row>
     <row r="600" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT600"/>
       <c r="CJ600" s="3"/>
     </row>
-    <row r="631" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT631"/>
+    <row r="601" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ601" s="3"/>
     </row>
     <row r="632" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT632"/>
-      <c r="CJ632" s="3"/>
     </row>
     <row r="633" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT633"/>
@@ -8947,26 +8957,26 @@
       <c r="CJ638" s="3"/>
     </row>
     <row r="639" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT639"/>
       <c r="CJ639" s="3"/>
     </row>
-    <row r="641" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT641"/>
+    <row r="640" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ640" s="3"/>
     </row>
     <row r="642" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ642" s="3"/>
-    </row>
-    <row r="646" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT646"/>
+      <c r="BT642"/>
+    </row>
+    <row r="643" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ643" s="3"/>
     </row>
     <row r="647" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ647" s="3"/>
-    </row>
-    <row r="650" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT650"/>
+      <c r="BT647"/>
+    </row>
+    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ648" s="3"/>
     </row>
     <row r="651" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT651"/>
-      <c r="CJ651" s="3"/>
     </row>
     <row r="652" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT652"/>
@@ -8977,20 +8987,20 @@
       <c r="CJ653" s="3"/>
     </row>
     <row r="654" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT654"/>
       <c r="CJ654" s="3"/>
     </row>
-    <row r="661" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT661"/>
+    <row r="655" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ655" s="3"/>
     </row>
     <row r="662" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ662" s="3"/>
-    </row>
-    <row r="665" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT665"/>
+      <c r="BT662"/>
+    </row>
+    <row r="663" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ663" s="3"/>
     </row>
     <row r="666" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT666"/>
-      <c r="CJ666" s="3"/>
     </row>
     <row r="667" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT667"/>
@@ -9001,74 +9011,74 @@
       <c r="CJ668" s="3"/>
     </row>
     <row r="669" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT669"/>
       <c r="CJ669" s="3"/>
     </row>
-    <row r="671" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT671"/>
+    <row r="670" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ670" s="3"/>
     </row>
     <row r="672" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT672"/>
-      <c r="CJ672" s="3"/>
-    </row>
-    <row r="673" spans="88:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="673" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT673"/>
       <c r="CJ673" s="3"/>
     </row>
-    <row r="674" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ674">
+    <row r="674" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ674" s="3"/>
+    </row>
+    <row r="675" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ675">
         <v>0.15</v>
       </c>
     </row>
-    <row r="676" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ676">
+    <row r="677" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ677">
         <v>0.2</v>
       </c>
     </row>
-    <row r="677" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ677">
+    <row r="678" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ678">
         <v>0.1</v>
       </c>
     </row>
-    <row r="679" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ679">
+    <row r="680" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ680">
         <v>0.2</v>
       </c>
     </row>
-    <row r="686" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ686">
+    <row r="687" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ687">
         <v>1</v>
-      </c>
-    </row>
-    <row r="688" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ688">
-        <v>0.4</v>
       </c>
     </row>
     <row r="689" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ689">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="690" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ690">
         <v>0.6</v>
-      </c>
-    </row>
-    <row r="692" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ692">
-        <v>0.5</v>
       </c>
     </row>
     <row r="693" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ693">
-        <v>0.66700000000000004</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="694" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ694">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="695" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ695">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="697" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT697"/>
     </row>
     <row r="698" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT698"/>
-      <c r="CJ698" s="3"/>
     </row>
     <row r="699" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT699"/>
@@ -9099,20 +9109,20 @@
       <c r="CJ705" s="3"/>
     </row>
     <row r="706" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT706"/>
       <c r="CJ706" s="3"/>
     </row>
     <row r="707" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT707"/>
+      <c r="CJ707" s="3"/>
     </row>
     <row r="708" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ708" s="3"/>
-    </row>
-    <row r="717" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT717"/>
+      <c r="BT708"/>
+    </row>
+    <row r="709" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ709" s="3"/>
     </row>
     <row r="718" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT718"/>
-      <c r="CJ718" s="3"/>
     </row>
     <row r="719" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT719"/>
@@ -9139,86 +9149,86 @@
       <c r="CJ724" s="3"/>
     </row>
     <row r="725" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT725"/>
       <c r="CJ725" s="3"/>
     </row>
     <row r="726" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT726"/>
+      <c r="CJ726" s="3"/>
     </row>
     <row r="727" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ727" s="3"/>
-    </row>
-    <row r="732" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT732"/>
+      <c r="BT727"/>
+    </row>
+    <row r="728" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ728" s="3"/>
     </row>
     <row r="733" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT733"/>
-      <c r="CJ733" s="3"/>
     </row>
     <row r="734" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT734"/>
       <c r="CJ734" s="3"/>
     </row>
     <row r="735" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT735"/>
+      <c r="CJ735" s="3"/>
     </row>
     <row r="736" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT736"/>
-      <c r="CJ736" s="3"/>
-    </row>
-    <row r="737" spans="71:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="737" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT737"/>
       <c r="CJ737" s="3"/>
     </row>
-    <row r="738" spans="71:88" x14ac:dyDescent="0.25">
-      <c r="BT738"/>
-    </row>
-    <row r="739" spans="71:88" x14ac:dyDescent="0.25">
+    <row r="738" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ738" s="3"/>
+    </row>
+    <row r="739" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT739"/>
-      <c r="CJ739" s="3"/>
-    </row>
-    <row r="740" spans="71:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="740" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT740"/>
       <c r="CJ740" s="3"/>
     </row>
-    <row r="741" spans="71:88" x14ac:dyDescent="0.25">
+    <row r="741" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT741"/>
       <c r="CJ741" s="3"/>
     </row>
-    <row r="742" spans="71:88" x14ac:dyDescent="0.25">
+    <row r="742" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT742"/>
       <c r="CJ742" s="3"/>
     </row>
-    <row r="746" spans="71:88" x14ac:dyDescent="0.25">
-      <c r="BT746"/>
-    </row>
-    <row r="747" spans="71:88" x14ac:dyDescent="0.25">
+    <row r="743" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ743" s="3"/>
+    </row>
+    <row r="747" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT747"/>
-      <c r="CJ747" s="3"/>
-    </row>
-    <row r="748" spans="71:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="748" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT748"/>
       <c r="CJ748" s="3"/>
     </row>
-    <row r="749" spans="71:88" x14ac:dyDescent="0.25">
+    <row r="749" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT749"/>
       <c r="CJ749" s="3"/>
     </row>
-    <row r="750" spans="71:88" x14ac:dyDescent="0.25">
-      <c r="BT750"/>
-    </row>
-    <row r="751" spans="71:88" x14ac:dyDescent="0.25">
-      <c r="CJ751" s="3"/>
-    </row>
-    <row r="752" spans="71:88" x14ac:dyDescent="0.25">
-      <c r="BS752" s="10"/>
-      <c r="BT752" s="11"/>
+    <row r="750" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ750" s="3"/>
+    </row>
+    <row r="751" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT751"/>
+    </row>
+    <row r="752" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ752" s="3"/>
     </row>
     <row r="753" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H753" s="10"/>
-      <c r="CJ753" s="10"/>
-    </row>
-    <row r="770" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT770"/>
+      <c r="BS753" s="10"/>
+      <c r="BT753" s="11"/>
+    </row>
+    <row r="754" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H754" s="10"/>
+      <c r="CJ754" s="10"/>
     </row>
     <row r="771" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT771"/>
-      <c r="CJ771" s="3"/>
     </row>
     <row r="772" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT772"/>
@@ -9229,30 +9239,30 @@
       <c r="CJ773" s="3"/>
     </row>
     <row r="774" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT774"/>
       <c r="CJ774" s="3"/>
     </row>
     <row r="775" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT775"/>
+      <c r="CJ775" s="3"/>
     </row>
     <row r="776" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT776"/>
-      <c r="CJ776" s="3"/>
     </row>
     <row r="777" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS777" s="10"/>
-      <c r="BT777" s="11"/>
+      <c r="BT777"/>
       <c r="CJ777" s="3"/>
     </row>
     <row r="778" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H778" s="10"/>
-      <c r="CJ778" s="10"/>
-    </row>
-    <row r="781" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT781"/>
+      <c r="BS778" s="10"/>
+      <c r="BT778" s="11"/>
+      <c r="CJ778" s="3"/>
+    </row>
+    <row r="779" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H779" s="10"/>
+      <c r="CJ779" s="10"/>
     </row>
     <row r="782" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT782"/>
-      <c r="CJ782" s="3"/>
     </row>
     <row r="783" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT783"/>
@@ -9279,14 +9289,14 @@
       <c r="CJ788" s="3"/>
     </row>
     <row r="789" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT789"/>
       <c r="CJ789" s="3"/>
     </row>
-    <row r="791" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT791"/>
+    <row r="790" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ790" s="3"/>
     </row>
     <row r="792" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT792"/>
-      <c r="CJ792" s="3"/>
     </row>
     <row r="793" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT793"/>
@@ -9305,14 +9315,14 @@
       <c r="CJ796" s="3"/>
     </row>
     <row r="797" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT797"/>
       <c r="CJ797" s="3"/>
     </row>
     <row r="798" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT798"/>
+      <c r="CJ798" s="3"/>
     </row>
     <row r="799" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT799"/>
-      <c r="CJ799" s="3"/>
     </row>
     <row r="800" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT800"/>
@@ -9427,21 +9437,25 @@
       <c r="CJ827" s="3"/>
     </row>
     <row r="828" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT828"/>
       <c r="CJ828" s="3"/>
     </row>
     <row r="829" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT829"/>
+      <c r="CJ829" s="3"/>
     </row>
     <row r="830" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT830"/>
-      <c r="CJ830" s="3"/>
     </row>
     <row r="831" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT831"/>
       <c r="CJ831" s="3"/>
     </row>
     <row r="832" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT832"/>
       <c r="CJ832" s="3"/>
+    </row>
+    <row r="833" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ833" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -9474,34 +9488,34 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" t="s">
         <v>355</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>356</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>357</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>358</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>359</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>360</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>361</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>362</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>363</v>
-      </c>
-      <c r="O1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -9515,37 +9529,37 @@
         <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F2" t="s">
         <v>365</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>366</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>367</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>368</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>369</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>370</v>
-      </c>
-      <c r="K2" t="s">
-        <v>371</v>
       </c>
       <c r="L2" t="s">
         <v>51</v>
       </c>
       <c r="M2" t="s">
+        <v>371</v>
+      </c>
+      <c r="N2" t="s">
         <v>372</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>373</v>
-      </c>
-      <c r="O2" t="s">
-        <v>374</v>
       </c>
       <c r="P2" t="s">
         <v>314</v>
@@ -9624,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9635,7 +9649,7 @@
         <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D2" t="s">
         <v>314</v>
@@ -9684,19 +9698,19 @@
         <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
       </c>
       <c r="F2" t="s">
+        <v>377</v>
+      </c>
+      <c r="G2" t="s">
         <v>378</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>379</v>
-      </c>
-      <c r="H2" t="s">
-        <v>380</v>
       </c>
       <c r="I2" t="s">
         <v>314</v>
@@ -9728,24 +9742,24 @@
         <v>114</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="C4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -9772,34 +9786,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
         <v>381</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>382</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>383</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>384</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>385</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>386</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>387</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>388</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>389</v>
-      </c>
-      <c r="L1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9807,34 +9821,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" t="s">
         <v>391</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>392</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>393</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>394</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>395</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>396</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>397</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>398</v>
       </c>
-      <c r="J2" t="s">
-        <v>399</v>
-      </c>
       <c r="K2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L2" t="s">
         <v>94</v>
@@ -9851,7 +9865,7 @@
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -9911,22 +9925,22 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E2" t="s">
         <v>401</v>
-      </c>
-      <c r="E2" t="s">
-        <v>402</v>
       </c>
       <c r="F2" t="s">
         <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2" t="s">
         <v>256</v>
       </c>
       <c r="I2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J2" t="s">
         <v>52</v>
@@ -9955,7 +9969,7 @@
         <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I3" t="s">
         <v>114</v>

--- a/Excel/Main/Test.xlsx
+++ b/Excel/Main/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7241B5CF-2F70-42BC-912B-D9D7582146C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0549E192-3A9D-4AA3-93B7-46587D6035C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="656">
   <si>
     <t>Id</t>
   </si>
@@ -1627,10 +1627,6 @@
     <t>0,0#1,0#2,0</t>
   </si>
   <si>
-    <t>入场</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>frostl_attack_01_trail</t>
   </si>
   <si>
@@ -1810,10 +1806,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":10,"CanBack":"false","SkillId":"链式弹道索敌"}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Normal</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -1866,41 +1858,535 @@
     <t>离场</t>
   </si>
   <si>
+    <t>终点距离</t>
+  </si>
+  <si>
+    <t>猫后续死亡</t>
+  </si>
+  <si>
+    <t>{"Sanity":0.25}</t>
+  </si>
+  <si>
+    <t>猫诱导</t>
+  </si>
+  <si>
+    <t>token_10004_otter_motter</t>
+  </si>
+  <si>
+    <t>猫索敌,猫诱导</t>
+  </si>
+  <si>
+    <t>特种</t>
+  </si>
+  <si>
+    <t>头像_召唤物_机械水獭</t>
+  </si>
+  <si>
+    <t>猫诱导后续</t>
+  </si>
+  <si>
+    <t>自己入场</t>
+  </si>
+  <si>
+    <t>干员链式弹道索敌</t>
+  </si>
+  <si>
+    <t>干员m3攻击</t>
+  </si>
+  <si>
+    <t>血量比例升序</t>
+  </si>
+  <si>
+    <t>0,0#0,1#0,-1#1,0#2,0#1,1#1,-1#2,1#2,-1#-1,0#-1,1#-1,-1</t>
+  </si>
+  <si>
+    <t>跟随攻击</t>
+  </si>
+  <si>
+    <t>M3链式弹道</t>
+  </si>
+  <si>
+    <t>m3攻速提升buff</t>
+  </si>
+  <si>
+    <t>夜莺普攻击中</t>
+  </si>
+  <si>
+    <t>获取重构体</t>
+  </si>
+  <si>
+    <t>获取单位</t>
+  </si>
+  <si>
+    <t>{"Count":1,"UnitId":"重构体"}</t>
+  </si>
+  <si>
+    <t>重构体天赋</t>
+  </si>
+  <si>
+    <t>重构体天赋加攻</t>
+  </si>
+  <si>
+    <t>重构体中毒</t>
+  </si>
+  <si>
+    <t>0,0#0,1#0,-1#1,0#1,1#1,-1#-1,0#-1,1#-1,-1</t>
+  </si>
+  <si>
+    <t>重构体加攻</t>
+  </si>
+  <si>
+    <t>重构体绝食</t>
+  </si>
+  <si>
+    <t>重构体绝食1,重构体绝食2</t>
+  </si>
+  <si>
+    <t>干员M3</t>
+  </si>
+  <si>
+    <t>monstr</t>
+  </si>
+  <si>
+    <t>4179</t>
+  </si>
+  <si>
+    <t>Mon3tr</t>
+  </si>
+  <si>
+    <t>干员m3攻击,获取重构体</t>
+  </si>
+  <si>
+    <t>医疗</t>
+  </si>
+  <si>
+    <t>链愈师</t>
+  </si>
+  <si>
+    <t>头像_召唤物_Mon3tr</t>
+  </si>
+  <si>
+    <t>half_kalts</t>
+  </si>
+  <si>
+    <t>kalts</t>
+  </si>
+  <si>
+    <t>远程位</t>
+  </si>
+  <si>
+    <t>远程,Mon3tr</t>
+  </si>
+  <si>
+    <t>重构体</t>
+  </si>
+  <si>
+    <t>头像_召唤物_幻影</t>
+  </si>
+  <si>
+    <t>链式弹道</t>
+  </si>
+  <si>
+    <t>0,0#-1,-1#0,-1#1,-1#-1,0#1,0#-1,1#0,1#1,1</t>
+  </si>
+  <si>
+    <t>数值变化</t>
+  </si>
+  <si>
+    <t>银灰真银斩buff</t>
+  </si>
+  <si>
+    <t>{"t":["AgiAdd"]}</t>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>棘刺中毒</t>
+  </si>
+  <si>
+    <t>{"FarAttackUnitRate":1,"DamageType":"Real","TriggerTime":0.1}</t>
+  </si>
+  <si>
+    <t>{"t":["AttackRate"]}</t>
+  </si>
+  <si>
+    <t>重构体绝食1</t>
+  </si>
+  <si>
+    <t>绝食</t>
+  </si>
+  <si>
+    <t>{"HealOnly":"干员M3"}</t>
+  </si>
+  <si>
+    <t>重构体绝食2</t>
+  </si>
+  <si>
+    <t>{"HealOnly":"重构体"}</t>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxLinkNum":4,"SkillId":"干员链式弹道索敌","ReductionRate":0.1,"CanBack":"false"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MoveHeight":0,"MaxLinkNum":10,"ReductionRate":0.25,"SkillId":"链式弹道索敌","CanBack":"false"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"ShowRange":1}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>禁止主动</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置降序</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>m3自身攻速</t>
+  </si>
+  <si>
+    <t>m32加成</t>
+  </si>
+  <si>
+    <t>m32</t>
+  </si>
+  <si>
+    <t>策略：超负荷</t>
+  </si>
+  <si>
+    <t>技能期间重构体每受到一次攻击，就会进行一次跳跃治疗，第二天赋的效果额外追加1.8倍</t>
+  </si>
+  <si>
+    <t>skill_icon_skchr_kalts_2</t>
+  </si>
+  <si>
+    <t>手动</t>
+  </si>
+  <si>
+    <t>m32攻击,m32结束,m32重构体,m32自身结束</t>
+  </si>
+  <si>
+    <t>m32追加,m32启动</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>m32加成,m32动作</t>
+  </si>
+  <si>
+    <t>m32攻击</t>
+  </si>
+  <si>
+    <t>m3额外伤害,m32自身攻速</t>
+  </si>
+  <si>
+    <t>Skill_2_Loop</t>
+  </si>
+  <si>
+    <t>m3攻速提升buff,m32攻速提升buff</t>
+  </si>
+  <si>
+    <t>m3额外伤害</t>
+  </si>
+  <si>
+    <t>普通法球</t>
+  </si>
+  <si>
+    <t>m32自身攻速</t>
+  </si>
+  <si>
+    <t>m32重构体</t>
+  </si>
+  <si>
+    <t>m32追加</t>
+  </si>
+  <si>
+    <t>m32结束</t>
+  </si>
+  <si>
+    <t>m32攻速提升buff</t>
+  </si>
+  <si>
+    <t>m32启动</t>
+  </si>
+  <si>
+    <t>Skill_2_Begin</t>
+  </si>
+  <si>
+    <t>m32自身结束</t>
+  </si>
+  <si>
+    <t>技能结束</t>
+  </si>
+  <si>
+    <t>Skill_2_End</t>
+  </si>
+  <si>
+    <t>重构体2</t>
+  </si>
+  <si>
+    <t>受击</t>
+  </si>
+  <si>
+    <t>m33</t>
+  </si>
+  <si>
+    <t>策略：熔毁</t>
+  </si>
+  <si>
+    <t>攻击范围改变，攻击力+330%，攻击间隔降低(-1.5)，阻挡数+2，生命上限+5000，每秒流失80点生命值，同时攻击阻挡的所有敌人，伤害类型变为真实，攻击治疗自身相当于攻击力50%的生命值\n受到致命伤害时结束技能</t>
+  </si>
+  <si>
+    <t>skill_icon_skchr_kalts_3</t>
+  </si>
+  <si>
+    <t>m33启动</t>
+  </si>
+  <si>
+    <t>m33加成,m3阻挡变化,m3中毒,m33特效,m33动作</t>
+  </si>
+  <si>
+    <t>3.3,-1.5,5000</t>
+  </si>
+  <si>
+    <t>m33加成</t>
+  </si>
+  <si>
+    <t>m3标记</t>
+  </si>
+  <si>
+    <t>m33攻击</t>
+  </si>
+  <si>
+    <t>群攻</t>
+  </si>
+  <si>
+    <t>m33治疗</t>
+  </si>
+  <si>
+    <t>Skill_3_Loop</t>
+  </si>
+  <si>
+    <t>m33锁血</t>
+  </si>
+  <si>
+    <t>锁血治疗</t>
+  </si>
+  <si>
+    <t>致命</t>
+  </si>
+  <si>
+    <t>m33结束</t>
+  </si>
+  <si>
+    <t>m33自身结束</t>
+  </si>
+  <si>
+    <t>Skill_3_End,Skill_3_Back</t>
+  </si>
+  <si>
+    <t>m32,m33</t>
+  </si>
+  <si>
+    <t>重构体天赋,重构体绝食,重构体2</t>
+  </si>
+  <si>
+    <t>眩晕,眩晕2,寒冷,冻结</t>
+  </si>
+  <si>
+    <t>普通Buff</t>
+  </si>
+  <si>
+    <t>m32动作</t>
+  </si>
+  <si>
+    <t>{"IdleAnimation":["Skill_2_Idle"]}</t>
+  </si>
+  <si>
+    <t>{"t":["AttackRate","AttackGapAdd","HpAdd"]}</t>
+  </si>
+  <si>
+    <t>m3阻挡变化</t>
+  </si>
+  <si>
+    <t>{"t":["StopCountAdd"]}</t>
+  </si>
+  <si>
+    <t>m3中毒</t>
+  </si>
+  <si>
+    <t>m33特效</t>
+  </si>
+  <si>
+    <t>星熊2buff</t>
+  </si>
+  <si>
+    <t>阿米娅2buff</t>
+  </si>
+  <si>
+    <t>m33动作</t>
+  </si>
+  <si>
+    <t>{"IdleAnimation":["Skill_3_Idle"]}</t>
+  </si>
+  <si>
+    <t>设置属性</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"t":["ModelScale"],"v":[0.25]}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0</t>
+  </si>
+  <si>
+    <t>高台m3buff</t>
+  </si>
+  <si>
+    <t>释放技能</t>
+  </si>
+  <si>
+    <t>{"Count":1,"UnitId":"地面M3"}</t>
+  </si>
+  <si>
+    <t>地面m3</t>
+  </si>
+  <si>
+    <t>m33攻击,m33治疗,m33锁血,地面m3死亡</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{"LockHp":0.0001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+  </si>
+  <si>
+    <t>地面m3死亡</t>
+  </si>
+  <si>
+    <t>强制撤退</t>
+  </si>
+  <si>
+    <t>{"Time":25}</t>
+  </si>
+  <si>
+    <t>地面m3落地无敌</t>
+  </si>
+  <si>
+    <t>无敌</t>
+  </si>
+  <si>
+    <t>地面m3释放buff</t>
+  </si>
+  <si>
+    <t>m33加成,m3阻挡变化,m3中毒,m33动作</t>
+  </si>
+  <si>
+    <t>地面M3</t>
+  </si>
+  <si>
+    <t>地面m3,地面m3落地无敌,地面m3释放buff</t>
+  </si>
+  <si>
+    <t>部署地面m3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>重构体</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>{"UnitId":"猫诱导后续","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"猫诱导"}</t>
-  </si>
-  <si>
-    <t>终点距离</t>
-  </si>
-  <si>
-    <t>猫后续死亡</t>
-  </si>
-  <si>
-    <t>{"Sanity":0.25}</t>
-  </si>
-  <si>
-    <t>猫诱导</t>
-  </si>
-  <si>
-    <t>token_10004_otter_motter</t>
-  </si>
-  <si>
-    <t>猫索敌,猫诱导</t>
-  </si>
-  <si>
-    <t>特种</t>
-  </si>
-  <si>
-    <t>头像_召唤物_机械水獭</t>
-  </si>
-  <si>
-    <t>猫诱导后续</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>#m33重构体</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>#重构体死亡</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>#获取地面m3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>m33自身结束,高台m3buff</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>重构体撤退，获得地面m3在25秒内获得以下效果：攻击范围改变，攻击力+330%，攻击间隔降低(-1.5)，阻挡数+2，生命上限+5000，每秒流失80点生命值，同时攻击阻挡的所有敌人，伤害类型变为真实，攻击治疗自身相当于攻击力50%的生命值，生命值不会低于1。\n地面m3存在期间，自身获得无敌、缴械、不进行攻击、技力回复速度-100</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_3_Back</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>#模型缩小</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>技力回复变化,无敌,缴械</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>m33启动,部署地面m3,高台m3buff</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mon3tr</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"UnitId":"地面M3","TargetPos":"useSelfTargetPos","SetMod":"Replace","UseMod":"UserDirection","UserName":"Mon3tr"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_3_Idle</t>
+  </si>
+  <si>
+    <t>Skill_3_Idle</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_3_Begin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1999,6 +2485,53 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF333639"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333639"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333639"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2034,7 +2567,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2073,6 +2606,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2379,7 +2933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:B4"/>
+  <dimension ref="A2:B5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -2403,10 +2957,18 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B5" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -2575,7 +3137,7 @@
         <v>39</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="BA1" t="s">
         <v>40</v>
@@ -2745,7 +3307,7 @@
         <v>93</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="BA2" t="s">
         <v>94</v>
@@ -2787,7 +3349,7 @@
         <v>106</v>
       </c>
       <c r="BN2" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="BO2" t="s">
         <v>107</v>
@@ -3013,7 +3575,7 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>406</v>
@@ -3062,13 +3624,13 @@
         <v>1</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AH5" s="8" t="s">
         <v>408</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3143,7 +3705,7 @@
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B8" t="s">
         <v>126</v>
@@ -3155,7 +3717,7 @@
         <v>429</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3201,13 +3763,13 @@
         <v>-1</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AH8" t="s">
         <v>122</v>
       </c>
       <c r="AI8" s="8" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AK8">
         <v>3</v>
@@ -3234,10 +3796,10 @@
         <v>1</v>
       </c>
       <c r="BB8" s="8" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="BD8" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="BE8" t="str">
         <f t="shared" ref="BE8:BE9" si="0">"half_"&amp;D8</f>
@@ -3274,7 +3836,7 @@
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B9" t="s">
         <v>126</v>
@@ -3286,7 +3848,7 @@
         <v>429</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3335,13 +3897,13 @@
         <v>-1</v>
       </c>
       <c r="AG9" s="8" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="AH9" t="s">
         <v>122</v>
       </c>
       <c r="AI9" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AK9">
         <v>3</v>
@@ -3368,10 +3930,10 @@
         <v>1</v>
       </c>
       <c r="BB9" s="8" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="BD9" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="BE9" t="str">
         <f t="shared" si="0"/>
@@ -3417,7 +3979,7 @@
     </row>
     <row r="11" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B11" t="s">
         <v>126</v>
@@ -3475,7 +4037,7 @@
         <v>1</v>
       </c>
       <c r="AG11" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AH11" t="s">
         <v>122</v>
@@ -3541,6 +4103,376 @@
         <v>125</v>
       </c>
       <c r="BS11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>524</v>
+      </c>
+      <c r="B13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" t="s">
+        <v>525</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="F13" t="str">
+        <f>"char_"&amp;E13&amp;"_"&amp;D13</f>
+        <v>char_4179_monstr</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>90</v>
+      </c>
+      <c r="K13">
+        <v>2235</v>
+      </c>
+      <c r="M13">
+        <v>583</v>
+      </c>
+      <c r="O13">
+        <v>221</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>16</v>
+      </c>
+      <c r="U13">
+        <v>0.5</v>
+      </c>
+      <c r="V13">
+        <v>70</v>
+      </c>
+      <c r="Y13">
+        <v>0.05</v>
+      </c>
+      <c r="Z13">
+        <v>2.85</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>527</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>528</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>605</v>
+      </c>
+      <c r="AM13">
+        <v>1</v>
+      </c>
+      <c r="AO13">
+        <v>1</v>
+      </c>
+      <c r="AP13">
+        <v>0.5</v>
+      </c>
+      <c r="AW13">
+        <v>0.25</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>529</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>530</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>531</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>532</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>533</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>128</v>
+      </c>
+      <c r="BH13">
+        <v>6</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>534</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>535</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>124</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>125</v>
+      </c>
+      <c r="BQ13" t="s">
+        <v>125</v>
+      </c>
+      <c r="BS13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>536</v>
+      </c>
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" t="s">
+        <v>428</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F14" t="s">
+        <v>500</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>90</v>
+      </c>
+      <c r="K14">
+        <v>5433</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>221</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>3</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>15</v>
+      </c>
+      <c r="Y14">
+        <v>0.05</v>
+      </c>
+      <c r="Z14">
+        <v>1</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>-1</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>536</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>606</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>1</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>607</v>
+      </c>
+      <c r="AW14">
+        <v>0.25</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>529</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>537</v>
+      </c>
+      <c r="BE14" t="str">
+        <f>"half_"&amp;D14</f>
+        <v>half_otter</v>
+      </c>
+      <c r="BF14" t="str">
+        <f>D14</f>
+        <v>otter</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>128</v>
+      </c>
+      <c r="BH14">
+        <v>6</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>127</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>536</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>123</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>124</v>
+      </c>
+      <c r="BS14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>636</v>
+      </c>
+      <c r="B15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" t="s">
+        <v>525</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="F15" t="str">
+        <f>"char_"&amp;E15&amp;"_"&amp;D15</f>
+        <v>char_4179_monstr</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>90</v>
+      </c>
+      <c r="K15">
+        <v>2235</v>
+      </c>
+      <c r="M15">
+        <v>583</v>
+      </c>
+      <c r="O15">
+        <v>221</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>-1</v>
+      </c>
+      <c r="U15">
+        <v>0.5</v>
+      </c>
+      <c r="V15">
+        <v>70</v>
+      </c>
+      <c r="Y15">
+        <v>0.05</v>
+      </c>
+      <c r="Z15">
+        <v>2.85</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>637</v>
+      </c>
+      <c r="AN15">
+        <v>1</v>
+      </c>
+      <c r="AO15">
+        <v>3</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0.25</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>529</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>530</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>531</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>532</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>533</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>128</v>
+      </c>
+      <c r="BH15">
+        <v>6</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>534</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>535</v>
+      </c>
+      <c r="BM15" s="19" t="s">
+        <v>654</v>
+      </c>
+      <c r="BN15" s="19" t="s">
+        <v>653</v>
+      </c>
+      <c r="BP15" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="BQ15" t="s">
+        <v>125</v>
+      </c>
+      <c r="BS15">
         <v>1</v>
       </c>
     </row>
@@ -6323,7 +7255,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH833"/>
+  <dimension ref="A1:DH836"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6343,8 +7275,10 @@
     <col min="17" max="17" width="21.5" style="3" customWidth="1"/>
     <col min="18" max="18" width="19.83203125" style="3" customWidth="1"/>
     <col min="19" max="19" width="16.58203125" style="3" customWidth="1"/>
-    <col min="20" max="20" width="12.75" style="3" customWidth="1"/>
-    <col min="21" max="23" width="8.33203125" style="3" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" style="3" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" style="3" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" style="3" customWidth="1"/>
     <col min="24" max="24" width="18.5" style="3" customWidth="1"/>
     <col min="25" max="25" width="16.58203125" customWidth="1"/>
     <col min="26" max="26" width="10.6640625" customWidth="1"/>
@@ -6420,7 +7354,7 @@
         <v>133</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I1" t="s">
         <v>134</v>
@@ -6552,7 +7486,7 @@
         <v>175</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="BA1" t="s">
         <v>176</v>
@@ -6606,10 +7540,10 @@
         <v>191</v>
       </c>
       <c r="BS1" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="BT1" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="BU1" s="4" t="s">
         <v>192</v>
@@ -6657,7 +7591,7 @@
         <v>206</v>
       </c>
       <c r="CJ1" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="CK1" t="s">
         <v>207</v>
@@ -6749,7 +7683,7 @@
         <v>51</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I2" t="s">
         <v>230</v>
@@ -6938,10 +7872,10 @@
         <v>290</v>
       </c>
       <c r="BS2" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="BT2" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="BU2" s="4" t="s">
         <v>291</v>
@@ -6989,7 +7923,7 @@
         <v>305</v>
       </c>
       <c r="CJ2" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="CK2" t="s">
         <v>306</v>
@@ -7081,7 +8015,7 @@
         <v>114</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I3" t="s">
         <v>112</v>
@@ -7093,7 +8027,7 @@
         <v>330</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>114</v>
@@ -7270,7 +8204,7 @@
         <v>113</v>
       </c>
       <c r="BS3" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BT3" s="4" t="s">
         <v>113</v>
@@ -7321,7 +8255,7 @@
         <v>342</v>
       </c>
       <c r="CJ3" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="CK3" t="s">
         <v>116</v>
@@ -7408,7 +8342,7 @@
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>405</v>
@@ -7443,13 +8377,13 @@
         <v>425</v>
       </c>
       <c r="CF6" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="CG6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="CJ6" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="CK6" s="8"/>
       <c r="CW6" t="s">
@@ -7458,12 +8392,17 @@
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="J7" s="8"/>
+      <c r="J7" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>420</v>
+      </c>
       <c r="O7"/>
       <c r="AC7">
         <v>2</v>
@@ -7472,7 +8411,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AT7">
         <v>2.5</v>
@@ -7482,16 +8421,16 @@
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>420</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AC8">
         <v>2</v>
@@ -7501,7 +8440,7 @@
         <v>423</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AX8">
         <v>0</v>
@@ -7514,12 +8453,12 @@
       </c>
       <c r="CE8" s="8"/>
       <c r="CJ8" s="8" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="CL8" s="8"/>
       <c r="CM8" s="8"/>
       <c r="CW8" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
@@ -7537,16 +8476,16 @@
     </row>
     <row r="10" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>420</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="AC10">
         <v>1</v>
@@ -7562,7 +8501,7 @@
       </c>
       <c r="CJ10" s="3"/>
       <c r="CS10" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="DB10">
         <v>1</v>
@@ -7576,7 +8515,7 @@
     </row>
     <row r="11" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>405</v>
@@ -7585,7 +8524,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>422</v>
@@ -7601,7 +8540,7 @@
         <v>99</v>
       </c>
       <c r="AV11" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AX11">
         <v>99999</v>
@@ -7644,10 +8583,10 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>456</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>457</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -7665,7 +8604,7 @@
         <v>423</v>
       </c>
       <c r="AR12" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="BB12">
         <v>4</v>
@@ -7675,10 +8614,10 @@
       </c>
       <c r="CJ12" s="3"/>
       <c r="CS12" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="CW12" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
@@ -7691,7 +8630,7 @@
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C14" t="s">
         <v>346</v>
@@ -7700,10 +8639,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14"/>
@@ -7732,10 +8671,10 @@
         <v>1</v>
       </c>
       <c r="BM14" s="8" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="BN14" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="BR14">
         <v>6</v>
@@ -7750,7 +8689,7 @@
         <v>1</v>
       </c>
       <c r="BW14" s="13" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="BX14" s="13"/>
       <c r="BY14" s="13"/>
@@ -7767,7 +8706,7 @@
     </row>
     <row r="15" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>346</v>
@@ -7790,7 +8729,7 @@
         <v>351</v>
       </c>
       <c r="AV15" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AX15">
         <v>999</v>
@@ -7817,16 +8756,16 @@
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>494</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>496</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>347</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AC16">
         <v>1</v>
@@ -7841,7 +8780,7 @@
       <c r="BT16"/>
       <c r="CJ16" s="3"/>
       <c r="CS16" s="8" t="s">
-        <v>498</v>
+        <v>640</v>
       </c>
     </row>
     <row r="17" spans="1:110" x14ac:dyDescent="0.25">
@@ -7849,13 +8788,13 @@
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C18" t="s">
         <v>346</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>422</v>
@@ -7881,10 +8820,10 @@
         <v>1</v>
       </c>
       <c r="AO18" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AR18" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AV18" s="8" t="s">
         <v>350</v>
@@ -7902,7 +8841,7 @@
         <v>0.5</v>
       </c>
       <c r="BN18" s="8" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="BR18">
         <v>6</v>
@@ -7917,7 +8856,7 @@
         <v>1</v>
       </c>
       <c r="BW18" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="BX18" s="13"/>
       <c r="BY18" s="13"/>
@@ -7925,11 +8864,11 @@
       <c r="CE18" s="8"/>
       <c r="CH18" s="8"/>
       <c r="CJ18" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="CK18" s="8"/>
       <c r="CL18" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="CM18">
         <v>-0.8</v>
@@ -7949,7 +8888,7 @@
     </row>
     <row r="19" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>346</v>
@@ -7969,7 +8908,7 @@
       </c>
       <c r="AJ19" s="8"/>
       <c r="AV19" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AX19">
         <v>9</v>
@@ -8014,10 +8953,10 @@
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -8029,12 +8968,12 @@
         <v>1</v>
       </c>
       <c r="AR21" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BT21"/>
       <c r="CJ21" s="3"/>
       <c r="CS21" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="22" spans="1:110" x14ac:dyDescent="0.25">
@@ -8042,79 +8981,1791 @@
       <c r="CJ22" s="3"/>
     </row>
     <row r="23" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="BT23"/>
-      <c r="CJ23" s="3"/>
+      <c r="A23" t="s">
+        <v>506</v>
+      </c>
+      <c r="C23" t="s">
+        <v>346</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="O23"/>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AO23" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>539</v>
+      </c>
+      <c r="CS23" s="8" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="24" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="BT24"/>
-      <c r="CJ24" s="3"/>
+      <c r="A24" t="s">
+        <v>507</v>
+      </c>
+      <c r="C24" t="s">
+        <v>346</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="P24"/>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>508</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>509</v>
+      </c>
+      <c r="AW24">
+        <v>1</v>
+      </c>
+      <c r="AX24">
+        <v>1</v>
+      </c>
+      <c r="BB24">
+        <v>1</v>
+      </c>
+      <c r="BZ24" t="s">
+        <v>55</v>
+      </c>
+      <c r="CE24" t="s">
+        <v>510</v>
+      </c>
+      <c r="CF24" t="s">
+        <v>511</v>
+      </c>
+      <c r="CG24" t="s">
+        <v>475</v>
+      </c>
+      <c r="CL24" t="s">
+        <v>512</v>
+      </c>
+      <c r="CM24">
+        <v>22</v>
+      </c>
+      <c r="CP24">
+        <v>10</v>
+      </c>
+      <c r="CW24" t="s">
+        <v>513</v>
+      </c>
     </row>
     <row r="25" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>514</v>
+      </c>
+      <c r="C25" t="s">
+        <v>515</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB25">
+        <v>1</v>
+      </c>
       <c r="CJ25" s="3"/>
+      <c r="CS25" t="s">
+        <v>516</v>
+      </c>
+      <c r="DB25">
+        <v>1</v>
+      </c>
+      <c r="DE25">
+        <v>1</v>
+      </c>
+      <c r="DF25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>517</v>
+      </c>
+      <c r="C26" t="s">
+        <v>346</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26" s="12"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="12"/>
+      <c r="X26"/>
+      <c r="AC26">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>348</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>351</v>
+      </c>
+      <c r="BB26">
+        <v>1</v>
+      </c>
+      <c r="BM26" t="s">
+        <v>518</v>
+      </c>
+      <c r="BS26" s="13"/>
+      <c r="BT26" s="13"/>
+      <c r="BU26" s="13"/>
+      <c r="BV26" s="13"/>
+      <c r="BW26" s="13"/>
+      <c r="BX26" s="13"/>
+      <c r="BY26"/>
+      <c r="CL26" t="s">
+        <v>519</v>
+      </c>
+      <c r="CM26">
+        <v>8</v>
+      </c>
+      <c r="CP26">
+        <v>9999</v>
+      </c>
+      <c r="DB26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ27" s="3"/>
+      <c r="A27" t="s">
+        <v>518</v>
+      </c>
+      <c r="C27" t="s">
+        <v>346</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27" s="12"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27"/>
+      <c r="AC27">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>520</v>
+      </c>
+      <c r="BB27">
+        <v>99</v>
+      </c>
+      <c r="BQ27">
+        <v>0.1</v>
+      </c>
+      <c r="BS27" s="13"/>
+      <c r="BT27" s="13"/>
+      <c r="BU27" s="13"/>
+      <c r="BV27" s="13"/>
+      <c r="BW27" s="13"/>
+      <c r="BX27" s="13"/>
+      <c r="BY27"/>
+      <c r="CL27" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="CM27">
+        <v>0.2</v>
+      </c>
+      <c r="CP27">
+        <v>0.2</v>
+      </c>
+      <c r="DB27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>522</v>
+      </c>
+      <c r="C28" t="s">
+        <v>346</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>348</v>
+      </c>
+      <c r="AW28" s="3"/>
+      <c r="BB28">
+        <v>1</v>
+      </c>
       <c r="BT28"/>
+      <c r="BU28"/>
+      <c r="BV28"/>
+      <c r="BW28"/>
+      <c r="BX28"/>
+      <c r="BY28"/>
+      <c r="BZ28" s="3"/>
+      <c r="CA28" s="3"/>
+      <c r="CB28" s="3"/>
+      <c r="CC28" s="3"/>
+      <c r="CD28" s="3"/>
+      <c r="CF28" s="3"/>
+      <c r="CG28" s="3"/>
+      <c r="CH28" s="3"/>
+      <c r="CI28" s="3"/>
+      <c r="CJ28" s="3"/>
+      <c r="CK28" s="3"/>
+      <c r="CL28" t="s">
+        <v>523</v>
+      </c>
+      <c r="CP28">
+        <v>99999</v>
+      </c>
     </row>
     <row r="29" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ29" s="3"/>
+      <c r="A29" t="s">
+        <v>557</v>
+      </c>
+      <c r="C29" t="s">
+        <v>346</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="L29" s="15"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="16"/>
+      <c r="S29"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="15"/>
+      <c r="W29" s="15"/>
+      <c r="X29"/>
+      <c r="AC29">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>348</v>
+      </c>
+      <c r="AR29" t="s">
+        <v>351</v>
+      </c>
+      <c r="BB29">
+        <v>1</v>
+      </c>
+      <c r="BT29"/>
+      <c r="BU29" s="17"/>
+      <c r="BV29" s="17"/>
+      <c r="BW29" s="17"/>
+      <c r="BX29" s="17"/>
+      <c r="BY29" s="17"/>
+      <c r="BZ29" s="17"/>
+      <c r="CL29" t="s">
+        <v>512</v>
+      </c>
+      <c r="CM29">
+        <v>22</v>
+      </c>
+      <c r="CP29">
+        <v>10</v>
+      </c>
     </row>
     <row r="30" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ30" s="3"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="15"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="15"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
+      <c r="BT30"/>
+      <c r="BU30" s="17"/>
+      <c r="BV30" s="17"/>
+      <c r="BW30" s="17"/>
+      <c r="BX30" s="17"/>
+      <c r="BY30" s="17"/>
     </row>
     <row r="31" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ31" s="3"/>
-    </row>
-    <row r="34" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ34" s="3"/>
-    </row>
-    <row r="35" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ35" s="3"/>
-    </row>
-    <row r="39" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>559</v>
+      </c>
+      <c r="C31" t="s">
+        <v>346</v>
+      </c>
+      <c r="D31" t="s">
+        <v>560</v>
+      </c>
+      <c r="E31" t="s">
+        <v>561</v>
+      </c>
+      <c r="F31" t="s">
+        <v>562</v>
+      </c>
+      <c r="G31">
+        <v>3</v>
+      </c>
+      <c r="J31" t="s">
+        <v>490</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="L31" s="15"/>
+      <c r="M31"/>
+      <c r="N31" s="15"/>
+      <c r="O31"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="15"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB31">
+        <v>1</v>
+      </c>
+      <c r="BM31" t="s">
+        <v>564</v>
+      </c>
+      <c r="BN31" t="s">
+        <v>565</v>
+      </c>
+      <c r="BR31">
+        <v>30</v>
+      </c>
+      <c r="BT31" s="17">
+        <v>13</v>
+      </c>
+      <c r="BU31" s="17">
+        <v>15</v>
+      </c>
+      <c r="BV31" s="17">
+        <v>1</v>
+      </c>
+      <c r="BW31" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="BX31" s="17"/>
+      <c r="BY31" s="17"/>
+      <c r="CL31" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="CP31">
+        <v>30</v>
+      </c>
+      <c r="DB31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>568</v>
+      </c>
+      <c r="C32" t="s">
+        <v>346</v>
+      </c>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="15"/>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
+      <c r="AC32">
+        <v>1</v>
+      </c>
+      <c r="AD32">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="s">
+        <v>508</v>
+      </c>
+      <c r="AQ32" t="s">
+        <v>536</v>
+      </c>
+      <c r="AU32">
+        <v>1</v>
+      </c>
+      <c r="AW32">
+        <v>1</v>
+      </c>
+      <c r="AX32">
+        <v>1</v>
+      </c>
+      <c r="BB32">
+        <v>1</v>
+      </c>
+      <c r="BN32" t="s">
+        <v>569</v>
+      </c>
+      <c r="BT32" s="17"/>
+      <c r="BU32" s="17"/>
+      <c r="BV32" s="17"/>
+      <c r="BW32" s="17"/>
+      <c r="BX32" s="17"/>
+      <c r="BY32" s="17"/>
+      <c r="BZ32" t="s">
+        <v>570</v>
+      </c>
+      <c r="CE32" t="s">
+        <v>510</v>
+      </c>
+      <c r="CF32" t="s">
+        <v>511</v>
+      </c>
+      <c r="CG32" t="s">
+        <v>475</v>
+      </c>
+      <c r="CL32" t="s">
+        <v>571</v>
+      </c>
+      <c r="CM32">
+        <v>22</v>
+      </c>
+      <c r="CN32">
+        <v>39.6</v>
+      </c>
+      <c r="CP32">
+        <v>10</v>
+      </c>
+      <c r="CW32" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="33" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>572</v>
+      </c>
+      <c r="C33" t="s">
+        <v>346</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="L33" s="15"/>
+      <c r="M33"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="AC33">
+        <v>1</v>
+      </c>
+      <c r="AD33">
+        <v>1</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>536</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>508</v>
+      </c>
+      <c r="AR33" t="s">
+        <v>509</v>
+      </c>
+      <c r="AV33" t="s">
+        <v>471</v>
+      </c>
+      <c r="AX33">
+        <v>1</v>
+      </c>
+      <c r="AZ33">
+        <v>2</v>
+      </c>
+      <c r="BB33">
+        <v>1</v>
+      </c>
+      <c r="BT33" s="17"/>
+      <c r="BU33" s="17"/>
+      <c r="BV33" s="17"/>
+      <c r="BW33" s="17"/>
+      <c r="BX33" s="17"/>
+      <c r="BY33" s="17"/>
+      <c r="BZ33" s="18"/>
+      <c r="CF33" t="s">
+        <v>573</v>
+      </c>
+      <c r="CG33" t="s">
+        <v>475</v>
+      </c>
+      <c r="DB33">
+        <v>1</v>
+      </c>
+      <c r="DF33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>574</v>
+      </c>
+      <c r="C34" t="s">
+        <v>346</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="L34" s="15"/>
+      <c r="M34"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="15"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+      <c r="AC34">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>348</v>
+      </c>
+      <c r="AU34">
+        <v>1</v>
+      </c>
+      <c r="BB34">
+        <v>1</v>
+      </c>
+      <c r="BT34" s="17"/>
+      <c r="BU34" s="17"/>
+      <c r="BV34" s="17"/>
+      <c r="BW34" s="17"/>
+      <c r="BX34" s="17"/>
+      <c r="BY34" s="17"/>
+      <c r="CL34" t="s">
+        <v>571</v>
+      </c>
+      <c r="CM34">
+        <v>22</v>
+      </c>
+      <c r="CN34">
+        <v>39.6</v>
+      </c>
+      <c r="CP34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>575</v>
+      </c>
+      <c r="C35" t="s">
+        <v>346</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="AC35">
+        <v>1</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>536</v>
+      </c>
+      <c r="AR35" t="s">
+        <v>509</v>
+      </c>
+      <c r="BB35">
+        <v>1</v>
+      </c>
+      <c r="BQ35">
+        <v>0.1</v>
+      </c>
+      <c r="BT35" s="17"/>
+      <c r="BU35" s="17"/>
+      <c r="BV35" s="17"/>
+      <c r="BW35" s="17"/>
+      <c r="BX35" s="17"/>
+      <c r="BY35" s="17"/>
+      <c r="CL35" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="CP35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>576</v>
+      </c>
+      <c r="C36" t="s">
+        <v>346</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="L36" s="15"/>
+      <c r="M36"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
+      <c r="AC36">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>348</v>
+      </c>
+      <c r="AW36" s="15"/>
+      <c r="BB36">
+        <v>1</v>
+      </c>
+      <c r="BT36"/>
+      <c r="BU36"/>
+      <c r="BV36"/>
+      <c r="BW36"/>
+      <c r="BX36"/>
+      <c r="BY36"/>
+      <c r="BZ36" s="15"/>
+      <c r="CA36" s="15"/>
+      <c r="CB36" s="15"/>
+      <c r="CC36" s="15"/>
+      <c r="CD36" s="15"/>
+      <c r="CF36" s="15"/>
+      <c r="CG36" s="15"/>
+      <c r="CH36" s="15"/>
+      <c r="CI36" s="15"/>
+      <c r="CL36" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="CP36">
+        <v>40</v>
+      </c>
+      <c r="DB36">
+        <v>1</v>
+      </c>
+      <c r="DF36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>577</v>
+      </c>
+      <c r="C37" t="s">
+        <v>346</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="P37" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AT37">
+        <v>20</v>
+      </c>
+      <c r="BB37">
+        <v>99</v>
+      </c>
+      <c r="BT37" s="17"/>
+      <c r="BU37" s="17"/>
+      <c r="BV37" s="17"/>
+      <c r="BW37" s="17"/>
+      <c r="BX37" s="17"/>
+      <c r="BY37" s="17"/>
+      <c r="CK37" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="38" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>579</v>
+      </c>
+      <c r="C38" t="s">
+        <v>346</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="L38" s="15"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="15"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
+      <c r="AC38">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB38">
+        <v>1</v>
+      </c>
+      <c r="BQ38">
+        <v>0.1</v>
+      </c>
+      <c r="BT38"/>
+      <c r="BU38" s="17"/>
+      <c r="BV38" s="17"/>
+      <c r="BW38" s="17"/>
+      <c r="BX38" s="17"/>
+      <c r="BY38" s="17"/>
+      <c r="BZ38" t="s">
+        <v>580</v>
+      </c>
+      <c r="CE38" t="s">
+        <v>510</v>
+      </c>
+      <c r="CG38" s="15"/>
+      <c r="CH38" s="15"/>
+      <c r="DB38">
+        <v>1</v>
+      </c>
+      <c r="DE38">
+        <v>1</v>
+      </c>
+      <c r="DF38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>581</v>
+      </c>
+      <c r="C39" t="s">
+        <v>346</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="L39" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="15"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="15"/>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
+      <c r="AC39">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB39">
+        <v>1</v>
+      </c>
+      <c r="BQ39">
+        <v>0.2</v>
+      </c>
       <c r="BT39"/>
-    </row>
-    <row r="40" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ40" s="3"/>
-    </row>
-    <row r="45" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT45"/>
-    </row>
-    <row r="48" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT48"/>
+      <c r="BU39" s="17"/>
+      <c r="BV39" s="17"/>
+      <c r="BW39" s="17"/>
+      <c r="BX39" s="17"/>
+      <c r="BY39" s="17"/>
+      <c r="BZ39" t="s">
+        <v>583</v>
+      </c>
+      <c r="CE39" t="s">
+        <v>510</v>
+      </c>
+      <c r="CH39" s="15"/>
+      <c r="DB39">
+        <v>1</v>
+      </c>
+      <c r="DE39">
+        <v>1</v>
+      </c>
+      <c r="DF39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>584</v>
+      </c>
+      <c r="C40" t="s">
+        <v>346</v>
+      </c>
+      <c r="D40" t="s">
+        <v>560</v>
+      </c>
+      <c r="E40" t="s">
+        <v>561</v>
+      </c>
+      <c r="F40" t="s">
+        <v>562</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="J40" t="s">
+        <v>490</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="L40" s="15"/>
+      <c r="M40"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+      <c r="T40" s="15"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
+      <c r="AC40">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="s">
+        <v>508</v>
+      </c>
+      <c r="AR40" t="s">
+        <v>520</v>
+      </c>
+      <c r="AW40">
+        <v>1</v>
+      </c>
+      <c r="AX40">
+        <v>583</v>
+      </c>
+      <c r="AZ40">
+        <v>2</v>
+      </c>
+      <c r="BB40">
+        <v>1</v>
+      </c>
+      <c r="BQ40">
+        <v>0.1</v>
+      </c>
+      <c r="BT40" s="17">
+        <v>0</v>
+      </c>
+      <c r="BU40" s="17">
+        <v>1</v>
+      </c>
+      <c r="BV40" s="17">
+        <v>1</v>
+      </c>
+      <c r="BW40" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="BX40" s="17"/>
+      <c r="BY40" s="17"/>
+      <c r="CE40" t="s">
+        <v>510</v>
+      </c>
+      <c r="CF40" t="s">
+        <v>511</v>
+      </c>
+      <c r="CG40" t="s">
+        <v>475</v>
+      </c>
+      <c r="CL40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CM40">
+        <v>22</v>
+      </c>
+      <c r="CN40">
+        <v>39.6</v>
+      </c>
+      <c r="CP40">
+        <v>10</v>
+      </c>
+      <c r="CW40" t="s">
+        <v>513</v>
+      </c>
+      <c r="DB40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15"/>
+      <c r="R41" s="15"/>
+      <c r="S41" s="15"/>
+      <c r="T41" s="15"/>
+      <c r="U41" s="15"/>
+      <c r="V41" s="15"/>
+      <c r="W41" s="15"/>
+      <c r="X41" s="15"/>
+      <c r="BS41" s="17"/>
+      <c r="BT41" s="17"/>
+      <c r="BU41" s="17"/>
+      <c r="BV41" s="17"/>
+      <c r="BW41" s="17"/>
+      <c r="BX41" s="17"/>
+      <c r="BY41"/>
+    </row>
+    <row r="42" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>586</v>
+      </c>
+      <c r="C42" t="s">
+        <v>346</v>
+      </c>
+      <c r="D42" t="s">
+        <v>587</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="F42" t="s">
+        <v>589</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+      <c r="J42" t="s">
+        <v>490</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="O42"/>
+      <c r="W42"/>
+      <c r="X42"/>
+      <c r="AC42">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB42">
+        <v>1</v>
+      </c>
+      <c r="BM42" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="BN42" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="BR42">
+        <v>1</v>
+      </c>
+      <c r="BT42" s="4">
+        <v>11</v>
+      </c>
+      <c r="BU42" s="4">
+        <v>15</v>
+      </c>
+      <c r="BV42" s="4">
+        <v>1</v>
+      </c>
+      <c r="BW42" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="CL42" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="CM42" t="s">
+        <v>622</v>
+      </c>
+      <c r="CP42">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>623</v>
+      </c>
+      <c r="C43" t="s">
+        <v>346</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="M43"/>
+      <c r="O43" s="14"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="AC43">
+        <v>1</v>
+      </c>
+      <c r="AG43" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB43">
+        <v>1</v>
+      </c>
+      <c r="BQ43">
+        <v>0.1</v>
+      </c>
+      <c r="CL43" s="14" t="s">
+        <v>648</v>
+      </c>
+      <c r="CM43">
+        <v>-100</v>
+      </c>
+      <c r="CP43">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="C44" t="s">
+        <v>346</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="M44"/>
+      <c r="O44" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="P44"/>
+      <c r="Q44"/>
+      <c r="AC44">
+        <v>1</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>536</v>
+      </c>
+      <c r="AR44" t="s">
+        <v>509</v>
+      </c>
+      <c r="BB44">
+        <v>1</v>
+      </c>
+      <c r="CL44" s="14" t="s">
+        <v>594</v>
+      </c>
+      <c r="CP44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="C45" t="s">
+        <v>346</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="O45" s="14" t="s">
+        <v>594</v>
+      </c>
+      <c r="AC45">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>348</v>
+      </c>
+      <c r="AV45" t="s">
+        <v>471</v>
+      </c>
+      <c r="AX45">
+        <v>1</v>
+      </c>
+      <c r="AZ45">
+        <v>1</v>
+      </c>
+      <c r="BB45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="C46" t="s">
+        <v>515</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="AC46">
+        <v>1</v>
+      </c>
+      <c r="AF46">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB46">
+        <v>1</v>
+      </c>
+      <c r="CJ46" s="3"/>
+      <c r="CS46" t="s">
+        <v>625</v>
+      </c>
+      <c r="DB46">
+        <v>1</v>
+      </c>
+      <c r="DE46">
+        <v>1</v>
+      </c>
+      <c r="DF46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ47" s="3"/>
+    </row>
+    <row r="48" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="AC48">
+        <v>1</v>
+      </c>
+      <c r="AJ48" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="AR48" t="s">
+        <v>509</v>
+      </c>
+      <c r="BB48">
+        <v>1</v>
+      </c>
+      <c r="BQ48">
+        <v>0.1</v>
+      </c>
       <c r="CJ48" s="3"/>
-    </row>
-    <row r="49" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT49"/>
-    </row>
-    <row r="51" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT51"/>
-    </row>
-    <row r="52" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ52" s="3"/>
-    </row>
-    <row r="53" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ53" s="3"/>
-    </row>
-    <row r="54" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ54" s="3"/>
-    </row>
-    <row r="55" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ55" s="3"/>
-    </row>
-    <row r="60" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ60" s="3"/>
-    </row>
-    <row r="61" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ61" s="3"/>
-    </row>
-    <row r="67" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ67" s="3"/>
-    </row>
-    <row r="68" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ68" s="3"/>
+      <c r="CS48" s="8" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="49" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ49" s="3"/>
+    </row>
+    <row r="50" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>626</v>
+      </c>
+      <c r="C50" t="s">
+        <v>346</v>
+      </c>
+      <c r="D50" t="s">
+        <v>587</v>
+      </c>
+      <c r="E50" t="s">
+        <v>588</v>
+      </c>
+      <c r="F50" t="s">
+        <v>589</v>
+      </c>
+      <c r="G50">
+        <v>3</v>
+      </c>
+      <c r="J50" t="s">
+        <v>490</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="O50"/>
+      <c r="W50"/>
+      <c r="X50"/>
+      <c r="AC50">
+        <v>1</v>
+      </c>
+      <c r="AG50" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB50">
+        <v>1</v>
+      </c>
+      <c r="BM50" t="s">
+        <v>627</v>
+      </c>
+      <c r="BR50">
+        <v>25</v>
+      </c>
+      <c r="BT50" s="4">
+        <v>1</v>
+      </c>
+      <c r="BU50" s="4">
+        <v>1</v>
+      </c>
+      <c r="BV50" s="4">
+        <v>1</v>
+      </c>
+      <c r="BW50" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="CL50" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="CM50" t="s">
+        <v>592</v>
+      </c>
+      <c r="CN50">
+        <v>2</v>
+      </c>
+      <c r="CO50">
+        <v>80</v>
+      </c>
+      <c r="CP50">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>595</v>
+      </c>
+      <c r="C51" t="s">
+        <v>596</v>
+      </c>
+      <c r="O51" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="X51"/>
+      <c r="AC51">
+        <v>2</v>
+      </c>
+      <c r="AO51" t="s">
+        <v>496</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>520</v>
+      </c>
+      <c r="AV51" t="s">
+        <v>471</v>
+      </c>
+      <c r="AX51">
+        <v>1</v>
+      </c>
+      <c r="BB51">
+        <v>1</v>
+      </c>
+      <c r="BN51" t="s">
+        <v>597</v>
+      </c>
+      <c r="BZ51" t="s">
+        <v>598</v>
+      </c>
+      <c r="CE51" t="s">
+        <v>510</v>
+      </c>
+      <c r="CW51" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="52" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>597</v>
+      </c>
+      <c r="C52" t="s">
+        <v>346</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="O52" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="P52"/>
+      <c r="Q52"/>
+      <c r="X52"/>
+      <c r="AC52">
+        <v>1</v>
+      </c>
+      <c r="AG52" t="s">
+        <v>348</v>
+      </c>
+      <c r="AH52">
+        <v>1</v>
+      </c>
+      <c r="AO52" t="s">
+        <v>508</v>
+      </c>
+      <c r="AT52">
+        <v>1</v>
+      </c>
+      <c r="AW52">
+        <v>1</v>
+      </c>
+      <c r="AX52">
+        <v>0.5</v>
+      </c>
+      <c r="BB52">
+        <v>1</v>
+      </c>
+      <c r="CF52" t="s">
+        <v>511</v>
+      </c>
+      <c r="CG52" t="s">
+        <v>475</v>
+      </c>
+      <c r="CL52" t="s">
+        <v>512</v>
+      </c>
+      <c r="CM52">
+        <v>22</v>
+      </c>
+      <c r="CP52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>599</v>
+      </c>
+      <c r="C53" t="s">
+        <v>600</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="O53" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="X53"/>
+      <c r="AC53">
+        <v>1</v>
+      </c>
+      <c r="AG53" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB53">
+        <v>1</v>
+      </c>
+      <c r="CS53" t="s">
+        <v>628</v>
+      </c>
+      <c r="DB53">
+        <v>1</v>
+      </c>
+      <c r="DE53">
+        <v>1</v>
+      </c>
+      <c r="DF53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>629</v>
+      </c>
+      <c r="C54" t="s">
+        <v>630</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="AC54">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB54">
+        <v>1</v>
+      </c>
+      <c r="CS54" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="55" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>632</v>
+      </c>
+      <c r="C55" t="s">
+        <v>346</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="AC55">
+        <v>1</v>
+      </c>
+      <c r="AG55" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB55">
+        <v>1</v>
+      </c>
+      <c r="CL55" t="s">
+        <v>633</v>
+      </c>
+      <c r="CP55">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>634</v>
+      </c>
+      <c r="C56" t="s">
+        <v>346</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="AC56">
+        <v>1</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>524</v>
+      </c>
+      <c r="AT56">
+        <v>20</v>
+      </c>
+      <c r="BB56">
+        <v>1</v>
+      </c>
+      <c r="CK56" s="14" t="s">
+        <v>648</v>
+      </c>
+      <c r="CL56" s="14"/>
+      <c r="DB56">
+        <v>1</v>
+      </c>
+      <c r="DE56">
+        <v>1</v>
+      </c>
+      <c r="DF56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>590</v>
+      </c>
+      <c r="C58" t="s">
+        <v>346</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="M58"/>
+      <c r="N58"/>
+      <c r="AC58">
+        <v>1</v>
+      </c>
+      <c r="AG58" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB58">
+        <v>1</v>
+      </c>
+      <c r="BQ58">
+        <v>0.5</v>
+      </c>
+      <c r="BT58"/>
+      <c r="BZ58" s="20" t="s">
+        <v>655</v>
+      </c>
+      <c r="CE58" t="s">
+        <v>510</v>
+      </c>
+      <c r="CG58" s="3"/>
+      <c r="CH58" s="3"/>
+      <c r="DB58">
+        <v>1</v>
+      </c>
+      <c r="DE58">
+        <v>1</v>
+      </c>
+      <c r="DF58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>603</v>
+      </c>
+      <c r="C59" t="s">
+        <v>346</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="M59"/>
+      <c r="N59"/>
+      <c r="AC59">
+        <v>1</v>
+      </c>
+      <c r="AG59" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB59">
+        <v>1</v>
+      </c>
+      <c r="BQ59">
+        <v>1</v>
+      </c>
+      <c r="BT59"/>
+      <c r="BZ59" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="CE59" t="s">
+        <v>510</v>
+      </c>
+      <c r="CH59" s="3"/>
+      <c r="DB59">
+        <v>1</v>
+      </c>
+      <c r="DE59">
+        <v>1</v>
+      </c>
+      <c r="DF59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>602</v>
+      </c>
+      <c r="C60" t="s">
+        <v>346</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="O60"/>
+      <c r="X60"/>
+      <c r="AC60">
+        <v>1</v>
+      </c>
+      <c r="AG60" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB60">
+        <v>1</v>
+      </c>
+      <c r="CK60" s="14" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="63" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ63" s="3"/>
+    </row>
+    <row r="64" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ64" s="3"/>
     </row>
     <row r="70" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ70" s="3"/>
@@ -8122,70 +10773,67 @@
     <row r="71" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ71" s="3"/>
     </row>
-    <row r="72" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ72" s="3"/>
-    </row>
     <row r="73" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ73" s="3"/>
     </row>
     <row r="74" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT74"/>
+      <c r="CJ74" s="3"/>
     </row>
     <row r="75" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT75"/>
+      <c r="CJ75" s="3"/>
     </row>
     <row r="76" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT76"/>
       <c r="CJ76" s="3"/>
     </row>
     <row r="77" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ77" s="3"/>
+      <c r="BT77"/>
     </row>
     <row r="78" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ78" s="3"/>
+      <c r="BT78"/>
     </row>
     <row r="79" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT79"/>
+      <c r="CJ79" s="3"/>
     </row>
     <row r="80" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ80" s="3"/>
     </row>
-    <row r="84" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT84"/>
-    </row>
-    <row r="85" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ85" s="3"/>
-    </row>
-    <row r="93" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ93" s="3"/>
-    </row>
-    <row r="94" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ94" s="3"/>
-    </row>
-    <row r="95" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT95"/>
-    </row>
-    <row r="100" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT100"/>
-    </row>
-    <row r="101" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT101"/>
-      <c r="CJ101" s="3"/>
-    </row>
-    <row r="102" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ102" s="3"/>
+    <row r="81" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ81" s="3"/>
+    </row>
+    <row r="82" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT82"/>
+    </row>
+    <row r="83" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ83" s="3"/>
+    </row>
+    <row r="87" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT87"/>
+    </row>
+    <row r="88" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ88" s="3"/>
+    </row>
+    <row r="96" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ96" s="3"/>
+    </row>
+    <row r="97" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ97" s="3"/>
+    </row>
+    <row r="98" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT98"/>
     </row>
     <row r="103" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ103" s="3"/>
+      <c r="BT103"/>
     </row>
     <row r="104" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT104"/>
       <c r="CJ104" s="3"/>
     </row>
     <row r="105" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ105" s="3"/>
     </row>
     <row r="106" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT106"/>
+      <c r="CJ106" s="3"/>
     </row>
     <row r="107" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ107" s="3"/>
@@ -8194,13 +10842,13 @@
       <c r="CJ108" s="3"/>
     </row>
     <row r="109" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ109" s="3"/>
+      <c r="BT109"/>
     </row>
     <row r="110" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ110" s="3"/>
     </row>
     <row r="111" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT111"/>
+      <c r="CJ111" s="3"/>
     </row>
     <row r="112" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ112" s="3"/>
@@ -8209,71 +10857,74 @@
       <c r="CJ113" s="3"/>
     </row>
     <row r="114" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ114" s="3"/>
+      <c r="BT114"/>
     </row>
     <row r="115" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ115" s="3"/>
     </row>
+    <row r="116" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ116" s="3"/>
+    </row>
+    <row r="117" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ117" s="3"/>
+    </row>
     <row r="118" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ118" s="3"/>
     </row>
-    <row r="119" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ119" s="3"/>
-    </row>
-    <row r="120" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ120" s="3"/>
-    </row>
     <row r="121" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ121" s="3"/>
     </row>
     <row r="122" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ122" s="3"/>
     </row>
+    <row r="123" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ123" s="3"/>
+    </row>
     <row r="124" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT124"/>
+      <c r="CJ124" s="3"/>
     </row>
     <row r="125" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ125" s="3"/>
     </row>
-    <row r="126" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ126" s="3"/>
-    </row>
     <row r="127" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ127" s="3"/>
+      <c r="BT127"/>
     </row>
     <row r="128" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ128" s="3"/>
     </row>
-    <row r="132" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ132" s="3"/>
-    </row>
-    <row r="134" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT134"/>
+    <row r="129" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ129" s="3"/>
+    </row>
+    <row r="130" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ130" s="3"/>
+    </row>
+    <row r="131" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ131" s="3"/>
     </row>
     <row r="135" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT135"/>
       <c r="CJ135" s="3"/>
     </row>
-    <row r="136" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ136" s="3"/>
-    </row>
     <row r="137" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ137" s="3"/>
+      <c r="BT137"/>
     </row>
     <row r="138" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT138"/>
       <c r="CJ138" s="3"/>
     </row>
     <row r="139" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ139" s="3"/>
     </row>
+    <row r="140" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ140" s="3"/>
+    </row>
     <row r="141" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT141"/>
+      <c r="CJ141" s="3"/>
     </row>
     <row r="142" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ142" s="3"/>
     </row>
-    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ143" s="3"/>
+    <row r="144" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT144"/>
     </row>
     <row r="145" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ145" s="3"/>
@@ -8282,191 +10933,191 @@
       <c r="CJ146" s="3"/>
     </row>
     <row r="148" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT148"/>
+      <c r="CJ148" s="3"/>
     </row>
     <row r="149" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ149" s="3"/>
     </row>
+    <row r="151" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT151"/>
+    </row>
     <row r="152" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ152" s="3"/>
     </row>
-    <row r="153" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ153" s="3"/>
+    <row r="155" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ155" s="3"/>
     </row>
     <row r="156" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ156" s="3"/>
     </row>
-    <row r="158" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ158" s="3"/>
-    </row>
-    <row r="160" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT160"/>
-    </row>
-    <row r="161" spans="88:88" x14ac:dyDescent="0.25">
+    <row r="159" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ159" s="3"/>
+    </row>
+    <row r="161" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ161" s="3"/>
     </row>
-    <row r="162" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ162" s="3"/>
-    </row>
-    <row r="164" spans="88:88" x14ac:dyDescent="0.25">
+    <row r="163" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT163"/>
+    </row>
+    <row r="164" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ164" s="3"/>
     </row>
-    <row r="165" spans="88:88" x14ac:dyDescent="0.25">
+    <row r="165" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ165" s="3"/>
     </row>
-    <row r="166" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ166" s="3"/>
-    </row>
-    <row r="171" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ171" s="3"/>
-    </row>
-    <row r="172" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ172" s="3"/>
-    </row>
-    <row r="175" spans="88:88" x14ac:dyDescent="0.25">
+    <row r="167" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ167" s="3"/>
+    </row>
+    <row r="168" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ168" s="3"/>
+    </row>
+    <row r="169" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ169" s="3"/>
+    </row>
+    <row r="174" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ174" s="3"/>
+    </row>
+    <row r="175" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ175" s="3"/>
     </row>
-    <row r="176" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ176" s="3"/>
-    </row>
-    <row r="180" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ180" s="3"/>
-    </row>
-    <row r="184" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ184" s="3"/>
-    </row>
-    <row r="186" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ186" s="3"/>
-    </row>
-    <row r="187" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="178" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ178" s="3"/>
+    </row>
+    <row r="179" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ179" s="3"/>
+    </row>
+    <row r="183" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ183" s="3"/>
+    </row>
+    <row r="187" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ187" s="3"/>
     </row>
-    <row r="189" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="189" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ189" s="3"/>
     </row>
-    <row r="190" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="190" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ190" s="3"/>
     </row>
-    <row r="192" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT192"/>
+    <row r="192" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ192" s="3"/>
     </row>
     <row r="193" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT193"/>
       <c r="CJ193" s="3"/>
     </row>
-    <row r="194" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ194" s="3"/>
+    <row r="195" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT195"/>
     </row>
     <row r="196" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT196"/>
       <c r="CJ196" s="3"/>
     </row>
-    <row r="205" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT205"/>
-    </row>
-    <row r="206" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT206"/>
-      <c r="CJ206" s="3"/>
-    </row>
-    <row r="207" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ207" s="3"/>
+    <row r="197" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ197" s="3"/>
+    </row>
+    <row r="199" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ199" s="3"/>
     </row>
     <row r="208" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ208" s="3"/>
+      <c r="BT208"/>
     </row>
     <row r="209" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT209"/>
+      <c r="CJ209" s="3"/>
     </row>
     <row r="210" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT210"/>
       <c r="CJ210" s="3"/>
     </row>
     <row r="211" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ211" s="3"/>
     </row>
+    <row r="212" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT212"/>
+    </row>
     <row r="213" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT213"/>
+      <c r="CJ213" s="3"/>
     </row>
     <row r="214" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT214"/>
       <c r="CJ214" s="3"/>
     </row>
-    <row r="215" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ215" s="3"/>
+    <row r="216" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT216"/>
     </row>
     <row r="217" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT217"/>
+      <c r="CJ217" s="3"/>
     </row>
     <row r="218" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ218" s="3"/>
     </row>
+    <row r="220" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT220"/>
+    </row>
     <row r="221" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ221" s="3"/>
     </row>
-    <row r="225" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ225" s="3"/>
-    </row>
-    <row r="227" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT227"/>
+    <row r="224" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ224" s="3"/>
     </row>
     <row r="228" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ228" s="3"/>
     </row>
-    <row r="235" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT235"/>
-    </row>
-    <row r="236" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ236" s="3"/>
-    </row>
-    <row r="237" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ237" s="3"/>
+    <row r="230" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT230"/>
+    </row>
+    <row r="231" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ231" s="3"/>
+    </row>
+    <row r="238" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT238"/>
     </row>
     <row r="239" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT239"/>
+      <c r="CJ239" s="3"/>
     </row>
     <row r="240" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT240"/>
       <c r="CJ240" s="3"/>
     </row>
-    <row r="241" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ241" s="3"/>
-    </row>
-    <row r="247" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT247"/>
-    </row>
-    <row r="248" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT248"/>
-      <c r="CJ248" s="3"/>
-    </row>
-    <row r="249" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT249"/>
-      <c r="CJ249" s="3"/>
+    <row r="242" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT242"/>
+    </row>
+    <row r="243" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT243"/>
+      <c r="CJ243" s="3"/>
+    </row>
+    <row r="244" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ244" s="3"/>
     </row>
     <row r="250" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ250" s="3"/>
-    </row>
-    <row r="255" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT255"/>
-    </row>
-    <row r="256" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT256"/>
-    </row>
-    <row r="260" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT260"/>
-    </row>
-    <row r="261" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ261" s="3"/>
-    </row>
-    <row r="262" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT262"/>
+      <c r="BT250"/>
+    </row>
+    <row r="251" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT251"/>
+      <c r="CJ251" s="3"/>
+    </row>
+    <row r="252" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT252"/>
+      <c r="CJ252" s="3"/>
+    </row>
+    <row r="253" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ253" s="3"/>
+    </row>
+    <row r="258" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT258"/>
+    </row>
+    <row r="259" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT259"/>
     </row>
     <row r="263" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ263" s="3"/>
-    </row>
-    <row r="273" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT273"/>
-    </row>
-    <row r="274" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ274" s="3"/>
+      <c r="BT263"/>
+    </row>
+    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ264" s="3"/>
+    </row>
+    <row r="265" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT265"/>
+    </row>
+    <row r="266" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ266" s="3"/>
     </row>
     <row r="276" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT276"/>
@@ -8474,17 +11125,17 @@
     <row r="277" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ277" s="3"/>
     </row>
-    <row r="285" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT285"/>
-    </row>
-    <row r="286" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ286" s="3"/>
-    </row>
-    <row r="290" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT290"/>
-    </row>
-    <row r="291" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ291" s="3"/>
+    <row r="279" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT279"/>
+    </row>
+    <row r="280" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ280" s="3"/>
+    </row>
+    <row r="288" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT288"/>
+    </row>
+    <row r="289" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ289" s="3"/>
     </row>
     <row r="293" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT293"/>
@@ -8492,72 +11143,69 @@
     <row r="294" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ294" s="3"/>
     </row>
-    <row r="310" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT310"/>
-    </row>
-    <row r="311" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT311"/>
-      <c r="CJ311" s="3"/>
-    </row>
-    <row r="312" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT312"/>
-      <c r="CJ312" s="3"/>
+    <row r="296" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT296"/>
+    </row>
+    <row r="297" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ297" s="3"/>
     </row>
     <row r="313" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT313"/>
-      <c r="CJ313" s="3"/>
     </row>
     <row r="314" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT314"/>
+      <c r="CJ314" s="3"/>
+    </row>
+    <row r="315" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT315"/>
+      <c r="CJ315" s="3"/>
     </row>
     <row r="316" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT316"/>
+      <c r="CJ316" s="3"/>
     </row>
     <row r="317" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT317"/>
-      <c r="CJ317" s="3"/>
-    </row>
-    <row r="318" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT318"/>
-      <c r="CJ318" s="3"/>
     </row>
     <row r="319" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ319" s="3"/>
-    </row>
-    <row r="323" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT323"/>
-    </row>
-    <row r="324" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ324" s="3"/>
+      <c r="BT319"/>
+    </row>
+    <row r="320" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT320"/>
+      <c r="CJ320" s="3"/>
+    </row>
+    <row r="321" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT321"/>
+      <c r="CJ321" s="3"/>
+    </row>
+    <row r="322" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ322" s="3"/>
     </row>
     <row r="326" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT326"/>
     </row>
     <row r="327" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT327"/>
       <c r="CJ327" s="3"/>
     </row>
-    <row r="328" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT328"/>
-      <c r="CJ328" s="3"/>
-    </row>
     <row r="329" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ329" s="3"/>
-    </row>
-    <row r="345" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT345"/>
-    </row>
-    <row r="346" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ346" s="3"/>
-    </row>
-    <row r="354" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ354" s="3"/>
-    </row>
-    <row r="355" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ355" s="3"/>
-    </row>
-    <row r="356" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ356" s="3"/>
+      <c r="BT329"/>
+    </row>
+    <row r="330" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT330"/>
+      <c r="CJ330" s="3"/>
+    </row>
+    <row r="331" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT331"/>
+      <c r="CJ331" s="3"/>
+    </row>
+    <row r="332" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ332" s="3"/>
+    </row>
+    <row r="348" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT348"/>
+    </row>
+    <row r="349" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ349" s="3"/>
     </row>
     <row r="357" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ357" s="3"/>
@@ -8565,54 +11213,54 @@
     <row r="358" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ358" s="3"/>
     </row>
+    <row r="359" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ359" s="3"/>
+    </row>
     <row r="360" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT360"/>
+      <c r="CJ360" s="3"/>
     </row>
     <row r="361" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ361" s="3"/>
     </row>
-    <row r="362" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT362"/>
-    </row>
     <row r="363" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT363"/>
-      <c r="CJ363" s="3"/>
     </row>
     <row r="364" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ364" s="3"/>
     </row>
+    <row r="365" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT365"/>
+    </row>
     <row r="366" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT366"/>
+      <c r="CJ366" s="3"/>
     </row>
     <row r="367" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT367"/>
       <c r="CJ367" s="3"/>
     </row>
-    <row r="368" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT368"/>
-      <c r="CJ368" s="3"/>
-    </row>
     <row r="369" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ369" s="3"/>
+      <c r="BT369"/>
+    </row>
+    <row r="370" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT370"/>
+      <c r="CJ370" s="3"/>
     </row>
     <row r="371" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT371"/>
       <c r="CJ371" s="3"/>
     </row>
-    <row r="373" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ373" s="3"/>
-    </row>
-    <row r="375" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ375" s="3"/>
+    <row r="372" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ372" s="3"/>
+    </row>
+    <row r="374" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ374" s="3"/>
+    </row>
+    <row r="376" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ376" s="3"/>
     </row>
     <row r="378" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ378" s="3"/>
     </row>
-    <row r="379" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ379" s="3"/>
-    </row>
-    <row r="380" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ380" s="3"/>
-    </row>
     <row r="381" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ381" s="3"/>
     </row>
@@ -8623,50 +11271,53 @@
       <c r="CJ383" s="3"/>
     </row>
     <row r="384" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT384"/>
+      <c r="CJ384" s="3"/>
     </row>
     <row r="385" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT385"/>
       <c r="CJ385" s="3"/>
     </row>
     <row r="386" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT386"/>
       <c r="CJ386" s="3"/>
     </row>
     <row r="387" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ387" s="3"/>
+      <c r="BT387"/>
     </row>
     <row r="388" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT388"/>
       <c r="CJ388" s="3"/>
     </row>
     <row r="389" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT389"/>
       <c r="CJ389" s="3"/>
     </row>
     <row r="390" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ390" s="3"/>
     </row>
+    <row r="391" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ391" s="3"/>
+    </row>
     <row r="392" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ392" s="3"/>
     </row>
     <row r="393" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ393" s="3"/>
     </row>
-    <row r="394" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT394"/>
-    </row>
     <row r="395" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT395"/>
       <c r="CJ395" s="3"/>
     </row>
     <row r="396" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT396"/>
       <c r="CJ396" s="3"/>
     </row>
     <row r="397" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ397" s="3"/>
+      <c r="BT397"/>
     </row>
     <row r="398" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT398"/>
       <c r="CJ398" s="3"/>
+    </row>
+    <row r="399" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT399"/>
+      <c r="CJ399" s="3"/>
     </row>
     <row r="400" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ400" s="3"/>
@@ -8674,81 +11325,81 @@
     <row r="401" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ401" s="3"/>
     </row>
-    <row r="402" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT402"/>
-      <c r="CJ402" s="3"/>
-    </row>
     <row r="403" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT403"/>
       <c r="CJ403" s="3"/>
     </row>
     <row r="404" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ404" s="3"/>
     </row>
     <row r="405" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT405"/>
       <c r="CJ405" s="3"/>
     </row>
     <row r="406" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT406"/>
       <c r="CJ406" s="3"/>
     </row>
+    <row r="407" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ407" s="3"/>
+    </row>
     <row r="408" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT408"/>
       <c r="CJ408" s="3"/>
     </row>
     <row r="409" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ409" s="3"/>
     </row>
-    <row r="410" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ410" s="3"/>
+    <row r="411" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT411"/>
+      <c r="CJ411" s="3"/>
     </row>
     <row r="412" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT412"/>
       <c r="CJ412" s="3"/>
     </row>
     <row r="413" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT413"/>
       <c r="CJ413" s="3"/>
     </row>
-    <row r="414" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ414" s="3"/>
+    <row r="415" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT415"/>
+      <c r="CJ415" s="3"/>
     </row>
     <row r="416" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT416"/>
       <c r="CJ416" s="3"/>
     </row>
-    <row r="418" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ418" s="3"/>
+    <row r="417" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ417" s="3"/>
+    </row>
+    <row r="419" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ419" s="3"/>
     </row>
     <row r="421" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ421" s="3"/>
     </row>
-    <row r="422" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ422" s="3"/>
-    </row>
-    <row r="426" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT426"/>
-    </row>
-    <row r="427" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT427"/>
-      <c r="CJ427" s="3"/>
-    </row>
-    <row r="428" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT428"/>
-      <c r="CJ428" s="3"/>
+    <row r="424" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ424" s="3"/>
+    </row>
+    <row r="425" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ425" s="3"/>
     </row>
     <row r="429" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ429" s="3"/>
+      <c r="BT429"/>
     </row>
     <row r="430" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT430"/>
       <c r="CJ430" s="3"/>
     </row>
     <row r="431" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT431"/>
+      <c r="CJ431" s="3"/>
     </row>
     <row r="432" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ432" s="3"/>
     </row>
+    <row r="433" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ433" s="3"/>
+    </row>
     <row r="434" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ434" s="3"/>
+      <c r="BT434"/>
     </row>
     <row r="435" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ435" s="3"/>
@@ -8759,9 +11410,6 @@
     <row r="438" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ438" s="3"/>
     </row>
-    <row r="439" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ439" s="3"/>
-    </row>
     <row r="440" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ440" s="3"/>
     </row>
@@ -8774,83 +11422,80 @@
     <row r="443" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ443" s="3"/>
     </row>
+    <row r="444" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ444" s="3"/>
+    </row>
     <row r="445" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT445"/>
+      <c r="CJ445" s="3"/>
     </row>
     <row r="446" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ446" s="3"/>
     </row>
-    <row r="447" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ447" s="3"/>
-    </row>
-    <row r="480" spans="71:72" x14ac:dyDescent="0.25">
-      <c r="BS480" s="10"/>
-      <c r="BT480" s="11"/>
-    </row>
-    <row r="481" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H481" s="10"/>
-      <c r="CJ481" s="10"/>
-    </row>
-    <row r="487" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT487"/>
-    </row>
-    <row r="488" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT488"/>
-      <c r="CJ488" s="3"/>
-    </row>
-    <row r="489" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT489"/>
-      <c r="CJ489" s="3"/>
+    <row r="448" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT448"/>
+    </row>
+    <row r="449" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ449" s="3"/>
+    </row>
+    <row r="450" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ450" s="3"/>
+    </row>
+    <row r="483" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS483" s="10"/>
+      <c r="BT483" s="11"/>
+    </row>
+    <row r="484" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H484" s="10"/>
+      <c r="CJ484" s="10"/>
     </row>
     <row r="490" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ490" s="3"/>
-    </row>
-    <row r="507" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT507"/>
-    </row>
-    <row r="508" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ508" s="3"/>
-    </row>
-    <row r="540" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT540"/>
-    </row>
-    <row r="541" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT541"/>
-      <c r="CJ541" s="3"/>
-    </row>
-    <row r="542" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ542" s="3"/>
-    </row>
-    <row r="558" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT558"/>
-    </row>
-    <row r="559" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ559" s="3"/>
-    </row>
-    <row r="565" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT565"/>
-    </row>
-    <row r="566" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT566"/>
-      <c r="CJ566" s="3"/>
-    </row>
-    <row r="567" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ567" s="3"/>
-    </row>
-    <row r="572" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT572"/>
-    </row>
-    <row r="573" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT573"/>
-      <c r="CJ573" s="3"/>
-    </row>
-    <row r="574" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT574"/>
-      <c r="CJ574" s="3"/>
+      <c r="BT490"/>
+    </row>
+    <row r="491" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT491"/>
+      <c r="CJ491" s="3"/>
+    </row>
+    <row r="492" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT492"/>
+      <c r="CJ492" s="3"/>
+    </row>
+    <row r="493" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CJ493" s="3"/>
+    </row>
+    <row r="510" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT510"/>
+    </row>
+    <row r="511" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ511" s="3"/>
+    </row>
+    <row r="543" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT543"/>
+    </row>
+    <row r="544" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT544"/>
+      <c r="CJ544" s="3"/>
+    </row>
+    <row r="545" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ545" s="3"/>
+    </row>
+    <row r="561" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT561"/>
+    </row>
+    <row r="562" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ562" s="3"/>
+    </row>
+    <row r="568" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT568"/>
+    </row>
+    <row r="569" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT569"/>
+      <c r="CJ569" s="3"/>
+    </row>
+    <row r="570" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ570" s="3"/>
     </row>
     <row r="575" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT575"/>
-      <c r="CJ575" s="3"/>
     </row>
     <row r="576" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT576"/>
@@ -8901,48 +11546,48 @@
       <c r="CJ587" s="3"/>
     </row>
     <row r="588" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT588"/>
       <c r="CJ588" s="3"/>
     </row>
-    <row r="592" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT592"/>
-    </row>
-    <row r="593" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT593"/>
-      <c r="CJ593" s="3"/>
-    </row>
-    <row r="594" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ594" s="3"/>
+    <row r="589" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT589"/>
+      <c r="CJ589" s="3"/>
+    </row>
+    <row r="590" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT590"/>
+      <c r="CJ590" s="3"/>
+    </row>
+    <row r="591" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ591" s="3"/>
     </row>
     <row r="595" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT595"/>
     </row>
     <row r="596" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT596"/>
       <c r="CJ596" s="3"/>
     </row>
+    <row r="597" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ597" s="3"/>
+    </row>
+    <row r="598" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT598"/>
+    </row>
     <row r="599" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT599"/>
-    </row>
-    <row r="600" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT600"/>
-      <c r="CJ600" s="3"/>
-    </row>
-    <row r="601" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ601" s="3"/>
-    </row>
-    <row r="632" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT632"/>
-    </row>
-    <row r="633" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT633"/>
-      <c r="CJ633" s="3"/>
-    </row>
-    <row r="634" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT634"/>
-      <c r="CJ634" s="3"/>
+      <c r="CJ599" s="3"/>
+    </row>
+    <row r="602" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT602"/>
+    </row>
+    <row r="603" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT603"/>
+      <c r="CJ603" s="3"/>
+    </row>
+    <row r="604" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ604" s="3"/>
     </row>
     <row r="635" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT635"/>
-      <c r="CJ635" s="3"/>
     </row>
     <row r="636" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT636"/>
@@ -8961,85 +11606,87 @@
       <c r="CJ639" s="3"/>
     </row>
     <row r="640" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT640"/>
       <c r="CJ640" s="3"/>
+    </row>
+    <row r="641" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT641"/>
+      <c r="CJ641" s="3"/>
     </row>
     <row r="642" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT642"/>
+      <c r="CJ642" s="3"/>
     </row>
     <row r="643" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ643" s="3"/>
     </row>
-    <row r="647" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT647"/>
-    </row>
-    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ648" s="3"/>
+    <row r="645" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT645"/>
+    </row>
+    <row r="646" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ646" s="3"/>
+    </row>
+    <row r="650" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT650"/>
     </row>
     <row r="651" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT651"/>
-    </row>
-    <row r="652" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT652"/>
-      <c r="CJ652" s="3"/>
-    </row>
-    <row r="653" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT653"/>
-      <c r="CJ653" s="3"/>
+      <c r="CJ651" s="3"/>
     </row>
     <row r="654" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT654"/>
-      <c r="CJ654" s="3"/>
     </row>
     <row r="655" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT655"/>
       <c r="CJ655" s="3"/>
     </row>
-    <row r="662" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT662"/>
-    </row>
-    <row r="663" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ663" s="3"/>
+    <row r="656" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT656"/>
+      <c r="CJ656" s="3"/>
+    </row>
+    <row r="657" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT657"/>
+      <c r="CJ657" s="3"/>
+    </row>
+    <row r="658" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ658" s="3"/>
+    </row>
+    <row r="665" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT665"/>
     </row>
     <row r="666" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT666"/>
-    </row>
-    <row r="667" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT667"/>
-      <c r="CJ667" s="3"/>
-    </row>
-    <row r="668" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT668"/>
-      <c r="CJ668" s="3"/>
+      <c r="CJ666" s="3"/>
     </row>
     <row r="669" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT669"/>
-      <c r="CJ669" s="3"/>
     </row>
     <row r="670" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT670"/>
       <c r="CJ670" s="3"/>
+    </row>
+    <row r="671" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT671"/>
+      <c r="CJ671" s="3"/>
     </row>
     <row r="672" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT672"/>
+      <c r="CJ672" s="3"/>
     </row>
     <row r="673" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT673"/>
       <c r="CJ673" s="3"/>
     </row>
-    <row r="674" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ674" s="3"/>
-    </row>
     <row r="675" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ675">
-        <v>0.15</v>
-      </c>
+      <c r="BT675"/>
+    </row>
+    <row r="676" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT676"/>
+      <c r="CJ676" s="3"/>
     </row>
     <row r="677" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ677">
-        <v>0.2</v>
-      </c>
+      <c r="CJ677" s="3"/>
     </row>
     <row r="678" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ678">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="680" spans="72:88" x14ac:dyDescent="0.25">
@@ -9047,50 +11694,48 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="687" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ687">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="689" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ689">
-        <v>0.4</v>
+    <row r="681" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ681">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="683" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ683">
+        <v>0.2</v>
       </c>
     </row>
     <row r="690" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ690">
-        <v>0.6</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="692" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ692">
+        <v>0.4</v>
       </c>
     </row>
     <row r="693" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ693">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="696" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ696">
         <v>0.5</v>
       </c>
     </row>
-    <row r="694" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ694">
+    <row r="697" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ697">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="695" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ695">
+    <row r="698" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ698">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="698" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT698"/>
-    </row>
-    <row r="699" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT699"/>
-      <c r="CJ699" s="3"/>
-    </row>
-    <row r="700" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT700"/>
-      <c r="CJ700" s="3"/>
     </row>
     <row r="701" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT701"/>
-      <c r="CJ701" s="3"/>
     </row>
     <row r="702" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT702"/>
@@ -9113,28 +11758,28 @@
       <c r="CJ706" s="3"/>
     </row>
     <row r="707" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT707"/>
       <c r="CJ707" s="3"/>
     </row>
     <row r="708" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT708"/>
+      <c r="CJ708" s="3"/>
     </row>
     <row r="709" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT709"/>
       <c r="CJ709" s="3"/>
     </row>
-    <row r="718" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT718"/>
-    </row>
-    <row r="719" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT719"/>
-      <c r="CJ719" s="3"/>
-    </row>
-    <row r="720" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT720"/>
-      <c r="CJ720" s="3"/>
+    <row r="710" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ710" s="3"/>
+    </row>
+    <row r="711" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT711"/>
+    </row>
+    <row r="712" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ712" s="3"/>
     </row>
     <row r="721" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT721"/>
-      <c r="CJ721" s="3"/>
     </row>
     <row r="722" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT722"/>
@@ -9153,23 +11798,25 @@
       <c r="CJ725" s="3"/>
     </row>
     <row r="726" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT726"/>
       <c r="CJ726" s="3"/>
     </row>
     <row r="727" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT727"/>
+      <c r="CJ727" s="3"/>
     </row>
     <row r="728" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT728"/>
       <c r="CJ728" s="3"/>
     </row>
-    <row r="733" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT733"/>
-    </row>
-    <row r="734" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT734"/>
-      <c r="CJ734" s="3"/>
-    </row>
-    <row r="735" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ735" s="3"/>
+    <row r="729" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ729" s="3"/>
+    </row>
+    <row r="730" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT730"/>
+    </row>
+    <row r="731" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ731" s="3"/>
     </row>
     <row r="736" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT736"/>
@@ -9189,92 +11836,90 @@
       <c r="CJ740" s="3"/>
     </row>
     <row r="741" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT741"/>
       <c r="CJ741" s="3"/>
     </row>
     <row r="742" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT742"/>
-      <c r="CJ742" s="3"/>
     </row>
     <row r="743" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT743"/>
       <c r="CJ743" s="3"/>
     </row>
-    <row r="747" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT747"/>
-    </row>
-    <row r="748" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT748"/>
-      <c r="CJ748" s="3"/>
-    </row>
-    <row r="749" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT749"/>
-      <c r="CJ749" s="3"/>
+    <row r="744" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT744"/>
+      <c r="CJ744" s="3"/>
+    </row>
+    <row r="745" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT745"/>
+      <c r="CJ745" s="3"/>
+    </row>
+    <row r="746" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ746" s="3"/>
     </row>
     <row r="750" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ750" s="3"/>
+      <c r="BT750"/>
     </row>
     <row r="751" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT751"/>
+      <c r="CJ751" s="3"/>
     </row>
     <row r="752" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT752"/>
       <c r="CJ752" s="3"/>
     </row>
     <row r="753" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS753" s="10"/>
-      <c r="BT753" s="11"/>
+      <c r="CJ753" s="3"/>
     </row>
     <row r="754" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H754" s="10"/>
-      <c r="CJ754" s="10"/>
-    </row>
-    <row r="771" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT771"/>
-    </row>
-    <row r="772" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT772"/>
-      <c r="CJ772" s="3"/>
-    </row>
-    <row r="773" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT773"/>
-      <c r="CJ773" s="3"/>
+      <c r="BT754"/>
+    </row>
+    <row r="755" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CJ755" s="3"/>
+    </row>
+    <row r="756" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS756" s="10"/>
+      <c r="BT756" s="11"/>
+    </row>
+    <row r="757" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H757" s="10"/>
+      <c r="CJ757" s="10"/>
     </row>
     <row r="774" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT774"/>
-      <c r="CJ774" s="3"/>
     </row>
     <row r="775" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT775"/>
       <c r="CJ775" s="3"/>
     </row>
     <row r="776" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT776"/>
+      <c r="CJ776" s="3"/>
     </row>
     <row r="777" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT777"/>
       <c r="CJ777" s="3"/>
     </row>
     <row r="778" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS778" s="10"/>
-      <c r="BT778" s="11"/>
       <c r="CJ778" s="3"/>
     </row>
     <row r="779" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H779" s="10"/>
-      <c r="CJ779" s="10"/>
+      <c r="BT779"/>
+    </row>
+    <row r="780" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT780"/>
+      <c r="CJ780" s="3"/>
+    </row>
+    <row r="781" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS781" s="10"/>
+      <c r="BT781" s="11"/>
+      <c r="CJ781" s="3"/>
     </row>
     <row r="782" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT782"/>
-    </row>
-    <row r="783" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT783"/>
-      <c r="CJ783" s="3"/>
-    </row>
-    <row r="784" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT784"/>
-      <c r="CJ784" s="3"/>
+      <c r="H782" s="10"/>
+      <c r="CJ782" s="10"/>
     </row>
     <row r="785" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT785"/>
-      <c r="CJ785" s="3"/>
     </row>
     <row r="786" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT786"/>
@@ -9293,22 +11938,22 @@
       <c r="CJ789" s="3"/>
     </row>
     <row r="790" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT790"/>
       <c r="CJ790" s="3"/>
+    </row>
+    <row r="791" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT791"/>
+      <c r="CJ791" s="3"/>
     </row>
     <row r="792" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT792"/>
+      <c r="CJ792" s="3"/>
     </row>
     <row r="793" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT793"/>
       <c r="CJ793" s="3"/>
-    </row>
-    <row r="794" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT794"/>
-      <c r="CJ794" s="3"/>
     </row>
     <row r="795" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT795"/>
-      <c r="CJ795" s="3"/>
     </row>
     <row r="796" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT796"/>
@@ -9319,22 +11964,22 @@
       <c r="CJ797" s="3"/>
     </row>
     <row r="798" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT798"/>
       <c r="CJ798" s="3"/>
     </row>
     <row r="799" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT799"/>
+      <c r="CJ799" s="3"/>
     </row>
     <row r="800" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT800"/>
       <c r="CJ800" s="3"/>
     </row>
     <row r="801" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT801"/>
       <c r="CJ801" s="3"/>
     </row>
     <row r="802" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT802"/>
-      <c r="CJ802" s="3"/>
     </row>
     <row r="803" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT803"/>
@@ -9441,21 +12086,33 @@
       <c r="CJ828" s="3"/>
     </row>
     <row r="829" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT829"/>
       <c r="CJ829" s="3"/>
     </row>
     <row r="830" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT830"/>
+      <c r="CJ830" s="3"/>
     </row>
     <row r="831" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT831"/>
       <c r="CJ831" s="3"/>
     </row>
     <row r="832" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT832"/>
       <c r="CJ832" s="3"/>
     </row>
-    <row r="833" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ833" s="3"/>
+    <row r="833" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT833"/>
+    </row>
+    <row r="834" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT834"/>
+      <c r="CJ834" s="3"/>
+    </row>
+    <row r="835" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT835"/>
+      <c r="CJ835" s="3"/>
+    </row>
+    <row r="836" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ836" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -9467,7 +12124,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -9613,8 +12270,237 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="C4" s="8"/>
+      <c r="A4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C4" t="s">
+        <v>540</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>541</v>
+      </c>
+      <c r="P4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>519</v>
+      </c>
+      <c r="C5" t="s">
+        <v>543</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>544</v>
+      </c>
+      <c r="P5" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="H6" s="14">
+        <v>1</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>547</v>
+      </c>
+      <c r="C7" t="s">
+        <v>548</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="P7" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>550</v>
+      </c>
+      <c r="C8" t="s">
+        <v>548</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>558</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="H9" s="14">
+        <v>1</v>
+      </c>
+      <c r="K9"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>578</v>
+      </c>
+      <c r="C10" t="s">
+        <v>540</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="P10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>576</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="H11" s="14">
+        <v>1</v>
+      </c>
+      <c r="K11"/>
+    </row>
+    <row r="12" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>575</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="H12" s="14">
+        <v>1</v>
+      </c>
+      <c r="K12"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>609</v>
+      </c>
+      <c r="C13" t="s">
+        <v>200</v>
+      </c>
+      <c r="P13" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="H14" s="14">
+        <v>1</v>
+      </c>
+      <c r="J14"/>
+      <c r="P14" s="14" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>612</v>
+      </c>
+      <c r="C15" t="s">
+        <v>540</v>
+      </c>
+      <c r="P15" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>614</v>
+      </c>
+      <c r="C16" t="s">
+        <v>543</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>544</v>
+      </c>
+      <c r="P16" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>615</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="J17" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>594</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="H18" s="14">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>618</v>
+      </c>
+      <c r="C19" t="s">
+        <v>200</v>
+      </c>
+      <c r="P19" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>621</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -9678,7 +12564,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I4"/>
+  <dimension ref="A2:I5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -9742,24 +12628,47 @@
         <v>114</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="I4" s="8" t="s">
-        <v>482</v>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>511</v>
+      </c>
+      <c r="B5" t="s">
+        <v>538</v>
+      </c>
+      <c r="C5" t="s">
+        <v>434</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Main/Test.xlsx
+++ b/Excel/Main/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0549E192-3A9D-4AA3-93B7-46587D6035C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1E3FB7-8E4C-4243-88C4-925DD96A2241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="655">
   <si>
     <t>Id</t>
   </si>
@@ -2370,9 +2370,6 @@
   <si>
     <t>{"UnitId":"地面M3","TargetPos":"useSelfTargetPos","SetMod":"Replace","UseMod":"UserDirection","UserName":"Mon3tr"}</t>
     <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_3_Idle</t>
   </si>
   <si>
     <t>Skill_3_Idle</t>
@@ -4461,10 +4458,10 @@
         <v>535</v>
       </c>
       <c r="BM15" s="19" t="s">
-        <v>654</v>
-      </c>
-      <c r="BN15" s="19" t="s">
         <v>653</v>
+      </c>
+      <c r="BN15" t="s">
+        <v>124</v>
       </c>
       <c r="BP15" s="19" t="s">
         <v>604</v>
@@ -10665,7 +10662,7 @@
       </c>
       <c r="BT58"/>
       <c r="BZ58" s="20" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="CE58" t="s">
         <v>510</v>

--- a/Excel/Main/Test.xlsx
+++ b/Excel/Main/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1E3FB7-8E4C-4243-88C4-925DD96A2241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601B46AC-3176-49E7-BEB7-10468BAC2430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="656">
   <si>
     <t>Id</t>
   </si>
@@ -1755,10 +1755,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{"Count":1,"UnitId":"猫诱导"}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>猫爆炸</t>
   </si>
   <si>
@@ -2128,9 +2124,6 @@
   </si>
   <si>
     <t>重构体2</t>
-  </si>
-  <si>
-    <t>受击</t>
   </si>
   <si>
     <t>m33</t>
@@ -2372,11 +2365,23 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_3_Idle</t>
+    <t>Skill_3_Begin</t>
+  </si>
+  <si>
+    <t>本能的召唤</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_3_Begin</t>
+    <t>部署猫</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Count":1,"UnitId":"本能的召唤"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"UnitId":"猫诱导","TargetPos":"useSelfPos","SetMod":"Replace","UseMod":"UserDirection","UserName":"本能的召唤"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2954,18 +2959,18 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -3572,7 +3577,7 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>406</v>
@@ -3621,13 +3626,13 @@
         <v>1</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AH5" s="8" t="s">
         <v>408</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3692,17 +3697,136 @@
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="8"/>
+      <c r="A7" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="B7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" t="s">
+        <v>428</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>90</v>
+      </c>
+      <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>553</v>
+      </c>
       <c r="N7" s="8"/>
-      <c r="AG7" s="8"/>
-      <c r="AI7" s="8"/>
-      <c r="BB7" s="8"/>
+      <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>10</v>
+      </c>
+      <c r="Y7">
+        <v>0.05</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>-1</v>
+      </c>
+      <c r="AG7" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI7" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="AK7">
+        <v>3</v>
+      </c>
+      <c r="AL7">
+        <v>-0.5</v>
+      </c>
+      <c r="AN7">
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>502</v>
+      </c>
+      <c r="BE7" t="str">
+        <f t="shared" ref="BE7" si="0">"half_"&amp;D7</f>
+        <v>half_otter</v>
+      </c>
+      <c r="BF7" t="str">
+        <f t="shared" ref="BF7" si="1">D7</f>
+        <v>otter</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>128</v>
+      </c>
+      <c r="BH7">
+        <v>5</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>127</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>123</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>124</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>125</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>125</v>
+      </c>
+      <c r="BS7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B8" t="s">
         <v>126</v>
@@ -3714,7 +3838,7 @@
         <v>429</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3756,17 +3880,20 @@
       <c r="AC8">
         <v>0</v>
       </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
       <c r="AE8">
         <v>-1</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AH8" t="s">
         <v>122</v>
       </c>
       <c r="AI8" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AK8">
         <v>3</v>
@@ -3783,9 +3910,6 @@
       <c r="AP8">
         <v>0</v>
       </c>
-      <c r="AQ8">
-        <v>1</v>
-      </c>
       <c r="AW8">
         <v>0</v>
       </c>
@@ -3793,17 +3917,17 @@
         <v>1</v>
       </c>
       <c r="BB8" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="BD8" t="s">
         <v>502</v>
       </c>
-      <c r="BD8" t="s">
-        <v>503</v>
-      </c>
       <c r="BE8" t="str">
-        <f t="shared" ref="BE8:BE9" si="0">"half_"&amp;D8</f>
+        <f t="shared" ref="BE8:BE9" si="2">"half_"&amp;D8</f>
         <v>half_otter</v>
       </c>
       <c r="BF8" t="str">
-        <f t="shared" ref="BF8:BF9" si="1">D8</f>
+        <f t="shared" ref="BF8:BF9" si="3">D8</f>
         <v>otter</v>
       </c>
       <c r="BG8" t="s">
@@ -3833,7 +3957,7 @@
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B9" t="s">
         <v>126</v>
@@ -3845,7 +3969,7 @@
         <v>429</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3894,13 +4018,13 @@
         <v>-1</v>
       </c>
       <c r="AG9" s="8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AH9" t="s">
         <v>122</v>
       </c>
       <c r="AI9" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AK9">
         <v>3</v>
@@ -3927,17 +4051,17 @@
         <v>1</v>
       </c>
       <c r="BB9" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="BD9" t="s">
         <v>502</v>
       </c>
-      <c r="BD9" t="s">
-        <v>503</v>
-      </c>
       <c r="BE9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>half_otter</v>
       </c>
       <c r="BF9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>otter</v>
       </c>
       <c r="BG9" t="s">
@@ -4071,11 +4195,11 @@
         <v>431</v>
       </c>
       <c r="BE11" t="str">
-        <f t="shared" ref="BE11" si="2">"half_"&amp;D11</f>
+        <f t="shared" ref="BE11" si="4">"half_"&amp;D11</f>
         <v>half_otter</v>
       </c>
       <c r="BF11" t="str">
-        <f t="shared" ref="BF11" si="3">D11</f>
+        <f t="shared" ref="BF11" si="5">D11</f>
         <v>otter</v>
       </c>
       <c r="BG11" t="s">
@@ -4105,16 +4229,16 @@
     </row>
     <row r="13" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B13" t="s">
         <v>126</v>
       </c>
       <c r="D13" t="s">
+        <v>524</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>526</v>
       </c>
       <c r="F13" t="str">
         <f>"char_"&amp;E13&amp;"_"&amp;D13</f>
@@ -4160,16 +4284,16 @@
         <v>1</v>
       </c>
       <c r="AG13" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AH13" t="s">
         <v>122</v>
       </c>
       <c r="AI13" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ13" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AM13">
         <v>1</v>
@@ -4184,19 +4308,19 @@
         <v>0.25</v>
       </c>
       <c r="BB13" t="s">
+        <v>528</v>
+      </c>
+      <c r="BC13" t="s">
         <v>529</v>
       </c>
-      <c r="BC13" t="s">
+      <c r="BD13" t="s">
         <v>530</v>
       </c>
-      <c r="BD13" t="s">
+      <c r="BE13" t="s">
         <v>531</v>
       </c>
-      <c r="BE13" t="s">
+      <c r="BF13" t="s">
         <v>532</v>
-      </c>
-      <c r="BF13" t="s">
-        <v>533</v>
       </c>
       <c r="BG13" t="s">
         <v>128</v>
@@ -4205,10 +4329,10 @@
         <v>6</v>
       </c>
       <c r="BI13" t="s">
+        <v>533</v>
+      </c>
+      <c r="BJ13" t="s">
         <v>534</v>
-      </c>
-      <c r="BJ13" t="s">
-        <v>535</v>
       </c>
       <c r="BM13" t="s">
         <v>123</v>
@@ -4228,7 +4352,7 @@
     </row>
     <row r="14" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B14" t="s">
         <v>126</v>
@@ -4240,7 +4364,7 @@
         <v>429</v>
       </c>
       <c r="F14" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -4285,13 +4409,13 @@
         <v>-1</v>
       </c>
       <c r="AG14" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AH14" t="s">
         <v>122</v>
       </c>
       <c r="AI14" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AK14">
         <v>0</v>
@@ -4306,16 +4430,16 @@
         <v>0</v>
       </c>
       <c r="AV14" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AW14">
         <v>0.25</v>
       </c>
       <c r="BB14" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="BD14" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="BE14" t="str">
         <f>"half_"&amp;D14</f>
@@ -4335,7 +4459,7 @@
         <v>127</v>
       </c>
       <c r="BJ14" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="BM14" t="s">
         <v>123</v>
@@ -4349,16 +4473,16 @@
     </row>
     <row r="15" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B15" t="s">
         <v>126</v>
       </c>
       <c r="D15" t="s">
+        <v>524</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>526</v>
       </c>
       <c r="F15" t="str">
         <f>"char_"&amp;E15&amp;"_"&amp;D15</f>
@@ -4410,13 +4534,13 @@
         <v>1</v>
       </c>
       <c r="AG15" s="8" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AH15" t="s">
         <v>122</v>
       </c>
       <c r="AI15" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AN15">
         <v>1</v>
@@ -4431,19 +4555,19 @@
         <v>0.25</v>
       </c>
       <c r="BB15" t="s">
+        <v>528</v>
+      </c>
+      <c r="BC15" t="s">
         <v>529</v>
       </c>
-      <c r="BC15" t="s">
+      <c r="BD15" t="s">
         <v>530</v>
       </c>
-      <c r="BD15" t="s">
+      <c r="BE15" t="s">
         <v>531</v>
       </c>
-      <c r="BE15" t="s">
+      <c r="BF15" t="s">
         <v>532</v>
-      </c>
-      <c r="BF15" t="s">
-        <v>533</v>
       </c>
       <c r="BG15" t="s">
         <v>128</v>
@@ -4452,19 +4576,19 @@
         <v>6</v>
       </c>
       <c r="BI15" t="s">
+        <v>533</v>
+      </c>
+      <c r="BJ15" t="s">
         <v>534</v>
       </c>
-      <c r="BJ15" t="s">
-        <v>535</v>
-      </c>
-      <c r="BM15" s="19" t="s">
-        <v>653</v>
+      <c r="BM15" t="s">
+        <v>124</v>
       </c>
       <c r="BN15" t="s">
         <v>124</v>
       </c>
       <c r="BP15" s="19" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="BQ15" t="s">
         <v>125</v>
@@ -7252,7 +7376,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH836"/>
+  <dimension ref="A1:DH839"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -7483,7 +7607,7 @@
         <v>175</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="BA1" t="s">
         <v>176</v>
@@ -8339,7 +8463,7 @@
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>405</v>
@@ -8374,10 +8498,10 @@
         <v>425</v>
       </c>
       <c r="CF6" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="CG6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="CJ6" s="8" t="s">
         <v>450</v>
@@ -8389,13 +8513,13 @@
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>405</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>420</v>
@@ -8408,7 +8532,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AT7">
         <v>2.5</v>
@@ -8418,16 +8542,16 @@
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>484</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>485</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>420</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AC8">
         <v>2</v>
@@ -8437,7 +8561,7 @@
         <v>423</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AX8">
         <v>0</v>
@@ -8450,12 +8574,12 @@
       </c>
       <c r="CE8" s="8"/>
       <c r="CJ8" s="8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="CL8" s="8"/>
       <c r="CM8" s="8"/>
       <c r="CW8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
@@ -8498,7 +8622,7 @@
       </c>
       <c r="CJ10" s="3"/>
       <c r="CS10" s="8" t="s">
-        <v>467</v>
+        <v>654</v>
       </c>
       <c r="DB10">
         <v>1</v>
@@ -8511,373 +8635,284 @@
       </c>
     </row>
     <row r="11" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="AJ11" s="8"/>
-      <c r="AT11">
-        <v>99</v>
-      </c>
-      <c r="AV11" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="AX11">
-        <v>99999</v>
-      </c>
-      <c r="AZ11">
-        <v>2</v>
-      </c>
-      <c r="BB11">
-        <v>1</v>
-      </c>
-      <c r="BR11">
-        <v>0.2</v>
-      </c>
-      <c r="BT11">
-        <v>0</v>
-      </c>
-      <c r="BU11" s="4">
-        <v>5</v>
-      </c>
-      <c r="BV11" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW11" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="CE11" s="8" t="s">
-        <v>427</v>
-      </c>
+      <c r="A11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="AG11" s="8"/>
       <c r="CJ11" s="3"/>
-      <c r="CL11" s="8"/>
-      <c r="DB11">
-        <v>1</v>
-      </c>
-      <c r="DE11">
-        <v>1</v>
-      </c>
-      <c r="DF11">
-        <v>1</v>
-      </c>
+      <c r="CS11" s="8"/>
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>455</v>
+        <v>653</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
+        <v>493</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>420</v>
+        <v>347</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>426</v>
       </c>
       <c r="AC12">
-        <v>2</v>
-      </c>
-      <c r="AO12" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>454</v>
+        <v>1</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>348</v>
       </c>
       <c r="BB12">
-        <v>4</v>
-      </c>
-      <c r="BR12">
-        <v>0.2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BM12" s="8"/>
+      <c r="BT12"/>
       <c r="CJ12" s="3"/>
       <c r="CS12" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="CW12" s="8" t="s">
-        <v>457</v>
+        <v>655</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="C13" s="8"/>
-      <c r="AO13" s="8"/>
+      <c r="AG13" s="8"/>
       <c r="CJ13" s="3"/>
       <c r="CS13" s="8"/>
-      <c r="CW13" s="8"/>
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="C14" t="s">
-        <v>346</v>
+        <v>453</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>405</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>490</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="L14" s="12"/>
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="O14" s="12"/>
-      <c r="P14"/>
-      <c r="Q14"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
+      <c r="J14" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>422</v>
+      </c>
       <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="AJ14" s="8"/>
+      <c r="AT14">
+        <v>99</v>
+      </c>
+      <c r="AV14" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="AX14">
+        <v>99999</v>
+      </c>
+      <c r="AZ14">
         <v>2</v>
       </c>
-      <c r="AD14">
-        <v>1</v>
-      </c>
-      <c r="AT14" s="8">
-        <v>0.4</v>
-      </c>
       <c r="BB14">
         <v>1</v>
       </c>
-      <c r="BM14" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="BN14" s="8" t="s">
-        <v>469</v>
-      </c>
       <c r="BR14">
-        <v>6</v>
-      </c>
-      <c r="BT14" s="13">
-        <v>1</v>
-      </c>
-      <c r="BU14" s="13">
-        <v>1</v>
-      </c>
-      <c r="BV14" s="13">
-        <v>1</v>
-      </c>
-      <c r="BW14" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="BX14" s="13"/>
-      <c r="BY14" s="13"/>
-      <c r="BZ14" s="8"/>
-      <c r="CE14" s="8"/>
-      <c r="CH14" s="8"/>
-      <c r="CK14" s="8"/>
-      <c r="CR14" s="8"/>
-      <c r="CU14" s="8"/>
-      <c r="CV14" s="8"/>
+        <v>0.2</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14" s="4">
+        <v>5</v>
+      </c>
+      <c r="BV14" s="4">
+        <v>1</v>
+      </c>
+      <c r="BW14" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="CE14" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="CJ14" s="3"/>
+      <c r="CL14" s="8"/>
+      <c r="DB14">
+        <v>1</v>
+      </c>
+      <c r="DE14">
+        <v>1</v>
+      </c>
       <c r="DF14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="AC15">
+        <v>2</v>
+      </c>
+      <c r="AO15" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>454</v>
+      </c>
+      <c r="BB15">
+        <v>4</v>
+      </c>
+      <c r="BR15">
+        <v>0.2</v>
+      </c>
+      <c r="CJ15" s="3"/>
+      <c r="CS15" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="CW15" s="8" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="A16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="AO16" s="8"/>
+      <c r="CJ16" s="3"/>
+      <c r="CS16" s="8"/>
+      <c r="CW16" s="8"/>
+    </row>
+    <row r="17" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="C17" t="s">
         <v>346</v>
       </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="AC15">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="AJ15" s="8"/>
-      <c r="AR15" t="s">
-        <v>351</v>
-      </c>
-      <c r="AV15" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="AX15">
-        <v>999</v>
-      </c>
-      <c r="AZ15">
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17" s="12"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="12"/>
+      <c r="AC17">
         <v>2</v>
       </c>
-      <c r="BB15">
-        <v>1</v>
-      </c>
-      <c r="BT15"/>
-      <c r="CE15" s="8"/>
-      <c r="CJ15" s="3"/>
-      <c r="CL15" s="8"/>
-      <c r="DB15">
-        <v>1</v>
-      </c>
-      <c r="DE15">
-        <v>1</v>
-      </c>
-      <c r="DF15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="AD17">
+        <v>1</v>
+      </c>
+      <c r="AT17" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="BB17">
+        <v>1</v>
+      </c>
+      <c r="BM17" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="BN17" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="BR17">
+        <v>6</v>
+      </c>
+      <c r="BT17" s="13">
+        <v>1</v>
+      </c>
+      <c r="BU17" s="13">
+        <v>1</v>
+      </c>
+      <c r="BV17" s="13">
+        <v>1</v>
+      </c>
+      <c r="BW17" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="AC16">
-        <v>1</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB16">
-        <v>1</v>
-      </c>
-      <c r="BM16" s="8"/>
-      <c r="BT16"/>
-      <c r="CJ16" s="3"/>
-      <c r="CS16" s="8" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="17" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ17" s="3"/>
+      <c r="BX17" s="13"/>
+      <c r="BY17" s="13"/>
+      <c r="BZ17" s="8"/>
+      <c r="CE17" s="8"/>
+      <c r="CH17" s="8"/>
+      <c r="CK17" s="8"/>
+      <c r="CR17" s="8"/>
+      <c r="CU17" s="8"/>
+      <c r="CV17" s="8"/>
+      <c r="DF17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="J18" s="8" t="s">
-        <v>459</v>
-      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8"/>
       <c r="K18" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="L18" s="12"/>
-      <c r="M18"/>
-      <c r="N18"/>
-      <c r="O18" s="12"/>
-      <c r="P18"/>
-      <c r="Q18"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="12"/>
+        <v>347</v>
+      </c>
       <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="AJ18" s="8"/>
+      <c r="AR18" t="s">
+        <v>351</v>
+      </c>
+      <c r="AV18" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="AX18">
+        <v>999</v>
+      </c>
+      <c r="AZ18">
         <v>2</v>
       </c>
-      <c r="AD18">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="s">
-        <v>496</v>
-      </c>
-      <c r="AR18" t="s">
-        <v>454</v>
-      </c>
-      <c r="AV18" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="AX18">
-        <v>1.5</v>
-      </c>
       <c r="BB18">
-        <v>99</v>
-      </c>
-      <c r="BC18">
-        <v>11</v>
-      </c>
-      <c r="BD18">
-        <v>0.5</v>
-      </c>
-      <c r="BN18" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="BR18">
-        <v>6</v>
-      </c>
-      <c r="BT18" s="13">
-        <v>1</v>
-      </c>
-      <c r="BU18" s="13">
-        <v>1</v>
-      </c>
-      <c r="BV18" s="13">
-        <v>1</v>
-      </c>
-      <c r="BW18" s="13" t="s">
-        <v>472</v>
-      </c>
-      <c r="BX18" s="13"/>
-      <c r="BY18" s="13"/>
-      <c r="BZ18" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="BT18"/>
       <c r="CE18" s="8"/>
-      <c r="CH18" s="8"/>
-      <c r="CJ18" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="CK18" s="8"/>
-      <c r="CL18" t="s">
-        <v>470</v>
-      </c>
-      <c r="CM18">
-        <v>-0.8</v>
-      </c>
-      <c r="CP18">
-        <v>6</v>
-      </c>
-      <c r="CR18" s="8"/>
-      <c r="CU18" s="8"/>
-      <c r="CV18" s="8"/>
-      <c r="CW18" t="s">
-        <v>352</v>
+      <c r="CJ18" s="3"/>
+      <c r="CL18" s="8"/>
+      <c r="DB18">
+        <v>1</v>
+      </c>
+      <c r="DE18">
+        <v>1</v>
       </c>
       <c r="DF18">
         <v>1</v>
@@ -8885,387 +8920,353 @@
     </row>
     <row r="19" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19" s="8"/>
+        <v>493</v>
+      </c>
       <c r="K19" s="3" t="s">
         <v>347</v>
       </c>
+      <c r="L19" s="3" t="s">
+        <v>494</v>
+      </c>
       <c r="AC19">
         <v>1</v>
       </c>
-      <c r="AG19" s="8" t="s">
+      <c r="AG19" t="s">
         <v>348</v>
       </c>
-      <c r="AJ19" s="8"/>
-      <c r="AV19" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="AX19">
-        <v>9</v>
-      </c>
-      <c r="AZ19">
-        <v>2</v>
-      </c>
       <c r="BB19">
         <v>1</v>
       </c>
-      <c r="BC19">
-        <v>11</v>
-      </c>
-      <c r="BD19">
-        <v>0.5</v>
-      </c>
+      <c r="BM19" s="8"/>
       <c r="BT19"/>
-      <c r="CE19" s="8"/>
       <c r="CJ19" s="3"/>
-      <c r="CL19" s="8"/>
-      <c r="DB19">
-        <v>1</v>
-      </c>
-      <c r="DE19">
-        <v>1</v>
-      </c>
-      <c r="DF19">
-        <v>1</v>
+      <c r="CS19" s="8" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="AG20" s="8"/>
-      <c r="AJ20" s="8"/>
-      <c r="AV20" s="8"/>
-      <c r="BT20"/>
-      <c r="CE20" s="8"/>
       <c r="CJ20" s="3"/>
-      <c r="CL20" s="8"/>
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="C21" t="s">
+        <v>346</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="L21" s="12"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21" s="12"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+      <c r="AC21">
+        <v>2</v>
+      </c>
+      <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>495</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>454</v>
+      </c>
+      <c r="AV21" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="AX21">
+        <v>1.5</v>
+      </c>
+      <c r="BB21">
+        <v>99</v>
+      </c>
+      <c r="BC21">
+        <v>11</v>
+      </c>
+      <c r="BD21">
+        <v>0.5</v>
+      </c>
+      <c r="BN21" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="BR21">
+        <v>6</v>
+      </c>
+      <c r="BT21" s="13">
+        <v>1</v>
+      </c>
+      <c r="BU21" s="13">
+        <v>1</v>
+      </c>
+      <c r="BV21" s="13">
+        <v>1</v>
+      </c>
+      <c r="BW21" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="BX21" s="13"/>
+      <c r="BY21" s="13"/>
+      <c r="BZ21" s="8"/>
+      <c r="CE21" s="8"/>
+      <c r="CH21" s="8"/>
+      <c r="CJ21" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="CK21" s="8"/>
+      <c r="CL21" t="s">
+        <v>469</v>
+      </c>
+      <c r="CM21">
+        <v>-0.8</v>
+      </c>
+      <c r="CP21">
+        <v>6</v>
+      </c>
+      <c r="CR21" s="8"/>
+      <c r="CU21" s="8"/>
+      <c r="CV21" s="8"/>
+      <c r="CW21" t="s">
+        <v>352</v>
+      </c>
+      <c r="DF21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="AJ22" s="8"/>
+      <c r="AV22" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="AX22">
+        <v>9</v>
+      </c>
+      <c r="AZ22">
+        <v>2</v>
+      </c>
+      <c r="BB22">
+        <v>1</v>
+      </c>
+      <c r="BC22">
+        <v>11</v>
+      </c>
+      <c r="BD22">
+        <v>0.5</v>
+      </c>
+      <c r="BT22"/>
+      <c r="CE22" s="8"/>
+      <c r="CJ22" s="3"/>
+      <c r="CL22" s="8"/>
+      <c r="DB22">
+        <v>1</v>
+      </c>
+      <c r="DE22">
+        <v>1</v>
+      </c>
+      <c r="DF22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="AG23" s="8"/>
+      <c r="AJ23" s="8"/>
+      <c r="AV23" s="8"/>
+      <c r="BT23"/>
+      <c r="CE23" s="8"/>
+      <c r="CJ23" s="3"/>
+      <c r="CL23" s="8"/>
+    </row>
+    <row r="24" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C24" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="K21" s="3" t="s">
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="AC21">
-        <v>1</v>
-      </c>
-      <c r="AR21" s="8" t="s">
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AR24" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="BT21"/>
-      <c r="CJ21" s="3"/>
-      <c r="CS21" s="8" t="s">
+      <c r="BT24"/>
+      <c r="CJ24" s="3"/>
+      <c r="CS24" s="8" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="22" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="BT22"/>
-      <c r="CJ22" s="3"/>
-    </row>
-    <row r="23" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>506</v>
-      </c>
-      <c r="C23" t="s">
-        <v>346</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>555</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="O23"/>
-      <c r="AC23">
-        <v>1</v>
-      </c>
-      <c r="AO23" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>539</v>
-      </c>
-      <c r="CS23" s="8" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="24" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>507</v>
-      </c>
-      <c r="C24" t="s">
-        <v>346</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="P24"/>
-      <c r="AC24">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="s">
-        <v>508</v>
-      </c>
-      <c r="AR24" t="s">
-        <v>509</v>
-      </c>
-      <c r="AW24">
-        <v>1</v>
-      </c>
-      <c r="AX24">
-        <v>1</v>
-      </c>
-      <c r="BB24">
-        <v>1</v>
-      </c>
-      <c r="BZ24" t="s">
-        <v>55</v>
-      </c>
-      <c r="CE24" t="s">
-        <v>510</v>
-      </c>
-      <c r="CF24" t="s">
-        <v>511</v>
-      </c>
-      <c r="CG24" t="s">
-        <v>475</v>
-      </c>
-      <c r="CL24" t="s">
-        <v>512</v>
-      </c>
-      <c r="CM24">
-        <v>22</v>
-      </c>
-      <c r="CP24">
-        <v>10</v>
-      </c>
-      <c r="CW24" t="s">
-        <v>513</v>
-      </c>
-    </row>
     <row r="25" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>514</v>
-      </c>
-      <c r="C25" t="s">
-        <v>515</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="AC25">
-        <v>1</v>
-      </c>
-      <c r="AF25">
-        <v>1</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB25">
-        <v>1</v>
-      </c>
+      <c r="BT25"/>
       <c r="CJ25" s="3"/>
-      <c r="CS25" t="s">
-        <v>516</v>
-      </c>
-      <c r="DB25">
-        <v>1</v>
-      </c>
-      <c r="DE25">
-        <v>1</v>
-      </c>
-      <c r="DF25">
-        <v>1</v>
-      </c>
     </row>
     <row r="26" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C26" t="s">
         <v>346</v>
       </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>505</v>
-      </c>
-      <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26" s="12"/>
-      <c r="P26"/>
-      <c r="Q26"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="12"/>
-      <c r="U26" s="12"/>
-      <c r="V26" s="12"/>
-      <c r="W26" s="12"/>
-      <c r="X26"/>
+      <c r="J26" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="O26"/>
       <c r="AC26">
         <v>1</v>
       </c>
-      <c r="AG26" t="s">
-        <v>348</v>
+      <c r="AO26" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="AR26" t="s">
-        <v>351</v>
-      </c>
-      <c r="BB26">
-        <v>1</v>
-      </c>
-      <c r="BM26" t="s">
-        <v>518</v>
-      </c>
-      <c r="BS26" s="13"/>
-      <c r="BT26" s="13"/>
-      <c r="BU26" s="13"/>
-      <c r="BV26" s="13"/>
-      <c r="BW26" s="13"/>
-      <c r="BX26" s="13"/>
-      <c r="BY26"/>
-      <c r="CL26" t="s">
-        <v>519</v>
-      </c>
-      <c r="CM26">
-        <v>8</v>
-      </c>
-      <c r="CP26">
-        <v>9999</v>
-      </c>
-      <c r="DB26">
-        <v>1</v>
+        <v>538</v>
+      </c>
+      <c r="CS26" s="8" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C27" t="s">
         <v>346</v>
       </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27"/>
-      <c r="N27"/>
-      <c r="O27" s="12"/>
+      <c r="K27" s="3" t="s">
+        <v>490</v>
+      </c>
       <c r="P27"/>
-      <c r="Q27"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="12"/>
-      <c r="V27" s="12"/>
-      <c r="W27" s="12"/>
-      <c r="X27"/>
       <c r="AC27">
         <v>1</v>
       </c>
+      <c r="AO27" t="s">
+        <v>507</v>
+      </c>
       <c r="AR27" t="s">
-        <v>520</v>
+        <v>508</v>
+      </c>
+      <c r="AW27">
+        <v>1</v>
+      </c>
+      <c r="AX27">
+        <v>1</v>
       </c>
       <c r="BB27">
-        <v>99</v>
-      </c>
-      <c r="BQ27">
-        <v>0.1</v>
-      </c>
-      <c r="BS27" s="13"/>
-      <c r="BT27" s="13"/>
-      <c r="BU27" s="13"/>
-      <c r="BV27" s="13"/>
-      <c r="BW27" s="13"/>
-      <c r="BX27" s="13"/>
-      <c r="BY27"/>
-      <c r="CL27" s="14" t="s">
-        <v>521</v>
+        <v>1</v>
+      </c>
+      <c r="BZ27" t="s">
+        <v>55</v>
+      </c>
+      <c r="CE27" t="s">
+        <v>509</v>
+      </c>
+      <c r="CF27" t="s">
+        <v>510</v>
+      </c>
+      <c r="CG27" t="s">
+        <v>474</v>
+      </c>
+      <c r="CL27" t="s">
+        <v>511</v>
       </c>
       <c r="CM27">
-        <v>0.2</v>
+        <v>22</v>
       </c>
       <c r="CP27">
-        <v>0.2</v>
-      </c>
-      <c r="DB27">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="CW27" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="28" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="C28" t="s">
-        <v>346</v>
+        <v>514</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>347</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AF28">
         <v>1</v>
       </c>
       <c r="AG28" t="s">
         <v>348</v>
       </c>
-      <c r="AW28" s="3"/>
       <c r="BB28">
         <v>1</v>
       </c>
-      <c r="BT28"/>
-      <c r="BU28"/>
-      <c r="BV28"/>
-      <c r="BW28"/>
-      <c r="BX28"/>
-      <c r="BY28"/>
-      <c r="BZ28" s="3"/>
-      <c r="CA28" s="3"/>
-      <c r="CB28" s="3"/>
-      <c r="CC28" s="3"/>
-      <c r="CD28" s="3"/>
-      <c r="CF28" s="3"/>
-      <c r="CG28" s="3"/>
-      <c r="CH28" s="3"/>
-      <c r="CI28" s="3"/>
       <c r="CJ28" s="3"/>
-      <c r="CK28" s="3"/>
-      <c r="CL28" t="s">
-        <v>523</v>
-      </c>
-      <c r="CP28">
-        <v>99999</v>
+      <c r="CS28" t="s">
+        <v>515</v>
+      </c>
+      <c r="DB28">
+        <v>1</v>
+      </c>
+      <c r="DE28">
+        <v>1</v>
+      </c>
+      <c r="DF28">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>557</v>
+        <v>516</v>
       </c>
       <c r="C29" t="s">
         <v>346</v>
@@ -9273,23 +9274,23 @@
       <c r="I29">
         <v>1</v>
       </c>
-      <c r="K29" s="15" t="s">
+      <c r="K29" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="L29" s="15"/>
+      <c r="L29" s="12" t="s">
+        <v>504</v>
+      </c>
       <c r="M29"/>
       <c r="N29"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="16"/>
-      <c r="S29"/>
-      <c r="T29" s="15"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="15"/>
-      <c r="W29" s="15"/>
+      <c r="O29" s="12"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
       <c r="X29"/>
       <c r="AC29">
         <v>1</v>
@@ -9303,225 +9304,193 @@
       <c r="BB29">
         <v>1</v>
       </c>
-      <c r="BT29"/>
-      <c r="BU29" s="17"/>
-      <c r="BV29" s="17"/>
-      <c r="BW29" s="17"/>
-      <c r="BX29" s="17"/>
-      <c r="BY29" s="17"/>
-      <c r="BZ29" s="17"/>
+      <c r="BM29" t="s">
+        <v>517</v>
+      </c>
+      <c r="BS29" s="13"/>
+      <c r="BT29" s="13"/>
+      <c r="BU29" s="13"/>
+      <c r="BV29" s="13"/>
+      <c r="BW29" s="13"/>
+      <c r="BX29" s="13"/>
+      <c r="BY29"/>
       <c r="CL29" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="CM29">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="CP29">
-        <v>10</v>
+        <v>9999</v>
+      </c>
+      <c r="DB29">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
-      <c r="R30" s="15"/>
-      <c r="S30" s="15"/>
-      <c r="T30" s="15"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="15"/>
-      <c r="W30" s="15"/>
-      <c r="X30" s="15"/>
-      <c r="BT30"/>
-      <c r="BU30" s="17"/>
-      <c r="BV30" s="17"/>
-      <c r="BW30" s="17"/>
-      <c r="BX30" s="17"/>
-      <c r="BY30" s="17"/>
+      <c r="A30" t="s">
+        <v>517</v>
+      </c>
+      <c r="C30" t="s">
+        <v>346</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30" s="12"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30"/>
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="s">
+        <v>519</v>
+      </c>
+      <c r="BB30">
+        <v>99</v>
+      </c>
+      <c r="BQ30">
+        <v>0.1</v>
+      </c>
+      <c r="BS30" s="13"/>
+      <c r="BT30" s="13"/>
+      <c r="BU30" s="13"/>
+      <c r="BV30" s="13"/>
+      <c r="BW30" s="13"/>
+      <c r="BX30" s="13"/>
+      <c r="BY30"/>
+      <c r="CL30" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="CM30">
+        <v>0.2</v>
+      </c>
+      <c r="CP30">
+        <v>0.2</v>
+      </c>
+      <c r="DB30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>559</v>
+        <v>521</v>
       </c>
       <c r="C31" t="s">
         <v>346</v>
       </c>
-      <c r="D31" t="s">
-        <v>560</v>
-      </c>
-      <c r="E31" t="s">
-        <v>561</v>
-      </c>
-      <c r="F31" t="s">
-        <v>562</v>
-      </c>
-      <c r="G31">
-        <v>3</v>
-      </c>
-      <c r="J31" t="s">
-        <v>490</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>563</v>
-      </c>
-      <c r="L31" s="15"/>
-      <c r="M31"/>
-      <c r="N31" s="15"/>
-      <c r="O31"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
-      <c r="T31" s="15"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="15"/>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15"/>
+      <c r="K31" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>504</v>
+      </c>
       <c r="AC31">
         <v>1</v>
       </c>
       <c r="AG31" t="s">
         <v>348</v>
       </c>
+      <c r="AW31" s="3"/>
       <c r="BB31">
         <v>1</v>
       </c>
-      <c r="BM31" t="s">
-        <v>564</v>
-      </c>
-      <c r="BN31" t="s">
-        <v>565</v>
-      </c>
-      <c r="BR31">
-        <v>30</v>
-      </c>
-      <c r="BT31" s="17">
-        <v>13</v>
-      </c>
-      <c r="BU31" s="17">
-        <v>15</v>
-      </c>
-      <c r="BV31" s="17">
-        <v>1</v>
-      </c>
-      <c r="BW31" s="17" t="s">
-        <v>566</v>
-      </c>
-      <c r="BX31" s="17"/>
-      <c r="BY31" s="17"/>
-      <c r="CL31" s="16" t="s">
-        <v>567</v>
+      <c r="BT31"/>
+      <c r="BU31"/>
+      <c r="BV31"/>
+      <c r="BW31"/>
+      <c r="BX31"/>
+      <c r="BY31"/>
+      <c r="BZ31" s="3"/>
+      <c r="CA31" s="3"/>
+      <c r="CB31" s="3"/>
+      <c r="CC31" s="3"/>
+      <c r="CD31" s="3"/>
+      <c r="CF31" s="3"/>
+      <c r="CG31" s="3"/>
+      <c r="CH31" s="3"/>
+      <c r="CI31" s="3"/>
+      <c r="CJ31" s="3"/>
+      <c r="CK31" s="3"/>
+      <c r="CL31" t="s">
+        <v>522</v>
       </c>
       <c r="CP31">
-        <v>30</v>
-      </c>
-      <c r="DB31">
-        <v>1</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="32" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C32" t="s">
         <v>346</v>
       </c>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>347</v>
+      </c>
       <c r="L32" s="15"/>
       <c r="M32"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="P32"/>
-      <c r="Q32"/>
-      <c r="R32" s="15"/>
-      <c r="S32" s="15"/>
+      <c r="N32"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="16"/>
+      <c r="S32"/>
       <c r="T32" s="15"/>
       <c r="U32" s="15"/>
       <c r="V32" s="15"/>
       <c r="W32" s="15"/>
-      <c r="X32" s="15"/>
+      <c r="X32"/>
       <c r="AC32">
         <v>1</v>
       </c>
-      <c r="AD32">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="s">
-        <v>508</v>
-      </c>
-      <c r="AQ32" t="s">
-        <v>536</v>
-      </c>
-      <c r="AU32">
-        <v>1</v>
-      </c>
-      <c r="AW32">
-        <v>1</v>
-      </c>
-      <c r="AX32">
-        <v>1</v>
+      <c r="AG32" t="s">
+        <v>348</v>
+      </c>
+      <c r="AR32" t="s">
+        <v>351</v>
       </c>
       <c r="BB32">
         <v>1</v>
       </c>
-      <c r="BN32" t="s">
-        <v>569</v>
-      </c>
-      <c r="BT32" s="17"/>
+      <c r="BT32"/>
       <c r="BU32" s="17"/>
       <c r="BV32" s="17"/>
       <c r="BW32" s="17"/>
       <c r="BX32" s="17"/>
       <c r="BY32" s="17"/>
-      <c r="BZ32" t="s">
-        <v>570</v>
-      </c>
-      <c r="CE32" t="s">
-        <v>510</v>
-      </c>
-      <c r="CF32" t="s">
+      <c r="BZ32" s="17"/>
+      <c r="CL32" t="s">
         <v>511</v>
-      </c>
-      <c r="CG32" t="s">
-        <v>475</v>
-      </c>
-      <c r="CL32" t="s">
-        <v>571</v>
       </c>
       <c r="CM32">
         <v>22</v>
       </c>
-      <c r="CN32">
-        <v>39.6</v>
-      </c>
       <c r="CP32">
         <v>10</v>
       </c>
-      <c r="CW32" t="s">
-        <v>513</v>
-      </c>
     </row>
     <row r="33" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>572</v>
-      </c>
-      <c r="C33" t="s">
-        <v>346</v>
-      </c>
-      <c r="I33">
-        <v>1</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>347</v>
-      </c>
+      <c r="K33" s="15"/>
       <c r="L33" s="15"/>
-      <c r="M33"/>
+      <c r="M33" s="15"/>
       <c r="N33" s="15"/>
       <c r="O33" s="15"/>
       <c r="P33" s="15"/>
@@ -9533,74 +9502,44 @@
       <c r="V33" s="15"/>
       <c r="W33" s="15"/>
       <c r="X33" s="15"/>
-      <c r="AC33">
-        <v>1</v>
-      </c>
-      <c r="AD33">
-        <v>1</v>
-      </c>
-      <c r="AJ33" t="s">
-        <v>536</v>
-      </c>
-      <c r="AO33" t="s">
-        <v>508</v>
-      </c>
-      <c r="AR33" t="s">
-        <v>509</v>
-      </c>
-      <c r="AV33" t="s">
-        <v>471</v>
-      </c>
-      <c r="AX33">
-        <v>1</v>
-      </c>
-      <c r="AZ33">
-        <v>2</v>
-      </c>
-      <c r="BB33">
-        <v>1</v>
-      </c>
-      <c r="BT33" s="17"/>
+      <c r="BT33"/>
       <c r="BU33" s="17"/>
       <c r="BV33" s="17"/>
       <c r="BW33" s="17"/>
       <c r="BX33" s="17"/>
       <c r="BY33" s="17"/>
-      <c r="BZ33" s="18"/>
-      <c r="CF33" t="s">
-        <v>573</v>
-      </c>
-      <c r="CG33" t="s">
-        <v>475</v>
-      </c>
-      <c r="DB33">
-        <v>1</v>
-      </c>
-      <c r="DF33">
-        <v>1</v>
-      </c>
     </row>
     <row r="34" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="C34" t="s">
         <v>346</v>
       </c>
-      <c r="I34">
-        <v>1</v>
+      <c r="D34" t="s">
+        <v>559</v>
+      </c>
+      <c r="E34" t="s">
+        <v>560</v>
+      </c>
+      <c r="F34" t="s">
+        <v>561</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="J34" t="s">
+        <v>489</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>347</v>
+        <v>562</v>
       </c>
       <c r="L34" s="15"/>
       <c r="M34"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="P34"/>
-      <c r="Q34"/>
+      <c r="O34"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
       <c r="R34" s="15"/>
       <c r="S34" s="15"/>
       <c r="T34" s="15"/>
@@ -9614,47 +9553,56 @@
       <c r="AG34" t="s">
         <v>348</v>
       </c>
-      <c r="AU34">
-        <v>1</v>
-      </c>
       <c r="BB34">
         <v>1</v>
       </c>
-      <c r="BT34" s="17"/>
-      <c r="BU34" s="17"/>
-      <c r="BV34" s="17"/>
-      <c r="BW34" s="17"/>
+      <c r="BM34" t="s">
+        <v>563</v>
+      </c>
+      <c r="BN34" t="s">
+        <v>564</v>
+      </c>
+      <c r="BR34">
+        <v>30</v>
+      </c>
+      <c r="BT34" s="17">
+        <v>13</v>
+      </c>
+      <c r="BU34" s="17">
+        <v>15</v>
+      </c>
+      <c r="BV34" s="17">
+        <v>1</v>
+      </c>
+      <c r="BW34" s="17" t="s">
+        <v>565</v>
+      </c>
       <c r="BX34" s="17"/>
       <c r="BY34" s="17"/>
-      <c r="CL34" t="s">
-        <v>571</v>
-      </c>
-      <c r="CM34">
-        <v>22</v>
-      </c>
-      <c r="CN34">
-        <v>39.6</v>
+      <c r="CL34" s="16" t="s">
+        <v>566</v>
       </c>
       <c r="CP34">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="DB34">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="C35" t="s">
         <v>346</v>
       </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
+      <c r="J35" s="15"/>
       <c r="K35" s="15"/>
       <c r="L35" s="15"/>
       <c r="M35"/>
       <c r="N35" s="15"/>
       <c r="O35" s="16" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="P35"/>
       <c r="Q35"/>
@@ -9668,17 +9616,29 @@
       <c r="AC35">
         <v>1</v>
       </c>
-      <c r="AJ35" t="s">
-        <v>536</v>
-      </c>
-      <c r="AR35" t="s">
-        <v>509</v>
+      <c r="AD35">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="s">
+        <v>507</v>
+      </c>
+      <c r="AQ35" t="s">
+        <v>535</v>
+      </c>
+      <c r="AU35">
+        <v>1</v>
+      </c>
+      <c r="AW35">
+        <v>1</v>
+      </c>
+      <c r="AX35">
+        <v>1</v>
       </c>
       <c r="BB35">
         <v>1</v>
       </c>
-      <c r="BQ35">
-        <v>0.1</v>
+      <c r="BN35" t="s">
+        <v>568</v>
       </c>
       <c r="BT35" s="17"/>
       <c r="BU35" s="17"/>
@@ -9686,16 +9646,37 @@
       <c r="BW35" s="17"/>
       <c r="BX35" s="17"/>
       <c r="BY35" s="17"/>
-      <c r="CL35" s="16" t="s">
-        <v>575</v>
+      <c r="BZ35" t="s">
+        <v>569</v>
+      </c>
+      <c r="CE35" t="s">
+        <v>509</v>
+      </c>
+      <c r="CF35" t="s">
+        <v>510</v>
+      </c>
+      <c r="CG35" t="s">
+        <v>474</v>
+      </c>
+      <c r="CL35" t="s">
+        <v>570</v>
+      </c>
+      <c r="CM35">
+        <v>22</v>
+      </c>
+      <c r="CN35">
+        <v>39.6</v>
       </c>
       <c r="CP35">
-        <v>0.2</v>
+        <v>10</v>
+      </c>
+      <c r="CW35" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="36" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C36" t="s">
         <v>346</v>
@@ -9722,33 +9703,42 @@
       <c r="AC36">
         <v>1</v>
       </c>
-      <c r="AG36" t="s">
-        <v>348</v>
-      </c>
-      <c r="AW36" s="15"/>
+      <c r="AD36">
+        <v>1</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>535</v>
+      </c>
+      <c r="AO36" t="s">
+        <v>507</v>
+      </c>
+      <c r="AR36" t="s">
+        <v>508</v>
+      </c>
+      <c r="AV36" t="s">
+        <v>470</v>
+      </c>
+      <c r="AX36">
+        <v>1</v>
+      </c>
+      <c r="AZ36">
+        <v>2</v>
+      </c>
       <c r="BB36">
         <v>1</v>
       </c>
-      <c r="BT36"/>
-      <c r="BU36"/>
-      <c r="BV36"/>
-      <c r="BW36"/>
-      <c r="BX36"/>
-      <c r="BY36"/>
-      <c r="BZ36" s="15"/>
-      <c r="CA36" s="15"/>
-      <c r="CB36" s="15"/>
-      <c r="CC36" s="15"/>
-      <c r="CD36" s="15"/>
-      <c r="CF36" s="15"/>
-      <c r="CG36" s="15"/>
-      <c r="CH36" s="15"/>
-      <c r="CI36" s="15"/>
-      <c r="CL36" s="16" t="s">
-        <v>576</v>
-      </c>
-      <c r="CP36">
-        <v>40</v>
+      <c r="BT36" s="17"/>
+      <c r="BU36" s="17"/>
+      <c r="BV36" s="17"/>
+      <c r="BW36" s="17"/>
+      <c r="BX36" s="17"/>
+      <c r="BY36" s="17"/>
+      <c r="BZ36" s="18"/>
+      <c r="CF36" t="s">
+        <v>572</v>
+      </c>
+      <c r="CG36" t="s">
+        <v>474</v>
       </c>
       <c r="DB36">
         <v>1</v>
@@ -9759,7 +9749,7 @@
     </row>
     <row r="37" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C37" t="s">
         <v>346</v>
@@ -9767,17 +9757,17 @@
       <c r="I37">
         <v>1</v>
       </c>
-      <c r="K37" s="15"/>
+      <c r="K37" s="15" t="s">
+        <v>347</v>
+      </c>
       <c r="L37" s="15"/>
       <c r="M37"/>
       <c r="N37" s="15"/>
       <c r="O37" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="P37" s="16" t="s">
-        <v>576</v>
-      </c>
-      <c r="Q37" s="15"/>
+        <v>557</v>
+      </c>
+      <c r="P37"/>
+      <c r="Q37"/>
       <c r="R37" s="15"/>
       <c r="S37" s="15"/>
       <c r="T37" s="15"/>
@@ -9788,11 +9778,14 @@
       <c r="AC37">
         <v>1</v>
       </c>
-      <c r="AT37">
-        <v>20</v>
+      <c r="AG37" t="s">
+        <v>348</v>
+      </c>
+      <c r="AU37">
+        <v>1</v>
       </c>
       <c r="BB37">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="BT37" s="17"/>
       <c r="BU37" s="17"/>
@@ -9800,13 +9793,22 @@
       <c r="BW37" s="17"/>
       <c r="BX37" s="17"/>
       <c r="BY37" s="17"/>
-      <c r="CK37" t="s">
-        <v>578</v>
+      <c r="CL37" t="s">
+        <v>570</v>
+      </c>
+      <c r="CM37">
+        <v>22</v>
+      </c>
+      <c r="CN37">
+        <v>39.6</v>
+      </c>
+      <c r="CP37">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C38" t="s">
         <v>346</v>
@@ -9814,15 +9816,15 @@
       <c r="I38">
         <v>1</v>
       </c>
-      <c r="K38" s="15" t="s">
-        <v>347</v>
-      </c>
+      <c r="K38" s="15"/>
       <c r="L38" s="15"/>
       <c r="M38"/>
-      <c r="N38"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="P38"/>
+      <c r="Q38"/>
       <c r="R38" s="15"/>
       <c r="S38" s="15"/>
       <c r="T38" s="15"/>
@@ -9833,8 +9835,11 @@
       <c r="AC38">
         <v>1</v>
       </c>
-      <c r="AG38" t="s">
-        <v>348</v>
+      <c r="AJ38" t="s">
+        <v>535</v>
+      </c>
+      <c r="AR38" t="s">
+        <v>508</v>
       </c>
       <c r="BB38">
         <v>1</v>
@@ -9842,33 +9847,22 @@
       <c r="BQ38">
         <v>0.1</v>
       </c>
-      <c r="BT38"/>
+      <c r="BT38" s="17"/>
       <c r="BU38" s="17"/>
       <c r="BV38" s="17"/>
       <c r="BW38" s="17"/>
       <c r="BX38" s="17"/>
       <c r="BY38" s="17"/>
-      <c r="BZ38" t="s">
-        <v>580</v>
-      </c>
-      <c r="CE38" t="s">
-        <v>510</v>
-      </c>
-      <c r="CG38" s="15"/>
-      <c r="CH38" s="15"/>
-      <c r="DB38">
-        <v>1</v>
-      </c>
-      <c r="DE38">
-        <v>1</v>
-      </c>
-      <c r="DF38">
-        <v>1</v>
+      <c r="CL38" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="CP38">
+        <v>0.2</v>
       </c>
     </row>
     <row r="39" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C39" t="s">
         <v>346</v>
@@ -9879,11 +9873,9 @@
       <c r="K39" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="L39" s="15" t="s">
-        <v>582</v>
-      </c>
+      <c r="L39" s="15"/>
       <c r="M39"/>
-      <c r="N39"/>
+      <c r="N39" s="15"/>
       <c r="O39" s="15"/>
       <c r="P39" s="15"/>
       <c r="Q39" s="15"/>
@@ -9900,29 +9892,32 @@
       <c r="AG39" t="s">
         <v>348</v>
       </c>
+      <c r="AW39" s="15"/>
       <c r="BB39">
         <v>1</v>
       </c>
-      <c r="BQ39">
-        <v>0.2</v>
-      </c>
       <c r="BT39"/>
-      <c r="BU39" s="17"/>
-      <c r="BV39" s="17"/>
-      <c r="BW39" s="17"/>
-      <c r="BX39" s="17"/>
-      <c r="BY39" s="17"/>
-      <c r="BZ39" t="s">
-        <v>583</v>
-      </c>
-      <c r="CE39" t="s">
-        <v>510</v>
-      </c>
+      <c r="BU39"/>
+      <c r="BV39"/>
+      <c r="BW39"/>
+      <c r="BX39"/>
+      <c r="BY39"/>
+      <c r="BZ39" s="15"/>
+      <c r="CA39" s="15"/>
+      <c r="CB39" s="15"/>
+      <c r="CC39" s="15"/>
+      <c r="CD39" s="15"/>
+      <c r="CF39" s="15"/>
+      <c r="CG39" s="15"/>
       <c r="CH39" s="15"/>
+      <c r="CI39" s="15"/>
+      <c r="CL39" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="CP39">
+        <v>40</v>
+      </c>
       <c r="DB39">
-        <v>1</v>
-      </c>
-      <c r="DE39">
         <v>1</v>
       </c>
       <c r="DF39">
@@ -9931,36 +9926,24 @@
     </row>
     <row r="40" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="C40" t="s">
         <v>346</v>
       </c>
-      <c r="D40" t="s">
-        <v>560</v>
-      </c>
-      <c r="E40" t="s">
-        <v>561</v>
-      </c>
-      <c r="F40" t="s">
-        <v>562</v>
-      </c>
-      <c r="G40">
-        <v>3</v>
-      </c>
-      <c r="J40" t="s">
-        <v>490</v>
-      </c>
-      <c r="K40" s="15" t="s">
-        <v>491</v>
-      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="K40" s="15"/>
       <c r="L40" s="15"/>
       <c r="M40"/>
       <c r="N40" s="15"/>
       <c r="O40" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="P40" s="16" t="s">
         <v>575</v>
       </c>
-      <c r="P40" s="15"/>
       <c r="Q40" s="15"/>
       <c r="R40" s="15"/>
       <c r="S40" s="15"/>
@@ -9972,74 +9955,38 @@
       <c r="AC40">
         <v>1</v>
       </c>
-      <c r="AO40" t="s">
-        <v>508</v>
-      </c>
-      <c r="AR40" t="s">
-        <v>520</v>
-      </c>
-      <c r="AW40">
-        <v>1</v>
-      </c>
-      <c r="AX40">
-        <v>583</v>
-      </c>
-      <c r="AZ40">
-        <v>2</v>
+      <c r="AT40">
+        <v>20</v>
       </c>
       <c r="BB40">
-        <v>1</v>
-      </c>
-      <c r="BQ40">
-        <v>0.1</v>
-      </c>
-      <c r="BT40" s="17">
-        <v>0</v>
-      </c>
-      <c r="BU40" s="17">
-        <v>1</v>
-      </c>
-      <c r="BV40" s="17">
-        <v>1</v>
-      </c>
-      <c r="BW40" s="17" t="s">
-        <v>585</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="BT40" s="17"/>
+      <c r="BU40" s="17"/>
+      <c r="BV40" s="17"/>
+      <c r="BW40" s="17"/>
       <c r="BX40" s="17"/>
       <c r="BY40" s="17"/>
-      <c r="CE40" t="s">
-        <v>510</v>
-      </c>
-      <c r="CF40" t="s">
-        <v>511</v>
-      </c>
-      <c r="CG40" t="s">
-        <v>475</v>
-      </c>
-      <c r="CL40" t="s">
-        <v>571</v>
-      </c>
-      <c r="CM40">
-        <v>22</v>
-      </c>
-      <c r="CN40">
-        <v>39.6</v>
-      </c>
-      <c r="CP40">
-        <v>10</v>
-      </c>
-      <c r="CW40" t="s">
-        <v>513</v>
-      </c>
-      <c r="DB40">
-        <v>1</v>
+      <c r="CK40" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="41" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="K41" s="15"/>
+      <c r="A41" t="s">
+        <v>578</v>
+      </c>
+      <c r="C41" t="s">
+        <v>346</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>347</v>
+      </c>
       <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="15"/>
+      <c r="M41"/>
+      <c r="N41"/>
       <c r="O41" s="15"/>
       <c r="P41" s="15"/>
       <c r="Q41" s="15"/>
@@ -10050,42 +9997,70 @@
       <c r="V41" s="15"/>
       <c r="W41" s="15"/>
       <c r="X41" s="15"/>
-      <c r="BS41" s="17"/>
-      <c r="BT41" s="17"/>
+      <c r="AC41">
+        <v>1</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB41">
+        <v>1</v>
+      </c>
+      <c r="BQ41">
+        <v>0.1</v>
+      </c>
+      <c r="BT41"/>
       <c r="BU41" s="17"/>
       <c r="BV41" s="17"/>
       <c r="BW41" s="17"/>
       <c r="BX41" s="17"/>
-      <c r="BY41"/>
+      <c r="BY41" s="17"/>
+      <c r="BZ41" t="s">
+        <v>579</v>
+      </c>
+      <c r="CE41" t="s">
+        <v>509</v>
+      </c>
+      <c r="CG41" s="15"/>
+      <c r="CH41" s="15"/>
+      <c r="DB41">
+        <v>1</v>
+      </c>
+      <c r="DE41">
+        <v>1</v>
+      </c>
+      <c r="DF41">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C42" t="s">
         <v>346</v>
       </c>
-      <c r="D42" t="s">
-        <v>587</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="F42" t="s">
-        <v>589</v>
-      </c>
-      <c r="G42">
-        <v>3</v>
-      </c>
-      <c r="J42" t="s">
-        <v>490</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="O42"/>
-      <c r="W42"/>
-      <c r="X42"/>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>581</v>
+      </c>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15"/>
+      <c r="R42" s="15"/>
+      <c r="S42" s="15"/>
+      <c r="T42" s="15"/>
+      <c r="U42" s="15"/>
+      <c r="V42" s="15"/>
+      <c r="W42" s="15"/>
+      <c r="X42" s="15"/>
       <c r="AC42">
         <v>1</v>
       </c>
@@ -10095,166 +10070,236 @@
       <c r="BB42">
         <v>1</v>
       </c>
-      <c r="BM42" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="BN42" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="BR42">
-        <v>1</v>
-      </c>
-      <c r="BT42" s="4">
-        <v>11</v>
-      </c>
-      <c r="BU42" s="4">
-        <v>15</v>
-      </c>
-      <c r="BV42" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW42" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="CL42" s="14" t="s">
-        <v>593</v>
-      </c>
-      <c r="CM42" t="s">
-        <v>622</v>
-      </c>
-      <c r="CP42">
-        <v>25</v>
+      <c r="BQ42">
+        <v>0.2</v>
+      </c>
+      <c r="BT42"/>
+      <c r="BU42" s="17"/>
+      <c r="BV42" s="17"/>
+      <c r="BW42" s="17"/>
+      <c r="BX42" s="17"/>
+      <c r="BY42" s="17"/>
+      <c r="BZ42" t="s">
+        <v>582</v>
+      </c>
+      <c r="CE42" t="s">
+        <v>509</v>
+      </c>
+      <c r="CH42" s="15"/>
+      <c r="DB42">
+        <v>1</v>
+      </c>
+      <c r="DE42">
+        <v>1</v>
+      </c>
+      <c r="DF42">
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>623</v>
+        <v>583</v>
       </c>
       <c r="C43" t="s">
         <v>346</v>
       </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>420</v>
-      </c>
+      <c r="D43" t="s">
+        <v>559</v>
+      </c>
+      <c r="E43" t="s">
+        <v>560</v>
+      </c>
+      <c r="F43" t="s">
+        <v>561</v>
+      </c>
+      <c r="G43">
+        <v>3</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="L43" s="15"/>
       <c r="M43"/>
-      <c r="O43" s="14"/>
-      <c r="P43"/>
-      <c r="Q43"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="P43" s="15"/>
+      <c r="Q43" s="15"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="15"/>
+      <c r="T43" s="15"/>
+      <c r="U43" s="15"/>
+      <c r="V43" s="15"/>
+      <c r="W43" s="15"/>
+      <c r="X43" s="15"/>
       <c r="AC43">
         <v>1</v>
       </c>
-      <c r="AG43" t="s">
-        <v>348</v>
+      <c r="AO43" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="AR43" t="s">
+        <v>519</v>
+      </c>
+      <c r="AW43">
+        <v>1</v>
+      </c>
+      <c r="AX43">
+        <v>583</v>
+      </c>
+      <c r="AZ43">
+        <v>2</v>
       </c>
       <c r="BB43">
         <v>1</v>
       </c>
       <c r="BQ43">
-        <v>0.1</v>
-      </c>
-      <c r="CL43" s="14" t="s">
-        <v>648</v>
+        <v>0.3</v>
+      </c>
+      <c r="BT43" s="17"/>
+      <c r="BU43" s="17"/>
+      <c r="BV43" s="17"/>
+      <c r="BW43" s="17"/>
+      <c r="BX43" s="17"/>
+      <c r="BY43" s="17"/>
+      <c r="CE43" t="s">
+        <v>509</v>
+      </c>
+      <c r="CF43" t="s">
+        <v>510</v>
+      </c>
+      <c r="CG43" t="s">
+        <v>474</v>
+      </c>
+      <c r="CL43" t="s">
+        <v>570</v>
       </c>
       <c r="CM43">
-        <v>-100</v>
+        <v>22</v>
+      </c>
+      <c r="CN43">
+        <v>39.6</v>
       </c>
       <c r="CP43">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="CW43" t="s">
+        <v>512</v>
+      </c>
+      <c r="DB43">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="C44" t="s">
-        <v>346</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="M44"/>
-      <c r="O44" s="14" t="s">
-        <v>593</v>
-      </c>
-      <c r="P44"/>
-      <c r="Q44"/>
-      <c r="AC44">
-        <v>1</v>
-      </c>
-      <c r="AJ44" t="s">
-        <v>536</v>
-      </c>
-      <c r="AR44" t="s">
-        <v>509</v>
-      </c>
-      <c r="BB44">
-        <v>1</v>
-      </c>
-      <c r="CL44" s="14" t="s">
-        <v>594</v>
-      </c>
-      <c r="CP44">
-        <v>1</v>
-      </c>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
+      <c r="O44" s="15"/>
+      <c r="P44" s="15"/>
+      <c r="Q44" s="15"/>
+      <c r="R44" s="15"/>
+      <c r="S44" s="15"/>
+      <c r="T44" s="15"/>
+      <c r="U44" s="15"/>
+      <c r="V44" s="15"/>
+      <c r="W44" s="15"/>
+      <c r="X44" s="15"/>
+      <c r="BS44" s="17"/>
+      <c r="BT44" s="17"/>
+      <c r="BU44" s="17"/>
+      <c r="BV44" s="17"/>
+      <c r="BW44" s="17"/>
+      <c r="BX44" s="17"/>
+      <c r="BY44"/>
     </row>
     <row r="45" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
-        <v>642</v>
+      <c r="A45" t="s">
+        <v>584</v>
       </c>
       <c r="C45" t="s">
         <v>346</v>
       </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-      <c r="O45" s="14" t="s">
-        <v>594</v>
-      </c>
+      <c r="D45" t="s">
+        <v>585</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="F45" t="s">
+        <v>587</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
+      </c>
+      <c r="J45" t="s">
+        <v>489</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="O45"/>
+      <c r="W45"/>
+      <c r="X45"/>
       <c r="AC45">
         <v>1</v>
       </c>
       <c r="AG45" t="s">
         <v>348</v>
       </c>
-      <c r="AV45" t="s">
-        <v>471</v>
-      </c>
-      <c r="AX45">
-        <v>1</v>
-      </c>
-      <c r="AZ45">
-        <v>1</v>
-      </c>
       <c r="BB45">
         <v>1</v>
       </c>
+      <c r="BM45" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="BN45" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="BR45">
+        <v>1</v>
+      </c>
+      <c r="BT45" s="4">
+        <v>11</v>
+      </c>
+      <c r="BU45" s="4">
+        <v>15</v>
+      </c>
+      <c r="BV45" s="4">
+        <v>1</v>
+      </c>
+      <c r="BW45" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="CL45" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="CM45" t="s">
+        <v>620</v>
+      </c>
+      <c r="CP45">
+        <v>25</v>
+      </c>
     </row>
     <row r="46" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
-        <v>643</v>
+      <c r="A46" t="s">
+        <v>621</v>
       </c>
       <c r="C46" t="s">
-        <v>515</v>
+        <v>346</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>624</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="M46"/>
+      <c r="O46" s="14"/>
+      <c r="P46"/>
+      <c r="Q46"/>
       <c r="AC46">
-        <v>1</v>
-      </c>
-      <c r="AF46">
         <v>1</v>
       </c>
       <c r="AG46" t="s">
@@ -10263,253 +10308,200 @@
       <c r="BB46">
         <v>1</v>
       </c>
-      <c r="CJ46" s="3"/>
-      <c r="CS46" t="s">
-        <v>625</v>
-      </c>
-      <c r="DB46">
-        <v>1</v>
-      </c>
-      <c r="DE46">
-        <v>1</v>
-      </c>
-      <c r="DF46">
-        <v>1</v>
+      <c r="BQ46">
+        <v>0.1</v>
+      </c>
+      <c r="CL46" s="14" t="s">
+        <v>646</v>
+      </c>
+      <c r="CM46">
+        <v>-100</v>
+      </c>
+      <c r="CP46">
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ47" s="3"/>
+      <c r="A47" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="C47" t="s">
+        <v>346</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="M47"/>
+      <c r="O47" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="P47"/>
+      <c r="Q47"/>
+      <c r="AC47">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>535</v>
+      </c>
+      <c r="AR47" t="s">
+        <v>508</v>
+      </c>
+      <c r="BB47">
+        <v>1</v>
+      </c>
+      <c r="CL47" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="CP47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="C48" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="C48" t="s">
+        <v>346</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="O48" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="AC48">
+        <v>1</v>
+      </c>
+      <c r="AG48" t="s">
+        <v>348</v>
+      </c>
+      <c r="AV48" t="s">
+        <v>470</v>
+      </c>
+      <c r="AX48">
+        <v>1</v>
+      </c>
+      <c r="AZ48">
+        <v>1</v>
+      </c>
+      <c r="BB48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="C49" t="s">
+        <v>514</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="AC49">
+        <v>1</v>
+      </c>
+      <c r="AF49">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB49">
+        <v>1</v>
+      </c>
+      <c r="CJ49" s="3"/>
+      <c r="CS49" t="s">
+        <v>623</v>
+      </c>
+      <c r="DB49">
+        <v>1</v>
+      </c>
+      <c r="DE49">
+        <v>1</v>
+      </c>
+      <c r="DF49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ50" s="3"/>
+    </row>
+    <row r="51" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="I48">
-        <v>1</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>555</v>
-      </c>
-      <c r="K48" s="3" t="s">
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="K51" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="AC48">
-        <v>1</v>
-      </c>
-      <c r="AJ48" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="AR48" t="s">
-        <v>509</v>
-      </c>
-      <c r="BB48">
-        <v>1</v>
-      </c>
-      <c r="BQ48">
+      <c r="AC51">
+        <v>1</v>
+      </c>
+      <c r="AJ51" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>508</v>
+      </c>
+      <c r="BB51">
+        <v>1</v>
+      </c>
+      <c r="BQ51">
         <v>0.1</v>
       </c>
-      <c r="CJ48" s="3"/>
-      <c r="CS48" s="8" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="49" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ49" s="3"/>
-    </row>
-    <row r="50" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>626</v>
-      </c>
-      <c r="C50" t="s">
-        <v>346</v>
-      </c>
-      <c r="D50" t="s">
-        <v>587</v>
-      </c>
-      <c r="E50" t="s">
-        <v>588</v>
-      </c>
-      <c r="F50" t="s">
-        <v>589</v>
-      </c>
-      <c r="G50">
-        <v>3</v>
-      </c>
-      <c r="J50" t="s">
-        <v>490</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="O50"/>
-      <c r="W50"/>
-      <c r="X50"/>
-      <c r="AC50">
-        <v>1</v>
-      </c>
-      <c r="AG50" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB50">
-        <v>1</v>
-      </c>
-      <c r="BM50" t="s">
-        <v>627</v>
-      </c>
-      <c r="BR50">
-        <v>25</v>
-      </c>
-      <c r="BT50" s="4">
-        <v>1</v>
-      </c>
-      <c r="BU50" s="4">
-        <v>1</v>
-      </c>
-      <c r="BV50" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW50" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="CL50" s="14" t="s">
-        <v>591</v>
-      </c>
-      <c r="CM50" t="s">
-        <v>592</v>
-      </c>
-      <c r="CN50">
-        <v>2</v>
-      </c>
-      <c r="CO50">
-        <v>80</v>
-      </c>
-      <c r="CP50">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>595</v>
-      </c>
-      <c r="C51" t="s">
-        <v>596</v>
-      </c>
-      <c r="O51" s="14" t="s">
-        <v>593</v>
-      </c>
-      <c r="X51"/>
-      <c r="AC51">
-        <v>2</v>
-      </c>
-      <c r="AO51" t="s">
-        <v>496</v>
-      </c>
-      <c r="AR51" t="s">
-        <v>520</v>
-      </c>
-      <c r="AV51" t="s">
-        <v>471</v>
-      </c>
-      <c r="AX51">
-        <v>1</v>
-      </c>
-      <c r="BB51">
-        <v>1</v>
-      </c>
-      <c r="BN51" t="s">
-        <v>597</v>
-      </c>
-      <c r="BZ51" t="s">
-        <v>598</v>
-      </c>
-      <c r="CE51" t="s">
-        <v>510</v>
-      </c>
-      <c r="CW51" t="s">
-        <v>352</v>
+      <c r="CJ51" s="3"/>
+      <c r="CS51" s="8" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="52" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>597</v>
-      </c>
-      <c r="C52" t="s">
-        <v>346</v>
-      </c>
-      <c r="I52">
-        <v>1</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="O52" s="14" t="s">
-        <v>593</v>
-      </c>
-      <c r="P52"/>
-      <c r="Q52"/>
-      <c r="X52"/>
-      <c r="AC52">
-        <v>1</v>
-      </c>
-      <c r="AG52" t="s">
-        <v>348</v>
-      </c>
-      <c r="AH52">
-        <v>1</v>
-      </c>
-      <c r="AO52" t="s">
-        <v>508</v>
-      </c>
-      <c r="AT52">
-        <v>1</v>
-      </c>
-      <c r="AW52">
-        <v>1</v>
-      </c>
-      <c r="AX52">
-        <v>0.5</v>
-      </c>
-      <c r="BB52">
-        <v>1</v>
-      </c>
-      <c r="CF52" t="s">
-        <v>511</v>
-      </c>
-      <c r="CG52" t="s">
-        <v>475</v>
-      </c>
-      <c r="CL52" t="s">
-        <v>512</v>
-      </c>
-      <c r="CM52">
-        <v>22</v>
-      </c>
-      <c r="CP52">
-        <v>10</v>
-      </c>
+      <c r="CJ52" s="3"/>
     </row>
     <row r="53" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="C53" t="s">
-        <v>600</v>
-      </c>
-      <c r="I53">
-        <v>1</v>
+        <v>346</v>
+      </c>
+      <c r="D53" t="s">
+        <v>585</v>
+      </c>
+      <c r="E53" t="s">
+        <v>586</v>
+      </c>
+      <c r="F53" t="s">
+        <v>587</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+      <c r="J53" t="s">
+        <v>489</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="O53" s="14" t="s">
-        <v>593</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="O53"/>
+      <c r="W53"/>
       <c r="X53"/>
       <c r="AC53">
         <v>1</v>
@@ -10520,48 +10512,85 @@
       <c r="BB53">
         <v>1</v>
       </c>
-      <c r="CS53" t="s">
-        <v>628</v>
-      </c>
-      <c r="DB53">
-        <v>1</v>
-      </c>
-      <c r="DE53">
-        <v>1</v>
-      </c>
-      <c r="DF53">
-        <v>1</v>
+      <c r="BM53" t="s">
+        <v>625</v>
+      </c>
+      <c r="BR53">
+        <v>25</v>
+      </c>
+      <c r="BT53" s="4">
+        <v>1</v>
+      </c>
+      <c r="BU53" s="4">
+        <v>1</v>
+      </c>
+      <c r="BV53" s="4">
+        <v>1</v>
+      </c>
+      <c r="BW53" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="CL53" s="14" t="s">
+        <v>589</v>
+      </c>
+      <c r="CM53" t="s">
+        <v>590</v>
+      </c>
+      <c r="CN53">
+        <v>2</v>
+      </c>
+      <c r="CO53">
+        <v>80</v>
+      </c>
+      <c r="CP53">
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>629</v>
+        <v>593</v>
       </c>
       <c r="C54" t="s">
-        <v>630</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>505</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="O54" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="X54"/>
       <c r="AC54">
-        <v>1</v>
-      </c>
-      <c r="AG54" t="s">
-        <v>348</v>
+        <v>2</v>
+      </c>
+      <c r="AO54" t="s">
+        <v>495</v>
+      </c>
+      <c r="AR54" t="s">
+        <v>519</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>470</v>
+      </c>
+      <c r="AX54">
+        <v>1</v>
       </c>
       <c r="BB54">
         <v>1</v>
       </c>
-      <c r="CS54" t="s">
-        <v>631</v>
+      <c r="BN54" t="s">
+        <v>595</v>
+      </c>
+      <c r="BZ54" t="s">
+        <v>596</v>
+      </c>
+      <c r="CE54" t="s">
+        <v>509</v>
+      </c>
+      <c r="CW54" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="55" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>632</v>
+        <v>595</v>
       </c>
       <c r="C55" t="s">
         <v>346</v>
@@ -10572,57 +10601,84 @@
       <c r="K55" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L55" s="3" t="s">
-        <v>505</v>
-      </c>
+      <c r="O55" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="P55"/>
+      <c r="Q55"/>
+      <c r="X55"/>
       <c r="AC55">
         <v>1</v>
       </c>
       <c r="AG55" t="s">
         <v>348</v>
       </c>
+      <c r="AH55">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="s">
+        <v>507</v>
+      </c>
+      <c r="AT55">
+        <v>1</v>
+      </c>
+      <c r="AW55">
+        <v>1</v>
+      </c>
+      <c r="AX55">
+        <v>0.5</v>
+      </c>
       <c r="BB55">
         <v>1</v>
       </c>
+      <c r="CF55" t="s">
+        <v>510</v>
+      </c>
+      <c r="CG55" t="s">
+        <v>474</v>
+      </c>
       <c r="CL55" t="s">
-        <v>633</v>
+        <v>511</v>
+      </c>
+      <c r="CM55">
+        <v>22</v>
       </c>
       <c r="CP55">
-        <v>0.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>634</v>
+        <v>597</v>
       </c>
       <c r="C56" t="s">
-        <v>346</v>
+        <v>598</v>
       </c>
       <c r="I56">
         <v>1</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>420</v>
+        <v>347</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>650</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="O56" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="X56"/>
       <c r="AC56">
         <v>1</v>
       </c>
-      <c r="AJ56" t="s">
-        <v>524</v>
-      </c>
-      <c r="AT56">
-        <v>20</v>
+      <c r="AG56" t="s">
+        <v>348</v>
       </c>
       <c r="BB56">
         <v>1</v>
       </c>
-      <c r="CK56" s="14" t="s">
-        <v>648</v>
-      </c>
-      <c r="CL56" s="14"/>
+      <c r="CS56" t="s">
+        <v>626</v>
+      </c>
       <c r="DB56">
         <v>1</v>
       </c>
@@ -10631,11 +10687,37 @@
       </c>
       <c r="DF56">
         <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>627</v>
+      </c>
+      <c r="C57" t="s">
+        <v>628</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="AC57">
+        <v>1</v>
+      </c>
+      <c r="AG57" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB57">
+        <v>1</v>
+      </c>
+      <c r="CS57" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="58" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="C58" t="s">
         <v>346</v>
@@ -10646,8 +10728,9 @@
       <c r="K58" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="M58"/>
-      <c r="N58"/>
+      <c r="L58" s="3" t="s">
+        <v>504</v>
+      </c>
       <c r="AC58">
         <v>1</v>
       </c>
@@ -10657,31 +10740,16 @@
       <c r="BB58">
         <v>1</v>
       </c>
-      <c r="BQ58">
+      <c r="CL58" t="s">
+        <v>631</v>
+      </c>
+      <c r="CP58">
         <v>0.5</v>
-      </c>
-      <c r="BT58"/>
-      <c r="BZ58" s="20" t="s">
-        <v>654</v>
-      </c>
-      <c r="CE58" t="s">
-        <v>510</v>
-      </c>
-      <c r="CG58" s="3"/>
-      <c r="CH58" s="3"/>
-      <c r="DB58">
-        <v>1</v>
-      </c>
-      <c r="DE58">
-        <v>1</v>
-      </c>
-      <c r="DF58">
-        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>603</v>
+        <v>632</v>
       </c>
       <c r="C59" t="s">
         <v>346</v>
@@ -10690,85 +10758,167 @@
         <v>1</v>
       </c>
       <c r="K59" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="AC59">
+        <v>1</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>523</v>
+      </c>
+      <c r="AT59">
+        <v>20</v>
+      </c>
+      <c r="BB59">
+        <v>1</v>
+      </c>
+      <c r="CK59" s="14" t="s">
+        <v>646</v>
+      </c>
+      <c r="CL59" s="14"/>
+      <c r="DB59">
+        <v>1</v>
+      </c>
+      <c r="DE59">
+        <v>1</v>
+      </c>
+      <c r="DF59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>588</v>
+      </c>
+      <c r="C61" t="s">
+        <v>346</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="K61" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="M59"/>
-      <c r="N59"/>
-      <c r="AC59">
-        <v>1</v>
-      </c>
-      <c r="AG59" t="s">
+      <c r="M61"/>
+      <c r="N61"/>
+      <c r="AC61">
+        <v>1</v>
+      </c>
+      <c r="AG61" t="s">
         <v>348</v>
       </c>
-      <c r="BB59">
-        <v>1</v>
-      </c>
-      <c r="BQ59">
-        <v>1</v>
-      </c>
-      <c r="BT59"/>
-      <c r="BZ59" s="20" t="s">
-        <v>646</v>
-      </c>
-      <c r="CE59" t="s">
-        <v>510</v>
-      </c>
-      <c r="CH59" s="3"/>
-      <c r="DB59">
-        <v>1</v>
-      </c>
-      <c r="DE59">
-        <v>1</v>
-      </c>
-      <c r="DF59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>602</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="BB61">
+        <v>1</v>
+      </c>
+      <c r="BQ61">
+        <v>0.5</v>
+      </c>
+      <c r="BT61"/>
+      <c r="BZ61" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="CE61" t="s">
+        <v>509</v>
+      </c>
+      <c r="CG61" s="3"/>
+      <c r="CH61" s="3"/>
+      <c r="DB61">
+        <v>1</v>
+      </c>
+      <c r="DE61">
+        <v>1</v>
+      </c>
+      <c r="DF61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>601</v>
+      </c>
+      <c r="C62" t="s">
         <v>346</v>
       </c>
-      <c r="I60">
-        <v>1</v>
-      </c>
-      <c r="K60" s="3" t="s">
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="K62" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="O60"/>
-      <c r="X60"/>
-      <c r="AC60">
-        <v>1</v>
-      </c>
-      <c r="AG60" t="s">
+      <c r="L62" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="M62"/>
+      <c r="N62"/>
+      <c r="AC62">
+        <v>1</v>
+      </c>
+      <c r="AG62" t="s">
         <v>348</v>
       </c>
-      <c r="BB60">
-        <v>1</v>
-      </c>
-      <c r="CK60" s="14" t="s">
-        <v>635</v>
+      <c r="BB62">
+        <v>1</v>
+      </c>
+      <c r="BQ62">
+        <v>1</v>
+      </c>
+      <c r="BT62"/>
+      <c r="BZ62" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="CE62" t="s">
+        <v>509</v>
+      </c>
+      <c r="CH62" s="3"/>
+      <c r="DB62">
+        <v>1</v>
+      </c>
+      <c r="DE62">
+        <v>1</v>
+      </c>
+      <c r="DF62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ63" s="3"/>
-    </row>
-    <row r="64" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ64" s="3"/>
-    </row>
-    <row r="70" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ70" s="3"/>
-    </row>
-    <row r="71" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ71" s="3"/>
+      <c r="A63" t="s">
+        <v>600</v>
+      </c>
+      <c r="C63" t="s">
+        <v>346</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="O63"/>
+      <c r="X63"/>
+      <c r="AC63">
+        <v>1</v>
+      </c>
+      <c r="AG63" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB63">
+        <v>1</v>
+      </c>
+      <c r="CK63" s="14" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="66" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ66" s="3"/>
+    </row>
+    <row r="67" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ67" s="3"/>
     </row>
     <row r="73" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ73" s="3"/>
@@ -10776,70 +10926,67 @@
     <row r="74" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ74" s="3"/>
     </row>
-    <row r="75" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ75" s="3"/>
-    </row>
     <row r="76" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ76" s="3"/>
     </row>
     <row r="77" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT77"/>
+      <c r="CJ77" s="3"/>
     </row>
     <row r="78" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT78"/>
+      <c r="CJ78" s="3"/>
     </row>
     <row r="79" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT79"/>
       <c r="CJ79" s="3"/>
     </row>
     <row r="80" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ80" s="3"/>
+      <c r="BT80"/>
     </row>
     <row r="81" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ81" s="3"/>
+      <c r="BT81"/>
     </row>
     <row r="82" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT82"/>
+      <c r="CJ82" s="3"/>
     </row>
     <row r="83" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ83" s="3"/>
     </row>
-    <row r="87" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT87"/>
-    </row>
-    <row r="88" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ88" s="3"/>
-    </row>
-    <row r="96" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ96" s="3"/>
-    </row>
-    <row r="97" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ97" s="3"/>
-    </row>
-    <row r="98" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT98"/>
-    </row>
-    <row r="103" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT103"/>
-    </row>
-    <row r="104" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT104"/>
-      <c r="CJ104" s="3"/>
-    </row>
-    <row r="105" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ105" s="3"/>
+    <row r="84" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ84" s="3"/>
+    </row>
+    <row r="85" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT85"/>
+    </row>
+    <row r="86" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ86" s="3"/>
+    </row>
+    <row r="90" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT90"/>
+    </row>
+    <row r="91" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ91" s="3"/>
+    </row>
+    <row r="99" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ99" s="3"/>
+    </row>
+    <row r="100" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ100" s="3"/>
+    </row>
+    <row r="101" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT101"/>
     </row>
     <row r="106" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ106" s="3"/>
+      <c r="BT106"/>
     </row>
     <row r="107" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT107"/>
       <c r="CJ107" s="3"/>
     </row>
     <row r="108" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ108" s="3"/>
     </row>
     <row r="109" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT109"/>
+      <c r="CJ109" s="3"/>
     </row>
     <row r="110" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ110" s="3"/>
@@ -10848,13 +10995,13 @@
       <c r="CJ111" s="3"/>
     </row>
     <row r="112" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ112" s="3"/>
+      <c r="BT112"/>
     </row>
     <row r="113" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ113" s="3"/>
     </row>
     <row r="114" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT114"/>
+      <c r="CJ114" s="3"/>
     </row>
     <row r="115" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ115" s="3"/>
@@ -10863,71 +11010,74 @@
       <c r="CJ116" s="3"/>
     </row>
     <row r="117" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ117" s="3"/>
+      <c r="BT117"/>
     </row>
     <row r="118" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ118" s="3"/>
     </row>
+    <row r="119" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ119" s="3"/>
+    </row>
+    <row r="120" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ120" s="3"/>
+    </row>
     <row r="121" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ121" s="3"/>
     </row>
-    <row r="122" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ122" s="3"/>
-    </row>
-    <row r="123" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ123" s="3"/>
-    </row>
     <row r="124" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ124" s="3"/>
     </row>
     <row r="125" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ125" s="3"/>
     </row>
+    <row r="126" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ126" s="3"/>
+    </row>
     <row r="127" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT127"/>
+      <c r="CJ127" s="3"/>
     </row>
     <row r="128" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ128" s="3"/>
     </row>
-    <row r="129" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ129" s="3"/>
-    </row>
     <row r="130" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ130" s="3"/>
+      <c r="BT130"/>
     </row>
     <row r="131" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ131" s="3"/>
     </row>
-    <row r="135" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ135" s="3"/>
-    </row>
-    <row r="137" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT137"/>
+    <row r="132" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ132" s="3"/>
+    </row>
+    <row r="133" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ133" s="3"/>
+    </row>
+    <row r="134" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ134" s="3"/>
     </row>
     <row r="138" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT138"/>
       <c r="CJ138" s="3"/>
     </row>
-    <row r="139" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ139" s="3"/>
-    </row>
     <row r="140" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ140" s="3"/>
+      <c r="BT140"/>
     </row>
     <row r="141" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT141"/>
       <c r="CJ141" s="3"/>
     </row>
     <row r="142" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ142" s="3"/>
     </row>
+    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ143" s="3"/>
+    </row>
     <row r="144" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT144"/>
+      <c r="CJ144" s="3"/>
     </row>
     <row r="145" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ145" s="3"/>
     </row>
-    <row r="146" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ146" s="3"/>
+    <row r="147" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT147"/>
     </row>
     <row r="148" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ148" s="3"/>
@@ -10936,31 +11086,31 @@
       <c r="CJ149" s="3"/>
     </row>
     <row r="151" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT151"/>
+      <c r="CJ151" s="3"/>
     </row>
     <row r="152" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ152" s="3"/>
     </row>
+    <row r="154" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT154"/>
+    </row>
     <row r="155" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ155" s="3"/>
     </row>
-    <row r="156" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ156" s="3"/>
+    <row r="158" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ158" s="3"/>
     </row>
     <row r="159" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ159" s="3"/>
     </row>
-    <row r="161" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ161" s="3"/>
-    </row>
-    <row r="163" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT163"/>
+    <row r="162" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ162" s="3"/>
     </row>
     <row r="164" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ164" s="3"/>
     </row>
-    <row r="165" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ165" s="3"/>
+    <row r="166" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT166"/>
     </row>
     <row r="167" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ167" s="3"/>
@@ -10968,29 +11118,29 @@
     <row r="168" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ168" s="3"/>
     </row>
-    <row r="169" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ169" s="3"/>
-    </row>
-    <row r="174" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ174" s="3"/>
-    </row>
-    <row r="175" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ175" s="3"/>
+    <row r="170" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ170" s="3"/>
+    </row>
+    <row r="171" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ171" s="3"/>
+    </row>
+    <row r="172" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ172" s="3"/>
+    </row>
+    <row r="177" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ177" s="3"/>
     </row>
     <row r="178" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ178" s="3"/>
     </row>
-    <row r="179" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ179" s="3"/>
-    </row>
-    <row r="183" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ183" s="3"/>
-    </row>
-    <row r="187" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ187" s="3"/>
-    </row>
-    <row r="189" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ189" s="3"/>
+    <row r="181" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ181" s="3"/>
+    </row>
+    <row r="182" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ182" s="3"/>
+    </row>
+    <row r="186" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ186" s="3"/>
     </row>
     <row r="190" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ190" s="3"/>
@@ -11002,125 +11152,125 @@
       <c r="CJ193" s="3"/>
     </row>
     <row r="195" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT195"/>
+      <c r="CJ195" s="3"/>
     </row>
     <row r="196" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT196"/>
       <c r="CJ196" s="3"/>
     </row>
-    <row r="197" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ197" s="3"/>
+    <row r="198" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT198"/>
     </row>
     <row r="199" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT199"/>
       <c r="CJ199" s="3"/>
     </row>
-    <row r="208" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT208"/>
-    </row>
-    <row r="209" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT209"/>
-      <c r="CJ209" s="3"/>
-    </row>
-    <row r="210" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ210" s="3"/>
+    <row r="200" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ200" s="3"/>
+    </row>
+    <row r="202" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ202" s="3"/>
     </row>
     <row r="211" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ211" s="3"/>
+      <c r="BT211"/>
     </row>
     <row r="212" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT212"/>
+      <c r="CJ212" s="3"/>
     </row>
     <row r="213" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT213"/>
       <c r="CJ213" s="3"/>
     </row>
     <row r="214" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ214" s="3"/>
     </row>
+    <row r="215" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT215"/>
+    </row>
     <row r="216" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT216"/>
+      <c r="CJ216" s="3"/>
     </row>
     <row r="217" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT217"/>
       <c r="CJ217" s="3"/>
     </row>
-    <row r="218" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ218" s="3"/>
+    <row r="219" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT219"/>
     </row>
     <row r="220" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT220"/>
+      <c r="CJ220" s="3"/>
     </row>
     <row r="221" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ221" s="3"/>
     </row>
+    <row r="223" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT223"/>
+    </row>
     <row r="224" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ224" s="3"/>
     </row>
-    <row r="228" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ228" s="3"/>
-    </row>
-    <row r="230" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT230"/>
+    <row r="227" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ227" s="3"/>
     </row>
     <row r="231" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ231" s="3"/>
     </row>
-    <row r="238" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT238"/>
-    </row>
-    <row r="239" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ239" s="3"/>
-    </row>
-    <row r="240" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ240" s="3"/>
+    <row r="233" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT233"/>
+    </row>
+    <row r="234" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ234" s="3"/>
+    </row>
+    <row r="241" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT241"/>
     </row>
     <row r="242" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT242"/>
+      <c r="CJ242" s="3"/>
     </row>
     <row r="243" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT243"/>
       <c r="CJ243" s="3"/>
     </row>
-    <row r="244" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ244" s="3"/>
-    </row>
-    <row r="250" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT250"/>
-    </row>
-    <row r="251" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT251"/>
-      <c r="CJ251" s="3"/>
-    </row>
-    <row r="252" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT252"/>
-      <c r="CJ252" s="3"/>
+    <row r="245" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT245"/>
+    </row>
+    <row r="246" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT246"/>
+      <c r="CJ246" s="3"/>
+    </row>
+    <row r="247" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ247" s="3"/>
     </row>
     <row r="253" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ253" s="3"/>
-    </row>
-    <row r="258" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT258"/>
-    </row>
-    <row r="259" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT259"/>
-    </row>
-    <row r="263" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT263"/>
-    </row>
-    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ264" s="3"/>
-    </row>
-    <row r="265" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT265"/>
+      <c r="BT253"/>
+    </row>
+    <row r="254" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT254"/>
+      <c r="CJ254" s="3"/>
+    </row>
+    <row r="255" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT255"/>
+      <c r="CJ255" s="3"/>
+    </row>
+    <row r="256" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ256" s="3"/>
+    </row>
+    <row r="261" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT261"/>
+    </row>
+    <row r="262" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT262"/>
     </row>
     <row r="266" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ266" s="3"/>
-    </row>
-    <row r="276" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT276"/>
-    </row>
-    <row r="277" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ277" s="3"/>
+      <c r="BT266"/>
+    </row>
+    <row r="267" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ267" s="3"/>
+    </row>
+    <row r="268" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT268"/>
+    </row>
+    <row r="269" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ269" s="3"/>
     </row>
     <row r="279" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT279"/>
@@ -11128,17 +11278,17 @@
     <row r="280" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ280" s="3"/>
     </row>
-    <row r="288" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT288"/>
-    </row>
-    <row r="289" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ289" s="3"/>
-    </row>
-    <row r="293" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT293"/>
-    </row>
-    <row r="294" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ294" s="3"/>
+    <row r="282" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT282"/>
+    </row>
+    <row r="283" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ283" s="3"/>
+    </row>
+    <row r="291" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT291"/>
+    </row>
+    <row r="292" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ292" s="3"/>
     </row>
     <row r="296" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT296"/>
@@ -11146,72 +11296,69 @@
     <row r="297" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ297" s="3"/>
     </row>
-    <row r="313" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT313"/>
-    </row>
-    <row r="314" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT314"/>
-      <c r="CJ314" s="3"/>
-    </row>
-    <row r="315" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT315"/>
-      <c r="CJ315" s="3"/>
+    <row r="299" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT299"/>
+    </row>
+    <row r="300" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ300" s="3"/>
     </row>
     <row r="316" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT316"/>
-      <c r="CJ316" s="3"/>
     </row>
     <row r="317" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT317"/>
+      <c r="CJ317" s="3"/>
+    </row>
+    <row r="318" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT318"/>
+      <c r="CJ318" s="3"/>
     </row>
     <row r="319" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT319"/>
+      <c r="CJ319" s="3"/>
     </row>
     <row r="320" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT320"/>
-      <c r="CJ320" s="3"/>
-    </row>
-    <row r="321" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT321"/>
-      <c r="CJ321" s="3"/>
     </row>
     <row r="322" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ322" s="3"/>
-    </row>
-    <row r="326" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT326"/>
-    </row>
-    <row r="327" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ327" s="3"/>
+      <c r="BT322"/>
+    </row>
+    <row r="323" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT323"/>
+      <c r="CJ323" s="3"/>
+    </row>
+    <row r="324" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT324"/>
+      <c r="CJ324" s="3"/>
+    </row>
+    <row r="325" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ325" s="3"/>
     </row>
     <row r="329" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT329"/>
     </row>
     <row r="330" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT330"/>
       <c r="CJ330" s="3"/>
     </row>
-    <row r="331" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT331"/>
-      <c r="CJ331" s="3"/>
-    </row>
     <row r="332" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ332" s="3"/>
-    </row>
-    <row r="348" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT348"/>
-    </row>
-    <row r="349" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ349" s="3"/>
-    </row>
-    <row r="357" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ357" s="3"/>
-    </row>
-    <row r="358" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ358" s="3"/>
-    </row>
-    <row r="359" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ359" s="3"/>
+      <c r="BT332"/>
+    </row>
+    <row r="333" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT333"/>
+      <c r="CJ333" s="3"/>
+    </row>
+    <row r="334" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT334"/>
+      <c r="CJ334" s="3"/>
+    </row>
+    <row r="335" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ335" s="3"/>
+    </row>
+    <row r="351" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT351"/>
+    </row>
+    <row r="352" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ352" s="3"/>
     </row>
     <row r="360" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ360" s="3"/>
@@ -11219,54 +11366,54 @@
     <row r="361" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ361" s="3"/>
     </row>
+    <row r="362" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ362" s="3"/>
+    </row>
     <row r="363" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT363"/>
+      <c r="CJ363" s="3"/>
     </row>
     <row r="364" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ364" s="3"/>
     </row>
-    <row r="365" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT365"/>
-    </row>
     <row r="366" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT366"/>
-      <c r="CJ366" s="3"/>
     </row>
     <row r="367" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ367" s="3"/>
     </row>
+    <row r="368" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT368"/>
+    </row>
     <row r="369" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT369"/>
+      <c r="CJ369" s="3"/>
     </row>
     <row r="370" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT370"/>
       <c r="CJ370" s="3"/>
     </row>
-    <row r="371" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT371"/>
-      <c r="CJ371" s="3"/>
-    </row>
     <row r="372" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ372" s="3"/>
+      <c r="BT372"/>
+    </row>
+    <row r="373" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT373"/>
+      <c r="CJ373" s="3"/>
     </row>
     <row r="374" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT374"/>
       <c r="CJ374" s="3"/>
     </row>
-    <row r="376" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ376" s="3"/>
-    </row>
-    <row r="378" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ378" s="3"/>
+    <row r="375" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ375" s="3"/>
+    </row>
+    <row r="377" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ377" s="3"/>
+    </row>
+    <row r="379" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ379" s="3"/>
     </row>
     <row r="381" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ381" s="3"/>
     </row>
-    <row r="382" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ382" s="3"/>
-    </row>
-    <row r="383" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ383" s="3"/>
-    </row>
     <row r="384" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ384" s="3"/>
     </row>
@@ -11277,50 +11424,53 @@
       <c r="CJ386" s="3"/>
     </row>
     <row r="387" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT387"/>
+      <c r="CJ387" s="3"/>
     </row>
     <row r="388" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT388"/>
       <c r="CJ388" s="3"/>
     </row>
     <row r="389" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT389"/>
       <c r="CJ389" s="3"/>
     </row>
     <row r="390" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ390" s="3"/>
+      <c r="BT390"/>
     </row>
     <row r="391" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT391"/>
       <c r="CJ391" s="3"/>
     </row>
     <row r="392" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT392"/>
       <c r="CJ392" s="3"/>
     </row>
     <row r="393" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ393" s="3"/>
     </row>
+    <row r="394" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ394" s="3"/>
+    </row>
     <row r="395" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ395" s="3"/>
     </row>
     <row r="396" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ396" s="3"/>
     </row>
-    <row r="397" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT397"/>
-    </row>
     <row r="398" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT398"/>
       <c r="CJ398" s="3"/>
     </row>
     <row r="399" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT399"/>
       <c r="CJ399" s="3"/>
     </row>
     <row r="400" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ400" s="3"/>
+      <c r="BT400"/>
     </row>
     <row r="401" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT401"/>
       <c r="CJ401" s="3"/>
+    </row>
+    <row r="402" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT402"/>
+      <c r="CJ402" s="3"/>
     </row>
     <row r="403" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ403" s="3"/>
@@ -11328,81 +11478,81 @@
     <row r="404" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ404" s="3"/>
     </row>
-    <row r="405" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT405"/>
-      <c r="CJ405" s="3"/>
-    </row>
     <row r="406" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT406"/>
       <c r="CJ406" s="3"/>
     </row>
     <row r="407" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ407" s="3"/>
     </row>
     <row r="408" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT408"/>
       <c r="CJ408" s="3"/>
     </row>
     <row r="409" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT409"/>
       <c r="CJ409" s="3"/>
     </row>
+    <row r="410" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ410" s="3"/>
+    </row>
     <row r="411" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT411"/>
       <c r="CJ411" s="3"/>
     </row>
     <row r="412" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ412" s="3"/>
     </row>
-    <row r="413" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ413" s="3"/>
+    <row r="414" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT414"/>
+      <c r="CJ414" s="3"/>
     </row>
     <row r="415" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT415"/>
       <c r="CJ415" s="3"/>
     </row>
     <row r="416" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT416"/>
       <c r="CJ416" s="3"/>
     </row>
-    <row r="417" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ417" s="3"/>
+    <row r="418" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT418"/>
+      <c r="CJ418" s="3"/>
     </row>
     <row r="419" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT419"/>
       <c r="CJ419" s="3"/>
     </row>
-    <row r="421" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ421" s="3"/>
+    <row r="420" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ420" s="3"/>
+    </row>
+    <row r="422" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ422" s="3"/>
     </row>
     <row r="424" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ424" s="3"/>
     </row>
-    <row r="425" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ425" s="3"/>
-    </row>
-    <row r="429" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT429"/>
-    </row>
-    <row r="430" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT430"/>
-      <c r="CJ430" s="3"/>
-    </row>
-    <row r="431" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT431"/>
-      <c r="CJ431" s="3"/>
+    <row r="427" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ427" s="3"/>
+    </row>
+    <row r="428" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ428" s="3"/>
     </row>
     <row r="432" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ432" s="3"/>
+      <c r="BT432"/>
     </row>
     <row r="433" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT433"/>
       <c r="CJ433" s="3"/>
     </row>
     <row r="434" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT434"/>
+      <c r="CJ434" s="3"/>
     </row>
     <row r="435" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ435" s="3"/>
     </row>
+    <row r="436" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ436" s="3"/>
+    </row>
     <row r="437" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ437" s="3"/>
+      <c r="BT437"/>
     </row>
     <row r="438" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ438" s="3"/>
@@ -11413,9 +11563,6 @@
     <row r="441" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ441" s="3"/>
     </row>
-    <row r="442" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ442" s="3"/>
-    </row>
     <row r="443" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ443" s="3"/>
     </row>
@@ -11428,83 +11575,80 @@
     <row r="446" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ446" s="3"/>
     </row>
+    <row r="447" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ447" s="3"/>
+    </row>
     <row r="448" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT448"/>
-    </row>
-    <row r="449" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ448" s="3"/>
+    </row>
+    <row r="449" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ449" s="3"/>
     </row>
-    <row r="450" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ450" s="3"/>
-    </row>
-    <row r="483" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS483" s="10"/>
-      <c r="BT483" s="11"/>
-    </row>
-    <row r="484" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H484" s="10"/>
-      <c r="CJ484" s="10"/>
-    </row>
-    <row r="490" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT490"/>
-    </row>
-    <row r="491" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT491"/>
-      <c r="CJ491" s="3"/>
-    </row>
-    <row r="492" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT492"/>
-      <c r="CJ492" s="3"/>
+    <row r="451" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT451"/>
+    </row>
+    <row r="452" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ452" s="3"/>
+    </row>
+    <row r="453" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ453" s="3"/>
+    </row>
+    <row r="486" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS486" s="10"/>
+      <c r="BT486" s="11"/>
+    </row>
+    <row r="487" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H487" s="10"/>
+      <c r="CJ487" s="10"/>
     </row>
     <row r="493" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ493" s="3"/>
-    </row>
-    <row r="510" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT510"/>
-    </row>
-    <row r="511" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ511" s="3"/>
-    </row>
-    <row r="543" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT543"/>
-    </row>
-    <row r="544" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT544"/>
-      <c r="CJ544" s="3"/>
-    </row>
-    <row r="545" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ545" s="3"/>
-    </row>
-    <row r="561" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT561"/>
-    </row>
-    <row r="562" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ562" s="3"/>
-    </row>
-    <row r="568" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT568"/>
-    </row>
-    <row r="569" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT569"/>
-      <c r="CJ569" s="3"/>
-    </row>
-    <row r="570" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ570" s="3"/>
-    </row>
-    <row r="575" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT575"/>
-    </row>
-    <row r="576" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT576"/>
-      <c r="CJ576" s="3"/>
-    </row>
-    <row r="577" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT577"/>
-      <c r="CJ577" s="3"/>
+      <c r="BT493"/>
+    </row>
+    <row r="494" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT494"/>
+      <c r="CJ494" s="3"/>
+    </row>
+    <row r="495" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT495"/>
+      <c r="CJ495" s="3"/>
+    </row>
+    <row r="496" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CJ496" s="3"/>
+    </row>
+    <row r="513" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT513"/>
+    </row>
+    <row r="514" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ514" s="3"/>
+    </row>
+    <row r="546" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT546"/>
+    </row>
+    <row r="547" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT547"/>
+      <c r="CJ547" s="3"/>
+    </row>
+    <row r="548" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ548" s="3"/>
+    </row>
+    <row r="564" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT564"/>
+    </row>
+    <row r="565" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ565" s="3"/>
+    </row>
+    <row r="571" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT571"/>
+    </row>
+    <row r="572" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT572"/>
+      <c r="CJ572" s="3"/>
+    </row>
+    <row r="573" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ573" s="3"/>
     </row>
     <row r="578" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT578"/>
-      <c r="CJ578" s="3"/>
     </row>
     <row r="579" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT579"/>
@@ -11555,48 +11699,48 @@
       <c r="CJ590" s="3"/>
     </row>
     <row r="591" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT591"/>
       <c r="CJ591" s="3"/>
     </row>
-    <row r="595" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT595"/>
-    </row>
-    <row r="596" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT596"/>
-      <c r="CJ596" s="3"/>
-    </row>
-    <row r="597" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ597" s="3"/>
+    <row r="592" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT592"/>
+      <c r="CJ592" s="3"/>
+    </row>
+    <row r="593" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT593"/>
+      <c r="CJ593" s="3"/>
+    </row>
+    <row r="594" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ594" s="3"/>
     </row>
     <row r="598" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT598"/>
     </row>
     <row r="599" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT599"/>
       <c r="CJ599" s="3"/>
     </row>
+    <row r="600" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ600" s="3"/>
+    </row>
+    <row r="601" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT601"/>
+    </row>
     <row r="602" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT602"/>
-    </row>
-    <row r="603" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT603"/>
-      <c r="CJ603" s="3"/>
-    </row>
-    <row r="604" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ604" s="3"/>
-    </row>
-    <row r="635" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT635"/>
-    </row>
-    <row r="636" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT636"/>
-      <c r="CJ636" s="3"/>
-    </row>
-    <row r="637" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT637"/>
-      <c r="CJ637" s="3"/>
+      <c r="CJ602" s="3"/>
+    </row>
+    <row r="605" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT605"/>
+    </row>
+    <row r="606" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT606"/>
+      <c r="CJ606" s="3"/>
+    </row>
+    <row r="607" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ607" s="3"/>
     </row>
     <row r="638" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT638"/>
-      <c r="CJ638" s="3"/>
     </row>
     <row r="639" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT639"/>
@@ -11615,85 +11759,87 @@
       <c r="CJ642" s="3"/>
     </row>
     <row r="643" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT643"/>
       <c r="CJ643" s="3"/>
+    </row>
+    <row r="644" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT644"/>
+      <c r="CJ644" s="3"/>
     </row>
     <row r="645" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT645"/>
+      <c r="CJ645" s="3"/>
     </row>
     <row r="646" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ646" s="3"/>
     </row>
-    <row r="650" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT650"/>
-    </row>
-    <row r="651" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ651" s="3"/>
+    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT648"/>
+    </row>
+    <row r="649" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ649" s="3"/>
+    </row>
+    <row r="653" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT653"/>
     </row>
     <row r="654" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT654"/>
-    </row>
-    <row r="655" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT655"/>
-      <c r="CJ655" s="3"/>
-    </row>
-    <row r="656" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT656"/>
-      <c r="CJ656" s="3"/>
+      <c r="CJ654" s="3"/>
     </row>
     <row r="657" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT657"/>
-      <c r="CJ657" s="3"/>
     </row>
     <row r="658" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT658"/>
       <c r="CJ658" s="3"/>
     </row>
-    <row r="665" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT665"/>
-    </row>
-    <row r="666" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ666" s="3"/>
+    <row r="659" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT659"/>
+      <c r="CJ659" s="3"/>
+    </row>
+    <row r="660" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT660"/>
+      <c r="CJ660" s="3"/>
+    </row>
+    <row r="661" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ661" s="3"/>
+    </row>
+    <row r="668" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT668"/>
     </row>
     <row r="669" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT669"/>
-    </row>
-    <row r="670" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT670"/>
-      <c r="CJ670" s="3"/>
-    </row>
-    <row r="671" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT671"/>
-      <c r="CJ671" s="3"/>
+      <c r="CJ669" s="3"/>
     </row>
     <row r="672" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT672"/>
-      <c r="CJ672" s="3"/>
     </row>
     <row r="673" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT673"/>
       <c r="CJ673" s="3"/>
+    </row>
+    <row r="674" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT674"/>
+      <c r="CJ674" s="3"/>
     </row>
     <row r="675" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT675"/>
+      <c r="CJ675" s="3"/>
     </row>
     <row r="676" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT676"/>
       <c r="CJ676" s="3"/>
     </row>
-    <row r="677" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ677" s="3"/>
-    </row>
     <row r="678" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ678">
-        <v>0.15</v>
-      </c>
+      <c r="BT678"/>
+    </row>
+    <row r="679" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT679"/>
+      <c r="CJ679" s="3"/>
     </row>
     <row r="680" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ680">
-        <v>0.2</v>
-      </c>
+      <c r="CJ680" s="3"/>
     </row>
     <row r="681" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ681">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="683" spans="72:88" x14ac:dyDescent="0.25">
@@ -11701,50 +11847,48 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="690" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ690">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="692" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ692">
-        <v>0.4</v>
+    <row r="684" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ684">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="686" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ686">
+        <v>0.2</v>
       </c>
     </row>
     <row r="693" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ693">
-        <v>0.6</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="695" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ695">
+        <v>0.4</v>
       </c>
     </row>
     <row r="696" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ696">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="699" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ699">
         <v>0.5</v>
       </c>
     </row>
-    <row r="697" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ697">
+    <row r="700" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ700">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="698" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ698">
+    <row r="701" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ701">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="701" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT701"/>
-    </row>
-    <row r="702" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT702"/>
-      <c r="CJ702" s="3"/>
-    </row>
-    <row r="703" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT703"/>
-      <c r="CJ703" s="3"/>
     </row>
     <row r="704" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT704"/>
-      <c r="CJ704" s="3"/>
     </row>
     <row r="705" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT705"/>
@@ -11767,28 +11911,28 @@
       <c r="CJ709" s="3"/>
     </row>
     <row r="710" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT710"/>
       <c r="CJ710" s="3"/>
     </row>
     <row r="711" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT711"/>
+      <c r="CJ711" s="3"/>
     </row>
     <row r="712" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT712"/>
       <c r="CJ712" s="3"/>
     </row>
-    <row r="721" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT721"/>
-    </row>
-    <row r="722" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT722"/>
-      <c r="CJ722" s="3"/>
-    </row>
-    <row r="723" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT723"/>
-      <c r="CJ723" s="3"/>
+    <row r="713" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ713" s="3"/>
+    </row>
+    <row r="714" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT714"/>
+    </row>
+    <row r="715" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ715" s="3"/>
     </row>
     <row r="724" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT724"/>
-      <c r="CJ724" s="3"/>
     </row>
     <row r="725" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT725"/>
@@ -11807,23 +11951,25 @@
       <c r="CJ728" s="3"/>
     </row>
     <row r="729" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT729"/>
       <c r="CJ729" s="3"/>
     </row>
     <row r="730" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT730"/>
+      <c r="CJ730" s="3"/>
     </row>
     <row r="731" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT731"/>
       <c r="CJ731" s="3"/>
     </row>
-    <row r="736" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT736"/>
-    </row>
-    <row r="737" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT737"/>
-      <c r="CJ737" s="3"/>
-    </row>
-    <row r="738" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ738" s="3"/>
+    <row r="732" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ732" s="3"/>
+    </row>
+    <row r="733" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT733"/>
+    </row>
+    <row r="734" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ734" s="3"/>
     </row>
     <row r="739" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT739"/>
@@ -11843,152 +11989,150 @@
       <c r="CJ743" s="3"/>
     </row>
     <row r="744" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT744"/>
       <c r="CJ744" s="3"/>
     </row>
     <row r="745" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT745"/>
-      <c r="CJ745" s="3"/>
     </row>
     <row r="746" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT746"/>
       <c r="CJ746" s="3"/>
     </row>
-    <row r="750" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT750"/>
-    </row>
-    <row r="751" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT751"/>
-      <c r="CJ751" s="3"/>
-    </row>
-    <row r="752" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT752"/>
-      <c r="CJ752" s="3"/>
+    <row r="747" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT747"/>
+      <c r="CJ747" s="3"/>
+    </row>
+    <row r="748" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT748"/>
+      <c r="CJ748" s="3"/>
+    </row>
+    <row r="749" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ749" s="3"/>
     </row>
     <row r="753" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ753" s="3"/>
+      <c r="BT753"/>
     </row>
     <row r="754" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT754"/>
+      <c r="CJ754" s="3"/>
     </row>
     <row r="755" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT755"/>
       <c r="CJ755" s="3"/>
     </row>
     <row r="756" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS756" s="10"/>
-      <c r="BT756" s="11"/>
+      <c r="CJ756" s="3"/>
     </row>
     <row r="757" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H757" s="10"/>
-      <c r="CJ757" s="10"/>
-    </row>
-    <row r="774" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT774"/>
-    </row>
-    <row r="775" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT775"/>
-      <c r="CJ775" s="3"/>
-    </row>
-    <row r="776" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT776"/>
-      <c r="CJ776" s="3"/>
-    </row>
-    <row r="777" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT757"/>
+    </row>
+    <row r="758" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CJ758" s="3"/>
+    </row>
+    <row r="759" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS759" s="10"/>
+      <c r="BT759" s="11"/>
+    </row>
+    <row r="760" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H760" s="10"/>
+      <c r="CJ760" s="10"/>
+    </row>
+    <row r="777" spans="71:88" x14ac:dyDescent="0.25">
       <c r="BT777"/>
-      <c r="CJ777" s="3"/>
-    </row>
-    <row r="778" spans="8:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="778" spans="71:88" x14ac:dyDescent="0.25">
+      <c r="BT778"/>
       <c r="CJ778" s="3"/>
     </row>
-    <row r="779" spans="8:88" x14ac:dyDescent="0.25">
+    <row r="779" spans="71:88" x14ac:dyDescent="0.25">
       <c r="BT779"/>
-    </row>
-    <row r="780" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CJ779" s="3"/>
+    </row>
+    <row r="780" spans="71:88" x14ac:dyDescent="0.25">
       <c r="BT780"/>
       <c r="CJ780" s="3"/>
     </row>
-    <row r="781" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS781" s="10"/>
-      <c r="BT781" s="11"/>
+    <row r="781" spans="71:88" x14ac:dyDescent="0.25">
       <c r="CJ781" s="3"/>
     </row>
-    <row r="782" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H782" s="10"/>
-      <c r="CJ782" s="10"/>
-    </row>
-    <row r="785" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT785"/>
-    </row>
-    <row r="786" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT786"/>
-      <c r="CJ786" s="3"/>
-    </row>
-    <row r="787" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT787"/>
-      <c r="CJ787" s="3"/>
-    </row>
-    <row r="788" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="782" spans="71:88" x14ac:dyDescent="0.25">
+      <c r="BT782"/>
+    </row>
+    <row r="783" spans="71:88" x14ac:dyDescent="0.25">
+      <c r="BT783"/>
+      <c r="CJ783" s="3"/>
+    </row>
+    <row r="784" spans="71:88" x14ac:dyDescent="0.25">
+      <c r="BS784" s="10"/>
+      <c r="BT784" s="11"/>
+      <c r="CJ784" s="3"/>
+    </row>
+    <row r="785" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H785" s="10"/>
+      <c r="CJ785" s="10"/>
+    </row>
+    <row r="788" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT788"/>
-      <c r="CJ788" s="3"/>
-    </row>
-    <row r="789" spans="72:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="789" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT789"/>
       <c r="CJ789" s="3"/>
     </row>
-    <row r="790" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="790" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT790"/>
       <c r="CJ790" s="3"/>
     </row>
-    <row r="791" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="791" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT791"/>
       <c r="CJ791" s="3"/>
     </row>
-    <row r="792" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="792" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT792"/>
       <c r="CJ792" s="3"/>
     </row>
-    <row r="793" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="793" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT793"/>
       <c r="CJ793" s="3"/>
     </row>
-    <row r="795" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="794" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT794"/>
+      <c r="CJ794" s="3"/>
+    </row>
+    <row r="795" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT795"/>
-    </row>
-    <row r="796" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT796"/>
+      <c r="CJ795" s="3"/>
+    </row>
+    <row r="796" spans="8:88" x14ac:dyDescent="0.25">
       <c r="CJ796" s="3"/>
     </row>
-    <row r="797" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT797"/>
-      <c r="CJ797" s="3"/>
-    </row>
-    <row r="798" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="798" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT798"/>
-      <c r="CJ798" s="3"/>
-    </row>
-    <row r="799" spans="72:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="799" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT799"/>
       <c r="CJ799" s="3"/>
     </row>
-    <row r="800" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="800" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT800"/>
       <c r="CJ800" s="3"/>
     </row>
     <row r="801" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT801"/>
       <c r="CJ801" s="3"/>
     </row>
     <row r="802" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT802"/>
+      <c r="CJ802" s="3"/>
     </row>
     <row r="803" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT803"/>
       <c r="CJ803" s="3"/>
     </row>
     <row r="804" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT804"/>
       <c r="CJ804" s="3"/>
     </row>
     <row r="805" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT805"/>
-      <c r="CJ805" s="3"/>
     </row>
     <row r="806" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT806"/>
@@ -12095,21 +12239,33 @@
       <c r="CJ831" s="3"/>
     </row>
     <row r="832" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT832"/>
       <c r="CJ832" s="3"/>
     </row>
     <row r="833" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT833"/>
+      <c r="CJ833" s="3"/>
     </row>
     <row r="834" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT834"/>
       <c r="CJ834" s="3"/>
     </row>
     <row r="835" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT835"/>
       <c r="CJ835" s="3"/>
     </row>
     <row r="836" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ836" s="3"/>
+      <c r="BT836"/>
+    </row>
+    <row r="837" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT837"/>
+      <c r="CJ837" s="3"/>
+    </row>
+    <row r="838" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT838"/>
+      <c r="CJ838" s="3"/>
+    </row>
+    <row r="839" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ839" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -12268,92 +12424,92 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C4" t="s">
+        <v>539</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>540</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="P4" t="s">
         <v>541</v>
-      </c>
-      <c r="P4" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C5" t="s">
+        <v>542</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
         <v>543</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="P5" t="s">
         <v>544</v>
-      </c>
-      <c r="P5" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H6" s="14">
         <v>1</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>546</v>
+      </c>
+      <c r="C7" t="s">
         <v>547</v>
       </c>
-      <c r="C7" t="s">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="P7" t="s">
         <v>548</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="P7" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>549</v>
+      </c>
+      <c r="C8" t="s">
+        <v>547</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
         <v>550</v>
-      </c>
-      <c r="C8" t="s">
-        <v>548</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H9" s="14">
         <v>1</v>
@@ -12362,24 +12518,24 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H11" s="14">
         <v>1</v>
@@ -12388,10 +12544,10 @@
     </row>
     <row r="12" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H12" s="14">
         <v>1</v>
@@ -12400,103 +12556,103 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C13" t="s">
         <v>200</v>
       </c>
       <c r="P13" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H14" s="14">
         <v>1</v>
       </c>
       <c r="J14"/>
       <c r="P14" s="14" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C15" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="P15" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C16" t="s">
+        <v>542</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
         <v>543</v>
       </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="P16" t="s">
         <v>544</v>
-      </c>
-      <c r="P16" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="J17" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H18" s="14">
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C19" t="s">
         <v>200</v>
       </c>
       <c r="P19" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -12630,10 +12786,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C4" t="s">
         <v>434</v>
@@ -12645,15 +12801,15 @@
         <v>1</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C5" t="s">
         <v>434</v>
@@ -12665,7 +12821,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Main/Test.xlsx
+++ b/Excel/Main/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601B46AC-3176-49E7-BEB7-10468BAC2430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850151D1-62F9-49FF-829F-EB16DB3B6A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="661">
   <si>
     <t>Id</t>
   </si>
@@ -2061,9 +2061,6 @@
   </si>
   <si>
     <t>手动</t>
-  </si>
-  <si>
-    <t>m32攻击,m32结束,m32重构体,m32自身结束</t>
   </si>
   <si>
     <t>m32追加,m32启动</t>
@@ -2381,6 +2378,30 @@
   </si>
   <si>
     <t>{"UnitId":"猫诱导","TargetPos":"useSelfPos","SetMod":"Replace","UseMod":"UserDirection","UserName":"本能的召唤"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>m3攻速提升buff,m32攻速提升buff</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>#m32重构体</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>m32攻击,m32结束,m32自身结束</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己以外</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>#重构体消除自身buff</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>被治疗</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3698,7 +3719,7 @@
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B7" t="s">
         <v>126</v>
@@ -3756,13 +3777,13 @@
         <v>-1</v>
       </c>
       <c r="AG7" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AH7" t="s">
         <v>122</v>
       </c>
       <c r="AI7" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AK7">
         <v>3</v>
@@ -4293,7 +4314,7 @@
         <v>527</v>
       </c>
       <c r="AJ13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AM13">
         <v>1</v>
@@ -4415,7 +4436,7 @@
         <v>122</v>
       </c>
       <c r="AI14" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AK14">
         <v>0</v>
@@ -4430,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="AV14" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AW14">
         <v>0.25</v>
@@ -4473,7 +4494,7 @@
     </row>
     <row r="15" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B15" t="s">
         <v>126</v>
@@ -4534,13 +4555,13 @@
         <v>1</v>
       </c>
       <c r="AG15" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AH15" t="s">
         <v>122</v>
       </c>
       <c r="AI15" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AN15">
         <v>1</v>
@@ -4588,7 +4609,7 @@
         <v>124</v>
       </c>
       <c r="BP15" s="19" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="BQ15" t="s">
         <v>125</v>
@@ -7376,7 +7397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH839"/>
+  <dimension ref="A1:DH840"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -8622,7 +8643,7 @@
       </c>
       <c r="CJ10" s="3"/>
       <c r="CS10" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="DB10">
         <v>1</v>
@@ -8643,7 +8664,7 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>493</v>
@@ -8667,7 +8688,7 @@
       <c r="BT12"/>
       <c r="CJ12" s="3"/>
       <c r="CS12" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
@@ -8944,7 +8965,7 @@
       <c r="BT19"/>
       <c r="CJ19" s="3"/>
       <c r="CS19" s="8" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
@@ -9556,11 +9577,11 @@
       <c r="BB34">
         <v>1</v>
       </c>
-      <c r="BM34" t="s">
+      <c r="BM34" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="BN34" t="s">
         <v>563</v>
-      </c>
-      <c r="BN34" t="s">
-        <v>564</v>
       </c>
       <c r="BR34">
         <v>30</v>
@@ -9575,12 +9596,12 @@
         <v>1</v>
       </c>
       <c r="BW34" s="17" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="BX34" s="17"/>
       <c r="BY34" s="17"/>
       <c r="CL34" s="16" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="CP34">
         <v>30</v>
@@ -9591,7 +9612,7 @@
     </row>
     <row r="35" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C35" t="s">
         <v>346</v>
@@ -9638,7 +9659,7 @@
         <v>1</v>
       </c>
       <c r="BN35" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="BT35" s="17"/>
       <c r="BU35" s="17"/>
@@ -9647,7 +9668,7 @@
       <c r="BX35" s="17"/>
       <c r="BY35" s="17"/>
       <c r="BZ35" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="CE35" t="s">
         <v>509</v>
@@ -9658,8 +9679,8 @@
       <c r="CG35" t="s">
         <v>474</v>
       </c>
-      <c r="CL35" t="s">
-        <v>570</v>
+      <c r="CL35" s="8" t="s">
+        <v>655</v>
       </c>
       <c r="CM35">
         <v>22</v>
@@ -9676,7 +9697,7 @@
     </row>
     <row r="36" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C36" t="s">
         <v>346</v>
@@ -9735,7 +9756,7 @@
       <c r="BY36" s="17"/>
       <c r="BZ36" s="18"/>
       <c r="CF36" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="CG36" t="s">
         <v>474</v>
@@ -9749,7 +9770,7 @@
     </row>
     <row r="37" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C37" t="s">
         <v>346</v>
@@ -9794,7 +9815,7 @@
       <c r="BX37" s="17"/>
       <c r="BY37" s="17"/>
       <c r="CL37" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="CM37">
         <v>22</v>
@@ -9807,8 +9828,8 @@
       </c>
     </row>
     <row r="38" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>574</v>
+      <c r="A38" s="8" t="s">
+        <v>656</v>
       </c>
       <c r="C38" t="s">
         <v>346</v>
@@ -9854,7 +9875,7 @@
       <c r="BX38" s="17"/>
       <c r="BY38" s="17"/>
       <c r="CL38" s="16" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="CP38">
         <v>0.2</v>
@@ -9862,7 +9883,7 @@
     </row>
     <row r="39" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C39" t="s">
         <v>346</v>
@@ -9912,7 +9933,7 @@
       <c r="CH39" s="15"/>
       <c r="CI39" s="15"/>
       <c r="CL39" s="16" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="CP39">
         <v>40</v>
@@ -9926,7 +9947,7 @@
     </row>
     <row r="40" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C40" t="s">
         <v>346</v>
@@ -9942,7 +9963,7 @@
         <v>557</v>
       </c>
       <c r="P40" s="16" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="Q40" s="15"/>
       <c r="R40" s="15"/>
@@ -9968,12 +9989,12 @@
       <c r="BX40" s="17"/>
       <c r="BY40" s="17"/>
       <c r="CK40" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="41" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C41" t="s">
         <v>346</v>
@@ -10016,7 +10037,7 @@
       <c r="BX41" s="17"/>
       <c r="BY41" s="17"/>
       <c r="BZ41" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="CE41" t="s">
         <v>509</v>
@@ -10035,7 +10056,7 @@
     </row>
     <row r="42" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C42" t="s">
         <v>346</v>
@@ -10047,7 +10068,7 @@
         <v>347</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="M42"/>
       <c r="N42"/>
@@ -10080,7 +10101,7 @@
       <c r="BX42" s="17"/>
       <c r="BY42" s="17"/>
       <c r="BZ42" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="CE42" t="s">
         <v>509</v>
@@ -10098,7 +10119,7 @@
     </row>
     <row r="43" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C43" t="s">
         <v>346</v>
@@ -10115,15 +10136,15 @@
       <c r="G43">
         <v>3</v>
       </c>
-      <c r="K43" s="15" t="s">
-        <v>490</v>
-      </c>
-      <c r="L43" s="15"/>
+      <c r="K43" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>660</v>
+      </c>
       <c r="M43"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="16" t="s">
-        <v>574</v>
-      </c>
+      <c r="O43" s="16"/>
       <c r="P43" s="15"/>
       <c r="Q43" s="15"/>
       <c r="R43" s="15"/>
@@ -10136,6 +10157,9 @@
       <c r="AC43">
         <v>1</v>
       </c>
+      <c r="AG43" s="8" t="s">
+        <v>658</v>
+      </c>
       <c r="AO43" s="8" t="s">
         <v>555</v>
       </c>
@@ -10154,17 +10178,16 @@
       <c r="BB43">
         <v>1</v>
       </c>
-      <c r="BQ43">
-        <v>0.3</v>
-      </c>
+      <c r="BM43" s="8"/>
+      <c r="BN43" s="8"/>
       <c r="BT43" s="17"/>
       <c r="BU43" s="17"/>
       <c r="BV43" s="17"/>
       <c r="BW43" s="17"/>
       <c r="BX43" s="17"/>
       <c r="BY43" s="17"/>
-      <c r="CE43" t="s">
-        <v>509</v>
+      <c r="CE43" s="8" t="s">
+        <v>427</v>
       </c>
       <c r="CF43" t="s">
         <v>510</v>
@@ -10172,8 +10195,9 @@
       <c r="CG43" t="s">
         <v>474</v>
       </c>
+      <c r="CK43" s="8"/>
       <c r="CL43" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="CM43">
         <v>22</v>
@@ -10192,11 +10216,22 @@
       </c>
     </row>
     <row r="44" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="K44" s="15"/>
+      <c r="A44" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="C44" t="s">
+        <v>346</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>420</v>
+      </c>
       <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
+      <c r="M44"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="15"/>
+      <c r="O44" s="16"/>
       <c r="P44" s="15"/>
       <c r="Q44" s="15"/>
       <c r="R44" s="15"/>
@@ -10206,99 +10241,86 @@
       <c r="V44" s="15"/>
       <c r="W44" s="15"/>
       <c r="X44" s="15"/>
-      <c r="BS44" s="17"/>
+      <c r="AC44">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="AO44" s="8"/>
+      <c r="BB44">
+        <v>1</v>
+      </c>
+      <c r="BQ44">
+        <v>0.1</v>
+      </c>
       <c r="BT44" s="17"/>
       <c r="BU44" s="17"/>
       <c r="BV44" s="17"/>
       <c r="BW44" s="17"/>
       <c r="BX44" s="17"/>
-      <c r="BY44"/>
+      <c r="BY44" s="17"/>
+      <c r="CE44" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="CK44" t="s">
+        <v>569</v>
+      </c>
+      <c r="DB44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>584</v>
-      </c>
-      <c r="C45" t="s">
-        <v>346</v>
-      </c>
-      <c r="D45" t="s">
-        <v>585</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="F45" t="s">
-        <v>587</v>
-      </c>
-      <c r="G45">
-        <v>3</v>
-      </c>
-      <c r="J45" t="s">
-        <v>489</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="O45"/>
-      <c r="W45"/>
-      <c r="X45"/>
-      <c r="AC45">
-        <v>1</v>
-      </c>
-      <c r="AG45" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB45">
-        <v>1</v>
-      </c>
-      <c r="BM45" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="BN45" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="BR45">
-        <v>1</v>
-      </c>
-      <c r="BT45" s="4">
-        <v>11</v>
-      </c>
-      <c r="BU45" s="4">
-        <v>15</v>
-      </c>
-      <c r="BV45" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW45" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="CL45" s="14" t="s">
-        <v>591</v>
-      </c>
-      <c r="CM45" t="s">
-        <v>620</v>
-      </c>
-      <c r="CP45">
-        <v>25</v>
-      </c>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15"/>
+      <c r="P45" s="15"/>
+      <c r="Q45" s="15"/>
+      <c r="R45" s="15"/>
+      <c r="S45" s="15"/>
+      <c r="T45" s="15"/>
+      <c r="U45" s="15"/>
+      <c r="V45" s="15"/>
+      <c r="W45" s="15"/>
+      <c r="X45" s="15"/>
+      <c r="BS45" s="17"/>
+      <c r="BT45" s="17"/>
+      <c r="BU45" s="17"/>
+      <c r="BV45" s="17"/>
+      <c r="BW45" s="17"/>
+      <c r="BX45" s="17"/>
+      <c r="BY45"/>
     </row>
     <row r="46" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>621</v>
+        <v>583</v>
       </c>
       <c r="C46" t="s">
         <v>346</v>
       </c>
-      <c r="I46">
-        <v>1</v>
+      <c r="D46" t="s">
+        <v>584</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="F46" t="s">
+        <v>586</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
+      </c>
+      <c r="J46" t="s">
+        <v>489</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="M46"/>
-      <c r="O46" s="14"/>
-      <c r="P46"/>
-      <c r="Q46"/>
+        <v>562</v>
+      </c>
+      <c r="O46"/>
+      <c r="W46"/>
+      <c r="X46"/>
       <c r="AC46">
         <v>1</v>
       </c>
@@ -10308,22 +10330,40 @@
       <c r="BB46">
         <v>1</v>
       </c>
-      <c r="BQ46">
-        <v>0.1</v>
+      <c r="BM46" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="BN46" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="BR46">
+        <v>1</v>
+      </c>
+      <c r="BT46" s="4">
+        <v>11</v>
+      </c>
+      <c r="BU46" s="4">
+        <v>15</v>
+      </c>
+      <c r="BV46" s="4">
+        <v>1</v>
+      </c>
+      <c r="BW46" s="4" t="s">
+        <v>564</v>
       </c>
       <c r="CL46" s="14" t="s">
-        <v>646</v>
-      </c>
-      <c r="CM46">
-        <v>-100</v>
+        <v>590</v>
+      </c>
+      <c r="CM46" t="s">
+        <v>619</v>
       </c>
       <c r="CP46">
         <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
-        <v>639</v>
+      <c r="A47" t="s">
+        <v>620</v>
       </c>
       <c r="C47" t="s">
         <v>346</v>
@@ -10332,39 +10372,37 @@
         <v>1</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>622</v>
+        <v>420</v>
       </c>
       <c r="M47"/>
-      <c r="O47" s="14" t="s">
-        <v>591</v>
-      </c>
+      <c r="O47" s="14"/>
       <c r="P47"/>
       <c r="Q47"/>
       <c r="AC47">
         <v>1</v>
       </c>
-      <c r="AJ47" t="s">
-        <v>535</v>
-      </c>
-      <c r="AR47" t="s">
-        <v>508</v>
+      <c r="AG47" t="s">
+        <v>348</v>
       </c>
       <c r="BB47">
         <v>1</v>
       </c>
+      <c r="BQ47">
+        <v>0.1</v>
+      </c>
       <c r="CL47" s="14" t="s">
-        <v>592</v>
+        <v>645</v>
+      </c>
+      <c r="CM47">
+        <v>-100</v>
       </c>
       <c r="CP47">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C48" t="s">
         <v>346</v>
@@ -10372,287 +10410,269 @@
       <c r="I48">
         <v>1</v>
       </c>
+      <c r="K48" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="M48"/>
       <c r="O48" s="14" t="s">
-        <v>592</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="P48"/>
+      <c r="Q48"/>
       <c r="AC48">
         <v>1</v>
       </c>
-      <c r="AG48" t="s">
-        <v>348</v>
-      </c>
-      <c r="AV48" t="s">
-        <v>470</v>
-      </c>
-      <c r="AX48">
-        <v>1</v>
-      </c>
-      <c r="AZ48">
-        <v>1</v>
+      <c r="AJ48" t="s">
+        <v>535</v>
+      </c>
+      <c r="AR48" t="s">
+        <v>508</v>
       </c>
       <c r="BB48">
+        <v>1</v>
+      </c>
+      <c r="CL48" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="CP48">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C49" t="s">
-        <v>514</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>622</v>
+        <v>346</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="O49" s="14" t="s">
+        <v>591</v>
       </c>
       <c r="AC49">
-        <v>1</v>
-      </c>
-      <c r="AF49">
         <v>1</v>
       </c>
       <c r="AG49" t="s">
         <v>348</v>
       </c>
+      <c r="AV49" t="s">
+        <v>470</v>
+      </c>
+      <c r="AX49">
+        <v>1</v>
+      </c>
+      <c r="AZ49">
+        <v>1</v>
+      </c>
       <c r="BB49">
         <v>1</v>
       </c>
-      <c r="CJ49" s="3"/>
-      <c r="CS49" t="s">
-        <v>623</v>
-      </c>
-      <c r="DB49">
-        <v>1</v>
-      </c>
-      <c r="DE49">
-        <v>1</v>
-      </c>
-      <c r="DF49">
-        <v>1</v>
-      </c>
     </row>
     <row r="50" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="C50" t="s">
+        <v>514</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="AC50">
+        <v>1</v>
+      </c>
+      <c r="AF50">
+        <v>1</v>
+      </c>
+      <c r="AG50" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB50">
+        <v>1</v>
+      </c>
       <c r="CJ50" s="3"/>
+      <c r="CS50" t="s">
+        <v>622</v>
+      </c>
+      <c r="DB50">
+        <v>1</v>
+      </c>
+      <c r="DE50">
+        <v>1</v>
+      </c>
+      <c r="DF50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="CJ51" s="3"/>
+    </row>
+    <row r="52" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="AC52">
+        <v>1</v>
+      </c>
+      <c r="AJ52" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="I51">
-        <v>1</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>554</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="AC51">
-        <v>1</v>
-      </c>
-      <c r="AJ51" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="AR51" t="s">
+      <c r="AR52" t="s">
         <v>508</v>
       </c>
-      <c r="BB51">
-        <v>1</v>
-      </c>
-      <c r="BQ51">
+      <c r="BB52">
+        <v>1</v>
+      </c>
+      <c r="BQ52">
         <v>0.1</v>
       </c>
-      <c r="CJ51" s="3"/>
-      <c r="CS51" s="8" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="52" spans="1:110" x14ac:dyDescent="0.25">
       <c r="CJ52" s="3"/>
+      <c r="CS52" s="8" t="s">
+        <v>649</v>
+      </c>
     </row>
     <row r="53" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>624</v>
-      </c>
-      <c r="C53" t="s">
-        <v>346</v>
-      </c>
-      <c r="D53" t="s">
-        <v>585</v>
-      </c>
-      <c r="E53" t="s">
-        <v>586</v>
-      </c>
-      <c r="F53" t="s">
-        <v>587</v>
-      </c>
-      <c r="G53">
-        <v>3</v>
-      </c>
-      <c r="J53" t="s">
-        <v>489</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="O53"/>
-      <c r="W53"/>
-      <c r="X53"/>
-      <c r="AC53">
-        <v>1</v>
-      </c>
-      <c r="AG53" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB53">
-        <v>1</v>
-      </c>
-      <c r="BM53" t="s">
-        <v>625</v>
-      </c>
-      <c r="BR53">
-        <v>25</v>
-      </c>
-      <c r="BT53" s="4">
-        <v>1</v>
-      </c>
-      <c r="BU53" s="4">
-        <v>1</v>
-      </c>
-      <c r="BV53" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW53" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="CL53" s="14" t="s">
-        <v>589</v>
-      </c>
-      <c r="CM53" t="s">
-        <v>590</v>
-      </c>
-      <c r="CN53">
-        <v>2</v>
-      </c>
-      <c r="CO53">
-        <v>80</v>
-      </c>
-      <c r="CP53">
-        <v>25</v>
-      </c>
+      <c r="CJ53" s="3"/>
     </row>
     <row r="54" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>593</v>
+        <v>623</v>
       </c>
       <c r="C54" t="s">
-        <v>594</v>
-      </c>
-      <c r="O54" s="14" t="s">
-        <v>591</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="D54" t="s">
+        <v>584</v>
+      </c>
+      <c r="E54" t="s">
+        <v>585</v>
+      </c>
+      <c r="F54" t="s">
+        <v>586</v>
+      </c>
+      <c r="G54">
+        <v>3</v>
+      </c>
+      <c r="J54" t="s">
+        <v>489</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="O54"/>
+      <c r="W54"/>
       <c r="X54"/>
       <c r="AC54">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB54">
+        <v>1</v>
+      </c>
+      <c r="BM54" t="s">
+        <v>624</v>
+      </c>
+      <c r="BR54">
+        <v>25</v>
+      </c>
+      <c r="BT54" s="4">
+        <v>1</v>
+      </c>
+      <c r="BU54" s="4">
+        <v>1</v>
+      </c>
+      <c r="BV54" s="4">
+        <v>1</v>
+      </c>
+      <c r="BW54" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="CL54" s="14" t="s">
+        <v>588</v>
+      </c>
+      <c r="CM54" t="s">
+        <v>589</v>
+      </c>
+      <c r="CN54">
         <v>2</v>
       </c>
-      <c r="AO54" t="s">
-        <v>495</v>
-      </c>
-      <c r="AR54" t="s">
-        <v>519</v>
-      </c>
-      <c r="AV54" t="s">
-        <v>470</v>
-      </c>
-      <c r="AX54">
-        <v>1</v>
-      </c>
-      <c r="BB54">
-        <v>1</v>
-      </c>
-      <c r="BN54" t="s">
-        <v>595</v>
-      </c>
-      <c r="BZ54" t="s">
-        <v>596</v>
-      </c>
-      <c r="CE54" t="s">
-        <v>509</v>
-      </c>
-      <c r="CW54" t="s">
-        <v>352</v>
+      <c r="CO54">
+        <v>80</v>
+      </c>
+      <c r="CP54">
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C55" t="s">
-        <v>346</v>
-      </c>
-      <c r="I55">
-        <v>1</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>347</v>
+        <v>593</v>
       </c>
       <c r="O55" s="14" t="s">
-        <v>591</v>
-      </c>
-      <c r="P55"/>
-      <c r="Q55"/>
+        <v>590</v>
+      </c>
       <c r="X55"/>
       <c r="AC55">
-        <v>1</v>
-      </c>
-      <c r="AG55" t="s">
-        <v>348</v>
-      </c>
-      <c r="AH55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO55" t="s">
-        <v>507</v>
-      </c>
-      <c r="AT55">
-        <v>1</v>
-      </c>
-      <c r="AW55">
-        <v>1</v>
+        <v>495</v>
+      </c>
+      <c r="AR55" t="s">
+        <v>519</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>470</v>
       </c>
       <c r="AX55">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="BB55">
         <v>1</v>
       </c>
-      <c r="CF55" t="s">
-        <v>510</v>
-      </c>
-      <c r="CG55" t="s">
-        <v>474</v>
-      </c>
-      <c r="CL55" t="s">
-        <v>511</v>
-      </c>
-      <c r="CM55">
-        <v>22</v>
-      </c>
-      <c r="CP55">
-        <v>10</v>
+      <c r="BN55" t="s">
+        <v>594</v>
+      </c>
+      <c r="BZ55" t="s">
+        <v>595</v>
+      </c>
+      <c r="CE55" t="s">
+        <v>509</v>
+      </c>
+      <c r="CW55" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="56" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C56" t="s">
-        <v>598</v>
+        <v>346</v>
       </c>
       <c r="I56">
         <v>1</v>
@@ -10660,12 +10680,11 @@
       <c r="K56" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>599</v>
-      </c>
       <c r="O56" s="14" t="s">
-        <v>591</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="P56"/>
+      <c r="Q56"/>
       <c r="X56"/>
       <c r="AC56">
         <v>1</v>
@@ -10673,35 +10692,60 @@
       <c r="AG56" t="s">
         <v>348</v>
       </c>
+      <c r="AH56">
+        <v>1</v>
+      </c>
+      <c r="AO56" t="s">
+        <v>507</v>
+      </c>
+      <c r="AT56">
+        <v>1</v>
+      </c>
+      <c r="AW56">
+        <v>1</v>
+      </c>
+      <c r="AX56">
+        <v>0.5</v>
+      </c>
       <c r="BB56">
         <v>1</v>
       </c>
-      <c r="CS56" t="s">
-        <v>626</v>
-      </c>
-      <c r="DB56">
-        <v>1</v>
-      </c>
-      <c r="DE56">
-        <v>1</v>
-      </c>
-      <c r="DF56">
-        <v>1</v>
+      <c r="CF56" t="s">
+        <v>510</v>
+      </c>
+      <c r="CG56" t="s">
+        <v>474</v>
+      </c>
+      <c r="CL56" t="s">
+        <v>511</v>
+      </c>
+      <c r="CM56">
+        <v>22</v>
+      </c>
+      <c r="CP56">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>627</v>
+        <v>596</v>
       </c>
       <c r="C57" t="s">
-        <v>628</v>
+        <v>597</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>347</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>504</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="O57" s="14" t="s">
+        <v>590</v>
+      </c>
+      <c r="X57"/>
       <c r="AC57">
         <v>1</v>
       </c>
@@ -10712,18 +10756,24 @@
         <v>1</v>
       </c>
       <c r="CS57" t="s">
-        <v>629</v>
+        <v>625</v>
+      </c>
+      <c r="DB57">
+        <v>1</v>
+      </c>
+      <c r="DE57">
+        <v>1</v>
+      </c>
+      <c r="DF57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C58" t="s">
-        <v>346</v>
-      </c>
-      <c r="I58">
-        <v>1</v>
+        <v>627</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>347</v>
@@ -10740,16 +10790,13 @@
       <c r="BB58">
         <v>1</v>
       </c>
-      <c r="CL58" t="s">
-        <v>631</v>
-      </c>
-      <c r="CP58">
-        <v>0.5</v>
+      <c r="CS58" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="59" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C59" t="s">
         <v>346</v>
@@ -10758,86 +10805,72 @@
         <v>1</v>
       </c>
       <c r="K59" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="AC59">
+        <v>1</v>
+      </c>
+      <c r="AG59" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB59">
+        <v>1</v>
+      </c>
+      <c r="CL59" t="s">
+        <v>630</v>
+      </c>
+      <c r="CP59">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>631</v>
+      </c>
+      <c r="C60" t="s">
+        <v>346</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="K60" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="AC59">
-        <v>1</v>
-      </c>
-      <c r="AJ59" t="s">
+      <c r="L60" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="AC60">
+        <v>1</v>
+      </c>
+      <c r="AJ60" t="s">
         <v>523</v>
       </c>
-      <c r="AT59">
+      <c r="AT60">
         <v>20</v>
       </c>
-      <c r="BB59">
-        <v>1</v>
-      </c>
-      <c r="CK59" s="14" t="s">
-        <v>646</v>
-      </c>
-      <c r="CL59" s="14"/>
-      <c r="DB59">
-        <v>1</v>
-      </c>
-      <c r="DE59">
-        <v>1</v>
-      </c>
-      <c r="DF59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>588</v>
-      </c>
-      <c r="C61" t="s">
-        <v>346</v>
-      </c>
-      <c r="I61">
-        <v>1</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="M61"/>
-      <c r="N61"/>
-      <c r="AC61">
-        <v>1</v>
-      </c>
-      <c r="AG61" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB61">
-        <v>1</v>
-      </c>
-      <c r="BQ61">
-        <v>0.5</v>
-      </c>
-      <c r="BT61"/>
-      <c r="BZ61" s="20" t="s">
-        <v>651</v>
-      </c>
-      <c r="CE61" t="s">
-        <v>509</v>
-      </c>
-      <c r="CG61" s="3"/>
-      <c r="CH61" s="3"/>
-      <c r="DB61">
-        <v>1</v>
-      </c>
-      <c r="DE61">
-        <v>1</v>
-      </c>
-      <c r="DF61">
+      <c r="BB60">
+        <v>1</v>
+      </c>
+      <c r="CK60" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="CL60" s="14"/>
+      <c r="DB60">
+        <v>1</v>
+      </c>
+      <c r="DE60">
+        <v>1</v>
+      </c>
+      <c r="DF60">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="C62" t="s">
         <v>346</v>
@@ -10847,9 +10880,6 @@
       </c>
       <c r="K62" s="3" t="s">
         <v>347</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>581</v>
       </c>
       <c r="M62"/>
       <c r="N62"/>
@@ -10863,15 +10893,16 @@
         <v>1</v>
       </c>
       <c r="BQ62">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BT62"/>
       <c r="BZ62" s="20" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="CE62" t="s">
         <v>509</v>
       </c>
+      <c r="CG62" s="3"/>
       <c r="CH62" s="3"/>
       <c r="DB62">
         <v>1</v>
@@ -10897,10 +10928,10 @@
         <v>347</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="O63"/>
-      <c r="X63"/>
+        <v>580</v>
+      </c>
+      <c r="M63"/>
+      <c r="N63"/>
       <c r="AC63">
         <v>1</v>
       </c>
@@ -10910,79 +10941,124 @@
       <c r="BB63">
         <v>1</v>
       </c>
-      <c r="CK63" s="14" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="66" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ66" s="3"/>
-    </row>
-    <row r="67" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BQ63">
+        <v>1</v>
+      </c>
+      <c r="BT63"/>
+      <c r="BZ63" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="CE63" t="s">
+        <v>509</v>
+      </c>
+      <c r="CH63" s="3"/>
+      <c r="DB63">
+        <v>1</v>
+      </c>
+      <c r="DE63">
+        <v>1</v>
+      </c>
+      <c r="DF63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>599</v>
+      </c>
+      <c r="C64" t="s">
+        <v>346</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="O64"/>
+      <c r="X64"/>
+      <c r="AC64">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="s">
+        <v>348</v>
+      </c>
+      <c r="BB64">
+        <v>1</v>
+      </c>
+      <c r="CK64" s="14" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="67" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ67" s="3"/>
     </row>
-    <row r="73" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ73" s="3"/>
-    </row>
-    <row r="74" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="68" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ68" s="3"/>
+    </row>
+    <row r="74" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ74" s="3"/>
     </row>
-    <row r="76" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ76" s="3"/>
-    </row>
-    <row r="77" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="75" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ75" s="3"/>
+    </row>
+    <row r="77" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ77" s="3"/>
     </row>
-    <row r="78" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="78" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ78" s="3"/>
     </row>
-    <row r="79" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="79" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ79" s="3"/>
     </row>
-    <row r="80" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT80"/>
+    <row r="80" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ80" s="3"/>
     </row>
     <row r="81" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT81"/>
     </row>
     <row r="82" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT82"/>
-      <c r="CJ82" s="3"/>
     </row>
     <row r="83" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT83"/>
       <c r="CJ83" s="3"/>
     </row>
     <row r="84" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ84" s="3"/>
     </row>
     <row r="85" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT85"/>
+      <c r="CJ85" s="3"/>
     </row>
     <row r="86" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ86" s="3"/>
-    </row>
-    <row r="90" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT90"/>
+      <c r="BT86"/>
+    </row>
+    <row r="87" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ87" s="3"/>
     </row>
     <row r="91" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ91" s="3"/>
-    </row>
-    <row r="99" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ99" s="3"/>
+      <c r="BT91"/>
+    </row>
+    <row r="92" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ92" s="3"/>
     </row>
     <row r="100" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ100" s="3"/>
     </row>
     <row r="101" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT101"/>
-    </row>
-    <row r="106" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT106"/>
+      <c r="CJ101" s="3"/>
+    </row>
+    <row r="102" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT102"/>
     </row>
     <row r="107" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT107"/>
-      <c r="CJ107" s="3"/>
     </row>
     <row r="108" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT108"/>
       <c r="CJ108" s="3"/>
     </row>
     <row r="109" spans="72:88" x14ac:dyDescent="0.25">
@@ -10995,10 +11071,10 @@
       <c r="CJ111" s="3"/>
     </row>
     <row r="112" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT112"/>
+      <c r="CJ112" s="3"/>
     </row>
     <row r="113" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ113" s="3"/>
+      <c r="BT113"/>
     </row>
     <row r="114" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ114" s="3"/>
@@ -11010,10 +11086,10 @@
       <c r="CJ116" s="3"/>
     </row>
     <row r="117" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT117"/>
+      <c r="CJ117" s="3"/>
     </row>
     <row r="118" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ118" s="3"/>
+      <c r="BT118"/>
     </row>
     <row r="119" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ119" s="3"/>
@@ -11024,8 +11100,8 @@
     <row r="121" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ121" s="3"/>
     </row>
-    <row r="124" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ124" s="3"/>
+    <row r="122" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ122" s="3"/>
     </row>
     <row r="125" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ125" s="3"/>
@@ -11039,11 +11115,11 @@
     <row r="128" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ128" s="3"/>
     </row>
-    <row r="130" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT130"/>
+    <row r="129" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ129" s="3"/>
     </row>
     <row r="131" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ131" s="3"/>
+      <c r="BT131"/>
     </row>
     <row r="132" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ132" s="3"/>
@@ -11054,17 +11130,17 @@
     <row r="134" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ134" s="3"/>
     </row>
-    <row r="138" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ138" s="3"/>
-    </row>
-    <row r="140" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT140"/>
+    <row r="135" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ135" s="3"/>
+    </row>
+    <row r="139" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ139" s="3"/>
     </row>
     <row r="141" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT141"/>
-      <c r="CJ141" s="3"/>
     </row>
     <row r="142" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT142"/>
       <c r="CJ142" s="3"/>
     </row>
     <row r="143" spans="72:88" x14ac:dyDescent="0.25">
@@ -11076,50 +11152,50 @@
     <row r="145" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ145" s="3"/>
     </row>
-    <row r="147" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT147"/>
+    <row r="146" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ146" s="3"/>
     </row>
     <row r="148" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ148" s="3"/>
+      <c r="BT148"/>
     </row>
     <row r="149" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ149" s="3"/>
     </row>
-    <row r="151" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ151" s="3"/>
+    <row r="150" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ150" s="3"/>
     </row>
     <row r="152" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ152" s="3"/>
     </row>
-    <row r="154" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT154"/>
+    <row r="153" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ153" s="3"/>
     </row>
     <row r="155" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ155" s="3"/>
-    </row>
-    <row r="158" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ158" s="3"/>
+      <c r="BT155"/>
+    </row>
+    <row r="156" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ156" s="3"/>
     </row>
     <row r="159" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ159" s="3"/>
     </row>
-    <row r="162" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ162" s="3"/>
-    </row>
-    <row r="164" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ164" s="3"/>
-    </row>
-    <row r="166" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT166"/>
+    <row r="160" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ160" s="3"/>
+    </row>
+    <row r="163" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ163" s="3"/>
+    </row>
+    <row r="165" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ165" s="3"/>
     </row>
     <row r="167" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ167" s="3"/>
+      <c r="BT167"/>
     </row>
     <row r="168" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ168" s="3"/>
     </row>
-    <row r="170" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ170" s="3"/>
+    <row r="169" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ169" s="3"/>
     </row>
     <row r="171" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ171" s="3"/>
@@ -11127,187 +11203,186 @@
     <row r="172" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ172" s="3"/>
     </row>
-    <row r="177" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ177" s="3"/>
+    <row r="173" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ173" s="3"/>
     </row>
     <row r="178" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ178" s="3"/>
     </row>
-    <row r="181" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ181" s="3"/>
+    <row r="179" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ179" s="3"/>
     </row>
     <row r="182" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ182" s="3"/>
     </row>
-    <row r="186" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ186" s="3"/>
-    </row>
-    <row r="190" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ190" s="3"/>
-    </row>
-    <row r="192" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ192" s="3"/>
+    <row r="183" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ183" s="3"/>
+    </row>
+    <row r="187" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ187" s="3"/>
+    </row>
+    <row r="191" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ191" s="3"/>
     </row>
     <row r="193" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ193" s="3"/>
     </row>
-    <row r="195" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ195" s="3"/>
+    <row r="194" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ194" s="3"/>
     </row>
     <row r="196" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ196" s="3"/>
     </row>
-    <row r="198" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT198"/>
+    <row r="197" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ197" s="3"/>
     </row>
     <row r="199" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT199"/>
-      <c r="CJ199" s="3"/>
     </row>
     <row r="200" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT200"/>
       <c r="CJ200" s="3"/>
     </row>
-    <row r="202" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ202" s="3"/>
-    </row>
-    <row r="211" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT211"/>
+    <row r="201" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ201" s="3"/>
+    </row>
+    <row r="203" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ203" s="3"/>
     </row>
     <row r="212" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT212"/>
-      <c r="CJ212" s="3"/>
     </row>
     <row r="213" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT213"/>
       <c r="CJ213" s="3"/>
     </row>
     <row r="214" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ214" s="3"/>
     </row>
     <row r="215" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT215"/>
+      <c r="CJ215" s="3"/>
     </row>
     <row r="216" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT216"/>
-      <c r="CJ216" s="3"/>
     </row>
     <row r="217" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT217"/>
       <c r="CJ217" s="3"/>
     </row>
-    <row r="219" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT219"/>
+    <row r="218" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ218" s="3"/>
     </row>
     <row r="220" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT220"/>
-      <c r="CJ220" s="3"/>
     </row>
     <row r="221" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT221"/>
       <c r="CJ221" s="3"/>
     </row>
-    <row r="223" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT223"/>
+    <row r="222" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ222" s="3"/>
     </row>
     <row r="224" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ224" s="3"/>
-    </row>
-    <row r="227" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ227" s="3"/>
-    </row>
-    <row r="231" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ231" s="3"/>
-    </row>
-    <row r="233" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT233"/>
+      <c r="BT224"/>
+    </row>
+    <row r="225" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ225" s="3"/>
+    </row>
+    <row r="228" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ228" s="3"/>
+    </row>
+    <row r="232" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ232" s="3"/>
     </row>
     <row r="234" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ234" s="3"/>
-    </row>
-    <row r="241" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT241"/>
+      <c r="BT234"/>
+    </row>
+    <row r="235" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ235" s="3"/>
     </row>
     <row r="242" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ242" s="3"/>
+      <c r="BT242"/>
     </row>
     <row r="243" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ243" s="3"/>
     </row>
-    <row r="245" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT245"/>
+    <row r="244" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ244" s="3"/>
     </row>
     <row r="246" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT246"/>
-      <c r="CJ246" s="3"/>
     </row>
     <row r="247" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT247"/>
       <c r="CJ247" s="3"/>
     </row>
-    <row r="253" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT253"/>
+    <row r="248" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ248" s="3"/>
     </row>
     <row r="254" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT254"/>
-      <c r="CJ254" s="3"/>
     </row>
     <row r="255" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT255"/>
       <c r="CJ255" s="3"/>
     </row>
     <row r="256" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT256"/>
       <c r="CJ256" s="3"/>
     </row>
-    <row r="261" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT261"/>
+    <row r="257" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ257" s="3"/>
     </row>
     <row r="262" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT262"/>
     </row>
-    <row r="266" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT266"/>
+    <row r="263" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT263"/>
     </row>
     <row r="267" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ267" s="3"/>
+      <c r="BT267"/>
     </row>
     <row r="268" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT268"/>
+      <c r="CJ268" s="3"/>
     </row>
     <row r="269" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ269" s="3"/>
-    </row>
-    <row r="279" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT279"/>
+      <c r="BT269"/>
+    </row>
+    <row r="270" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ270" s="3"/>
     </row>
     <row r="280" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ280" s="3"/>
-    </row>
-    <row r="282" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT282"/>
+      <c r="BT280"/>
+    </row>
+    <row r="281" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ281" s="3"/>
     </row>
     <row r="283" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ283" s="3"/>
-    </row>
-    <row r="291" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT291"/>
+      <c r="BT283"/>
+    </row>
+    <row r="284" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ284" s="3"/>
     </row>
     <row r="292" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ292" s="3"/>
-    </row>
-    <row r="296" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT296"/>
+      <c r="BT292"/>
+    </row>
+    <row r="293" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ293" s="3"/>
     </row>
     <row r="297" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ297" s="3"/>
-    </row>
-    <row r="299" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT299"/>
+      <c r="BT297"/>
+    </row>
+    <row r="298" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ298" s="3"/>
     </row>
     <row r="300" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ300" s="3"/>
-    </row>
-    <row r="316" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT316"/>
+      <c r="BT300"/>
+    </row>
+    <row r="301" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ301" s="3"/>
     </row>
     <row r="317" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT317"/>
-      <c r="CJ317" s="3"/>
     </row>
     <row r="318" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT318"/>
@@ -11319,49 +11394,50 @@
     </row>
     <row r="320" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT320"/>
-    </row>
-    <row r="322" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT322"/>
+      <c r="CJ320" s="3"/>
+    </row>
+    <row r="321" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT321"/>
     </row>
     <row r="323" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT323"/>
-      <c r="CJ323" s="3"/>
     </row>
     <row r="324" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT324"/>
       <c r="CJ324" s="3"/>
     </row>
     <row r="325" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT325"/>
       <c r="CJ325" s="3"/>
     </row>
-    <row r="329" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT329"/>
+    <row r="326" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ326" s="3"/>
     </row>
     <row r="330" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ330" s="3"/>
-    </row>
-    <row r="332" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT332"/>
+      <c r="BT330"/>
+    </row>
+    <row r="331" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ331" s="3"/>
     </row>
     <row r="333" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT333"/>
-      <c r="CJ333" s="3"/>
     </row>
     <row r="334" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT334"/>
       <c r="CJ334" s="3"/>
     </row>
     <row r="335" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT335"/>
       <c r="CJ335" s="3"/>
     </row>
-    <row r="351" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT351"/>
-    </row>
-    <row r="352" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ352" s="3"/>
-    </row>
-    <row r="360" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ360" s="3"/>
+    <row r="336" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ336" s="3"/>
+    </row>
+    <row r="352" spans="72:72" x14ac:dyDescent="0.25">
+      <c r="BT352"/>
+    </row>
+    <row r="353" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ353" s="3"/>
     </row>
     <row r="361" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ361" s="3"/>
@@ -11375,47 +11451,47 @@
     <row r="364" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ364" s="3"/>
     </row>
-    <row r="366" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT366"/>
+    <row r="365" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ365" s="3"/>
     </row>
     <row r="367" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ367" s="3"/>
+      <c r="BT367"/>
     </row>
     <row r="368" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT368"/>
+      <c r="CJ368" s="3"/>
     </row>
     <row r="369" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT369"/>
-      <c r="CJ369" s="3"/>
     </row>
     <row r="370" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT370"/>
       <c r="CJ370" s="3"/>
     </row>
-    <row r="372" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT372"/>
+    <row r="371" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ371" s="3"/>
     </row>
     <row r="373" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT373"/>
-      <c r="CJ373" s="3"/>
     </row>
     <row r="374" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT374"/>
       <c r="CJ374" s="3"/>
     </row>
     <row r="375" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT375"/>
       <c r="CJ375" s="3"/>
     </row>
-    <row r="377" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ377" s="3"/>
-    </row>
-    <row r="379" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ379" s="3"/>
-    </row>
-    <row r="381" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ381" s="3"/>
-    </row>
-    <row r="384" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ384" s="3"/>
+    <row r="376" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ376" s="3"/>
+    </row>
+    <row r="378" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ378" s="3"/>
+    </row>
+    <row r="380" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ380" s="3"/>
+    </row>
+    <row r="382" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ382" s="3"/>
     </row>
     <row r="385" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ385" s="3"/>
@@ -11433,17 +11509,17 @@
       <c r="CJ389" s="3"/>
     </row>
     <row r="390" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT390"/>
+      <c r="CJ390" s="3"/>
     </row>
     <row r="391" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT391"/>
-      <c r="CJ391" s="3"/>
     </row>
     <row r="392" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT392"/>
       <c r="CJ392" s="3"/>
     </row>
     <row r="393" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT393"/>
       <c r="CJ393" s="3"/>
     </row>
     <row r="394" spans="72:88" x14ac:dyDescent="0.25">
@@ -11455,37 +11531,36 @@
     <row r="396" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ396" s="3"/>
     </row>
-    <row r="398" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ398" s="3"/>
+    <row r="397" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ397" s="3"/>
     </row>
     <row r="399" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ399" s="3"/>
     </row>
     <row r="400" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT400"/>
+      <c r="CJ400" s="3"/>
     </row>
     <row r="401" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT401"/>
-      <c r="CJ401" s="3"/>
     </row>
     <row r="402" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT402"/>
       <c r="CJ402" s="3"/>
     </row>
     <row r="403" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT403"/>
       <c r="CJ403" s="3"/>
     </row>
     <row r="404" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ404" s="3"/>
     </row>
-    <row r="406" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ406" s="3"/>
+    <row r="405" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ405" s="3"/>
     </row>
     <row r="407" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ407" s="3"/>
     </row>
     <row r="408" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT408"/>
       <c r="CJ408" s="3"/>
     </row>
     <row r="409" spans="72:88" x14ac:dyDescent="0.25">
@@ -11493,6 +11568,7 @@
       <c r="CJ409" s="3"/>
     </row>
     <row r="410" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT410"/>
       <c r="CJ410" s="3"/>
     </row>
     <row r="411" spans="72:88" x14ac:dyDescent="0.25">
@@ -11501,70 +11577,70 @@
     <row r="412" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ412" s="3"/>
     </row>
-    <row r="414" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT414"/>
-      <c r="CJ414" s="3"/>
+    <row r="413" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ413" s="3"/>
     </row>
     <row r="415" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT415"/>
       <c r="CJ415" s="3"/>
     </row>
     <row r="416" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ416" s="3"/>
     </row>
-    <row r="418" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT418"/>
-      <c r="CJ418" s="3"/>
+    <row r="417" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ417" s="3"/>
     </row>
     <row r="419" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT419"/>
       <c r="CJ419" s="3"/>
     </row>
     <row r="420" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT420"/>
       <c r="CJ420" s="3"/>
     </row>
-    <row r="422" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ422" s="3"/>
-    </row>
-    <row r="424" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ424" s="3"/>
-    </row>
-    <row r="427" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ427" s="3"/>
+    <row r="421" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ421" s="3"/>
+    </row>
+    <row r="423" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ423" s="3"/>
+    </row>
+    <row r="425" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ425" s="3"/>
     </row>
     <row r="428" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ428" s="3"/>
     </row>
-    <row r="432" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT432"/>
+    <row r="429" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ429" s="3"/>
     </row>
     <row r="433" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT433"/>
-      <c r="CJ433" s="3"/>
     </row>
     <row r="434" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT434"/>
       <c r="CJ434" s="3"/>
     </row>
     <row r="435" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT435"/>
       <c r="CJ435" s="3"/>
     </row>
     <row r="436" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ436" s="3"/>
     </row>
     <row r="437" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT437"/>
+      <c r="CJ437" s="3"/>
     </row>
     <row r="438" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ438" s="3"/>
-    </row>
-    <row r="440" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ440" s="3"/>
+      <c r="BT438"/>
+    </row>
+    <row r="439" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ439" s="3"/>
     </row>
     <row r="441" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ441" s="3"/>
     </row>
-    <row r="443" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ443" s="3"/>
+    <row r="442" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ442" s="3"/>
     </row>
     <row r="444" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ444" s="3"/>
@@ -11584,75 +11660,74 @@
     <row r="449" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ449" s="3"/>
     </row>
-    <row r="451" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT451"/>
+    <row r="450" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ450" s="3"/>
     </row>
     <row r="452" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ452" s="3"/>
+      <c r="BT452"/>
     </row>
     <row r="453" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ453" s="3"/>
     </row>
-    <row r="486" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS486" s="10"/>
-      <c r="BT486" s="11"/>
+    <row r="454" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ454" s="3"/>
     </row>
     <row r="487" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H487" s="10"/>
-      <c r="CJ487" s="10"/>
-    </row>
-    <row r="493" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT493"/>
+      <c r="BS487" s="10"/>
+      <c r="BT487" s="11"/>
+    </row>
+    <row r="488" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H488" s="10"/>
+      <c r="CJ488" s="10"/>
     </row>
     <row r="494" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT494"/>
-      <c r="CJ494" s="3"/>
     </row>
     <row r="495" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT495"/>
       <c r="CJ495" s="3"/>
     </row>
     <row r="496" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT496"/>
       <c r="CJ496" s="3"/>
     </row>
-    <row r="513" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT513"/>
+    <row r="497" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ497" s="3"/>
     </row>
     <row r="514" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ514" s="3"/>
-    </row>
-    <row r="546" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT546"/>
+      <c r="BT514"/>
+    </row>
+    <row r="515" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ515" s="3"/>
     </row>
     <row r="547" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT547"/>
-      <c r="CJ547" s="3"/>
     </row>
     <row r="548" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT548"/>
       <c r="CJ548" s="3"/>
     </row>
-    <row r="564" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT564"/>
+    <row r="549" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ549" s="3"/>
     </row>
     <row r="565" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ565" s="3"/>
-    </row>
-    <row r="571" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT571"/>
+      <c r="BT565"/>
+    </row>
+    <row r="566" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ566" s="3"/>
     </row>
     <row r="572" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT572"/>
-      <c r="CJ572" s="3"/>
     </row>
     <row r="573" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT573"/>
       <c r="CJ573" s="3"/>
     </row>
-    <row r="578" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT578"/>
+    <row r="574" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ574" s="3"/>
     </row>
     <row r="579" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT579"/>
-      <c r="CJ579" s="3"/>
     </row>
     <row r="580" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT580"/>
@@ -11711,40 +11786,40 @@
       <c r="CJ593" s="3"/>
     </row>
     <row r="594" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT594"/>
       <c r="CJ594" s="3"/>
     </row>
-    <row r="598" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT598"/>
+    <row r="595" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ595" s="3"/>
     </row>
     <row r="599" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT599"/>
-      <c r="CJ599" s="3"/>
     </row>
     <row r="600" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT600"/>
       <c r="CJ600" s="3"/>
     </row>
     <row r="601" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT601"/>
+      <c r="CJ601" s="3"/>
     </row>
     <row r="602" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ602" s="3"/>
-    </row>
-    <row r="605" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT605"/>
+      <c r="BT602"/>
+    </row>
+    <row r="603" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ603" s="3"/>
     </row>
     <row r="606" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT606"/>
-      <c r="CJ606" s="3"/>
     </row>
     <row r="607" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT607"/>
       <c r="CJ607" s="3"/>
     </row>
-    <row r="638" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT638"/>
+    <row r="608" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ608" s="3"/>
     </row>
     <row r="639" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT639"/>
-      <c r="CJ639" s="3"/>
     </row>
     <row r="640" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT640"/>
@@ -11771,26 +11846,26 @@
       <c r="CJ645" s="3"/>
     </row>
     <row r="646" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT646"/>
       <c r="CJ646" s="3"/>
     </row>
-    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT648"/>
+    <row r="647" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ647" s="3"/>
     </row>
     <row r="649" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ649" s="3"/>
-    </row>
-    <row r="653" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT653"/>
+      <c r="BT649"/>
+    </row>
+    <row r="650" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ650" s="3"/>
     </row>
     <row r="654" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ654" s="3"/>
-    </row>
-    <row r="657" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT657"/>
+      <c r="BT654"/>
+    </row>
+    <row r="655" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ655" s="3"/>
     </row>
     <row r="658" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT658"/>
-      <c r="CJ658" s="3"/>
     </row>
     <row r="659" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT659"/>
@@ -11801,20 +11876,20 @@
       <c r="CJ660" s="3"/>
     </row>
     <row r="661" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT661"/>
       <c r="CJ661" s="3"/>
     </row>
-    <row r="668" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT668"/>
+    <row r="662" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ662" s="3"/>
     </row>
     <row r="669" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ669" s="3"/>
-    </row>
-    <row r="672" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT672"/>
+      <c r="BT669"/>
+    </row>
+    <row r="670" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ670" s="3"/>
     </row>
     <row r="673" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT673"/>
-      <c r="CJ673" s="3"/>
     </row>
     <row r="674" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT674"/>
@@ -11825,74 +11900,74 @@
       <c r="CJ675" s="3"/>
     </row>
     <row r="676" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT676"/>
       <c r="CJ676" s="3"/>
     </row>
-    <row r="678" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT678"/>
+    <row r="677" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ677" s="3"/>
     </row>
     <row r="679" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT679"/>
-      <c r="CJ679" s="3"/>
     </row>
     <row r="680" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT680"/>
       <c r="CJ680" s="3"/>
     </row>
     <row r="681" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ681">
+      <c r="CJ681" s="3"/>
+    </row>
+    <row r="682" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ682">
         <v>0.15</v>
-      </c>
-    </row>
-    <row r="683" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ683">
-        <v>0.2</v>
       </c>
     </row>
     <row r="684" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ684">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="685" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ685">
         <v>0.1</v>
       </c>
     </row>
-    <row r="686" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ686">
+    <row r="687" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ687">
         <v>0.2</v>
       </c>
     </row>
-    <row r="693" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ693">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="695" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ695">
+    <row r="694" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ694">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="696" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ696">
         <v>0.4</v>
       </c>
     </row>
-    <row r="696" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ696">
+    <row r="697" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ697">
         <v>0.6</v>
       </c>
     </row>
-    <row r="699" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ699">
+    <row r="700" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ700">
         <v>0.5</v>
       </c>
     </row>
-    <row r="700" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ700">
+    <row r="701" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ701">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="701" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ701">
+    <row r="702" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ702">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="704" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT704"/>
     </row>
     <row r="705" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT705"/>
-      <c r="CJ705" s="3"/>
     </row>
     <row r="706" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT706"/>
@@ -11923,20 +11998,20 @@
       <c r="CJ712" s="3"/>
     </row>
     <row r="713" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT713"/>
       <c r="CJ713" s="3"/>
     </row>
     <row r="714" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT714"/>
+      <c r="CJ714" s="3"/>
     </row>
     <row r="715" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ715" s="3"/>
-    </row>
-    <row r="724" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT724"/>
+      <c r="BT715"/>
+    </row>
+    <row r="716" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ716" s="3"/>
     </row>
     <row r="725" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT725"/>
-      <c r="CJ725" s="3"/>
     </row>
     <row r="726" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT726"/>
@@ -11963,40 +12038,40 @@
       <c r="CJ731" s="3"/>
     </row>
     <row r="732" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT732"/>
       <c r="CJ732" s="3"/>
     </row>
     <row r="733" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT733"/>
+      <c r="CJ733" s="3"/>
     </row>
     <row r="734" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ734" s="3"/>
-    </row>
-    <row r="739" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT739"/>
+      <c r="BT734"/>
+    </row>
+    <row r="735" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ735" s="3"/>
     </row>
     <row r="740" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT740"/>
-      <c r="CJ740" s="3"/>
     </row>
     <row r="741" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT741"/>
       <c r="CJ741" s="3"/>
     </row>
     <row r="742" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT742"/>
+      <c r="CJ742" s="3"/>
     </row>
     <row r="743" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT743"/>
-      <c r="CJ743" s="3"/>
     </row>
     <row r="744" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT744"/>
       <c r="CJ744" s="3"/>
     </row>
     <row r="745" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT745"/>
+      <c r="CJ745" s="3"/>
     </row>
     <row r="746" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT746"/>
-      <c r="CJ746" s="3"/>
     </row>
     <row r="747" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT747"/>
@@ -12007,76 +12082,76 @@
       <c r="CJ748" s="3"/>
     </row>
     <row r="749" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT749"/>
       <c r="CJ749" s="3"/>
     </row>
-    <row r="753" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT753"/>
+    <row r="750" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ750" s="3"/>
     </row>
     <row r="754" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT754"/>
-      <c r="CJ754" s="3"/>
     </row>
     <row r="755" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT755"/>
       <c r="CJ755" s="3"/>
     </row>
     <row r="756" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT756"/>
       <c r="CJ756" s="3"/>
     </row>
     <row r="757" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT757"/>
+      <c r="CJ757" s="3"/>
     </row>
     <row r="758" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ758" s="3"/>
+      <c r="BT758"/>
     </row>
     <row r="759" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS759" s="10"/>
-      <c r="BT759" s="11"/>
+      <c r="CJ759" s="3"/>
     </row>
     <row r="760" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H760" s="10"/>
-      <c r="CJ760" s="10"/>
-    </row>
-    <row r="777" spans="71:88" x14ac:dyDescent="0.25">
-      <c r="BT777"/>
-    </row>
-    <row r="778" spans="71:88" x14ac:dyDescent="0.25">
+      <c r="BS760" s="10"/>
+      <c r="BT760" s="11"/>
+    </row>
+    <row r="761" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H761" s="10"/>
+      <c r="CJ761" s="10"/>
+    </row>
+    <row r="778" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT778"/>
-      <c r="CJ778" s="3"/>
-    </row>
-    <row r="779" spans="71:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="779" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT779"/>
       <c r="CJ779" s="3"/>
     </row>
-    <row r="780" spans="71:88" x14ac:dyDescent="0.25">
+    <row r="780" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT780"/>
       <c r="CJ780" s="3"/>
     </row>
-    <row r="781" spans="71:88" x14ac:dyDescent="0.25">
+    <row r="781" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT781"/>
       <c r="CJ781" s="3"/>
     </row>
-    <row r="782" spans="71:88" x14ac:dyDescent="0.25">
-      <c r="BT782"/>
-    </row>
-    <row r="783" spans="71:88" x14ac:dyDescent="0.25">
+    <row r="782" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ782" s="3"/>
+    </row>
+    <row r="783" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT783"/>
-      <c r="CJ783" s="3"/>
-    </row>
-    <row r="784" spans="71:88" x14ac:dyDescent="0.25">
-      <c r="BS784" s="10"/>
-      <c r="BT784" s="11"/>
+    </row>
+    <row r="784" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT784"/>
       <c r="CJ784" s="3"/>
     </row>
     <row r="785" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H785" s="10"/>
-      <c r="CJ785" s="10"/>
-    </row>
-    <row r="788" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT788"/>
+      <c r="BS785" s="10"/>
+      <c r="BT785" s="11"/>
+      <c r="CJ785" s="3"/>
+    </row>
+    <row r="786" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H786" s="10"/>
+      <c r="CJ786" s="10"/>
     </row>
     <row r="789" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT789"/>
-      <c r="CJ789" s="3"/>
     </row>
     <row r="790" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT790"/>
@@ -12103,14 +12178,14 @@
       <c r="CJ795" s="3"/>
     </row>
     <row r="796" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT796"/>
       <c r="CJ796" s="3"/>
     </row>
-    <row r="798" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT798"/>
+    <row r="797" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CJ797" s="3"/>
     </row>
     <row r="799" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT799"/>
-      <c r="CJ799" s="3"/>
     </row>
     <row r="800" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT800"/>
@@ -12129,14 +12204,14 @@
       <c r="CJ803" s="3"/>
     </row>
     <row r="804" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT804"/>
       <c r="CJ804" s="3"/>
     </row>
     <row r="805" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT805"/>
+      <c r="CJ805" s="3"/>
     </row>
     <row r="806" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT806"/>
-      <c r="CJ806" s="3"/>
     </row>
     <row r="807" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT807"/>
@@ -12251,21 +12326,25 @@
       <c r="CJ834" s="3"/>
     </row>
     <row r="835" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT835"/>
       <c r="CJ835" s="3"/>
     </row>
     <row r="836" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT836"/>
+      <c r="CJ836" s="3"/>
     </row>
     <row r="837" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT837"/>
-      <c r="CJ837" s="3"/>
     </row>
     <row r="838" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT838"/>
       <c r="CJ838" s="3"/>
     </row>
     <row r="839" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT839"/>
       <c r="CJ839" s="3"/>
+    </row>
+    <row r="840" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ840" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -12509,7 +12588,7 @@
         <v>557</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H9" s="14">
         <v>1</v>
@@ -12518,7 +12597,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C10" t="s">
         <v>539</v>
@@ -12532,10 +12611,10 @@
     </row>
     <row r="11" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H11" s="14">
         <v>1</v>
@@ -12544,10 +12623,10 @@
     </row>
     <row r="12" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H12" s="14">
         <v>1</v>
@@ -12556,18 +12635,18 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C13" t="s">
         <v>200</v>
       </c>
       <c r="P13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>539</v>
@@ -12577,23 +12656,23 @@
       </c>
       <c r="J14"/>
       <c r="P14" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C15" t="s">
         <v>539</v>
       </c>
       <c r="P15" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C16" t="s">
         <v>542</v>
@@ -12610,49 +12689,49 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>612</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="J17" t="s">
         <v>613</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="J17" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H18" s="14">
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C19" t="s">
         <v>200</v>
       </c>
       <c r="P19" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="P20" s="8" t="s">
         <v>618</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>619</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Main/Test.xlsx
+++ b/Excel/Main/Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850151D1-62F9-49FF-829F-EB16DB3B6A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BAA8A7-E43D-4721-9766-99CC31404881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="661">
   <si>
     <t>Id</t>
   </si>
@@ -2061,9 +2061,6 @@
   </si>
   <si>
     <t>手动</t>
-  </si>
-  <si>
-    <t>m32追加,m32启动</t>
   </si>
   <si>
     <t>攻击</t>
@@ -2385,14 +2382,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>#m32重构体</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>m32攻击,m32结束,m32自身结束</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>自己以外</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2402,6 +2391,18 @@
   </si>
   <si>
     <t>被治疗</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>m32重构体</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>m32追加,m32启动</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>m32攻击,m32结束,m32自身结束,m32重构体</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3719,7 +3720,7 @@
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B7" t="s">
         <v>126</v>
@@ -3777,13 +3778,13 @@
         <v>-1</v>
       </c>
       <c r="AG7" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AH7" t="s">
         <v>122</v>
       </c>
       <c r="AI7" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AK7">
         <v>3</v>
@@ -4314,7 +4315,7 @@
         <v>527</v>
       </c>
       <c r="AJ13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AM13">
         <v>1</v>
@@ -4436,7 +4437,7 @@
         <v>122</v>
       </c>
       <c r="AI14" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AK14">
         <v>0</v>
@@ -4451,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="AV14" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AW14">
         <v>0.25</v>
@@ -4494,7 +4495,7 @@
     </row>
     <row r="15" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B15" t="s">
         <v>126</v>
@@ -4555,13 +4556,13 @@
         <v>1</v>
       </c>
       <c r="AG15" s="8" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AH15" t="s">
         <v>122</v>
       </c>
       <c r="AI15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AN15">
         <v>1</v>
@@ -4609,7 +4610,7 @@
         <v>124</v>
       </c>
       <c r="BP15" s="19" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="BQ15" t="s">
         <v>125</v>
@@ -8643,7 +8644,7 @@
       </c>
       <c r="CJ10" s="3"/>
       <c r="CS10" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="DB10">
         <v>1</v>
@@ -8664,7 +8665,7 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>493</v>
@@ -8688,7 +8689,7 @@
       <c r="BT12"/>
       <c r="CJ12" s="3"/>
       <c r="CS12" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
@@ -8965,7 +8966,7 @@
       <c r="BT19"/>
       <c r="CJ19" s="3"/>
       <c r="CS19" s="8" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
@@ -9578,10 +9579,10 @@
         <v>1</v>
       </c>
       <c r="BM34" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="BN34" t="s">
-        <v>563</v>
+        <v>660</v>
+      </c>
+      <c r="BN34" s="8" t="s">
+        <v>659</v>
       </c>
       <c r="BR34">
         <v>30</v>
@@ -9596,12 +9597,12 @@
         <v>1</v>
       </c>
       <c r="BW34" s="17" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="BX34" s="17"/>
       <c r="BY34" s="17"/>
       <c r="CL34" s="16" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="CP34">
         <v>30</v>
@@ -9612,7 +9613,7 @@
     </row>
     <row r="35" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C35" t="s">
         <v>346</v>
@@ -9659,7 +9660,7 @@
         <v>1</v>
       </c>
       <c r="BN35" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="BT35" s="17"/>
       <c r="BU35" s="17"/>
@@ -9668,7 +9669,7 @@
       <c r="BX35" s="17"/>
       <c r="BY35" s="17"/>
       <c r="BZ35" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="CE35" t="s">
         <v>509</v>
@@ -9680,7 +9681,7 @@
         <v>474</v>
       </c>
       <c r="CL35" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="CM35">
         <v>22</v>
@@ -9697,7 +9698,7 @@
     </row>
     <row r="36" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C36" t="s">
         <v>346</v>
@@ -9756,7 +9757,7 @@
       <c r="BY36" s="17"/>
       <c r="BZ36" s="18"/>
       <c r="CF36" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="CG36" t="s">
         <v>474</v>
@@ -9770,7 +9771,7 @@
     </row>
     <row r="37" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C37" t="s">
         <v>346</v>
@@ -9815,7 +9816,7 @@
       <c r="BX37" s="17"/>
       <c r="BY37" s="17"/>
       <c r="CL37" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="CM37">
         <v>22</v>
@@ -9829,7 +9830,7 @@
     </row>
     <row r="38" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C38" t="s">
         <v>346</v>
@@ -9837,7 +9838,9 @@
       <c r="I38">
         <v>1</v>
       </c>
-      <c r="K38" s="15"/>
+      <c r="K38" s="3" t="s">
+        <v>422</v>
+      </c>
       <c r="L38" s="15"/>
       <c r="M38"/>
       <c r="N38" s="15"/>
@@ -9875,7 +9878,7 @@
       <c r="BX38" s="17"/>
       <c r="BY38" s="17"/>
       <c r="CL38" s="16" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="CP38">
         <v>0.2</v>
@@ -9883,7 +9886,7 @@
     </row>
     <row r="39" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C39" t="s">
         <v>346</v>
@@ -9933,7 +9936,7 @@
       <c r="CH39" s="15"/>
       <c r="CI39" s="15"/>
       <c r="CL39" s="16" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="CP39">
         <v>40</v>
@@ -9947,7 +9950,7 @@
     </row>
     <row r="40" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C40" t="s">
         <v>346</v>
@@ -9963,7 +9966,7 @@
         <v>557</v>
       </c>
       <c r="P40" s="16" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="Q40" s="15"/>
       <c r="R40" s="15"/>
@@ -9989,12 +9992,12 @@
       <c r="BX40" s="17"/>
       <c r="BY40" s="17"/>
       <c r="CK40" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="41" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C41" t="s">
         <v>346</v>
@@ -10037,7 +10040,7 @@
       <c r="BX41" s="17"/>
       <c r="BY41" s="17"/>
       <c r="BZ41" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="CE41" t="s">
         <v>509</v>
@@ -10056,7 +10059,7 @@
     </row>
     <row r="42" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C42" t="s">
         <v>346</v>
@@ -10068,7 +10071,7 @@
         <v>347</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="M42"/>
       <c r="N42"/>
@@ -10101,7 +10104,7 @@
       <c r="BX42" s="17"/>
       <c r="BY42" s="17"/>
       <c r="BZ42" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="CE42" t="s">
         <v>509</v>
@@ -10119,7 +10122,7 @@
     </row>
     <row r="43" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C43" t="s">
         <v>346</v>
@@ -10140,11 +10143,13 @@
         <v>420</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="M43"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="16"/>
+      <c r="O43" s="14" t="s">
+        <v>658</v>
+      </c>
       <c r="P43" s="15"/>
       <c r="Q43" s="15"/>
       <c r="R43" s="15"/>
@@ -10158,7 +10163,7 @@
         <v>1</v>
       </c>
       <c r="AG43" s="8" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="AO43" s="8" t="s">
         <v>555</v>
@@ -10180,6 +10185,9 @@
       </c>
       <c r="BM43" s="8"/>
       <c r="BN43" s="8"/>
+      <c r="BQ43">
+        <v>1</v>
+      </c>
       <c r="BT43" s="17"/>
       <c r="BU43" s="17"/>
       <c r="BV43" s="17"/>
@@ -10197,7 +10205,7 @@
       </c>
       <c r="CK43" s="8"/>
       <c r="CL43" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="CM43">
         <v>22</v>
@@ -10217,7 +10225,7 @@
     </row>
     <row r="44" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C44" t="s">
         <v>346</v>
@@ -10264,7 +10272,7 @@
         <v>427</v>
       </c>
       <c r="CK44" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="DB44">
         <v>1</v>
@@ -10295,19 +10303,19 @@
     </row>
     <row r="46" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C46" t="s">
         <v>346</v>
       </c>
       <c r="D46" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F46" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G46">
         <v>3</v>
@@ -10331,10 +10339,10 @@
         <v>1</v>
       </c>
       <c r="BM46" s="8" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="BN46" s="8" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="BR46">
         <v>1</v>
@@ -10349,13 +10357,13 @@
         <v>1</v>
       </c>
       <c r="BW46" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="CL46" s="14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="CM46" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="CP46">
         <v>25</v>
@@ -10363,7 +10371,7 @@
     </row>
     <row r="47" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C47" t="s">
         <v>346</v>
@@ -10391,7 +10399,7 @@
         <v>0.1</v>
       </c>
       <c r="CL47" s="14" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="CM47">
         <v>-100</v>
@@ -10402,7 +10410,7 @@
     </row>
     <row r="48" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C48" t="s">
         <v>346</v>
@@ -10414,11 +10422,11 @@
         <v>347</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="M48"/>
       <c r="O48" s="14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P48"/>
       <c r="Q48"/>
@@ -10435,7 +10443,7 @@
         <v>1</v>
       </c>
       <c r="CL48" s="14" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="CP48">
         <v>1</v>
@@ -10443,7 +10451,7 @@
     </row>
     <row r="49" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C49" t="s">
         <v>346</v>
@@ -10452,7 +10460,7 @@
         <v>1</v>
       </c>
       <c r="O49" s="14" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AC49">
         <v>1</v>
@@ -10475,7 +10483,7 @@
     </row>
     <row r="50" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C50" t="s">
         <v>514</v>
@@ -10484,7 +10492,7 @@
         <v>347</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AC50">
         <v>1</v>
@@ -10500,7 +10508,7 @@
       </c>
       <c r="CJ50" s="3"/>
       <c r="CS50" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="DB50">
         <v>1</v>
@@ -10517,7 +10525,7 @@
     </row>
     <row r="52" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>437</v>
@@ -10535,7 +10543,7 @@
         <v>1</v>
       </c>
       <c r="AJ52" s="8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AR52" t="s">
         <v>508</v>
@@ -10548,7 +10556,7 @@
       </c>
       <c r="CJ52" s="3"/>
       <c r="CS52" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="53" spans="1:110" x14ac:dyDescent="0.25">
@@ -10556,19 +10564,19 @@
     </row>
     <row r="54" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C54" t="s">
         <v>346</v>
       </c>
       <c r="D54" t="s">
+        <v>583</v>
+      </c>
+      <c r="E54" t="s">
         <v>584</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>585</v>
-      </c>
-      <c r="F54" t="s">
-        <v>586</v>
       </c>
       <c r="G54">
         <v>3</v>
@@ -10592,7 +10600,7 @@
         <v>1</v>
       </c>
       <c r="BM54" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="BR54">
         <v>25</v>
@@ -10607,13 +10615,13 @@
         <v>1</v>
       </c>
       <c r="BW54" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="CL54" s="14" t="s">
+        <v>587</v>
+      </c>
+      <c r="CM54" t="s">
         <v>588</v>
-      </c>
-      <c r="CM54" t="s">
-        <v>589</v>
       </c>
       <c r="CN54">
         <v>2</v>
@@ -10627,13 +10635,13 @@
     </row>
     <row r="55" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>591</v>
+      </c>
+      <c r="C55" t="s">
         <v>592</v>
       </c>
-      <c r="C55" t="s">
-        <v>593</v>
-      </c>
       <c r="O55" s="14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="X55"/>
       <c r="AC55">
@@ -10655,10 +10663,10 @@
         <v>1</v>
       </c>
       <c r="BN55" t="s">
+        <v>593</v>
+      </c>
+      <c r="BZ55" t="s">
         <v>594</v>
-      </c>
-      <c r="BZ55" t="s">
-        <v>595</v>
       </c>
       <c r="CE55" t="s">
         <v>509</v>
@@ -10669,7 +10677,7 @@
     </row>
     <row r="56" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C56" t="s">
         <v>346</v>
@@ -10681,7 +10689,7 @@
         <v>347</v>
       </c>
       <c r="O56" s="14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P56"/>
       <c r="Q56"/>
@@ -10728,10 +10736,10 @@
     </row>
     <row r="57" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>595</v>
+      </c>
+      <c r="C57" t="s">
         <v>596</v>
-      </c>
-      <c r="C57" t="s">
-        <v>597</v>
       </c>
       <c r="I57">
         <v>1</v>
@@ -10740,10 +10748,10 @@
         <v>347</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="O57" s="14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="X57"/>
       <c r="AC57">
@@ -10756,7 +10764,7 @@
         <v>1</v>
       </c>
       <c r="CS57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="DB57">
         <v>1</v>
@@ -10770,10 +10778,10 @@
     </row>
     <row r="58" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>625</v>
+      </c>
+      <c r="C58" t="s">
         <v>626</v>
-      </c>
-      <c r="C58" t="s">
-        <v>627</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>347</v>
@@ -10791,12 +10799,12 @@
         <v>1</v>
       </c>
       <c r="CS58" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="59" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C59" t="s">
         <v>346</v>
@@ -10820,7 +10828,7 @@
         <v>1</v>
       </c>
       <c r="CL59" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="CP59">
         <v>0.5</v>
@@ -10828,7 +10836,7 @@
     </row>
     <row r="60" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C60" t="s">
         <v>346</v>
@@ -10840,7 +10848,7 @@
         <v>420</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AC60">
         <v>1</v>
@@ -10855,7 +10863,7 @@
         <v>1</v>
       </c>
       <c r="CK60" s="14" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="CL60" s="14"/>
       <c r="DB60">
@@ -10870,7 +10878,7 @@
     </row>
     <row r="62" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C62" t="s">
         <v>346</v>
@@ -10897,7 +10905,7 @@
       </c>
       <c r="BT62"/>
       <c r="BZ62" s="20" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="CE62" t="s">
         <v>509</v>
@@ -10916,7 +10924,7 @@
     </row>
     <row r="63" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C63" t="s">
         <v>346</v>
@@ -10928,7 +10936,7 @@
         <v>347</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="M63"/>
       <c r="N63"/>
@@ -10946,7 +10954,7 @@
       </c>
       <c r="BT63"/>
       <c r="BZ63" s="20" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="CE63" t="s">
         <v>509</v>
@@ -10964,7 +10972,7 @@
     </row>
     <row r="64" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C64" t="s">
         <v>346</v>
@@ -10976,7 +10984,7 @@
         <v>347</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O64"/>
       <c r="X64"/>
@@ -10990,7 +10998,7 @@
         <v>1</v>
       </c>
       <c r="CK64" s="14" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="67" spans="88:88" x14ac:dyDescent="0.25">
@@ -12588,7 +12596,7 @@
         <v>557</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H9" s="14">
         <v>1</v>
@@ -12597,7 +12605,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C10" t="s">
         <v>539</v>
@@ -12611,10 +12619,10 @@
     </row>
     <row r="11" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H11" s="14">
         <v>1</v>
@@ -12623,10 +12631,10 @@
     </row>
     <row r="12" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H12" s="14">
         <v>1</v>
@@ -12635,18 +12643,18 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C13" t="s">
         <v>200</v>
       </c>
       <c r="P13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>539</v>
@@ -12656,23 +12664,23 @@
       </c>
       <c r="J14"/>
       <c r="P14" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C15" t="s">
         <v>539</v>
       </c>
       <c r="P15" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C16" t="s">
         <v>542</v>
@@ -12689,49 +12697,49 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>611</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="J17" t="s">
         <v>612</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>605</v>
-      </c>
-      <c r="J17" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H18" s="14">
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C19" t="s">
         <v>200</v>
       </c>
       <c r="P19" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="P20" s="8" t="s">
         <v>617</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Main/Test.xlsx
+++ b/Excel/Main/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BAA8A7-E43D-4721-9766-99CC31404881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E4C4C0-3A0B-42B0-A904-51410F7816DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="512">
   <si>
     <t>Id</t>
   </si>
@@ -1881,487 +1881,18 @@
     <t>猫诱导后续</t>
   </si>
   <si>
-    <t>自己入场</t>
-  </si>
-  <si>
-    <t>干员链式弹道索敌</t>
-  </si>
-  <si>
-    <t>干员m3攻击</t>
-  </si>
-  <si>
-    <t>血量比例升序</t>
-  </si>
-  <si>
-    <t>0,0#0,1#0,-1#1,0#2,0#1,1#1,-1#2,1#2,-1#-1,0#-1,1#-1,-1</t>
-  </si>
-  <si>
-    <t>跟随攻击</t>
-  </si>
-  <si>
-    <t>M3链式弹道</t>
-  </si>
-  <si>
-    <t>m3攻速提升buff</t>
-  </si>
-  <si>
-    <t>夜莺普攻击中</t>
-  </si>
-  <si>
-    <t>获取重构体</t>
-  </si>
-  <si>
-    <t>获取单位</t>
-  </si>
-  <si>
-    <t>{"Count":1,"UnitId":"重构体"}</t>
-  </si>
-  <si>
-    <t>重构体天赋</t>
-  </si>
-  <si>
-    <t>重构体天赋加攻</t>
-  </si>
-  <si>
-    <t>重构体中毒</t>
-  </si>
-  <si>
-    <t>0,0#0,1#0,-1#1,0#1,1#1,-1#-1,0#-1,1#-1,-1</t>
-  </si>
-  <si>
-    <t>重构体加攻</t>
-  </si>
-  <si>
-    <t>重构体绝食</t>
-  </si>
-  <si>
-    <t>重构体绝食1,重构体绝食2</t>
-  </si>
-  <si>
-    <t>干员M3</t>
-  </si>
-  <si>
-    <t>monstr</t>
-  </si>
-  <si>
-    <t>4179</t>
-  </si>
-  <si>
-    <t>Mon3tr</t>
-  </si>
-  <si>
-    <t>干员m3攻击,获取重构体</t>
-  </si>
-  <si>
-    <t>医疗</t>
-  </si>
-  <si>
-    <t>链愈师</t>
-  </si>
-  <si>
-    <t>头像_召唤物_Mon3tr</t>
-  </si>
-  <si>
-    <t>half_kalts</t>
-  </si>
-  <si>
-    <t>kalts</t>
-  </si>
-  <si>
-    <t>远程位</t>
-  </si>
-  <si>
-    <t>远程,Mon3tr</t>
-  </si>
-  <si>
-    <t>重构体</t>
-  </si>
-  <si>
-    <t>头像_召唤物_幻影</t>
-  </si>
-  <si>
-    <t>链式弹道</t>
-  </si>
-  <si>
-    <t>0,0#-1,-1#0,-1#1,-1#-1,0#1,0#-1,1#0,1#1,1</t>
-  </si>
-  <si>
-    <t>数值变化</t>
-  </si>
-  <si>
-    <t>银灰真银斩buff</t>
-  </si>
-  <si>
-    <t>{"t":["AgiAdd"]}</t>
-  </si>
-  <si>
-    <t>中毒</t>
-  </si>
-  <si>
-    <t>棘刺中毒</t>
-  </si>
-  <si>
-    <t>{"FarAttackUnitRate":1,"DamageType":"Real","TriggerTime":0.1}</t>
-  </si>
-  <si>
-    <t>{"t":["AttackRate"]}</t>
-  </si>
-  <si>
-    <t>重构体绝食1</t>
-  </si>
-  <si>
-    <t>绝食</t>
-  </si>
-  <si>
-    <t>{"HealOnly":"干员M3"}</t>
-  </si>
-  <si>
-    <t>重构体绝食2</t>
-  </si>
-  <si>
-    <t>{"HealOnly":"重构体"}</t>
-  </si>
-  <si>
-    <t>{"MoveHeight":0,"MaxLinkNum":4,"SkillId":"干员链式弹道索敌","ReductionRate":0.1,"CanBack":"false"}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>{"MoveHeight":0,"MaxLinkNum":10,"ReductionRate":0.25,"SkillId":"链式弹道索敌","CanBack":"false"}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{"ShowRange":1}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>禁止主动</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>放置降序</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>m3自身攻速</t>
-  </si>
-  <si>
-    <t>m32加成</t>
-  </si>
-  <si>
-    <t>m32</t>
-  </si>
-  <si>
-    <t>策略：超负荷</t>
-  </si>
-  <si>
-    <t>技能期间重构体每受到一次攻击，就会进行一次跳跃治疗，第二天赋的效果额外追加1.8倍</t>
-  </si>
-  <si>
-    <t>skill_icon_skchr_kalts_2</t>
-  </si>
-  <si>
-    <t>手动</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>m32加成,m32动作</t>
-  </si>
-  <si>
-    <t>m32攻击</t>
-  </si>
-  <si>
-    <t>m3额外伤害,m32自身攻速</t>
-  </si>
-  <si>
-    <t>Skill_2_Loop</t>
-  </si>
-  <si>
-    <t>m3攻速提升buff,m32攻速提升buff</t>
-  </si>
-  <si>
-    <t>m3额外伤害</t>
-  </si>
-  <si>
-    <t>普通法球</t>
-  </si>
-  <si>
-    <t>m32自身攻速</t>
-  </si>
-  <si>
-    <t>m32重构体</t>
-  </si>
-  <si>
-    <t>m32追加</t>
-  </si>
-  <si>
-    <t>m32结束</t>
-  </si>
-  <si>
-    <t>m32攻速提升buff</t>
-  </si>
-  <si>
-    <t>m32启动</t>
-  </si>
-  <si>
-    <t>Skill_2_Begin</t>
-  </si>
-  <si>
-    <t>m32自身结束</t>
-  </si>
-  <si>
-    <t>技能结束</t>
-  </si>
-  <si>
-    <t>Skill_2_End</t>
-  </si>
-  <si>
-    <t>重构体2</t>
-  </si>
-  <si>
-    <t>m33</t>
-  </si>
-  <si>
-    <t>策略：熔毁</t>
-  </si>
-  <si>
-    <t>攻击范围改变，攻击力+330%，攻击间隔降低(-1.5)，阻挡数+2，生命上限+5000，每秒流失80点生命值，同时攻击阻挡的所有敌人，伤害类型变为真实，攻击治疗自身相当于攻击力50%的生命值\n受到致命伤害时结束技能</t>
-  </si>
-  <si>
-    <t>skill_icon_skchr_kalts_3</t>
-  </si>
-  <si>
-    <t>m33启动</t>
-  </si>
-  <si>
-    <t>m33加成,m3阻挡变化,m3中毒,m33特效,m33动作</t>
-  </si>
-  <si>
-    <t>3.3,-1.5,5000</t>
-  </si>
-  <si>
-    <t>m33加成</t>
-  </si>
-  <si>
-    <t>m3标记</t>
-  </si>
-  <si>
-    <t>m33攻击</t>
-  </si>
-  <si>
-    <t>群攻</t>
-  </si>
-  <si>
-    <t>m33治疗</t>
-  </si>
-  <si>
-    <t>Skill_3_Loop</t>
-  </si>
-  <si>
-    <t>m33锁血</t>
-  </si>
-  <si>
-    <t>锁血治疗</t>
-  </si>
-  <si>
-    <t>致命</t>
-  </si>
-  <si>
-    <t>m33结束</t>
-  </si>
-  <si>
-    <t>m33自身结束</t>
-  </si>
-  <si>
-    <t>Skill_3_End,Skill_3_Back</t>
-  </si>
-  <si>
-    <t>m32,m33</t>
-  </si>
-  <si>
-    <t>重构体天赋,重构体绝食,重构体2</t>
-  </si>
-  <si>
-    <t>眩晕,眩晕2,寒冷,冻结</t>
-  </si>
-  <si>
-    <t>普通Buff</t>
-  </si>
-  <si>
-    <t>m32动作</t>
-  </si>
-  <si>
-    <t>{"IdleAnimation":["Skill_2_Idle"]}</t>
-  </si>
-  <si>
-    <t>{"t":["AttackRate","AttackGapAdd","HpAdd"]}</t>
-  </si>
-  <si>
-    <t>m3阻挡变化</t>
-  </si>
-  <si>
-    <t>{"t":["StopCountAdd"]}</t>
-  </si>
-  <si>
-    <t>m3中毒</t>
-  </si>
-  <si>
-    <t>m33特效</t>
-  </si>
-  <si>
-    <t>星熊2buff</t>
-  </si>
-  <si>
-    <t>阿米娅2buff</t>
-  </si>
-  <si>
-    <t>m33动作</t>
-  </si>
-  <si>
-    <t>{"IdleAnimation":["Skill_3_Idle"]}</t>
-  </si>
-  <si>
-    <t>设置属性</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"t":["ModelScale"],"v":[0.25]}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0,0</t>
-  </si>
-  <si>
-    <t>高台m3buff</t>
-  </si>
-  <si>
-    <t>释放技能</t>
-  </si>
-  <si>
-    <t>{"Count":1,"UnitId":"地面M3"}</t>
-  </si>
-  <si>
-    <t>地面m3</t>
-  </si>
-  <si>
-    <t>m33攻击,m33治疗,m33锁血,地面m3死亡</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{"LockHp":0.0001</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}</t>
-    </r>
-  </si>
-  <si>
-    <t>地面m3死亡</t>
-  </si>
-  <si>
-    <t>强制撤退</t>
-  </si>
-  <si>
-    <t>{"Time":25}</t>
-  </si>
-  <si>
-    <t>地面m3落地无敌</t>
-  </si>
-  <si>
-    <t>无敌</t>
-  </si>
-  <si>
-    <t>地面m3释放buff</t>
-  </si>
-  <si>
-    <t>m33加成,m3阻挡变化,m3中毒,m33动作</t>
-  </si>
-  <si>
-    <t>地面M3</t>
-  </si>
-  <si>
-    <t>地面m3,地面m3落地无敌,地面m3释放buff</t>
-  </si>
-  <si>
-    <t>部署地面m3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>重构体</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>{"UnitId":"猫诱导后续","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"猫诱导"}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>#m33重构体</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>#重构体死亡</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>#获取地面m3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>m33自身结束,高台m3buff</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>重构体撤退，获得地面m3在25秒内获得以下效果：攻击范围改变，攻击力+330%，攻击间隔降低(-1.5)，阻挡数+2，生命上限+5000，每秒流失80点生命值，同时攻击阻挡的所有敌人，伤害类型变为真实，攻击治疗自身相当于攻击力50%的生命值，生命值不会低于1。\n地面m3存在期间，自身获得无敌、缴械、不进行攻击、技力回复速度-100</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_3_Back</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>#模型缩小</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>技力回复变化,无敌,缴械</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>m33启动,部署地面m3,高台m3buff</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mon3tr</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"UnitId":"地面M3","TargetPos":"useSelfTargetPos","SetMod":"Replace","UseMod":"UserDirection","UserName":"Mon3tr"}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_3_Begin</t>
-  </si>
-  <si>
     <t>本能的召唤</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2378,31 +1909,7 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>m3攻速提升buff,m32攻速提升buff</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>自己以外</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>#重构体消除自身buff</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>被治疗</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>m32重构体</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>m32追加,m32启动</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>m32攻击,m32结束,m32自身结束,m32重构体</t>
+    <t>Target.Hp&gt;4000</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2957,7 +2464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:B5"/>
+  <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -2985,14 +2492,6 @@
       </c>
       <c r="B4" s="8" t="s">
         <v>479</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>523</v>
-      </c>
-      <c r="B5" t="s">
-        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -3720,7 +3219,7 @@
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>650</v>
+        <v>507</v>
       </c>
       <c r="B7" t="s">
         <v>126</v>
@@ -3778,13 +3277,13 @@
         <v>-1</v>
       </c>
       <c r="AG7" s="8" t="s">
-        <v>650</v>
+        <v>507</v>
       </c>
       <c r="AH7" t="s">
         <v>122</v>
       </c>
       <c r="AI7" s="8" t="s">
-        <v>651</v>
+        <v>508</v>
       </c>
       <c r="AK7">
         <v>3</v>
@@ -4250,374 +3749,15 @@
       </c>
     </row>
     <row r="13" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>523</v>
-      </c>
-      <c r="B13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" t="s">
-        <v>524</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="F13" t="str">
-        <f>"char_"&amp;E13&amp;"_"&amp;D13</f>
-        <v>char_4179_monstr</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-      <c r="J13">
-        <v>90</v>
-      </c>
-      <c r="K13">
-        <v>2235</v>
-      </c>
-      <c r="M13">
-        <v>583</v>
-      </c>
-      <c r="O13">
-        <v>221</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>16</v>
-      </c>
-      <c r="U13">
-        <v>0.5</v>
-      </c>
-      <c r="V13">
-        <v>70</v>
-      </c>
-      <c r="Y13">
-        <v>0.05</v>
-      </c>
-      <c r="Z13">
-        <v>2.85</v>
-      </c>
-      <c r="AC13">
-        <v>1</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>526</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>527</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>601</v>
-      </c>
-      <c r="AM13">
-        <v>1</v>
-      </c>
-      <c r="AO13">
-        <v>1</v>
-      </c>
-      <c r="AP13">
-        <v>0.5</v>
-      </c>
-      <c r="AW13">
-        <v>0.25</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>528</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>529</v>
-      </c>
-      <c r="BD13" t="s">
-        <v>530</v>
-      </c>
-      <c r="BE13" t="s">
-        <v>531</v>
-      </c>
-      <c r="BF13" t="s">
-        <v>532</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>128</v>
-      </c>
-      <c r="BH13">
-        <v>6</v>
-      </c>
-      <c r="BI13" t="s">
-        <v>533</v>
-      </c>
-      <c r="BJ13" t="s">
-        <v>534</v>
-      </c>
-      <c r="BM13" t="s">
-        <v>123</v>
-      </c>
-      <c r="BN13" t="s">
-        <v>124</v>
-      </c>
-      <c r="BP13" t="s">
-        <v>125</v>
-      </c>
-      <c r="BQ13" t="s">
-        <v>125</v>
-      </c>
-      <c r="BS13">
-        <v>1</v>
-      </c>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>535</v>
-      </c>
-      <c r="B14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D14" t="s">
-        <v>428</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="F14" t="s">
-        <v>499</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14">
-        <v>90</v>
-      </c>
-      <c r="K14">
-        <v>5433</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>221</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>3</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>15</v>
-      </c>
-      <c r="Y14">
-        <v>0.05</v>
-      </c>
-      <c r="Z14">
-        <v>1</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>-1</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>535</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>602</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>1</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="s">
-        <v>603</v>
-      </c>
-      <c r="AW14">
-        <v>0.25</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>528</v>
-      </c>
-      <c r="BD14" t="s">
-        <v>536</v>
-      </c>
-      <c r="BE14" t="str">
-        <f>"half_"&amp;D14</f>
-        <v>half_otter</v>
-      </c>
-      <c r="BF14" t="str">
-        <f>D14</f>
-        <v>otter</v>
-      </c>
-      <c r="BG14" t="s">
-        <v>128</v>
-      </c>
-      <c r="BH14">
-        <v>6</v>
-      </c>
-      <c r="BI14" t="s">
-        <v>127</v>
-      </c>
-      <c r="BJ14" t="s">
-        <v>535</v>
-      </c>
-      <c r="BM14" t="s">
-        <v>123</v>
-      </c>
-      <c r="BN14" t="s">
-        <v>124</v>
-      </c>
-      <c r="BS14">
-        <v>1</v>
-      </c>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>632</v>
-      </c>
-      <c r="B15" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" t="s">
-        <v>524</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="F15" t="str">
-        <f>"char_"&amp;E15&amp;"_"&amp;D15</f>
-        <v>char_4179_monstr</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>2</v>
-      </c>
-      <c r="J15">
-        <v>90</v>
-      </c>
-      <c r="K15">
-        <v>2235</v>
-      </c>
-      <c r="M15">
-        <v>583</v>
-      </c>
-      <c r="O15">
-        <v>221</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>-1</v>
-      </c>
-      <c r="U15">
-        <v>0.5</v>
-      </c>
-      <c r="V15">
-        <v>70</v>
-      </c>
-      <c r="Y15">
-        <v>0.05</v>
-      </c>
-      <c r="Z15">
-        <v>2.85</v>
-      </c>
-      <c r="AC15">
-        <v>1</v>
-      </c>
-      <c r="AD15">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>633</v>
-      </c>
-      <c r="AN15">
-        <v>1</v>
-      </c>
-      <c r="AO15">
-        <v>3</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0.25</v>
-      </c>
-      <c r="BB15" t="s">
-        <v>528</v>
-      </c>
-      <c r="BC15" t="s">
-        <v>529</v>
-      </c>
-      <c r="BD15" t="s">
-        <v>530</v>
-      </c>
-      <c r="BE15" t="s">
-        <v>531</v>
-      </c>
-      <c r="BF15" t="s">
-        <v>532</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>128</v>
-      </c>
-      <c r="BH15">
-        <v>6</v>
-      </c>
-      <c r="BI15" t="s">
-        <v>533</v>
-      </c>
-      <c r="BJ15" t="s">
-        <v>534</v>
-      </c>
-      <c r="BM15" t="s">
-        <v>124</v>
-      </c>
-      <c r="BN15" t="s">
-        <v>124</v>
-      </c>
-      <c r="BP15" s="19" t="s">
-        <v>600</v>
-      </c>
-      <c r="BQ15" t="s">
-        <v>125</v>
-      </c>
-      <c r="BS15">
-        <v>1</v>
-      </c>
+      <c r="E15" s="1"/>
+      <c r="AG15" s="8"/>
+      <c r="BP15" s="19"/>
     </row>
     <row r="25" spans="35:63" x14ac:dyDescent="0.25">
       <c r="AI25" s="8"/>
@@ -8490,6 +7630,9 @@
       <c r="C6" s="8" t="s">
         <v>405</v>
       </c>
+      <c r="H6" s="8" t="s">
+        <v>511</v>
+      </c>
       <c r="K6" s="9" t="s">
         <v>422</v>
       </c>
@@ -8541,7 +7684,7 @@
         <v>405</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>554</v>
+        <v>505</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>420</v>
@@ -8644,7 +7787,7 @@
       </c>
       <c r="CJ10" s="3"/>
       <c r="CS10" s="8" t="s">
-        <v>652</v>
+        <v>509</v>
       </c>
       <c r="DB10">
         <v>1</v>
@@ -8665,7 +7808,7 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>651</v>
+        <v>508</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>493</v>
@@ -8689,7 +7832,7 @@
       <c r="BT12"/>
       <c r="CJ12" s="3"/>
       <c r="CS12" s="8" t="s">
-        <v>653</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
@@ -8966,7 +8109,7 @@
       <c r="BT19"/>
       <c r="CJ19" s="3"/>
       <c r="CS19" s="8" t="s">
-        <v>636</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
@@ -9167,141 +8310,20 @@
       <c r="CJ25" s="3"/>
     </row>
     <row r="26" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>505</v>
-      </c>
-      <c r="C26" t="s">
-        <v>346</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>554</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>420</v>
-      </c>
+      <c r="J26" s="8"/>
       <c r="O26"/>
-      <c r="AC26">
-        <v>1</v>
-      </c>
-      <c r="AO26" s="8" t="s">
-        <v>555</v>
-      </c>
-      <c r="AR26" t="s">
-        <v>538</v>
-      </c>
-      <c r="CS26" s="8" t="s">
-        <v>553</v>
-      </c>
+      <c r="AO26" s="8"/>
+      <c r="CS26" s="8"/>
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>506</v>
-      </c>
-      <c r="C27" t="s">
-        <v>346</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>490</v>
-      </c>
       <c r="P27"/>
-      <c r="AC27">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="s">
-        <v>507</v>
-      </c>
-      <c r="AR27" t="s">
-        <v>508</v>
-      </c>
-      <c r="AW27">
-        <v>1</v>
-      </c>
-      <c r="AX27">
-        <v>1</v>
-      </c>
-      <c r="BB27">
-        <v>1</v>
-      </c>
-      <c r="BZ27" t="s">
-        <v>55</v>
-      </c>
-      <c r="CE27" t="s">
-        <v>509</v>
-      </c>
-      <c r="CF27" t="s">
-        <v>510</v>
-      </c>
-      <c r="CG27" t="s">
-        <v>474</v>
-      </c>
-      <c r="CL27" t="s">
-        <v>511</v>
-      </c>
-      <c r="CM27">
-        <v>22</v>
-      </c>
-      <c r="CP27">
-        <v>10</v>
-      </c>
-      <c r="CW27" t="s">
-        <v>512</v>
-      </c>
     </row>
     <row r="28" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>513</v>
-      </c>
-      <c r="C28" t="s">
-        <v>514</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="AC28">
-        <v>1</v>
-      </c>
-      <c r="AF28">
-        <v>1</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB28">
-        <v>1</v>
-      </c>
       <c r="CJ28" s="3"/>
-      <c r="CS28" t="s">
-        <v>515</v>
-      </c>
-      <c r="DB28">
-        <v>1</v>
-      </c>
-      <c r="DE28">
-        <v>1</v>
-      </c>
-      <c r="DF28">
-        <v>1</v>
-      </c>
     </row>
     <row r="29" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>516</v>
-      </c>
-      <c r="C29" t="s">
-        <v>346</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="K29" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="L29" s="12" t="s">
-        <v>504</v>
-      </c>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
       <c r="M29"/>
       <c r="N29"/>
       <c r="O29" s="12"/>
@@ -9314,21 +8336,6 @@
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
       <c r="X29"/>
-      <c r="AC29">
-        <v>1</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>348</v>
-      </c>
-      <c r="AR29" t="s">
-        <v>351</v>
-      </c>
-      <c r="BB29">
-        <v>1</v>
-      </c>
-      <c r="BM29" t="s">
-        <v>517</v>
-      </c>
       <c r="BS29" s="13"/>
       <c r="BT29" s="13"/>
       <c r="BU29" s="13"/>
@@ -9336,29 +8343,8 @@
       <c r="BW29" s="13"/>
       <c r="BX29" s="13"/>
       <c r="BY29"/>
-      <c r="CL29" t="s">
-        <v>518</v>
-      </c>
-      <c r="CM29">
-        <v>8</v>
-      </c>
-      <c r="CP29">
-        <v>9999</v>
-      </c>
-      <c r="DB29">
-        <v>1</v>
-      </c>
     </row>
     <row r="30" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>517</v>
-      </c>
-      <c r="C30" t="s">
-        <v>346</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
       <c r="K30" s="12"/>
       <c r="L30" s="12"/>
       <c r="M30"/>
@@ -9373,18 +8359,6 @@
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
       <c r="X30"/>
-      <c r="AC30">
-        <v>1</v>
-      </c>
-      <c r="AR30" t="s">
-        <v>519</v>
-      </c>
-      <c r="BB30">
-        <v>99</v>
-      </c>
-      <c r="BQ30">
-        <v>0.1</v>
-      </c>
       <c r="BS30" s="13"/>
       <c r="BT30" s="13"/>
       <c r="BU30" s="13"/>
@@ -9392,42 +8366,10 @@
       <c r="BW30" s="13"/>
       <c r="BX30" s="13"/>
       <c r="BY30"/>
-      <c r="CL30" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="CM30">
-        <v>0.2</v>
-      </c>
-      <c r="CP30">
-        <v>0.2</v>
-      </c>
-      <c r="DB30">
-        <v>1</v>
-      </c>
+      <c r="CL30" s="14"/>
     </row>
     <row r="31" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>521</v>
-      </c>
-      <c r="C31" t="s">
-        <v>346</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="AC31">
-        <v>1</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>348</v>
-      </c>
       <c r="AW31" s="3"/>
-      <c r="BB31">
-        <v>1</v>
-      </c>
       <c r="BT31"/>
       <c r="BU31"/>
       <c r="BV31"/>
@@ -9445,33 +8387,14 @@
       <c r="CI31" s="3"/>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
-      <c r="CL31" t="s">
-        <v>522</v>
-      </c>
-      <c r="CP31">
-        <v>99999</v>
-      </c>
     </row>
     <row r="32" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>556</v>
-      </c>
-      <c r="C32" t="s">
-        <v>346</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>347</v>
-      </c>
+      <c r="K32" s="15"/>
       <c r="L32" s="15"/>
       <c r="M32"/>
       <c r="N32"/>
       <c r="O32" s="15"/>
-      <c r="P32" s="16" t="s">
-        <v>557</v>
-      </c>
+      <c r="P32" s="16"/>
       <c r="Q32" s="15"/>
       <c r="R32" s="16"/>
       <c r="S32"/>
@@ -9480,18 +8403,6 @@
       <c r="V32" s="15"/>
       <c r="W32" s="15"/>
       <c r="X32"/>
-      <c r="AC32">
-        <v>1</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>348</v>
-      </c>
-      <c r="AR32" t="s">
-        <v>351</v>
-      </c>
-      <c r="BB32">
-        <v>1</v>
-      </c>
       <c r="BT32"/>
       <c r="BU32" s="17"/>
       <c r="BV32" s="17"/>
@@ -9499,17 +8410,8 @@
       <c r="BX32" s="17"/>
       <c r="BY32" s="17"/>
       <c r="BZ32" s="17"/>
-      <c r="CL32" t="s">
-        <v>511</v>
-      </c>
-      <c r="CM32">
-        <v>22</v>
-      </c>
-      <c r="CP32">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:110" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:90" x14ac:dyDescent="0.25">
       <c r="K33" s="15"/>
       <c r="L33" s="15"/>
       <c r="M33" s="15"/>
@@ -9531,31 +8433,8 @@
       <c r="BX33" s="17"/>
       <c r="BY33" s="17"/>
     </row>
-    <row r="34" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>558</v>
-      </c>
-      <c r="C34" t="s">
-        <v>346</v>
-      </c>
-      <c r="D34" t="s">
-        <v>559</v>
-      </c>
-      <c r="E34" t="s">
-        <v>560</v>
-      </c>
-      <c r="F34" t="s">
-        <v>561</v>
-      </c>
-      <c r="G34">
-        <v>3</v>
-      </c>
-      <c r="J34" t="s">
-        <v>489</v>
-      </c>
-      <c r="K34" s="15" t="s">
-        <v>562</v>
-      </c>
+    <row r="34" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="K34" s="15"/>
       <c r="L34" s="15"/>
       <c r="M34"/>
       <c r="N34" s="15"/>
@@ -9569,63 +8448,23 @@
       <c r="V34" s="15"/>
       <c r="W34" s="15"/>
       <c r="X34" s="15"/>
-      <c r="AC34">
-        <v>1</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB34">
-        <v>1</v>
-      </c>
-      <c r="BM34" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="BN34" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="BR34">
-        <v>30</v>
-      </c>
-      <c r="BT34" s="17">
-        <v>13</v>
-      </c>
-      <c r="BU34" s="17">
-        <v>15</v>
-      </c>
-      <c r="BV34" s="17">
-        <v>1</v>
-      </c>
-      <c r="BW34" s="17" t="s">
-        <v>563</v>
-      </c>
+      <c r="BM34" s="8"/>
+      <c r="BN34" s="8"/>
+      <c r="BT34" s="17"/>
+      <c r="BU34" s="17"/>
+      <c r="BV34" s="17"/>
+      <c r="BW34" s="17"/>
       <c r="BX34" s="17"/>
       <c r="BY34" s="17"/>
-      <c r="CL34" s="16" t="s">
-        <v>564</v>
-      </c>
-      <c r="CP34">
-        <v>30</v>
-      </c>
-      <c r="DB34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>565</v>
-      </c>
-      <c r="C35" t="s">
-        <v>346</v>
-      </c>
+      <c r="CL34" s="16"/>
+    </row>
+    <row r="35" spans="1:90" x14ac:dyDescent="0.25">
       <c r="J35" s="15"/>
       <c r="K35" s="15"/>
       <c r="L35" s="15"/>
       <c r="M35"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="16" t="s">
-        <v>557</v>
-      </c>
+      <c r="O35" s="16"/>
       <c r="P35"/>
       <c r="Q35"/>
       <c r="R35" s="15"/>
@@ -9635,80 +8474,16 @@
       <c r="V35" s="15"/>
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
-      <c r="AC35">
-        <v>1</v>
-      </c>
-      <c r="AD35">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="s">
-        <v>507</v>
-      </c>
-      <c r="AQ35" t="s">
-        <v>535</v>
-      </c>
-      <c r="AU35">
-        <v>1</v>
-      </c>
-      <c r="AW35">
-        <v>1</v>
-      </c>
-      <c r="AX35">
-        <v>1</v>
-      </c>
-      <c r="BB35">
-        <v>1</v>
-      </c>
-      <c r="BN35" t="s">
-        <v>566</v>
-      </c>
       <c r="BT35" s="17"/>
       <c r="BU35" s="17"/>
       <c r="BV35" s="17"/>
       <c r="BW35" s="17"/>
       <c r="BX35" s="17"/>
       <c r="BY35" s="17"/>
-      <c r="BZ35" t="s">
-        <v>567</v>
-      </c>
-      <c r="CE35" t="s">
-        <v>509</v>
-      </c>
-      <c r="CF35" t="s">
-        <v>510</v>
-      </c>
-      <c r="CG35" t="s">
-        <v>474</v>
-      </c>
-      <c r="CL35" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="CM35">
-        <v>22</v>
-      </c>
-      <c r="CN35">
-        <v>39.6</v>
-      </c>
-      <c r="CP35">
-        <v>10</v>
-      </c>
-      <c r="CW35" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="36" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>569</v>
-      </c>
-      <c r="C36" t="s">
-        <v>346</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="K36" s="15" t="s">
-        <v>347</v>
-      </c>
+      <c r="CL35" s="8"/>
+    </row>
+    <row r="36" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="K36" s="15"/>
       <c r="L36" s="15"/>
       <c r="M36"/>
       <c r="N36" s="15"/>
@@ -9722,33 +8497,6 @@
       <c r="V36" s="15"/>
       <c r="W36" s="15"/>
       <c r="X36" s="15"/>
-      <c r="AC36">
-        <v>1</v>
-      </c>
-      <c r="AD36">
-        <v>1</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>535</v>
-      </c>
-      <c r="AO36" t="s">
-        <v>507</v>
-      </c>
-      <c r="AR36" t="s">
-        <v>508</v>
-      </c>
-      <c r="AV36" t="s">
-        <v>470</v>
-      </c>
-      <c r="AX36">
-        <v>1</v>
-      </c>
-      <c r="AZ36">
-        <v>2</v>
-      </c>
-      <c r="BB36">
-        <v>1</v>
-      </c>
       <c r="BT36" s="17"/>
       <c r="BU36" s="17"/>
       <c r="BV36" s="17"/>
@@ -9756,38 +8504,13 @@
       <c r="BX36" s="17"/>
       <c r="BY36" s="17"/>
       <c r="BZ36" s="18"/>
-      <c r="CF36" t="s">
-        <v>570</v>
-      </c>
-      <c r="CG36" t="s">
-        <v>474</v>
-      </c>
-      <c r="DB36">
-        <v>1</v>
-      </c>
-      <c r="DF36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>571</v>
-      </c>
-      <c r="C37" t="s">
-        <v>346</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="K37" s="15" t="s">
-        <v>347</v>
-      </c>
+    </row>
+    <row r="37" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="K37" s="15"/>
       <c r="L37" s="15"/>
       <c r="M37"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="16" t="s">
-        <v>557</v>
-      </c>
+      <c r="O37" s="16"/>
       <c r="P37"/>
       <c r="Q37"/>
       <c r="R37" s="15"/>
@@ -9797,56 +8520,19 @@
       <c r="V37" s="15"/>
       <c r="W37" s="15"/>
       <c r="X37" s="15"/>
-      <c r="AC37">
-        <v>1</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>348</v>
-      </c>
-      <c r="AU37">
-        <v>1</v>
-      </c>
-      <c r="BB37">
-        <v>1</v>
-      </c>
       <c r="BT37" s="17"/>
       <c r="BU37" s="17"/>
       <c r="BV37" s="17"/>
       <c r="BW37" s="17"/>
       <c r="BX37" s="17"/>
       <c r="BY37" s="17"/>
-      <c r="CL37" t="s">
-        <v>568</v>
-      </c>
-      <c r="CM37">
-        <v>22</v>
-      </c>
-      <c r="CN37">
-        <v>39.6</v>
-      </c>
-      <c r="CP37">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
-        <v>658</v>
-      </c>
-      <c r="C38" t="s">
-        <v>346</v>
-      </c>
-      <c r="I38">
-        <v>1</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>422</v>
-      </c>
+    </row>
+    <row r="38" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="A38" s="8"/>
       <c r="L38" s="15"/>
       <c r="M38"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="16" t="s">
-        <v>557</v>
-      </c>
+      <c r="O38" s="16"/>
       <c r="P38"/>
       <c r="Q38"/>
       <c r="R38" s="15"/>
@@ -9856,47 +8542,16 @@
       <c r="V38" s="15"/>
       <c r="W38" s="15"/>
       <c r="X38" s="15"/>
-      <c r="AC38">
-        <v>1</v>
-      </c>
-      <c r="AJ38" t="s">
-        <v>535</v>
-      </c>
-      <c r="AR38" t="s">
-        <v>508</v>
-      </c>
-      <c r="BB38">
-        <v>1</v>
-      </c>
-      <c r="BQ38">
-        <v>0.1</v>
-      </c>
       <c r="BT38" s="17"/>
       <c r="BU38" s="17"/>
       <c r="BV38" s="17"/>
       <c r="BW38" s="17"/>
       <c r="BX38" s="17"/>
       <c r="BY38" s="17"/>
-      <c r="CL38" s="16" t="s">
-        <v>572</v>
-      </c>
-      <c r="CP38">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>573</v>
-      </c>
-      <c r="C39" t="s">
-        <v>346</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="K39" s="15" t="s">
-        <v>347</v>
-      </c>
+      <c r="CL38" s="16"/>
+    </row>
+    <row r="39" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="K39" s="15"/>
       <c r="L39" s="15"/>
       <c r="M39"/>
       <c r="N39" s="15"/>
@@ -9910,16 +8565,7 @@
       <c r="V39" s="15"/>
       <c r="W39" s="15"/>
       <c r="X39" s="15"/>
-      <c r="AC39">
-        <v>1</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>348</v>
-      </c>
       <c r="AW39" s="15"/>
-      <c r="BB39">
-        <v>1</v>
-      </c>
       <c r="BT39"/>
       <c r="BU39"/>
       <c r="BV39"/>
@@ -9935,39 +8581,15 @@
       <c r="CG39" s="15"/>
       <c r="CH39" s="15"/>
       <c r="CI39" s="15"/>
-      <c r="CL39" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="CP39">
-        <v>40</v>
-      </c>
-      <c r="DB39">
-        <v>1</v>
-      </c>
-      <c r="DF39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>574</v>
-      </c>
-      <c r="C40" t="s">
-        <v>346</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
+      <c r="CL39" s="16"/>
+    </row>
+    <row r="40" spans="1:90" x14ac:dyDescent="0.25">
       <c r="K40" s="15"/>
       <c r="L40" s="15"/>
       <c r="M40"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="16" t="s">
-        <v>557</v>
-      </c>
-      <c r="P40" s="16" t="s">
-        <v>573</v>
-      </c>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
       <c r="Q40" s="15"/>
       <c r="R40" s="15"/>
       <c r="S40" s="15"/>
@@ -9976,38 +8598,15 @@
       <c r="V40" s="15"/>
       <c r="W40" s="15"/>
       <c r="X40" s="15"/>
-      <c r="AC40">
-        <v>1</v>
-      </c>
-      <c r="AT40">
-        <v>20</v>
-      </c>
-      <c r="BB40">
-        <v>99</v>
-      </c>
       <c r="BT40" s="17"/>
       <c r="BU40" s="17"/>
       <c r="BV40" s="17"/>
       <c r="BW40" s="17"/>
       <c r="BX40" s="17"/>
       <c r="BY40" s="17"/>
-      <c r="CK40" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="41" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>576</v>
-      </c>
-      <c r="C41" t="s">
-        <v>346</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="K41" s="15" t="s">
-        <v>347</v>
-      </c>
+    </row>
+    <row r="41" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="K41" s="15"/>
       <c r="L41" s="15"/>
       <c r="M41"/>
       <c r="N41"/>
@@ -10021,58 +8620,18 @@
       <c r="V41" s="15"/>
       <c r="W41" s="15"/>
       <c r="X41" s="15"/>
-      <c r="AC41">
-        <v>1</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB41">
-        <v>1</v>
-      </c>
-      <c r="BQ41">
-        <v>0.1</v>
-      </c>
       <c r="BT41"/>
       <c r="BU41" s="17"/>
       <c r="BV41" s="17"/>
       <c r="BW41" s="17"/>
       <c r="BX41" s="17"/>
       <c r="BY41" s="17"/>
-      <c r="BZ41" t="s">
-        <v>577</v>
-      </c>
-      <c r="CE41" t="s">
-        <v>509</v>
-      </c>
       <c r="CG41" s="15"/>
       <c r="CH41" s="15"/>
-      <c r="DB41">
-        <v>1</v>
-      </c>
-      <c r="DE41">
-        <v>1</v>
-      </c>
-      <c r="DF41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>578</v>
-      </c>
-      <c r="C42" t="s">
-        <v>346</v>
-      </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="L42" s="15" t="s">
-        <v>579</v>
-      </c>
+    </row>
+    <row r="42" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
       <c r="M42"/>
       <c r="N42"/>
       <c r="O42" s="15"/>
@@ -10085,71 +8644,18 @@
       <c r="V42" s="15"/>
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
-      <c r="AC42">
-        <v>1</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB42">
-        <v>1</v>
-      </c>
-      <c r="BQ42">
-        <v>0.2</v>
-      </c>
       <c r="BT42"/>
       <c r="BU42" s="17"/>
       <c r="BV42" s="17"/>
       <c r="BW42" s="17"/>
       <c r="BX42" s="17"/>
       <c r="BY42" s="17"/>
-      <c r="BZ42" t="s">
-        <v>580</v>
-      </c>
-      <c r="CE42" t="s">
-        <v>509</v>
-      </c>
       <c r="CH42" s="15"/>
-      <c r="DB42">
-        <v>1</v>
-      </c>
-      <c r="DE42">
-        <v>1</v>
-      </c>
-      <c r="DF42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>581</v>
-      </c>
-      <c r="C43" t="s">
-        <v>346</v>
-      </c>
-      <c r="D43" t="s">
-        <v>559</v>
-      </c>
-      <c r="E43" t="s">
-        <v>560</v>
-      </c>
-      <c r="F43" t="s">
-        <v>561</v>
-      </c>
-      <c r="G43">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>657</v>
-      </c>
+    </row>
+    <row r="43" spans="1:90" x14ac:dyDescent="0.25">
       <c r="M43"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="14" t="s">
-        <v>658</v>
-      </c>
+      <c r="O43" s="14"/>
       <c r="P43" s="15"/>
       <c r="Q43" s="15"/>
       <c r="R43" s="15"/>
@@ -10159,83 +8665,21 @@
       <c r="V43" s="15"/>
       <c r="W43" s="15"/>
       <c r="X43" s="15"/>
-      <c r="AC43">
-        <v>1</v>
-      </c>
-      <c r="AG43" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="AO43" s="8" t="s">
-        <v>555</v>
-      </c>
-      <c r="AR43" t="s">
-        <v>519</v>
-      </c>
-      <c r="AW43">
-        <v>1</v>
-      </c>
-      <c r="AX43">
-        <v>583</v>
-      </c>
-      <c r="AZ43">
-        <v>2</v>
-      </c>
-      <c r="BB43">
-        <v>1</v>
-      </c>
+      <c r="AG43" s="8"/>
+      <c r="AO43" s="8"/>
       <c r="BM43" s="8"/>
       <c r="BN43" s="8"/>
-      <c r="BQ43">
-        <v>1</v>
-      </c>
       <c r="BT43" s="17"/>
       <c r="BU43" s="17"/>
       <c r="BV43" s="17"/>
       <c r="BW43" s="17"/>
       <c r="BX43" s="17"/>
       <c r="BY43" s="17"/>
-      <c r="CE43" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="CF43" t="s">
-        <v>510</v>
-      </c>
-      <c r="CG43" t="s">
-        <v>474</v>
-      </c>
+      <c r="CE43" s="8"/>
       <c r="CK43" s="8"/>
-      <c r="CL43" t="s">
-        <v>568</v>
-      </c>
-      <c r="CM43">
-        <v>22</v>
-      </c>
-      <c r="CN43">
-        <v>39.6</v>
-      </c>
-      <c r="CP43">
-        <v>10</v>
-      </c>
-      <c r="CW43" t="s">
-        <v>512</v>
-      </c>
-      <c r="DB43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="C44" t="s">
-        <v>346</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>420</v>
-      </c>
+    </row>
+    <row r="44" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="A44" s="8"/>
       <c r="L44" s="15"/>
       <c r="M44"/>
       <c r="N44" s="15"/>
@@ -10249,36 +8693,17 @@
       <c r="V44" s="15"/>
       <c r="W44" s="15"/>
       <c r="X44" s="15"/>
-      <c r="AC44">
-        <v>1</v>
-      </c>
-      <c r="AG44" s="8" t="s">
-        <v>421</v>
-      </c>
+      <c r="AG44" s="8"/>
       <c r="AO44" s="8"/>
-      <c r="BB44">
-        <v>1</v>
-      </c>
-      <c r="BQ44">
-        <v>0.1</v>
-      </c>
       <c r="BT44" s="17"/>
       <c r="BU44" s="17"/>
       <c r="BV44" s="17"/>
       <c r="BW44" s="17"/>
       <c r="BX44" s="17"/>
       <c r="BY44" s="17"/>
-      <c r="CE44" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="CK44" t="s">
-        <v>568</v>
-      </c>
-      <c r="DB44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CE44" s="8"/>
+    </row>
+    <row r="45" spans="1:90" x14ac:dyDescent="0.25">
       <c r="K45" s="15"/>
       <c r="L45" s="15"/>
       <c r="M45" s="15"/>
@@ -10301,705 +8726,95 @@
       <c r="BX45" s="17"/>
       <c r="BY45"/>
     </row>
-    <row r="46" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>582</v>
-      </c>
-      <c r="C46" t="s">
-        <v>346</v>
-      </c>
-      <c r="D46" t="s">
-        <v>583</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="F46" t="s">
-        <v>585</v>
-      </c>
-      <c r="G46">
-        <v>3</v>
-      </c>
-      <c r="J46" t="s">
-        <v>489</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>562</v>
-      </c>
+    <row r="46" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="E46" s="8"/>
       <c r="O46"/>
       <c r="W46"/>
       <c r="X46"/>
-      <c r="AC46">
-        <v>1</v>
-      </c>
-      <c r="AG46" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB46">
-        <v>1</v>
-      </c>
-      <c r="BM46" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="BN46" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="BR46">
-        <v>1</v>
-      </c>
-      <c r="BT46" s="4">
-        <v>11</v>
-      </c>
-      <c r="BU46" s="4">
-        <v>15</v>
-      </c>
-      <c r="BV46" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW46" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="CL46" s="14" t="s">
-        <v>589</v>
-      </c>
-      <c r="CM46" t="s">
-        <v>618</v>
-      </c>
-      <c r="CP46">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>619</v>
-      </c>
-      <c r="C47" t="s">
-        <v>346</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>420</v>
-      </c>
+      <c r="BM46" s="8"/>
+      <c r="BN46" s="8"/>
+      <c r="CL46" s="14"/>
+    </row>
+    <row r="47" spans="1:90" x14ac:dyDescent="0.25">
       <c r="M47"/>
       <c r="O47" s="14"/>
       <c r="P47"/>
       <c r="Q47"/>
-      <c r="AC47">
-        <v>1</v>
-      </c>
-      <c r="AG47" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB47">
-        <v>1</v>
-      </c>
-      <c r="BQ47">
-        <v>0.1</v>
-      </c>
-      <c r="CL47" s="14" t="s">
-        <v>644</v>
-      </c>
-      <c r="CM47">
-        <v>-100</v>
-      </c>
-      <c r="CP47">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="C48" t="s">
-        <v>346</v>
-      </c>
-      <c r="I48">
-        <v>1</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>620</v>
-      </c>
+      <c r="CL47" s="14"/>
+    </row>
+    <row r="48" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="A48" s="8"/>
       <c r="M48"/>
-      <c r="O48" s="14" t="s">
-        <v>589</v>
-      </c>
+      <c r="O48" s="14"/>
       <c r="P48"/>
       <c r="Q48"/>
-      <c r="AC48">
-        <v>1</v>
-      </c>
-      <c r="AJ48" t="s">
-        <v>535</v>
-      </c>
-      <c r="AR48" t="s">
-        <v>508</v>
-      </c>
-      <c r="BB48">
-        <v>1</v>
-      </c>
-      <c r="CL48" s="14" t="s">
-        <v>590</v>
-      </c>
-      <c r="CP48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="C49" t="s">
-        <v>346</v>
-      </c>
-      <c r="I49">
-        <v>1</v>
-      </c>
-      <c r="O49" s="14" t="s">
-        <v>590</v>
-      </c>
-      <c r="AC49">
-        <v>1</v>
-      </c>
-      <c r="AG49" t="s">
-        <v>348</v>
-      </c>
-      <c r="AV49" t="s">
-        <v>470</v>
-      </c>
-      <c r="AX49">
-        <v>1</v>
-      </c>
-      <c r="AZ49">
-        <v>1</v>
-      </c>
-      <c r="BB49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="C50" t="s">
-        <v>514</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="AC50">
-        <v>1</v>
-      </c>
-      <c r="AF50">
-        <v>1</v>
-      </c>
-      <c r="AG50" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB50">
-        <v>1</v>
-      </c>
+      <c r="CL48" s="14"/>
+    </row>
+    <row r="49" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="A49" s="8"/>
+      <c r="O49" s="14"/>
+    </row>
+    <row r="50" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="A50" s="8"/>
       <c r="CJ50" s="3"/>
-      <c r="CS50" t="s">
-        <v>621</v>
-      </c>
-      <c r="DB50">
-        <v>1</v>
-      </c>
-      <c r="DE50">
-        <v>1</v>
-      </c>
-      <c r="DF50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:110" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:97" x14ac:dyDescent="0.25">
       <c r="CJ51" s="3"/>
     </row>
-    <row r="52" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="I52">
-        <v>1</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>554</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="AC52">
-        <v>1</v>
-      </c>
-      <c r="AJ52" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="AR52" t="s">
-        <v>508</v>
-      </c>
-      <c r="BB52">
-        <v>1</v>
-      </c>
-      <c r="BQ52">
-        <v>0.1</v>
-      </c>
+    <row r="52" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="A52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="AJ52" s="8"/>
       <c r="CJ52" s="3"/>
-      <c r="CS52" s="8" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="53" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CS52" s="8"/>
+    </row>
+    <row r="53" spans="1:97" x14ac:dyDescent="0.25">
       <c r="CJ53" s="3"/>
     </row>
-    <row r="54" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>622</v>
-      </c>
-      <c r="C54" t="s">
-        <v>346</v>
-      </c>
-      <c r="D54" t="s">
-        <v>583</v>
-      </c>
-      <c r="E54" t="s">
-        <v>584</v>
-      </c>
-      <c r="F54" t="s">
-        <v>585</v>
-      </c>
-      <c r="G54">
-        <v>3</v>
-      </c>
-      <c r="J54" t="s">
-        <v>489</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>490</v>
-      </c>
+    <row r="54" spans="1:97" x14ac:dyDescent="0.25">
       <c r="O54"/>
       <c r="W54"/>
       <c r="X54"/>
-      <c r="AC54">
-        <v>1</v>
-      </c>
-      <c r="AG54" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB54">
-        <v>1</v>
-      </c>
-      <c r="BM54" t="s">
-        <v>623</v>
-      </c>
-      <c r="BR54">
-        <v>25</v>
-      </c>
-      <c r="BT54" s="4">
-        <v>1</v>
-      </c>
-      <c r="BU54" s="4">
-        <v>1</v>
-      </c>
-      <c r="BV54" s="4">
-        <v>1</v>
-      </c>
-      <c r="BW54" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="CL54" s="14" t="s">
-        <v>587</v>
-      </c>
-      <c r="CM54" t="s">
-        <v>588</v>
-      </c>
-      <c r="CN54">
-        <v>2</v>
-      </c>
-      <c r="CO54">
-        <v>80</v>
-      </c>
-      <c r="CP54">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>591</v>
-      </c>
-      <c r="C55" t="s">
-        <v>592</v>
-      </c>
-      <c r="O55" s="14" t="s">
-        <v>589</v>
-      </c>
+      <c r="CL54" s="14"/>
+    </row>
+    <row r="55" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="O55" s="14"/>
       <c r="X55"/>
-      <c r="AC55">
-        <v>2</v>
-      </c>
-      <c r="AO55" t="s">
-        <v>495</v>
-      </c>
-      <c r="AR55" t="s">
-        <v>519</v>
-      </c>
-      <c r="AV55" t="s">
-        <v>470</v>
-      </c>
-      <c r="AX55">
-        <v>1</v>
-      </c>
-      <c r="BB55">
-        <v>1</v>
-      </c>
-      <c r="BN55" t="s">
-        <v>593</v>
-      </c>
-      <c r="BZ55" t="s">
-        <v>594</v>
-      </c>
-      <c r="CE55" t="s">
-        <v>509</v>
-      </c>
-      <c r="CW55" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="56" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>593</v>
-      </c>
-      <c r="C56" t="s">
-        <v>346</v>
-      </c>
-      <c r="I56">
-        <v>1</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="O56" s="14" t="s">
-        <v>589</v>
-      </c>
+    </row>
+    <row r="56" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="O56" s="14"/>
       <c r="P56"/>
       <c r="Q56"/>
       <c r="X56"/>
-      <c r="AC56">
-        <v>1</v>
-      </c>
-      <c r="AG56" t="s">
-        <v>348</v>
-      </c>
-      <c r="AH56">
-        <v>1</v>
-      </c>
-      <c r="AO56" t="s">
-        <v>507</v>
-      </c>
-      <c r="AT56">
-        <v>1</v>
-      </c>
-      <c r="AW56">
-        <v>1</v>
-      </c>
-      <c r="AX56">
-        <v>0.5</v>
-      </c>
-      <c r="BB56">
-        <v>1</v>
-      </c>
-      <c r="CF56" t="s">
-        <v>510</v>
-      </c>
-      <c r="CG56" t="s">
-        <v>474</v>
-      </c>
-      <c r="CL56" t="s">
-        <v>511</v>
-      </c>
-      <c r="CM56">
-        <v>22</v>
-      </c>
-      <c r="CP56">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>595</v>
-      </c>
-      <c r="C57" t="s">
-        <v>596</v>
-      </c>
-      <c r="I57">
-        <v>1</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="O57" s="14" t="s">
-        <v>589</v>
-      </c>
+    </row>
+    <row r="57" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="O57" s="14"/>
       <c r="X57"/>
-      <c r="AC57">
-        <v>1</v>
-      </c>
-      <c r="AG57" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB57">
-        <v>1</v>
-      </c>
-      <c r="CS57" t="s">
-        <v>624</v>
-      </c>
-      <c r="DB57">
-        <v>1</v>
-      </c>
-      <c r="DE57">
-        <v>1</v>
-      </c>
-      <c r="DF57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>625</v>
-      </c>
-      <c r="C58" t="s">
-        <v>626</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="AC58">
-        <v>1</v>
-      </c>
-      <c r="AG58" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB58">
-        <v>1</v>
-      </c>
-      <c r="CS58" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="59" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>628</v>
-      </c>
-      <c r="C59" t="s">
-        <v>346</v>
-      </c>
-      <c r="I59">
-        <v>1</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="AC59">
-        <v>1</v>
-      </c>
-      <c r="AG59" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB59">
-        <v>1</v>
-      </c>
-      <c r="CL59" t="s">
-        <v>629</v>
-      </c>
-      <c r="CP59">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>630</v>
-      </c>
-      <c r="C60" t="s">
-        <v>346</v>
-      </c>
-      <c r="I60">
-        <v>1</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="AC60">
-        <v>1</v>
-      </c>
-      <c r="AJ60" t="s">
-        <v>523</v>
-      </c>
-      <c r="AT60">
-        <v>20</v>
-      </c>
-      <c r="BB60">
-        <v>1</v>
-      </c>
-      <c r="CK60" s="14" t="s">
-        <v>644</v>
-      </c>
+    </row>
+    <row r="60" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CK60" s="14"/>
       <c r="CL60" s="14"/>
-      <c r="DB60">
-        <v>1</v>
-      </c>
-      <c r="DE60">
-        <v>1</v>
-      </c>
-      <c r="DF60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>586</v>
-      </c>
-      <c r="C62" t="s">
-        <v>346</v>
-      </c>
-      <c r="I62">
-        <v>1</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>347</v>
-      </c>
+    </row>
+    <row r="62" spans="1:97" x14ac:dyDescent="0.25">
       <c r="M62"/>
       <c r="N62"/>
-      <c r="AC62">
-        <v>1</v>
-      </c>
-      <c r="AG62" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB62">
-        <v>1</v>
-      </c>
-      <c r="BQ62">
-        <v>0.5</v>
-      </c>
       <c r="BT62"/>
-      <c r="BZ62" s="20" t="s">
-        <v>649</v>
-      </c>
-      <c r="CE62" t="s">
-        <v>509</v>
-      </c>
+      <c r="BZ62" s="20"/>
       <c r="CG62" s="3"/>
       <c r="CH62" s="3"/>
-      <c r="DB62">
-        <v>1</v>
-      </c>
-      <c r="DE62">
-        <v>1</v>
-      </c>
-      <c r="DF62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>599</v>
-      </c>
-      <c r="C63" t="s">
-        <v>346</v>
-      </c>
-      <c r="I63">
-        <v>1</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>579</v>
-      </c>
+    </row>
+    <row r="63" spans="1:97" x14ac:dyDescent="0.25">
       <c r="M63"/>
       <c r="N63"/>
-      <c r="AC63">
-        <v>1</v>
-      </c>
-      <c r="AG63" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB63">
-        <v>1</v>
-      </c>
-      <c r="BQ63">
-        <v>1</v>
-      </c>
       <c r="BT63"/>
-      <c r="BZ63" s="20" t="s">
-        <v>642</v>
-      </c>
-      <c r="CE63" t="s">
-        <v>509</v>
-      </c>
+      <c r="BZ63" s="20"/>
       <c r="CH63" s="3"/>
-      <c r="DB63">
-        <v>1</v>
-      </c>
-      <c r="DE63">
-        <v>1</v>
-      </c>
-      <c r="DF63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>598</v>
-      </c>
-      <c r="C64" t="s">
-        <v>346</v>
-      </c>
-      <c r="I64">
-        <v>1</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>579</v>
-      </c>
+    </row>
+    <row r="64" spans="1:97" x14ac:dyDescent="0.25">
       <c r="O64"/>
       <c r="X64"/>
-      <c r="AC64">
-        <v>1</v>
-      </c>
-      <c r="AG64" t="s">
-        <v>348</v>
-      </c>
-      <c r="BB64">
-        <v>1</v>
-      </c>
-      <c r="CK64" s="14" t="s">
-        <v>631</v>
-      </c>
+      <c r="CK64" s="14"/>
     </row>
     <row r="67" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ67" s="3"/>
@@ -12509,238 +10324,29 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>511</v>
-      </c>
-      <c r="C4" t="s">
-        <v>539</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>540</v>
-      </c>
-      <c r="P4" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>518</v>
-      </c>
-      <c r="C5" t="s">
-        <v>542</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>543</v>
-      </c>
-      <c r="P5" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>539</v>
-      </c>
-      <c r="H6" s="14">
-        <v>1</v>
-      </c>
-      <c r="P6" s="14" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>546</v>
-      </c>
-      <c r="C7" t="s">
-        <v>547</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="P7" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>549</v>
-      </c>
-      <c r="C8" t="s">
-        <v>547</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>550</v>
-      </c>
-    </row>
+    <row r="6" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>557</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>604</v>
-      </c>
-      <c r="H9" s="14">
-        <v>1</v>
-      </c>
       <c r="K9"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>575</v>
-      </c>
-      <c r="C10" t="s">
-        <v>539</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="P10" t="s">
-        <v>541</v>
-      </c>
-    </row>
     <row r="11" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>573</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>604</v>
-      </c>
-      <c r="H11" s="14">
-        <v>1</v>
-      </c>
       <c r="K11"/>
     </row>
     <row r="12" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>604</v>
-      </c>
-      <c r="H12" s="14">
-        <v>1</v>
-      </c>
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>605</v>
-      </c>
-      <c r="C13" t="s">
-        <v>200</v>
-      </c>
-      <c r="P13" t="s">
-        <v>606</v>
-      </c>
-    </row>
     <row r="14" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>589</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>539</v>
-      </c>
-      <c r="H14" s="14">
-        <v>1</v>
-      </c>
       <c r="J14"/>
-      <c r="P14" s="14" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>608</v>
-      </c>
-      <c r="C15" t="s">
-        <v>539</v>
-      </c>
-      <c r="P15" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>610</v>
-      </c>
-      <c r="C16" t="s">
-        <v>542</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="J16" t="s">
-        <v>543</v>
-      </c>
-      <c r="P16" t="s">
-        <v>544</v>
-      </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>611</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>604</v>
-      </c>
-      <c r="J17" t="s">
-        <v>612</v>
-      </c>
+      <c r="C17" s="14"/>
     </row>
     <row r="18" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>590</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>604</v>
-      </c>
-      <c r="H18" s="14">
-        <v>1</v>
-      </c>
-      <c r="J18" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>614</v>
-      </c>
-      <c r="C19" t="s">
-        <v>200</v>
-      </c>
-      <c r="P19" t="s">
-        <v>615</v>
-      </c>
+      <c r="J18"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>617</v>
-      </c>
+      <c r="A20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="P20" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -12888,28 +10494,11 @@
         <v>1</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>552</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>510</v>
-      </c>
-      <c r="B5" t="s">
-        <v>537</v>
-      </c>
-      <c r="C5" t="s">
-        <v>434</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>551</v>
-      </c>
+      <c r="I5" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
